--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C626D361-9D26-E14E-B543-B6951B9F72AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD7A633-E16E-4789-A570-43C33A6FA2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="17460" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="764">
   <si>
     <t>Class</t>
   </si>
@@ -2314,6 +2314,12 @@
   </si>
   <si>
     <t>CardLayoutTwoColumnSection</t>
+  </si>
+  <si>
+    <t>getSolidColor</t>
+  </si>
+  <si>
+    <t>getChartPointColor</t>
   </si>
 </sst>
 </file>
@@ -2398,7 +2404,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2421,10 +2427,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F410" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F410" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F410">
-    <sortCondition ref="B1:B410"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F411" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F411" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F411">
+    <sortCondition ref="B1:B411"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2755,18 +2761,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F410"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F411"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="28.1640625" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="55" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>682</v>
       </c>
@@ -2786,7 +2792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>684</v>
       </c>
@@ -2803,7 +2809,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>684</v>
       </c>
@@ -2820,7 +2826,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>684</v>
       </c>
@@ -2840,7 +2846,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>684</v>
       </c>
@@ -2860,7 +2866,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>684</v>
       </c>
@@ -2877,7 +2883,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>684</v>
       </c>
@@ -2894,7 +2900,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>684</v>
       </c>
@@ -2911,7 +2917,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>684</v>
       </c>
@@ -2928,7 +2934,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>684</v>
       </c>
@@ -2948,7 +2954,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>684</v>
       </c>
@@ -2968,7 +2974,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>684</v>
       </c>
@@ -2988,7 +2994,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>684</v>
       </c>
@@ -3008,7 +3014,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>684</v>
       </c>
@@ -3025,7 +3031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>684</v>
       </c>
@@ -3042,7 +3048,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>684</v>
       </c>
@@ -3059,7 +3065,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>684</v>
       </c>
@@ -3076,7 +3082,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>684</v>
       </c>
@@ -3093,7 +3099,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>684</v>
       </c>
@@ -3110,7 +3116,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>684</v>
       </c>
@@ -3128,7 +3134,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>684</v>
       </c>
@@ -3146,7 +3152,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>684</v>
       </c>
@@ -3164,7 +3170,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>684</v>
       </c>
@@ -3181,7 +3187,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>684</v>
       </c>
@@ -3198,7 +3204,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>684</v>
       </c>
@@ -3215,7 +3221,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>684</v>
       </c>
@@ -3232,7 +3238,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>684</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>684</v>
       </c>
@@ -3266,7 +3272,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>684</v>
       </c>
@@ -3283,7 +3289,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>684</v>
       </c>
@@ -3300,7 +3306,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>684</v>
       </c>
@@ -3317,7 +3323,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>684</v>
       </c>
@@ -3334,7 +3340,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>684</v>
       </c>
@@ -3351,7 +3357,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>684</v>
       </c>
@@ -3368,7 +3374,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>684</v>
       </c>
@@ -3388,7 +3394,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>684</v>
       </c>
@@ -3405,7 +3411,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>684</v>
       </c>
@@ -3422,7 +3428,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>684</v>
       </c>
@@ -3439,7 +3445,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>684</v>
       </c>
@@ -3456,7 +3462,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>684</v>
       </c>
@@ -3473,7 +3479,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>684</v>
       </c>
@@ -3490,7 +3496,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>684</v>
       </c>
@@ -3507,7 +3513,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>684</v>
       </c>
@@ -3524,7 +3530,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>684</v>
       </c>
@@ -3541,7 +3547,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>684</v>
       </c>
@@ -3558,7 +3564,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>684</v>
       </c>
@@ -3575,7 +3581,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>684</v>
       </c>
@@ -3592,7 +3598,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>684</v>
       </c>
@@ -3609,7 +3615,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>684</v>
       </c>
@@ -3626,7 +3632,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>684</v>
       </c>
@@ -3643,7 +3649,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>684</v>
       </c>
@@ -3660,7 +3666,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>684</v>
       </c>
@@ -3677,7 +3683,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>684</v>
       </c>
@@ -3694,7 +3700,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>684</v>
       </c>
@@ -3711,7 +3717,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>684</v>
       </c>
@@ -3719,7 +3725,7 @@
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>762</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3728,32 +3734,35 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>684</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>684</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>684</v>
+      </c>
+      <c r="B57" t="s">
         <v>741</v>
-      </c>
-      <c r="D56" t="s">
-        <v>692</v>
-      </c>
-      <c r="E56" t="s">
-        <v>737</v>
-      </c>
-      <c r="F56" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>684</v>
-      </c>
-      <c r="B57" t="s">
-        <v>743</v>
       </c>
       <c r="D57" t="s">
         <v>692</v>
@@ -3765,46 +3774,46 @@
         <v>742</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>684</v>
       </c>
       <c r="B58" t="s">
+        <v>743</v>
+      </c>
+      <c r="D58" t="s">
+        <v>692</v>
+      </c>
+      <c r="E58" t="s">
+        <v>737</v>
+      </c>
+      <c r="F58" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>684</v>
+      </c>
+      <c r="B59" t="s">
         <v>198</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>145</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" t="s">
         <v>146</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F59" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>684</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>684</v>
+      </c>
+      <c r="B60" t="s">
         <v>728</v>
-      </c>
-      <c r="D59" t="s">
-        <v>692</v>
-      </c>
-      <c r="E59" t="s">
-        <v>729</v>
-      </c>
-      <c r="F59" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>684</v>
-      </c>
-      <c r="B60" t="s">
-        <v>731</v>
       </c>
       <c r="D60" t="s">
         <v>692</v>
@@ -3816,27 +3825,24 @@
         <v>730</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>684</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" t="s">
-        <v>488</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
+        <v>731</v>
+      </c>
+      <c r="D61" t="s">
+        <v>692</v>
       </c>
       <c r="E61" t="s">
-        <v>485</v>
+        <v>729</v>
       </c>
       <c r="F61" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>684</v>
       </c>
@@ -3844,7 +3850,7 @@
         <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3853,10 +3859,10 @@
         <v>485</v>
       </c>
       <c r="F62" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>684</v>
       </c>
@@ -3864,19 +3870,19 @@
         <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>598</v>
+        <v>484</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>599</v>
+        <v>485</v>
       </c>
       <c r="F63" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>684</v>
       </c>
@@ -3884,7 +3890,7 @@
         <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3896,32 +3902,35 @@
         <v>600</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>684</v>
       </c>
       <c r="B65" t="s">
         <v>133</v>
       </c>
-      <c r="D65" t="s">
-        <v>692</v>
+      <c r="C65" t="s">
+        <v>601</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>737</v>
+        <v>599</v>
       </c>
       <c r="F65" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>684</v>
       </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
-      <c r="C66" t="s">
-        <v>738</v>
+      <c r="D66" t="s">
+        <v>692</v>
       </c>
       <c r="E66" t="s">
         <v>737</v>
@@ -3930,7 +3939,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>684</v>
       </c>
@@ -3938,7 +3947,7 @@
         <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E67" t="s">
         <v>737</v>
@@ -3947,7 +3956,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>684</v>
       </c>
@@ -3955,16 +3964,16 @@
         <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E68" t="s">
         <v>737</v>
       </c>
       <c r="F68" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>684</v>
       </c>
@@ -3972,19 +3981,16 @@
         <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
+        <v>740</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>737</v>
       </c>
       <c r="F69" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>684</v>
       </c>
@@ -3992,7 +3998,7 @@
         <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4001,10 +4007,10 @@
         <v>135</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>684</v>
       </c>
@@ -4012,16 +4018,19 @@
         <v>133</v>
       </c>
       <c r="C71" t="s">
-        <v>177</v>
+        <v>138</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>684</v>
       </c>
@@ -4029,7 +4038,7 @@
         <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>404</v>
+        <v>177</v>
       </c>
       <c r="E72" t="s">
         <v>174</v>
@@ -4038,7 +4047,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>684</v>
       </c>
@@ -4046,7 +4055,7 @@
         <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>404</v>
       </c>
       <c r="E73" t="s">
         <v>174</v>
@@ -4055,7 +4064,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>684</v>
       </c>
@@ -4063,7 +4072,7 @@
         <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E74" t="s">
         <v>174</v>
@@ -4072,61 +4081,58 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>684</v>
       </c>
       <c r="B75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>684</v>
+      </c>
+      <c r="B76" t="s">
         <v>621</v>
-      </c>
-      <c r="D75" t="s">
-        <v>582</v>
-      </c>
-      <c r="E75" t="s">
-        <v>599</v>
-      </c>
-      <c r="F75" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>684</v>
-      </c>
-      <c r="B76" t="s">
-        <v>623</v>
       </c>
       <c r="D76" t="s">
         <v>582</v>
       </c>
       <c r="E76" t="s">
+        <v>599</v>
+      </c>
+      <c r="F76" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>684</v>
+      </c>
+      <c r="B77" t="s">
+        <v>623</v>
+      </c>
+      <c r="D77" t="s">
+        <v>582</v>
+      </c>
+      <c r="E77" t="s">
         <v>485</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F77" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>684</v>
-      </c>
-      <c r="B77" t="s">
-        <v>248</v>
-      </c>
-      <c r="C77" t="s">
-        <v>249</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
-        <v>250</v>
-      </c>
-      <c r="F77" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>684</v>
       </c>
@@ -4134,172 +4140,175 @@
         <v>248</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>249</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
       </c>
       <c r="E78" t="s">
         <v>250</v>
       </c>
       <c r="F78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>684</v>
+      </c>
+      <c r="B79" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" t="s">
+        <v>250</v>
+      </c>
+      <c r="F79" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>684</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>684</v>
+      </c>
+      <c r="B80" t="s">
         <v>124</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>78</v>
-      </c>
-      <c r="E79" t="s">
-        <v>129</v>
-      </c>
-      <c r="F79" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>684</v>
-      </c>
-      <c r="B80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>129</v>
       </c>
       <c r="F80" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>684</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
       </c>
       <c r="E81" t="s">
         <v>129</v>
       </c>
       <c r="F81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>684</v>
+      </c>
+      <c r="B82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" t="s">
+        <v>132</v>
+      </c>
+      <c r="E82" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>684</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>684</v>
+      </c>
+      <c r="B83" t="s">
         <v>581</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D83" t="s">
         <v>582</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
         <v>583</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F83" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>684</v>
-      </c>
-      <c r="B83" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>684</v>
+      </c>
+      <c r="B84" t="s">
         <v>711</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D84" t="s">
         <v>712</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>709</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F84" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>684</v>
-      </c>
-      <c r="B84" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>684</v>
+      </c>
+      <c r="B85" t="s">
         <v>624</v>
-      </c>
-      <c r="D84" t="s">
-        <v>582</v>
-      </c>
-      <c r="E84" t="s">
-        <v>102</v>
-      </c>
-      <c r="F84" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>684</v>
-      </c>
-      <c r="B85" t="s">
-        <v>626</v>
       </c>
       <c r="D85" t="s">
         <v>582</v>
       </c>
       <c r="E85" t="s">
+        <v>102</v>
+      </c>
+      <c r="F85" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>684</v>
+      </c>
+      <c r="B86" t="s">
+        <v>626</v>
+      </c>
+      <c r="D86" t="s">
+        <v>582</v>
+      </c>
+      <c r="E86" t="s">
         <v>324</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F86" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>684</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>684</v>
+      </c>
+      <c r="B87" t="s">
         <v>58</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C87" t="s">
         <v>63</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>59</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F87" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>684</v>
-      </c>
-      <c r="B87" t="s">
-        <v>359</v>
-      </c>
-      <c r="C87" t="s">
-        <v>361</v>
-      </c>
-      <c r="E87" t="s">
-        <v>422</v>
-      </c>
-      <c r="F87" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>684</v>
       </c>
@@ -4307,19 +4316,16 @@
         <v>359</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="E88" t="s">
         <v>422</v>
       </c>
       <c r="F88" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>684</v>
       </c>
@@ -4327,19 +4333,19 @@
         <v>359</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="s">
         <v>422</v>
       </c>
       <c r="F89" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>684</v>
       </c>
@@ -4347,36 +4353,36 @@
         <v>359</v>
       </c>
       <c r="C90" t="s">
+        <v>199</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90" t="s">
+        <v>422</v>
+      </c>
+      <c r="F90" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>684</v>
+      </c>
+      <c r="B91" t="s">
+        <v>359</v>
+      </c>
+      <c r="C91" t="s">
         <v>425</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E91" t="s">
         <v>426</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F91" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>684</v>
-      </c>
-      <c r="B91" t="s">
-        <v>355</v>
-      </c>
-      <c r="C91" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>422</v>
-      </c>
-      <c r="F91" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>684</v>
       </c>
@@ -4384,16 +4390,19 @@
         <v>355</v>
       </c>
       <c r="C92" t="s">
-        <v>165</v>
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>483</v>
+        <v>422</v>
       </c>
       <c r="F92" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>684</v>
       </c>
@@ -4407,10 +4416,10 @@
         <v>483</v>
       </c>
       <c r="F93" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>684</v>
       </c>
@@ -4418,16 +4427,16 @@
         <v>355</v>
       </c>
       <c r="C94" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E94" t="s">
         <v>483</v>
       </c>
       <c r="F94" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>684</v>
       </c>
@@ -4441,10 +4450,10 @@
         <v>483</v>
       </c>
       <c r="F95" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>684</v>
       </c>
@@ -4452,16 +4461,16 @@
         <v>355</v>
       </c>
       <c r="C96" t="s">
-        <v>481</v>
+        <v>182</v>
       </c>
       <c r="E96" t="s">
         <v>483</v>
       </c>
       <c r="F96" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>684</v>
       </c>
@@ -4475,27 +4484,27 @@
         <v>483</v>
       </c>
       <c r="F97" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>355</v>
+      </c>
+      <c r="C98" t="s">
+        <v>481</v>
+      </c>
+      <c r="E98" t="s">
+        <v>483</v>
+      </c>
+      <c r="F98" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>684</v>
-      </c>
-      <c r="B98" t="s">
-        <v>362</v>
-      </c>
-      <c r="C98" t="s">
-        <v>361</v>
-      </c>
-      <c r="E98" t="s">
-        <v>423</v>
-      </c>
-      <c r="F98" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>684</v>
       </c>
@@ -4503,27 +4512,24 @@
         <v>362</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="E99" t="s">
         <v>423</v>
       </c>
       <c r="F99" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>684</v>
       </c>
       <c r="B100" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4532,44 +4538,47 @@
         <v>423</v>
       </c>
       <c r="F100" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>684</v>
+      </c>
+      <c r="B101" t="s">
+        <v>357</v>
+      </c>
+      <c r="C101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>423</v>
+      </c>
+      <c r="F101" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>684</v>
-      </c>
-      <c r="B101" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>684</v>
+      </c>
+      <c r="B102" t="s">
         <v>428</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>429</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E102" t="s">
         <v>430</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F102" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>684</v>
-      </c>
-      <c r="B102" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" t="s">
-        <v>59</v>
-      </c>
-      <c r="F102" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>684</v>
       </c>
@@ -4577,7 +4586,7 @@
         <v>89</v>
       </c>
       <c r="C103" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E103" t="s">
         <v>59</v>
@@ -4586,29 +4595,29 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>684</v>
       </c>
       <c r="B104" t="s">
-        <v>758</v>
-      </c>
-      <c r="D104" t="s">
-        <v>712</v>
+        <v>89</v>
+      </c>
+      <c r="C104" t="s">
+        <v>79</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
       </c>
       <c r="F104" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>684</v>
       </c>
       <c r="B105" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D105" t="s">
         <v>712</v>
@@ -4620,41 +4629,41 @@
         <v>60</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>684</v>
       </c>
       <c r="B106" t="s">
-        <v>628</v>
+        <v>759</v>
       </c>
       <c r="D106" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
       </c>
       <c r="F106" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>684</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
-      </c>
-      <c r="C107" t="s">
-        <v>87</v>
+        <v>628</v>
+      </c>
+      <c r="D107" t="s">
+        <v>582</v>
       </c>
       <c r="E107" t="s">
         <v>59</v>
       </c>
       <c r="F107" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>684</v>
       </c>
@@ -4662,16 +4671,16 @@
         <v>56</v>
       </c>
       <c r="C108" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E108" t="s">
         <v>59</v>
       </c>
       <c r="F108" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>684</v>
       </c>
@@ -4679,16 +4688,16 @@
         <v>56</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E109" t="s">
         <v>59</v>
       </c>
       <c r="F109" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>684</v>
       </c>
@@ -4696,16 +4705,16 @@
         <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E110" t="s">
         <v>59</v>
       </c>
       <c r="F110" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>684</v>
       </c>
@@ -4713,19 +4722,16 @@
         <v>56</v>
       </c>
       <c r="C111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D111">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>684</v>
       </c>
@@ -4733,16 +4739,19 @@
         <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>74</v>
+        <v>97</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
       </c>
       <c r="E112" t="s">
         <v>59</v>
       </c>
       <c r="F112" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>684</v>
       </c>
@@ -4750,16 +4759,16 @@
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E113" t="s">
         <v>59</v>
       </c>
       <c r="F113" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>684</v>
       </c>
@@ -4767,16 +4776,16 @@
         <v>56</v>
       </c>
       <c r="C114" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E114" t="s">
         <v>59</v>
       </c>
       <c r="F114" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>684</v>
       </c>
@@ -4784,36 +4793,33 @@
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
         <v>59</v>
       </c>
       <c r="F115" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>684</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E116" t="s">
         <v>59</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>684</v>
       </c>
@@ -4821,7 +4827,7 @@
         <v>54</v>
       </c>
       <c r="C117" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4830,10 +4836,10 @@
         <v>59</v>
       </c>
       <c r="F117" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>684</v>
       </c>
@@ -4841,7 +4847,7 @@
         <v>54</v>
       </c>
       <c r="C118" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4850,32 +4856,35 @@
         <v>59</v>
       </c>
       <c r="F118" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>684</v>
       </c>
       <c r="B119" t="s">
-        <v>629</v>
-      </c>
-      <c r="D119" t="s">
-        <v>582</v>
+        <v>54</v>
+      </c>
+      <c r="C119" t="s">
+        <v>96</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
       </c>
       <c r="E119" t="s">
         <v>59</v>
       </c>
       <c r="F119" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>684</v>
       </c>
       <c r="B120" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D120" t="s">
         <v>582</v>
@@ -4884,78 +4893,78 @@
         <v>59</v>
       </c>
       <c r="F120" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>684</v>
       </c>
       <c r="B121" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D121" t="s">
         <v>582</v>
       </c>
       <c r="E121" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>684</v>
+      </c>
+      <c r="B122" t="s">
+        <v>631</v>
+      </c>
+      <c r="D122" t="s">
+        <v>582</v>
+      </c>
+      <c r="E122" t="s">
         <v>633</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F122" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>684</v>
-      </c>
-      <c r="B122" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>684</v>
+      </c>
+      <c r="B123" t="s">
         <v>94</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>13</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E123" t="s">
         <v>59</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F123" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>684</v>
-      </c>
-      <c r="B123" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>684</v>
+      </c>
+      <c r="B124" t="s">
         <v>634</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D124" t="s">
         <v>582</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E124" t="s">
         <v>633</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F124" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>684</v>
-      </c>
-      <c r="B124" t="s">
-        <v>76</v>
-      </c>
-      <c r="C124" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>684</v>
       </c>
@@ -4963,7 +4972,7 @@
         <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E125" t="s">
         <v>59</v>
@@ -4972,7 +4981,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>684</v>
       </c>
@@ -4980,7 +4989,7 @@
         <v>76</v>
       </c>
       <c r="C126" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E126" t="s">
         <v>59</v>
@@ -4989,15 +4998,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>684</v>
       </c>
       <c r="B127" t="s">
-        <v>635</v>
-      </c>
-      <c r="D127" t="s">
-        <v>582</v>
+        <v>76</v>
+      </c>
+      <c r="C127" t="s">
+        <v>78</v>
       </c>
       <c r="E127" t="s">
         <v>59</v>
@@ -5006,49 +5015,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>684</v>
       </c>
       <c r="B128" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" t="s">
-        <v>69</v>
+        <v>635</v>
+      </c>
+      <c r="D128" t="s">
+        <v>582</v>
       </c>
       <c r="E128" t="s">
         <v>59</v>
       </c>
       <c r="F128" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>684</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C129" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E129" t="s">
         <v>59</v>
       </c>
       <c r="F129" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>684</v>
       </c>
       <c r="B130" t="s">
-        <v>636</v>
-      </c>
-      <c r="D130" t="s">
-        <v>582</v>
+        <v>83</v>
+      </c>
+      <c r="C130" t="s">
+        <v>86</v>
       </c>
       <c r="E130" t="s">
         <v>59</v>
@@ -5057,115 +5066,112 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>684</v>
       </c>
       <c r="B131" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D131" t="s">
         <v>582</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="F131" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>684</v>
       </c>
       <c r="B132" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D132" t="s">
         <v>582</v>
       </c>
       <c r="E132" t="s">
+        <v>337</v>
+      </c>
+      <c r="F132" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>684</v>
+      </c>
+      <c r="B133" t="s">
+        <v>638</v>
+      </c>
+      <c r="D133" t="s">
+        <v>582</v>
+      </c>
+      <c r="E133" t="s">
         <v>430</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F133" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>684</v>
-      </c>
-      <c r="B133" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>684</v>
+      </c>
+      <c r="B134" t="s">
         <v>461</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C134" t="s">
         <v>462</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E134" t="s">
         <v>463</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F134" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>684</v>
-      </c>
-      <c r="B134" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>684</v>
+      </c>
+      <c r="B135" t="s">
         <v>91</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C135" t="s">
         <v>84</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E135" t="s">
         <v>59</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F135" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>684</v>
-      </c>
-      <c r="B135" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>684</v>
+      </c>
+      <c r="B136" t="s">
         <v>455</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C136" t="s">
         <v>8</v>
       </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" t="s">
         <v>453</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F136" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>684</v>
-      </c>
-      <c r="B136" t="s">
-        <v>32</v>
-      </c>
-      <c r="C136" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136" t="s">
-        <v>33</v>
-      </c>
-      <c r="F136" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>684</v>
       </c>
@@ -5173,7 +5179,7 @@
         <v>32</v>
       </c>
       <c r="C137" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -5182,10 +5188,10 @@
         <v>33</v>
       </c>
       <c r="F137" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>684</v>
       </c>
@@ -5193,7 +5199,10 @@
         <v>32</v>
       </c>
       <c r="C138" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -5202,7 +5211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>684</v>
       </c>
@@ -5210,27 +5219,24 @@
         <v>32</v>
       </c>
       <c r="C139" t="s">
-        <v>39</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
       </c>
       <c r="F139" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>684</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -5239,10 +5245,10 @@
         <v>33</v>
       </c>
       <c r="F140" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>684</v>
       </c>
@@ -5250,7 +5256,7 @@
         <v>29</v>
       </c>
       <c r="C141" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -5259,10 +5265,10 @@
         <v>33</v>
       </c>
       <c r="F141" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>684</v>
       </c>
@@ -5270,39 +5276,39 @@
         <v>29</v>
       </c>
       <c r="C142" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
+        <v>33</v>
+      </c>
+      <c r="F142" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>684</v>
+      </c>
+      <c r="B143" t="s">
+        <v>29</v>
+      </c>
+      <c r="C143" t="s">
         <v>42</v>
       </c>
-      <c r="D142">
-        <v>1</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143" t="s">
         <v>43</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F143" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>684</v>
-      </c>
-      <c r="B143" t="s">
-        <v>41</v>
-      </c>
-      <c r="C143" t="s">
-        <v>22</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143" t="s">
-        <v>33</v>
-      </c>
-      <c r="F143" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>684</v>
       </c>
@@ -5310,19 +5316,19 @@
         <v>41</v>
       </c>
       <c r="C144" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F144" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>684</v>
       </c>
@@ -5330,7 +5336,7 @@
         <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5342,41 +5348,44 @@
         <v>44</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>684</v>
       </c>
       <c r="B146" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" t="s">
+        <v>47</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146" t="s">
+        <v>43</v>
+      </c>
+      <c r="F146" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>684</v>
+      </c>
+      <c r="B147" t="s">
         <v>68</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>73</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E147" t="s">
         <v>59</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F147" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>684</v>
-      </c>
-      <c r="B147" t="s">
-        <v>224</v>
-      </c>
-      <c r="C147" t="s">
-        <v>235</v>
-      </c>
-      <c r="E147" t="s">
-        <v>234</v>
-      </c>
-      <c r="F147" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>684</v>
       </c>
@@ -5384,50 +5393,50 @@
         <v>224</v>
       </c>
       <c r="C148" t="s">
+        <v>235</v>
+      </c>
+      <c r="E148" t="s">
+        <v>234</v>
+      </c>
+      <c r="F148" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>684</v>
+      </c>
+      <c r="B149" t="s">
+        <v>224</v>
+      </c>
+      <c r="C149" t="s">
         <v>223</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E149" t="s">
         <v>214</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F149" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>684</v>
-      </c>
-      <c r="B149" t="s">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>684</v>
+      </c>
+      <c r="B150" t="s">
         <v>745</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D150" t="s">
         <v>712</v>
-      </c>
-      <c r="E149" t="s">
-        <v>208</v>
-      </c>
-      <c r="F149" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>684</v>
-      </c>
-      <c r="B150" t="s">
-        <v>212</v>
-      </c>
-      <c r="C150" t="s">
-        <v>211</v>
       </c>
       <c r="E150" t="s">
         <v>208</v>
       </c>
       <c r="F150" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>684</v>
       </c>
@@ -5435,16 +5444,16 @@
         <v>212</v>
       </c>
       <c r="C151" t="s">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="E151" t="s">
         <v>208</v>
       </c>
       <c r="F151" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>684</v>
       </c>
@@ -5452,50 +5461,50 @@
         <v>212</v>
       </c>
       <c r="C152" t="s">
-        <v>67</v>
+        <v>387</v>
       </c>
       <c r="E152" t="s">
         <v>208</v>
       </c>
       <c r="F152" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>684</v>
       </c>
       <c r="B153" t="s">
-        <v>639</v>
-      </c>
-      <c r="D153" t="s">
-        <v>582</v>
+        <v>212</v>
+      </c>
+      <c r="C153" t="s">
+        <v>67</v>
       </c>
       <c r="E153" t="s">
         <v>208</v>
       </c>
       <c r="F153" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>684</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
-      </c>
-      <c r="C154" t="s">
-        <v>210</v>
+        <v>639</v>
+      </c>
+      <c r="D154" t="s">
+        <v>582</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
       </c>
       <c r="F154" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>684</v>
       </c>
@@ -5503,84 +5512,84 @@
         <v>243</v>
       </c>
       <c r="C155" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
       </c>
       <c r="F155" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>684</v>
+      </c>
+      <c r="B156" t="s">
+        <v>243</v>
+      </c>
+      <c r="C156" t="s">
+        <v>209</v>
+      </c>
+      <c r="E156" t="s">
+        <v>208</v>
+      </c>
+      <c r="F156" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>684</v>
-      </c>
-      <c r="B156" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>684</v>
+      </c>
+      <c r="B157" t="s">
         <v>640</v>
-      </c>
-      <c r="D156" t="s">
-        <v>582</v>
-      </c>
-      <c r="E156" t="s">
-        <v>475</v>
-      </c>
-      <c r="F156" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>684</v>
-      </c>
-      <c r="B157" t="s">
-        <v>641</v>
       </c>
       <c r="D157" t="s">
         <v>582</v>
       </c>
       <c r="E157" t="s">
+        <v>475</v>
+      </c>
+      <c r="F157" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>684</v>
+      </c>
+      <c r="B158" t="s">
+        <v>641</v>
+      </c>
+      <c r="D158" t="s">
+        <v>582</v>
+      </c>
+      <c r="E158" t="s">
         <v>256</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F158" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>684</v>
-      </c>
-      <c r="B158" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>684</v>
+      </c>
+      <c r="B159" t="s">
         <v>452</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C159" t="s">
         <v>92</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E159" t="s">
         <v>453</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F159" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>684</v>
-      </c>
-      <c r="B159" t="s">
-        <v>726</v>
-      </c>
-      <c r="C159" t="s">
-        <v>576</v>
-      </c>
-      <c r="E159" t="s">
-        <v>724</v>
-      </c>
-      <c r="F159" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>684</v>
       </c>
@@ -5588,92 +5597,92 @@
         <v>726</v>
       </c>
       <c r="C160" t="s">
-        <v>78</v>
+        <v>576</v>
       </c>
       <c r="E160" t="s">
         <v>724</v>
       </c>
       <c r="F160" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>684</v>
+      </c>
+      <c r="B161" t="s">
+        <v>726</v>
+      </c>
+      <c r="C161" t="s">
+        <v>78</v>
+      </c>
+      <c r="E161" t="s">
+        <v>724</v>
+      </c>
+      <c r="F161" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>684</v>
-      </c>
-      <c r="B161" t="s">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>684</v>
+      </c>
+      <c r="B162" t="s">
         <v>642</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D162" t="s">
         <v>582</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E162" t="s">
         <v>644</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F162" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>684</v>
-      </c>
-      <c r="B162" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>684</v>
+      </c>
+      <c r="B163" t="s">
         <v>750</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D163" t="s">
         <v>712</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E163" t="s">
         <v>752</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F163" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>684</v>
-      </c>
-      <c r="B163" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>684</v>
+      </c>
+      <c r="B164" t="s">
         <v>689</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D164" t="s">
         <v>582</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E164" t="s">
         <v>690</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F164" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>684</v>
-      </c>
-      <c r="B164" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>684</v>
+      </c>
+      <c r="B165" t="s">
         <v>747</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D165" t="s">
         <v>78</v>
-      </c>
-      <c r="E164" t="s">
-        <v>752</v>
-      </c>
-      <c r="F164" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>684</v>
-      </c>
-      <c r="B165" t="s">
-        <v>749</v>
-      </c>
-      <c r="D165" t="s">
-        <v>712</v>
       </c>
       <c r="E165" t="s">
         <v>752</v>
@@ -5682,32 +5691,32 @@
         <v>748</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>684</v>
       </c>
       <c r="B166" t="s">
+        <v>749</v>
+      </c>
+      <c r="D166" t="s">
+        <v>712</v>
+      </c>
+      <c r="E166" t="s">
+        <v>752</v>
+      </c>
+      <c r="F166" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>684</v>
+      </c>
+      <c r="B167" t="s">
         <v>589</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D167" t="s">
         <v>78</v>
-      </c>
-      <c r="E166" t="s">
-        <v>590</v>
-      </c>
-      <c r="F166" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>684</v>
-      </c>
-      <c r="B167" t="s">
-        <v>593</v>
-      </c>
-      <c r="D167" t="s">
-        <v>582</v>
       </c>
       <c r="E167" t="s">
         <v>590</v>
@@ -5716,86 +5725,83 @@
         <v>591</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>684</v>
       </c>
       <c r="B168" t="s">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="D168" t="s">
         <v>582</v>
       </c>
       <c r="E168" t="s">
+        <v>590</v>
+      </c>
+      <c r="F168" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>684</v>
+      </c>
+      <c r="B169" t="s">
+        <v>645</v>
+      </c>
+      <c r="D169" t="s">
+        <v>582</v>
+      </c>
+      <c r="E169" t="s">
         <v>391</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F169" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>684</v>
-      </c>
-      <c r="B169" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>684</v>
+      </c>
+      <c r="B170" t="s">
         <v>557</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>558</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E170" t="s">
         <v>369</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F170" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>684</v>
-      </c>
-      <c r="B170" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>684</v>
+      </c>
+      <c r="B171" t="s">
         <v>646</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D171" t="s">
         <v>582</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E171" t="s">
         <v>475</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F171" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>684</v>
-      </c>
-      <c r="B171" t="s">
-        <v>694</v>
-      </c>
-      <c r="D171" t="s">
-        <v>692</v>
-      </c>
-      <c r="E171" t="s">
-        <v>697</v>
-      </c>
-      <c r="F171" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>684</v>
       </c>
       <c r="B172" t="s">
         <v>694</v>
       </c>
-      <c r="C172" t="s">
-        <v>696</v>
-      </c>
-      <c r="D172">
-        <v>1</v>
+      <c r="D172" t="s">
+        <v>692</v>
       </c>
       <c r="E172" t="s">
         <v>697</v>
@@ -5804,7 +5810,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>684</v>
       </c>
@@ -5812,7 +5818,7 @@
         <v>694</v>
       </c>
       <c r="C173" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5821,86 +5827,89 @@
         <v>697</v>
       </c>
       <c r="F173" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>684</v>
+      </c>
+      <c r="B174" t="s">
+        <v>694</v>
+      </c>
+      <c r="C174" t="s">
+        <v>695</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
+        <v>697</v>
+      </c>
+      <c r="F174" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>684</v>
-      </c>
-      <c r="B174" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>684</v>
+      </c>
+      <c r="B175" t="s">
         <v>647</v>
-      </c>
-      <c r="D174" t="s">
-        <v>582</v>
-      </c>
-      <c r="E174" t="s">
-        <v>287</v>
-      </c>
-      <c r="F174" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>684</v>
-      </c>
-      <c r="B175" t="s">
-        <v>648</v>
       </c>
       <c r="D175" t="s">
         <v>582</v>
       </c>
       <c r="E175" t="s">
-        <v>414</v>
+        <v>287</v>
       </c>
       <c r="F175" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>684</v>
       </c>
       <c r="B176" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D176" t="s">
         <v>582</v>
       </c>
       <c r="E176" t="s">
-        <v>537</v>
+        <v>414</v>
       </c>
       <c r="F176" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>684</v>
       </c>
       <c r="B177" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
       <c r="D177" t="s">
         <v>582</v>
       </c>
       <c r="E177" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="F177" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>684</v>
       </c>
       <c r="B178" t="s">
-        <v>72</v>
-      </c>
-      <c r="C178" t="s">
-        <v>63</v>
+        <v>681</v>
+      </c>
+      <c r="D178" t="s">
+        <v>582</v>
       </c>
       <c r="E178" t="s">
         <v>59</v>
@@ -5909,7 +5918,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>684</v>
       </c>
@@ -5917,7 +5926,7 @@
         <v>72</v>
       </c>
       <c r="C179" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E179" t="s">
         <v>59</v>
@@ -5926,95 +5935,92 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>684</v>
       </c>
       <c r="B180" t="s">
+        <v>72</v>
+      </c>
+      <c r="C180" t="s">
+        <v>77</v>
+      </c>
+      <c r="E180" t="s">
+        <v>59</v>
+      </c>
+      <c r="F180" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>684</v>
+      </c>
+      <c r="B181" t="s">
         <v>295</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>84</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E181" t="s">
         <v>291</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F181" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>684</v>
-      </c>
-      <c r="B181" t="s">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>684</v>
+      </c>
+      <c r="B182" t="s">
         <v>650</v>
-      </c>
-      <c r="D181" t="s">
-        <v>582</v>
-      </c>
-      <c r="E181" t="s">
-        <v>651</v>
-      </c>
-      <c r="F181" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>684</v>
-      </c>
-      <c r="B182" t="s">
-        <v>653</v>
       </c>
       <c r="D182" t="s">
         <v>582</v>
       </c>
       <c r="E182" t="s">
-        <v>526</v>
+        <v>651</v>
       </c>
       <c r="F182" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>684</v>
       </c>
       <c r="B183" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D183" t="s">
         <v>582</v>
       </c>
       <c r="E183" t="s">
+        <v>526</v>
+      </c>
+      <c r="F183" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>684</v>
+      </c>
+      <c r="B184" t="s">
+        <v>654</v>
+      </c>
+      <c r="D184" t="s">
+        <v>582</v>
+      </c>
+      <c r="E184" t="s">
         <v>475</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F184" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>684</v>
-      </c>
-      <c r="B184" t="s">
-        <v>342</v>
-      </c>
-      <c r="C184" t="s">
-        <v>343</v>
-      </c>
-      <c r="D184">
-        <v>1</v>
-      </c>
-      <c r="E184" t="s">
-        <v>337</v>
-      </c>
-      <c r="F184" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>684</v>
       </c>
@@ -6022,7 +6028,7 @@
         <v>342</v>
       </c>
       <c r="C185" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -6034,7 +6040,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>684</v>
       </c>
@@ -6042,7 +6048,7 @@
         <v>342</v>
       </c>
       <c r="C186" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -6051,10 +6057,10 @@
         <v>337</v>
       </c>
       <c r="F186" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>684</v>
       </c>
@@ -6062,7 +6068,7 @@
         <v>342</v>
       </c>
       <c r="C187" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -6074,44 +6080,44 @@
         <v>341</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>684</v>
       </c>
       <c r="B188" t="s">
-        <v>9</v>
-      </c>
-      <c r="D188" t="s">
-        <v>692</v>
+        <v>342</v>
+      </c>
+      <c r="C188" t="s">
+        <v>346</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="F188" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>684</v>
       </c>
       <c r="B189" t="s">
         <v>9</v>
       </c>
-      <c r="C189" t="s">
-        <v>10</v>
-      </c>
-      <c r="D189">
-        <v>1</v>
+      <c r="D189" t="s">
+        <v>692</v>
       </c>
       <c r="E189" t="s">
         <v>11</v>
       </c>
       <c r="F189" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>684</v>
       </c>
@@ -6119,70 +6125,73 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>684</v>
+      </c>
+      <c r="B191" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" t="s">
         <v>13</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E191" t="s">
         <v>14</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F191" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>684</v>
-      </c>
-      <c r="B191" t="s">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>684</v>
+      </c>
+      <c r="B192" t="s">
         <v>7</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" t="s">
         <v>8</v>
       </c>
-      <c r="D191">
-        <v>1</v>
-      </c>
-      <c r="E191" t="s">
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192" t="s">
         <v>11</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F192" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>684</v>
-      </c>
-      <c r="B192" t="s">
-        <v>700</v>
-      </c>
-      <c r="D192" t="s">
-        <v>692</v>
-      </c>
-      <c r="E192" t="s">
-        <v>702</v>
-      </c>
-      <c r="F192" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>684</v>
       </c>
       <c r="B193" t="s">
         <v>700</v>
       </c>
-      <c r="C193" t="s">
-        <v>361</v>
+      <c r="D193" t="s">
+        <v>692</v>
       </c>
       <c r="E193" t="s">
         <v>702</v>
       </c>
       <c r="F193" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>684</v>
       </c>
@@ -6190,16 +6199,16 @@
         <v>700</v>
       </c>
       <c r="C194" t="s">
-        <v>714</v>
+        <v>361</v>
       </c>
       <c r="E194" t="s">
         <v>702</v>
       </c>
       <c r="F194" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>684</v>
       </c>
@@ -6207,16 +6216,16 @@
         <v>700</v>
       </c>
       <c r="C195" t="s">
-        <v>546</v>
+        <v>714</v>
       </c>
       <c r="E195" t="s">
         <v>702</v>
       </c>
       <c r="F195" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>684</v>
       </c>
@@ -6224,16 +6233,16 @@
         <v>700</v>
       </c>
       <c r="C196" t="s">
-        <v>715</v>
+        <v>546</v>
       </c>
       <c r="E196" t="s">
         <v>702</v>
       </c>
       <c r="F196" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>684</v>
       </c>
@@ -6241,47 +6250,44 @@
         <v>700</v>
       </c>
       <c r="C197" t="s">
-        <v>10</v>
-      </c>
-      <c r="D197">
-        <v>1</v>
+        <v>715</v>
       </c>
       <c r="E197" t="s">
         <v>702</v>
       </c>
       <c r="F197" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>684</v>
       </c>
       <c r="B198" t="s">
-        <v>701</v>
-      </c>
-      <c r="D198" t="s">
-        <v>692</v>
+        <v>700</v>
+      </c>
+      <c r="C198" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
       </c>
       <c r="E198" t="s">
         <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>684</v>
       </c>
       <c r="B199" t="s">
         <v>701</v>
       </c>
-      <c r="C199" t="s">
-        <v>8</v>
-      </c>
-      <c r="D199">
-        <v>1</v>
+      <c r="D199" t="s">
+        <v>692</v>
       </c>
       <c r="E199" t="s">
         <v>702</v>
@@ -6290,7 +6296,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>684</v>
       </c>
@@ -6298,7 +6304,7 @@
         <v>701</v>
       </c>
       <c r="C200" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -6307,10 +6313,10 @@
         <v>702</v>
       </c>
       <c r="F200" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>684</v>
       </c>
@@ -6318,7 +6324,7 @@
         <v>701</v>
       </c>
       <c r="C201" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -6327,27 +6333,30 @@
         <v>702</v>
       </c>
       <c r="F201" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>684</v>
+      </c>
+      <c r="B202" t="s">
+        <v>701</v>
+      </c>
+      <c r="C202" t="s">
+        <v>96</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
+        <v>702</v>
+      </c>
+      <c r="F202" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
-        <v>684</v>
-      </c>
-      <c r="B202" t="s">
-        <v>441</v>
-      </c>
-      <c r="C202" t="s">
-        <v>442</v>
-      </c>
-      <c r="E202" t="s">
-        <v>436</v>
-      </c>
-      <c r="F202" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>684</v>
       </c>
@@ -6355,53 +6364,53 @@
         <v>441</v>
       </c>
       <c r="C203" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E203" t="s">
         <v>436</v>
       </c>
       <c r="F203" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>684</v>
+      </c>
+      <c r="B204" t="s">
+        <v>441</v>
+      </c>
+      <c r="C204" t="s">
+        <v>438</v>
+      </c>
+      <c r="E204" t="s">
+        <v>436</v>
+      </c>
+      <c r="F204" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>684</v>
-      </c>
-      <c r="B204" t="s">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>684</v>
+      </c>
+      <c r="B205" t="s">
         <v>308</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" t="s">
         <v>8</v>
       </c>
-      <c r="D204">
-        <v>1</v>
-      </c>
-      <c r="E204" t="s">
-        <v>309</v>
-      </c>
-      <c r="F204" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
-        <v>684</v>
-      </c>
-      <c r="B205" t="s">
-        <v>313</v>
-      </c>
-      <c r="C205" t="s">
-        <v>311</v>
+      <c r="D205">
+        <v>1</v>
       </c>
       <c r="E205" t="s">
         <v>309</v>
       </c>
       <c r="F205" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>684</v>
       </c>
@@ -6409,7 +6418,7 @@
         <v>313</v>
       </c>
       <c r="C206" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E206" t="s">
         <v>309</v>
@@ -6418,7 +6427,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>684</v>
       </c>
@@ -6426,16 +6435,16 @@
         <v>313</v>
       </c>
       <c r="C207" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E207" t="s">
         <v>309</v>
       </c>
       <c r="F207" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>684</v>
       </c>
@@ -6443,19 +6452,16 @@
         <v>313</v>
       </c>
       <c r="C208" t="s">
-        <v>317</v>
-      </c>
-      <c r="D208">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="E208" t="s">
         <v>309</v>
       </c>
       <c r="F208" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>684</v>
       </c>
@@ -6463,7 +6469,7 @@
         <v>313</v>
       </c>
       <c r="C209" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -6472,10 +6478,10 @@
         <v>309</v>
       </c>
       <c r="F209" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>684</v>
       </c>
@@ -6483,87 +6489,90 @@
         <v>313</v>
       </c>
       <c r="C210" t="s">
-        <v>388</v>
+        <v>315</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
       </c>
       <c r="E210" t="s">
         <v>309</v>
       </c>
       <c r="F210" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>684</v>
       </c>
       <c r="B211" t="s">
-        <v>655</v>
-      </c>
-      <c r="D211" t="s">
-        <v>582</v>
+        <v>313</v>
+      </c>
+      <c r="C211" t="s">
+        <v>388</v>
       </c>
       <c r="E211" t="s">
         <v>309</v>
       </c>
       <c r="F211" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>684</v>
       </c>
       <c r="B212" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D212" t="s">
         <v>582</v>
       </c>
       <c r="E212" t="s">
+        <v>309</v>
+      </c>
+      <c r="F212" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>684</v>
+      </c>
+      <c r="B213" t="s">
+        <v>656</v>
+      </c>
+      <c r="D213" t="s">
+        <v>582</v>
+      </c>
+      <c r="E213" t="s">
         <v>291</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F213" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
-        <v>684</v>
-      </c>
-      <c r="B213" t="s">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>684</v>
+      </c>
+      <c r="B214" t="s">
         <v>472</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C214" t="s">
         <v>471</v>
       </c>
-      <c r="D213">
-        <v>1</v>
-      </c>
-      <c r="E213" t="s">
-        <v>475</v>
-      </c>
-      <c r="F213" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
-        <v>684</v>
-      </c>
-      <c r="B214" t="s">
-        <v>466</v>
-      </c>
-      <c r="C214" t="s">
-        <v>467</v>
+      <c r="D214">
+        <v>1</v>
       </c>
       <c r="E214" t="s">
         <v>475</v>
       </c>
       <c r="F214" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>684</v>
       </c>
@@ -6571,16 +6580,16 @@
         <v>466</v>
       </c>
       <c r="C215" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E215" t="s">
         <v>475</v>
       </c>
       <c r="F215" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>684</v>
       </c>
@@ -6588,16 +6597,16 @@
         <v>466</v>
       </c>
       <c r="C216" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E216" t="s">
         <v>475</v>
       </c>
       <c r="F216" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>684</v>
       </c>
@@ -6605,24 +6614,24 @@
         <v>466</v>
       </c>
       <c r="C217" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E217" t="s">
         <v>475</v>
       </c>
       <c r="F217" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>684</v>
+      </c>
+      <c r="B218" t="s">
+        <v>466</v>
+      </c>
+      <c r="C218" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>684</v>
-      </c>
-      <c r="B218" t="s">
-        <v>473</v>
-      </c>
-      <c r="C218" t="s">
-        <v>474</v>
       </c>
       <c r="E218" t="s">
         <v>475</v>
@@ -6631,27 +6640,24 @@
         <v>470</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>684</v>
       </c>
       <c r="B219" t="s">
-        <v>229</v>
+        <v>473</v>
       </c>
       <c r="C219" t="s">
-        <v>230</v>
-      </c>
-      <c r="D219">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="E219" t="s">
-        <v>233</v>
+        <v>475</v>
       </c>
       <c r="F219" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>684</v>
       </c>
@@ -6659,16 +6665,19 @@
         <v>229</v>
       </c>
       <c r="C220" t="s">
-        <v>494</v>
+        <v>230</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="F220" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>684</v>
       </c>
@@ -6676,19 +6685,16 @@
         <v>229</v>
       </c>
       <c r="C221" t="s">
-        <v>497</v>
-      </c>
-      <c r="D221">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="E221" t="s">
         <v>495</v>
       </c>
       <c r="F221" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>684</v>
       </c>
@@ -6696,16 +6702,19 @@
         <v>229</v>
       </c>
       <c r="C222" t="s">
-        <v>499</v>
+        <v>497</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
       </c>
       <c r="E222" t="s">
         <v>495</v>
       </c>
       <c r="F222" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>684</v>
       </c>
@@ -6713,16 +6722,16 @@
         <v>229</v>
       </c>
       <c r="C223" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E223" t="s">
         <v>495</v>
       </c>
       <c r="F223" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>684</v>
       </c>
@@ -6730,16 +6739,16 @@
         <v>229</v>
       </c>
       <c r="C224" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E224" t="s">
         <v>495</v>
       </c>
       <c r="F224" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>684</v>
       </c>
@@ -6747,16 +6756,16 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E225" t="s">
         <v>495</v>
       </c>
       <c r="F225" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>684</v>
       </c>
@@ -6764,19 +6773,16 @@
         <v>229</v>
       </c>
       <c r="C226" t="s">
-        <v>506</v>
-      </c>
-      <c r="D226">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="E226" t="s">
         <v>495</v>
       </c>
       <c r="F226" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>684</v>
       </c>
@@ -6784,16 +6790,19 @@
         <v>229</v>
       </c>
       <c r="C227" t="s">
-        <v>508</v>
+        <v>506</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
       </c>
       <c r="E227" t="s">
         <v>495</v>
       </c>
       <c r="F227" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>684</v>
       </c>
@@ -6801,16 +6810,16 @@
         <v>229</v>
       </c>
       <c r="C228" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E228" t="s">
         <v>495</v>
       </c>
       <c r="F228" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>684</v>
       </c>
@@ -6818,33 +6827,33 @@
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E229" t="s">
         <v>495</v>
       </c>
       <c r="F229" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>684</v>
+      </c>
+      <c r="B230" t="s">
+        <v>229</v>
+      </c>
+      <c r="C230" t="s">
+        <v>512</v>
+      </c>
+      <c r="E230" t="s">
+        <v>495</v>
+      </c>
+      <c r="F230" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
-        <v>684</v>
-      </c>
-      <c r="B230" t="s">
-        <v>216</v>
-      </c>
-      <c r="C230" t="s">
-        <v>219</v>
-      </c>
-      <c r="E230" t="s">
-        <v>214</v>
-      </c>
-      <c r="F230" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>684</v>
       </c>
@@ -6852,16 +6861,16 @@
         <v>216</v>
       </c>
       <c r="C231" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E231" t="s">
         <v>214</v>
       </c>
       <c r="F231" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>684</v>
       </c>
@@ -6869,19 +6878,16 @@
         <v>216</v>
       </c>
       <c r="C232" t="s">
-        <v>10</v>
-      </c>
-      <c r="D232">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="E232" t="s">
         <v>214</v>
       </c>
       <c r="F232" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>684</v>
       </c>
@@ -6889,16 +6895,19 @@
         <v>216</v>
       </c>
       <c r="C233" t="s">
-        <v>225</v>
+        <v>10</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
       </c>
       <c r="E233" t="s">
         <v>214</v>
       </c>
       <c r="F233" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>684</v>
       </c>
@@ -6906,19 +6915,16 @@
         <v>216</v>
       </c>
       <c r="C234" t="s">
-        <v>594</v>
-      </c>
-      <c r="D234">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="E234" t="s">
-        <v>595</v>
+        <v>214</v>
       </c>
       <c r="F234" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>684</v>
       </c>
@@ -6926,7 +6932,7 @@
         <v>216</v>
       </c>
       <c r="C235" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -6938,7 +6944,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>684</v>
       </c>
@@ -6946,16 +6952,19 @@
         <v>216</v>
       </c>
       <c r="C236" t="s">
-        <v>227</v>
+        <v>597</v>
+      </c>
+      <c r="D236">
+        <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>233</v>
+        <v>595</v>
       </c>
       <c r="F236" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>684</v>
       </c>
@@ -6963,39 +6972,36 @@
         <v>216</v>
       </c>
       <c r="C237" t="s">
+        <v>227</v>
+      </c>
+      <c r="E237" t="s">
+        <v>233</v>
+      </c>
+      <c r="F237" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>684</v>
+      </c>
+      <c r="B238" t="s">
+        <v>216</v>
+      </c>
+      <c r="C238" t="s">
         <v>602</v>
       </c>
-      <c r="D237">
-        <v>1</v>
-      </c>
-      <c r="E237" t="s">
+      <c r="D238">
+        <v>1</v>
+      </c>
+      <c r="E238" t="s">
         <v>603</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F238" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" t="s">
-        <v>684</v>
-      </c>
-      <c r="B238" t="s">
-        <v>213</v>
-      </c>
-      <c r="C238" t="s">
-        <v>8</v>
-      </c>
-      <c r="D238">
-        <v>1</v>
-      </c>
-      <c r="E238" t="s">
-        <v>214</v>
-      </c>
-      <c r="F238" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>684</v>
       </c>
@@ -7003,56 +7009,56 @@
         <v>213</v>
       </c>
       <c r="C239" t="s">
+        <v>8</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
+        <v>214</v>
+      </c>
+      <c r="F239" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>684</v>
+      </c>
+      <c r="B240" t="s">
+        <v>213</v>
+      </c>
+      <c r="C240" t="s">
         <v>35</v>
       </c>
-      <c r="D239">
-        <v>1</v>
-      </c>
-      <c r="E239" t="s">
+      <c r="D240">
+        <v>1</v>
+      </c>
+      <c r="E240" t="s">
         <v>603</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F240" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
-        <v>684</v>
-      </c>
-      <c r="B240" t="s">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>684</v>
+      </c>
+      <c r="B241" t="s">
         <v>62</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C241" t="s">
         <v>67</v>
       </c>
-      <c r="E240" t="s">
+      <c r="E241" t="s">
         <v>59</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F241" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A241" t="s">
-        <v>684</v>
-      </c>
-      <c r="B241" t="s">
-        <v>23</v>
-      </c>
-      <c r="C241" t="s">
-        <v>716</v>
-      </c>
-      <c r="D241">
-        <v>1</v>
-      </c>
-      <c r="E241" t="s">
-        <v>709</v>
-      </c>
-      <c r="F241" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>684</v>
       </c>
@@ -7060,16 +7066,19 @@
         <v>23</v>
       </c>
       <c r="C242" t="s">
-        <v>713</v>
+        <v>716</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
       </c>
       <c r="E242" t="s">
         <v>709</v>
       </c>
       <c r="F242" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>684</v>
       </c>
@@ -7077,16 +7086,16 @@
         <v>23</v>
       </c>
       <c r="C243" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E243" t="s">
         <v>709</v>
       </c>
       <c r="F243" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>684</v>
       </c>
@@ -7094,16 +7103,16 @@
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>575</v>
+        <v>718</v>
       </c>
       <c r="E244" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F244" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>684</v>
       </c>
@@ -7111,19 +7120,16 @@
         <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>513</v>
-      </c>
-      <c r="D245">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="E245" t="s">
-        <v>514</v>
+        <v>724</v>
       </c>
       <c r="F245" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>684</v>
       </c>
@@ -7131,16 +7137,19 @@
         <v>23</v>
       </c>
       <c r="C246" t="s">
-        <v>405</v>
+        <v>513</v>
+      </c>
+      <c r="D246">
+        <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
       <c r="F246" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>684</v>
       </c>
@@ -7148,19 +7157,16 @@
         <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>521</v>
-      </c>
-      <c r="D247">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="E247" t="s">
-        <v>537</v>
+        <v>406</v>
       </c>
       <c r="F247" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>684</v>
       </c>
@@ -7168,7 +7174,7 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -7177,10 +7183,10 @@
         <v>537</v>
       </c>
       <c r="F248" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>684</v>
       </c>
@@ -7188,19 +7194,19 @@
         <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>351</v>
+        <v>524</v>
       </c>
       <c r="D249">
         <v>1</v>
       </c>
       <c r="E249" t="s">
-        <v>414</v>
+        <v>537</v>
       </c>
       <c r="F249" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>684</v>
       </c>
@@ -7208,7 +7214,7 @@
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -7217,10 +7223,10 @@
         <v>414</v>
       </c>
       <c r="F250" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>684</v>
       </c>
@@ -7228,19 +7234,19 @@
         <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
       <c r="D251">
         <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="F251" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>684</v>
       </c>
@@ -7248,19 +7254,19 @@
         <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D252">
         <v>1</v>
       </c>
       <c r="E252" t="s">
-        <v>538</v>
+        <v>444</v>
       </c>
       <c r="F252" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>684</v>
       </c>
@@ -7268,7 +7274,7 @@
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -7277,10 +7283,10 @@
         <v>538</v>
       </c>
       <c r="F253" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>684</v>
       </c>
@@ -7288,19 +7294,19 @@
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>265</v>
+        <v>539</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="F254" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>684</v>
       </c>
@@ -7308,19 +7314,19 @@
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="D255">
         <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>418</v>
+        <v>286</v>
       </c>
       <c r="F255" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>684</v>
       </c>
@@ -7328,19 +7334,19 @@
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="F256" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>684</v>
       </c>
@@ -7348,7 +7354,7 @@
         <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -7357,10 +7363,10 @@
         <v>391</v>
       </c>
       <c r="F257" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>684</v>
       </c>
@@ -7368,19 +7374,19 @@
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="D258">
         <v>1</v>
       </c>
       <c r="E258" t="s">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="F258" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>684</v>
       </c>
@@ -7388,7 +7394,7 @@
         <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>433</v>
+        <v>275</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -7397,10 +7403,10 @@
         <v>288</v>
       </c>
       <c r="F259" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>684</v>
       </c>
@@ -7408,19 +7414,19 @@
         <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
       <c r="D260">
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>587</v>
+        <v>288</v>
       </c>
       <c r="F260" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>684</v>
       </c>
@@ -7428,19 +7434,19 @@
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>450</v>
+        <v>587</v>
       </c>
       <c r="F261" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>684</v>
       </c>
@@ -7448,19 +7454,19 @@
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="D262">
         <v>1</v>
       </c>
       <c r="E262" t="s">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="F262" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>684</v>
       </c>
@@ -7468,7 +7474,7 @@
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -7477,10 +7483,10 @@
         <v>289</v>
       </c>
       <c r="F263" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>684</v>
       </c>
@@ -7488,19 +7494,19 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>528</v>
+        <v>279</v>
       </c>
       <c r="D264">
         <v>1</v>
       </c>
       <c r="E264" t="s">
-        <v>526</v>
+        <v>289</v>
       </c>
       <c r="F264" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>684</v>
       </c>
@@ -7508,7 +7514,7 @@
         <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -7517,10 +7523,10 @@
         <v>526</v>
       </c>
       <c r="F265" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>684</v>
       </c>
@@ -7528,16 +7534,19 @@
         <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="F266" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>684</v>
       </c>
@@ -7545,19 +7554,16 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>26</v>
-      </c>
-      <c r="D267">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E267" t="s">
-        <v>245</v>
+        <v>102</v>
       </c>
       <c r="F267" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>684</v>
       </c>
@@ -7565,7 +7571,7 @@
         <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -7577,7 +7583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>684</v>
       </c>
@@ -7585,19 +7591,19 @@
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="D269">
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="F269" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>684</v>
       </c>
@@ -7605,16 +7611,19 @@
         <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>77</v>
+        <v>321</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
       </c>
       <c r="E270" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="F270" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>684</v>
       </c>
@@ -7622,19 +7631,16 @@
         <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>24</v>
-      </c>
-      <c r="D271">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E271" t="s">
-        <v>257</v>
+        <v>420</v>
       </c>
       <c r="F271" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>684</v>
       </c>
@@ -7642,87 +7648,90 @@
         <v>23</v>
       </c>
       <c r="C272" t="s">
+        <v>24</v>
+      </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
+      <c r="E272" t="s">
+        <v>257</v>
+      </c>
+      <c r="F272" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>684</v>
+      </c>
+      <c r="B273" t="s">
+        <v>23</v>
+      </c>
+      <c r="C273" t="s">
         <v>30</v>
       </c>
-      <c r="D272">
+      <c r="D273">
         <v>2</v>
       </c>
-      <c r="E272" t="s">
+      <c r="E273" t="s">
         <v>247</v>
       </c>
-      <c r="F272" t="s">
+      <c r="F273" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A273" t="s">
-        <v>684</v>
-      </c>
-      <c r="B273" t="s">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>684</v>
+      </c>
+      <c r="B274" t="s">
         <v>385</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C274" t="s">
         <v>84</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E274" t="s">
         <v>286</v>
       </c>
-      <c r="F273" t="s">
+      <c r="F274" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A274" t="s">
-        <v>684</v>
-      </c>
-      <c r="B274" t="s">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>684</v>
+      </c>
+      <c r="B275" t="s">
         <v>657</v>
       </c>
-      <c r="D274" t="s">
+      <c r="D275" t="s">
         <v>582</v>
       </c>
-      <c r="E274" t="s">
+      <c r="E275" t="s">
         <v>288</v>
       </c>
-      <c r="F274" t="s">
+      <c r="F275" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
-        <v>684</v>
-      </c>
-      <c r="B275" t="s">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>684</v>
+      </c>
+      <c r="B276" t="s">
         <v>106</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C276" t="s">
         <v>111</v>
       </c>
-      <c r="E275" t="s">
+      <c r="E276" t="s">
         <v>112</v>
       </c>
-      <c r="F275" t="s">
+      <c r="F276" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
-        <v>684</v>
-      </c>
-      <c r="B276" t="s">
-        <v>98</v>
-      </c>
-      <c r="C276" t="s">
-        <v>104</v>
-      </c>
-      <c r="E276" t="s">
-        <v>102</v>
-      </c>
-      <c r="F276" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>684</v>
       </c>
@@ -7730,16 +7739,16 @@
         <v>98</v>
       </c>
       <c r="C277" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E277" t="s">
         <v>102</v>
       </c>
       <c r="F277" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>684</v>
       </c>
@@ -7747,16 +7756,16 @@
         <v>98</v>
       </c>
       <c r="C278" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E278" t="s">
         <v>102</v>
       </c>
       <c r="F278" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>684</v>
       </c>
@@ -7764,7 +7773,7 @@
         <v>98</v>
       </c>
       <c r="C279" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E279" t="s">
         <v>102</v>
@@ -7773,166 +7782,163 @@
         <v>103</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>684</v>
       </c>
       <c r="B280" t="s">
-        <v>658</v>
-      </c>
-      <c r="D280" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="C280" t="s">
+        <v>107</v>
       </c>
       <c r="E280" t="s">
         <v>102</v>
       </c>
       <c r="F280" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>684</v>
       </c>
       <c r="B281" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D281" t="s">
         <v>582</v>
       </c>
       <c r="E281" t="s">
+        <v>102</v>
+      </c>
+      <c r="F281" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>684</v>
+      </c>
+      <c r="B282" t="s">
+        <v>659</v>
+      </c>
+      <c r="D282" t="s">
+        <v>582</v>
+      </c>
+      <c r="E282" t="s">
         <v>420</v>
       </c>
-      <c r="F281" t="s">
+      <c r="F282" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A282" t="s">
-        <v>684</v>
-      </c>
-      <c r="B282" t="s">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>684</v>
+      </c>
+      <c r="B283" t="s">
         <v>330</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C283" t="s">
         <v>322</v>
       </c>
-      <c r="E282" t="s">
+      <c r="E283" t="s">
         <v>320</v>
       </c>
-      <c r="F282" t="s">
+      <c r="F283" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A283" t="s">
-        <v>684</v>
-      </c>
-      <c r="B283" t="s">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>684</v>
+      </c>
+      <c r="B284" t="s">
         <v>239</v>
       </c>
-      <c r="C283" t="s">
+      <c r="C284" t="s">
         <v>240</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E284" t="s">
         <v>241</v>
       </c>
-      <c r="F283" t="s">
+      <c r="F284" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A284" t="s">
-        <v>684</v>
-      </c>
-      <c r="B284" t="s">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>684</v>
+      </c>
+      <c r="B285" t="s">
         <v>660</v>
-      </c>
-      <c r="D284" t="s">
-        <v>582</v>
-      </c>
-      <c r="E284" t="s">
-        <v>324</v>
-      </c>
-      <c r="F284" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A285" t="s">
-        <v>684</v>
-      </c>
-      <c r="B285" t="s">
-        <v>662</v>
       </c>
       <c r="D285" t="s">
         <v>582</v>
       </c>
       <c r="E285" t="s">
+        <v>324</v>
+      </c>
+      <c r="F285" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>684</v>
+      </c>
+      <c r="B286" t="s">
+        <v>662</v>
+      </c>
+      <c r="D286" t="s">
+        <v>582</v>
+      </c>
+      <c r="E286" t="s">
         <v>289</v>
       </c>
-      <c r="F285" t="s">
+      <c r="F286" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A286" t="s">
-        <v>684</v>
-      </c>
-      <c r="B286" t="s">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>684</v>
+      </c>
+      <c r="B287" t="s">
         <v>399</v>
       </c>
-      <c r="C286" t="s">
+      <c r="C287" t="s">
         <v>77</v>
       </c>
-      <c r="E286" t="s">
+      <c r="E287" t="s">
         <v>391</v>
       </c>
-      <c r="F286" t="s">
+      <c r="F287" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A287" t="s">
-        <v>684</v>
-      </c>
-      <c r="B287" t="s">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>684</v>
+      </c>
+      <c r="B288" t="s">
         <v>19</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C288" t="s">
         <v>10</v>
       </c>
-      <c r="D287">
-        <v>1</v>
-      </c>
-      <c r="E287" t="s">
+      <c r="D288">
+        <v>1</v>
+      </c>
+      <c r="E288" t="s">
         <v>20</v>
       </c>
-      <c r="F287" t="s">
+      <c r="F288" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
-        <v>684</v>
-      </c>
-      <c r="B288" t="s">
-        <v>16</v>
-      </c>
-      <c r="C288" t="s">
-        <v>8</v>
-      </c>
-      <c r="D288">
-        <v>1</v>
-      </c>
-      <c r="E288" t="s">
-        <v>255</v>
-      </c>
-      <c r="F288" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>684</v>
       </c>
@@ -7940,7 +7946,10 @@
         <v>16</v>
       </c>
       <c r="C289" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D289">
+        <v>1</v>
       </c>
       <c r="E289" t="s">
         <v>255</v>
@@ -7949,7 +7958,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>684</v>
       </c>
@@ -7957,39 +7966,36 @@
         <v>16</v>
       </c>
       <c r="C290" t="s">
+        <v>17</v>
+      </c>
+      <c r="E290" t="s">
+        <v>255</v>
+      </c>
+      <c r="F290" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>684</v>
+      </c>
+      <c r="B291" t="s">
+        <v>16</v>
+      </c>
+      <c r="C291" t="s">
         <v>22</v>
       </c>
-      <c r="D290">
-        <v>1</v>
-      </c>
-      <c r="E290" t="s">
+      <c r="D291">
+        <v>1</v>
+      </c>
+      <c r="E291" t="s">
         <v>20</v>
       </c>
-      <c r="F290" t="s">
+      <c r="F291" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A291" t="s">
-        <v>684</v>
-      </c>
-      <c r="B291" t="s">
-        <v>267</v>
-      </c>
-      <c r="C291" t="s">
-        <v>10</v>
-      </c>
-      <c r="D291">
-        <v>1</v>
-      </c>
-      <c r="E291" t="s">
-        <v>287</v>
-      </c>
-      <c r="F291" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>684</v>
       </c>
@@ -7997,16 +8003,19 @@
         <v>267</v>
       </c>
       <c r="C292" t="s">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="D292">
+        <v>1</v>
       </c>
       <c r="E292" t="s">
         <v>287</v>
       </c>
       <c r="F292" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>684</v>
       </c>
@@ -8014,16 +8023,16 @@
         <v>267</v>
       </c>
       <c r="C293" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E293" t="s">
         <v>287</v>
       </c>
       <c r="F293" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>684</v>
       </c>
@@ -8031,16 +8040,16 @@
         <v>267</v>
       </c>
       <c r="C294" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="E294" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F294" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>684</v>
       </c>
@@ -8048,19 +8057,16 @@
         <v>267</v>
       </c>
       <c r="C295" t="s">
-        <v>354</v>
-      </c>
-      <c r="D295">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="E295" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F295" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>684</v>
       </c>
@@ -8068,7 +8074,7 @@
         <v>267</v>
       </c>
       <c r="C296" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D296">
         <v>1</v>
@@ -8077,10 +8083,10 @@
         <v>291</v>
       </c>
       <c r="F296" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>684</v>
       </c>
@@ -8088,16 +8094,19 @@
         <v>267</v>
       </c>
       <c r="C297" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D297">
+        <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F297" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>684</v>
       </c>
@@ -8105,19 +8114,16 @@
         <v>267</v>
       </c>
       <c r="C298" t="s">
-        <v>299</v>
-      </c>
-      <c r="D298">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E298" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F298" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>684</v>
       </c>
@@ -8125,7 +8131,7 @@
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -8134,10 +8140,10 @@
         <v>301</v>
       </c>
       <c r="F299" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>684</v>
       </c>
@@ -8145,16 +8151,19 @@
         <v>267</v>
       </c>
       <c r="C300" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="D300">
+        <v>1</v>
       </c>
       <c r="E300" t="s">
         <v>301</v>
       </c>
       <c r="F300" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>684</v>
       </c>
@@ -8162,10 +8171,7 @@
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>307</v>
-      </c>
-      <c r="D301">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="E301" t="s">
         <v>301</v>
@@ -8174,7 +8180,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>684</v>
       </c>
@@ -8182,7 +8188,7 @@
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -8191,47 +8197,47 @@
         <v>301</v>
       </c>
       <c r="F302" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>684</v>
+      </c>
+      <c r="B303" t="s">
+        <v>267</v>
+      </c>
+      <c r="C303" t="s">
+        <v>306</v>
+      </c>
+      <c r="D303">
+        <v>1</v>
+      </c>
+      <c r="E303" t="s">
+        <v>301</v>
+      </c>
+      <c r="F303" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>684</v>
-      </c>
-      <c r="B303" t="s">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>684</v>
+      </c>
+      <c r="B304" t="s">
         <v>664</v>
       </c>
-      <c r="D303" t="s">
+      <c r="D304" t="s">
         <v>582</v>
       </c>
-      <c r="E303" t="s">
+      <c r="E304" t="s">
         <v>332</v>
       </c>
-      <c r="F303" t="s">
+      <c r="F304" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>684</v>
-      </c>
-      <c r="B304" t="s">
-        <v>270</v>
-      </c>
-      <c r="C304" t="s">
-        <v>271</v>
-      </c>
-      <c r="D304">
-        <v>1</v>
-      </c>
-      <c r="E304" t="s">
-        <v>287</v>
-      </c>
-      <c r="F304" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>684</v>
       </c>
@@ -8239,19 +8245,19 @@
         <v>270</v>
       </c>
       <c r="C305" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D305">
         <v>1</v>
       </c>
       <c r="E305" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F305" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>684</v>
       </c>
@@ -8259,19 +8265,19 @@
         <v>270</v>
       </c>
       <c r="C306" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="D306">
         <v>1</v>
       </c>
       <c r="E306" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F306" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>684</v>
       </c>
@@ -8279,19 +8285,19 @@
         <v>270</v>
       </c>
       <c r="C307" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D307">
         <v>1</v>
       </c>
       <c r="E307" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F307" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>684</v>
       </c>
@@ -8299,161 +8305,161 @@
         <v>270</v>
       </c>
       <c r="C308" t="s">
+        <v>336</v>
+      </c>
+      <c r="D308">
+        <v>1</v>
+      </c>
+      <c r="E308" t="s">
+        <v>337</v>
+      </c>
+      <c r="F308" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>684</v>
+      </c>
+      <c r="B309" t="s">
+        <v>270</v>
+      </c>
+      <c r="C309" t="s">
         <v>331</v>
       </c>
-      <c r="D308">
-        <v>1</v>
-      </c>
-      <c r="E308" t="s">
+      <c r="D309">
+        <v>1</v>
+      </c>
+      <c r="E309" t="s">
         <v>332</v>
       </c>
-      <c r="F308" t="s">
+      <c r="F309" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A309" t="s">
-        <v>684</v>
-      </c>
-      <c r="B309" t="s">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>684</v>
+      </c>
+      <c r="B310" t="s">
         <v>347</v>
       </c>
-      <c r="C309" t="s">
+      <c r="C310" t="s">
         <v>348</v>
       </c>
-      <c r="D309">
-        <v>1</v>
-      </c>
-      <c r="E309" t="s">
+      <c r="D310">
+        <v>1</v>
+      </c>
+      <c r="E310" t="s">
         <v>349</v>
       </c>
-      <c r="F309" t="s">
+      <c r="F310" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>684</v>
-      </c>
-      <c r="B310" t="s">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>684</v>
+      </c>
+      <c r="B311" t="s">
         <v>666</v>
-      </c>
-      <c r="D310" t="s">
-        <v>582</v>
-      </c>
-      <c r="E310" t="s">
-        <v>301</v>
-      </c>
-      <c r="F310" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>684</v>
-      </c>
-      <c r="B311" t="s">
-        <v>667</v>
       </c>
       <c r="D311" t="s">
         <v>582</v>
       </c>
       <c r="E311" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F311" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>684</v>
       </c>
       <c r="B312" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D312" t="s">
         <v>582</v>
       </c>
       <c r="E312" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="F312" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>684</v>
       </c>
       <c r="B313" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D313" t="s">
         <v>582</v>
       </c>
       <c r="E313" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="F313" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>684</v>
       </c>
       <c r="B314" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D314" t="s">
         <v>582</v>
       </c>
       <c r="E314" t="s">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="F314" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>684</v>
       </c>
       <c r="B315" t="s">
-        <v>236</v>
-      </c>
-      <c r="C315" t="s">
-        <v>237</v>
+        <v>673</v>
+      </c>
+      <c r="D315" t="s">
+        <v>582</v>
       </c>
       <c r="E315" t="s">
         <v>234</v>
       </c>
       <c r="F315" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>684</v>
+      </c>
+      <c r="B316" t="s">
+        <v>236</v>
+      </c>
+      <c r="C316" t="s">
+        <v>237</v>
+      </c>
+      <c r="E316" t="s">
+        <v>234</v>
+      </c>
+      <c r="F316" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A316" t="s">
-        <v>684</v>
-      </c>
-      <c r="B316" t="s">
-        <v>379</v>
-      </c>
-      <c r="C316" t="s">
-        <v>382</v>
-      </c>
-      <c r="D316">
-        <v>1</v>
-      </c>
-      <c r="E316" t="s">
-        <v>375</v>
-      </c>
-      <c r="F316" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>684</v>
       </c>
@@ -8461,7 +8467,7 @@
         <v>379</v>
       </c>
       <c r="C317" t="s">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="D317">
         <v>1</v>
@@ -8470,10 +8476,10 @@
         <v>375</v>
       </c>
       <c r="F317" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>684</v>
       </c>
@@ -8481,7 +8487,7 @@
         <v>379</v>
       </c>
       <c r="C318" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -8490,10 +8496,10 @@
         <v>375</v>
       </c>
       <c r="F318" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>684</v>
       </c>
@@ -8501,36 +8507,36 @@
         <v>379</v>
       </c>
       <c r="C319" t="s">
-        <v>77</v>
+        <v>381</v>
+      </c>
+      <c r="D319">
+        <v>1</v>
       </c>
       <c r="E319" t="s">
         <v>375</v>
       </c>
       <c r="F319" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>684</v>
       </c>
       <c r="B320" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C320" t="s">
-        <v>8</v>
-      </c>
-      <c r="D320">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E320" t="s">
         <v>375</v>
       </c>
       <c r="F320" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>684</v>
       </c>
@@ -8538,7 +8544,7 @@
         <v>373</v>
       </c>
       <c r="C321" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D321">
         <v>1</v>
@@ -8547,32 +8553,35 @@
         <v>375</v>
       </c>
       <c r="F321" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>684</v>
+      </c>
+      <c r="B322" t="s">
+        <v>373</v>
+      </c>
+      <c r="C322" t="s">
+        <v>35</v>
+      </c>
+      <c r="D322">
+        <v>1</v>
+      </c>
+      <c r="E322" t="s">
+        <v>375</v>
+      </c>
+      <c r="F322" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A322" t="s">
-        <v>684</v>
-      </c>
-      <c r="B322" t="s">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>684</v>
+      </c>
+      <c r="B323" t="s">
         <v>674</v>
-      </c>
-      <c r="D322" t="s">
-        <v>582</v>
-      </c>
-      <c r="E322" t="s">
-        <v>406</v>
-      </c>
-      <c r="F322" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A323" t="s">
-        <v>684</v>
-      </c>
-      <c r="B323" t="s">
-        <v>675</v>
       </c>
       <c r="D323" t="s">
         <v>582</v>
@@ -8581,47 +8590,44 @@
         <v>406</v>
       </c>
       <c r="F323" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>684</v>
+      </c>
+      <c r="B324" t="s">
+        <v>675</v>
+      </c>
+      <c r="D324" t="s">
+        <v>582</v>
+      </c>
+      <c r="E324" t="s">
+        <v>406</v>
+      </c>
+      <c r="F324" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A324" t="s">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
         <v>683</v>
       </c>
-      <c r="B324" t="s">
+      <c r="B325" t="s">
         <v>685</v>
       </c>
-      <c r="C324" t="s">
+      <c r="C325" t="s">
         <v>686</v>
       </c>
-      <c r="E324" t="s">
+      <c r="E325" t="s">
         <v>687</v>
       </c>
-      <c r="F324" t="s">
+      <c r="F325" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A325" t="s">
-        <v>684</v>
-      </c>
-      <c r="B325" t="s">
-        <v>148</v>
-      </c>
-      <c r="C325" t="s">
-        <v>10</v>
-      </c>
-      <c r="D325">
-        <v>1</v>
-      </c>
-      <c r="E325" t="s">
-        <v>420</v>
-      </c>
-      <c r="F325" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>684</v>
       </c>
@@ -8629,16 +8635,19 @@
         <v>148</v>
       </c>
       <c r="C326" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D326">
+        <v>1</v>
       </c>
       <c r="E326" t="s">
         <v>420</v>
       </c>
       <c r="F326" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>684</v>
       </c>
@@ -8646,16 +8655,16 @@
         <v>148</v>
       </c>
       <c r="C327" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E327" t="s">
         <v>420</v>
       </c>
       <c r="F327" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>684</v>
       </c>
@@ -8663,27 +8672,24 @@
         <v>148</v>
       </c>
       <c r="C328" t="s">
-        <v>199</v>
-      </c>
-      <c r="D328">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E328" t="s">
         <v>420</v>
       </c>
       <c r="F328" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>684</v>
       </c>
       <c r="B329" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C329" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D329">
         <v>1</v>
@@ -8692,10 +8698,10 @@
         <v>420</v>
       </c>
       <c r="F329" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>684</v>
       </c>
@@ -8703,7 +8709,7 @@
         <v>152</v>
       </c>
       <c r="C330" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D330">
         <v>1</v>
@@ -8715,24 +8721,27 @@
         <v>157</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>684</v>
       </c>
       <c r="B331" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C331" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D331">
+        <v>1</v>
       </c>
       <c r="E331" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="F331" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>684</v>
       </c>
@@ -8740,16 +8749,16 @@
         <v>201</v>
       </c>
       <c r="C332" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E332" t="s">
         <v>180</v>
       </c>
       <c r="F332" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>684</v>
       </c>
@@ -8757,36 +8766,36 @@
         <v>201</v>
       </c>
       <c r="C333" t="s">
+        <v>163</v>
+      </c>
+      <c r="E333" t="s">
+        <v>180</v>
+      </c>
+      <c r="F333" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>684</v>
+      </c>
+      <c r="B334" t="s">
+        <v>201</v>
+      </c>
+      <c r="C334" t="s">
         <v>518</v>
       </c>
-      <c r="D333">
-        <v>1</v>
-      </c>
-      <c r="E333" t="s">
+      <c r="D334">
+        <v>1</v>
+      </c>
+      <c r="E334" t="s">
         <v>520</v>
       </c>
-      <c r="F333" t="s">
+      <c r="F334" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A334" t="s">
-        <v>684</v>
-      </c>
-      <c r="B334" t="s">
-        <v>204</v>
-      </c>
-      <c r="C334" t="s">
-        <v>368</v>
-      </c>
-      <c r="E334" t="s">
-        <v>367</v>
-      </c>
-      <c r="F334" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>684</v>
       </c>
@@ -8794,16 +8803,16 @@
         <v>204</v>
       </c>
       <c r="C335" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="E335" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="F335" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>684</v>
       </c>
@@ -8811,7 +8820,7 @@
         <v>204</v>
       </c>
       <c r="C336" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E336" t="s">
         <v>178</v>
@@ -8820,44 +8829,41 @@
         <v>183</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>684</v>
       </c>
       <c r="B337" t="s">
-        <v>203</v>
-      </c>
-      <c r="D337" t="s">
-        <v>692</v>
+        <v>204</v>
+      </c>
+      <c r="C337" t="s">
+        <v>167</v>
       </c>
       <c r="E337" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F337" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>684</v>
       </c>
       <c r="B338" t="s">
         <v>203</v>
       </c>
-      <c r="C338" t="s">
-        <v>35</v>
-      </c>
-      <c r="D338">
-        <v>1</v>
+      <c r="D338" t="s">
+        <v>692</v>
       </c>
       <c r="E338" t="s">
         <v>709</v>
       </c>
       <c r="F338" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>684</v>
       </c>
@@ -8865,44 +8871,47 @@
         <v>203</v>
       </c>
       <c r="C339" t="s">
+        <v>35</v>
+      </c>
+      <c r="D339">
+        <v>1</v>
+      </c>
+      <c r="E339" t="s">
+        <v>709</v>
+      </c>
+      <c r="F339" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>684</v>
+      </c>
+      <c r="B340" t="s">
+        <v>203</v>
+      </c>
+      <c r="C340" t="s">
         <v>182</v>
       </c>
-      <c r="E339" t="s">
+      <c r="E340" t="s">
         <v>178</v>
       </c>
-      <c r="F339" t="s">
+      <c r="F340" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A340" t="s">
-        <v>684</v>
-      </c>
-      <c r="B340" t="s">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>684</v>
+      </c>
+      <c r="B341" t="s">
         <v>721</v>
       </c>
-      <c r="C340" t="s">
+      <c r="C341" t="s">
         <v>230</v>
       </c>
-      <c r="D340">
-        <v>1</v>
-      </c>
-      <c r="E340" t="s">
-        <v>709</v>
-      </c>
-      <c r="F340" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A341" t="s">
-        <v>684</v>
-      </c>
-      <c r="B341" t="s">
-        <v>723</v>
-      </c>
-      <c r="D341" t="s">
-        <v>692</v>
+      <c r="D341">
+        <v>1</v>
       </c>
       <c r="E341" t="s">
         <v>709</v>
@@ -8911,61 +8920,61 @@
         <v>710</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>684</v>
       </c>
       <c r="B342" t="s">
         <v>723</v>
       </c>
-      <c r="C342" t="s">
-        <v>35</v>
-      </c>
-      <c r="D342">
-        <v>1</v>
+      <c r="D342" t="s">
+        <v>692</v>
       </c>
       <c r="E342" t="s">
         <v>709</v>
       </c>
       <c r="F342" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>684</v>
+      </c>
+      <c r="B343" t="s">
+        <v>723</v>
+      </c>
+      <c r="C343" t="s">
+        <v>35</v>
+      </c>
+      <c r="D343">
+        <v>1</v>
+      </c>
+      <c r="E343" t="s">
+        <v>709</v>
+      </c>
+      <c r="F343" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A343" t="s">
-        <v>684</v>
-      </c>
-      <c r="B343" t="s">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>684</v>
+      </c>
+      <c r="B344" t="s">
         <v>200</v>
       </c>
-      <c r="C343" t="s">
+      <c r="C344" t="s">
         <v>104</v>
       </c>
-      <c r="E343" t="s">
+      <c r="E344" t="s">
         <v>180</v>
       </c>
-      <c r="F343" t="s">
+      <c r="F344" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A344" t="s">
-        <v>684</v>
-      </c>
-      <c r="B344" t="s">
-        <v>80</v>
-      </c>
-      <c r="C344" t="s">
-        <v>84</v>
-      </c>
-      <c r="E344" t="s">
-        <v>59</v>
-      </c>
-      <c r="F344" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>684</v>
       </c>
@@ -8973,7 +8982,7 @@
         <v>80</v>
       </c>
       <c r="C345" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E345" t="s">
         <v>59</v>
@@ -8982,78 +8991,78 @@
         <v>82</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>684</v>
       </c>
       <c r="B346" t="s">
+        <v>80</v>
+      </c>
+      <c r="C346" t="s">
+        <v>67</v>
+      </c>
+      <c r="E346" t="s">
+        <v>59</v>
+      </c>
+      <c r="F346" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>684</v>
+      </c>
+      <c r="B347" t="s">
         <v>335</v>
       </c>
-      <c r="C346" t="s">
+      <c r="C347" t="s">
         <v>334</v>
       </c>
-      <c r="D346">
-        <v>1</v>
-      </c>
-      <c r="E346" t="s">
+      <c r="D347">
+        <v>1</v>
+      </c>
+      <c r="E347" t="s">
         <v>332</v>
       </c>
-      <c r="F346" t="s">
+      <c r="F347" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A347" t="s">
-        <v>684</v>
-      </c>
-      <c r="B347" t="s">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>684</v>
+      </c>
+      <c r="B348" t="s">
         <v>677</v>
-      </c>
-      <c r="D347" t="s">
-        <v>582</v>
-      </c>
-      <c r="E347" t="s">
-        <v>475</v>
-      </c>
-      <c r="F347" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A348" t="s">
-        <v>684</v>
-      </c>
-      <c r="B348" t="s">
-        <v>678</v>
       </c>
       <c r="D348" t="s">
         <v>582</v>
       </c>
       <c r="E348" t="s">
+        <v>475</v>
+      </c>
+      <c r="F348" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>684</v>
+      </c>
+      <c r="B349" t="s">
+        <v>678</v>
+      </c>
+      <c r="D349" t="s">
+        <v>582</v>
+      </c>
+      <c r="E349" t="s">
         <v>420</v>
       </c>
-      <c r="F348" t="s">
+      <c r="F349" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A349" t="s">
-        <v>684</v>
-      </c>
-      <c r="B349" t="s">
-        <v>578</v>
-      </c>
-      <c r="C349" t="s">
-        <v>104</v>
-      </c>
-      <c r="E349" t="s">
-        <v>577</v>
-      </c>
-      <c r="F349" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>684</v>
       </c>
@@ -9061,50 +9070,50 @@
         <v>578</v>
       </c>
       <c r="C350" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E350" t="s">
         <v>577</v>
       </c>
       <c r="F350" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>684</v>
+      </c>
+      <c r="B351" t="s">
+        <v>578</v>
+      </c>
+      <c r="C351" t="s">
+        <v>78</v>
+      </c>
+      <c r="E351" t="s">
+        <v>577</v>
+      </c>
+      <c r="F351" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A351" t="s">
-        <v>684</v>
-      </c>
-      <c r="B351" t="s">
-        <v>184</v>
-      </c>
-      <c r="D351" t="s">
-        <v>692</v>
-      </c>
-      <c r="E351" t="s">
-        <v>186</v>
-      </c>
-      <c r="F351" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>684</v>
       </c>
       <c r="B352" t="s">
         <v>184</v>
       </c>
-      <c r="C352" t="s">
-        <v>153</v>
+      <c r="D352" t="s">
+        <v>692</v>
       </c>
       <c r="E352" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F352" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>684</v>
       </c>
@@ -9112,16 +9121,16 @@
         <v>184</v>
       </c>
       <c r="C353" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E353" t="s">
-        <v>515</v>
+        <v>154</v>
       </c>
       <c r="F353" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>684</v>
       </c>
@@ -9135,10 +9144,10 @@
         <v>515</v>
       </c>
       <c r="F354" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>684</v>
       </c>
@@ -9146,16 +9155,16 @@
         <v>184</v>
       </c>
       <c r="C355" t="s">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="E355" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F355" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>684</v>
       </c>
@@ -9163,19 +9172,16 @@
         <v>184</v>
       </c>
       <c r="C356" t="s">
-        <v>261</v>
-      </c>
-      <c r="D356">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E356" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F356" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>684</v>
       </c>
@@ -9183,16 +9189,19 @@
         <v>184</v>
       </c>
       <c r="C357" t="s">
-        <v>421</v>
+        <v>261</v>
+      </c>
+      <c r="D357">
+        <v>1</v>
       </c>
       <c r="E357" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="F357" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>684</v>
       </c>
@@ -9200,19 +9209,16 @@
         <v>184</v>
       </c>
       <c r="C358" t="s">
-        <v>734</v>
-      </c>
-      <c r="D358">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="E358" t="s">
-        <v>735</v>
+        <v>420</v>
       </c>
       <c r="F358" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>684</v>
       </c>
@@ -9220,19 +9226,19 @@
         <v>184</v>
       </c>
       <c r="C359" t="s">
-        <v>185</v>
+        <v>734</v>
       </c>
       <c r="D359">
         <v>1</v>
       </c>
       <c r="E359" t="s">
-        <v>186</v>
+        <v>735</v>
       </c>
       <c r="F359" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>684</v>
       </c>
@@ -9240,19 +9246,19 @@
         <v>184</v>
       </c>
       <c r="C360" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="D360">
         <v>1</v>
       </c>
       <c r="E360" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="F360" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>684</v>
       </c>
@@ -9269,10 +9275,10 @@
         <v>298</v>
       </c>
       <c r="F361" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>684</v>
       </c>
@@ -9280,19 +9286,19 @@
         <v>184</v>
       </c>
       <c r="C362" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="D362">
         <v>1</v>
       </c>
       <c r="E362" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F362" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>684</v>
       </c>
@@ -9300,7 +9306,7 @@
         <v>184</v>
       </c>
       <c r="C363" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D363">
         <v>1</v>
@@ -9309,30 +9315,30 @@
         <v>324</v>
       </c>
       <c r="F363" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>684</v>
+      </c>
+      <c r="B364" t="s">
+        <v>184</v>
+      </c>
+      <c r="C364" t="s">
+        <v>323</v>
+      </c>
+      <c r="D364">
+        <v>1</v>
+      </c>
+      <c r="E364" t="s">
+        <v>324</v>
+      </c>
+      <c r="F364" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A364" t="s">
-        <v>684</v>
-      </c>
-      <c r="B364" t="s">
-        <v>196</v>
-      </c>
-      <c r="C364" t="s">
-        <v>189</v>
-      </c>
-      <c r="D364">
-        <v>1</v>
-      </c>
-      <c r="E364" t="s">
-        <v>244</v>
-      </c>
-      <c r="F364" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>684</v>
       </c>
@@ -9340,7 +9346,7 @@
         <v>196</v>
       </c>
       <c r="C365" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D365">
         <v>1</v>
@@ -9349,44 +9355,47 @@
         <v>244</v>
       </c>
       <c r="F365" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>684</v>
+      </c>
+      <c r="B366" t="s">
+        <v>196</v>
+      </c>
+      <c r="C366" t="s">
+        <v>191</v>
+      </c>
+      <c r="D366">
+        <v>1</v>
+      </c>
+      <c r="E366" t="s">
+        <v>244</v>
+      </c>
+      <c r="F366" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A366" t="s">
-        <v>684</v>
-      </c>
-      <c r="B366" t="s">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>684</v>
+      </c>
+      <c r="B367" t="s">
         <v>476</v>
       </c>
-      <c r="C366" t="s">
+      <c r="C367" t="s">
         <v>477</v>
       </c>
-      <c r="E366" t="s">
+      <c r="E367" t="s">
         <v>538</v>
       </c>
-      <c r="F366" t="s">
+      <c r="F367" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A367" t="s">
-        <v>684</v>
-      </c>
-      <c r="B367" t="s">
-        <v>45</v>
-      </c>
-      <c r="C367" t="s">
-        <v>459</v>
-      </c>
-      <c r="E367" t="s">
-        <v>453</v>
-      </c>
-      <c r="F367" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>684</v>
       </c>
@@ -9394,16 +9403,16 @@
         <v>45</v>
       </c>
       <c r="C368" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="E368" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F368" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>684</v>
       </c>
@@ -9411,16 +9420,16 @@
         <v>45</v>
       </c>
       <c r="C369" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E369" t="s">
         <v>406</v>
       </c>
       <c r="F369" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>684</v>
       </c>
@@ -9428,16 +9437,16 @@
         <v>45</v>
       </c>
       <c r="C370" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E370" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F370" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>684</v>
       </c>
@@ -9445,16 +9454,16 @@
         <v>45</v>
       </c>
       <c r="C371" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="E371" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="F371" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>684</v>
       </c>
@@ -9468,10 +9477,10 @@
         <v>491</v>
       </c>
       <c r="F372" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>684</v>
       </c>
@@ -9479,16 +9488,16 @@
         <v>45</v>
       </c>
       <c r="C373" t="s">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="E373" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="F373" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>684</v>
       </c>
@@ -9496,16 +9505,16 @@
         <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="E374" t="s">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="F374" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>684</v>
       </c>
@@ -9519,10 +9528,10 @@
         <v>563</v>
       </c>
       <c r="F375" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>684</v>
       </c>
@@ -9530,19 +9539,16 @@
         <v>45</v>
       </c>
       <c r="C376" t="s">
-        <v>415</v>
-      </c>
-      <c r="D376">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="E376" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="F376" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>684</v>
       </c>
@@ -9550,16 +9556,19 @@
         <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="D377">
+        <v>1</v>
       </c>
       <c r="E377" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F377" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>684</v>
       </c>
@@ -9567,16 +9576,16 @@
         <v>45</v>
       </c>
       <c r="C378" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="E378" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="F378" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>684</v>
       </c>
@@ -9584,19 +9593,16 @@
         <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>264</v>
-      </c>
-      <c r="D379">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E379" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F379" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>684</v>
       </c>
@@ -9604,16 +9610,19 @@
         <v>45</v>
       </c>
       <c r="C380" t="s">
-        <v>372</v>
+        <v>264</v>
+      </c>
+      <c r="D380">
+        <v>1</v>
       </c>
       <c r="E380" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="F380" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>684</v>
       </c>
@@ -9621,19 +9630,16 @@
         <v>45</v>
       </c>
       <c r="C381" t="s">
-        <v>187</v>
-      </c>
-      <c r="D381">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="E381" t="s">
-        <v>188</v>
+        <v>369</v>
       </c>
       <c r="F381" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>684</v>
       </c>
@@ -9641,19 +9647,19 @@
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="D382">
         <v>1</v>
       </c>
       <c r="E382" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F382" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>684</v>
       </c>
@@ -9661,16 +9667,19 @@
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="D383">
+        <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="F383" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>684</v>
       </c>
@@ -9678,19 +9687,16 @@
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>52</v>
-      </c>
-      <c r="D384">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E384" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="F384" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>684</v>
       </c>
@@ -9698,7 +9704,7 @@
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D385">
         <v>1</v>
@@ -9707,10 +9713,10 @@
         <v>50</v>
       </c>
       <c r="F385" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>684</v>
       </c>
@@ -9718,50 +9724,53 @@
         <v>45</v>
       </c>
       <c r="C386" t="s">
+        <v>49</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
+      </c>
+      <c r="E386" t="s">
+        <v>50</v>
+      </c>
+      <c r="F386" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>684</v>
+      </c>
+      <c r="B387" t="s">
+        <v>45</v>
+      </c>
+      <c r="C387" t="s">
         <v>125</v>
       </c>
-      <c r="E386" t="s">
+      <c r="E387" t="s">
         <v>126</v>
       </c>
-      <c r="F386" t="s">
+      <c r="F387" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A387" t="s">
-        <v>684</v>
-      </c>
-      <c r="B387" t="s">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>684</v>
+      </c>
+      <c r="B388" t="s">
         <v>202</v>
       </c>
-      <c r="C387" t="s">
+      <c r="C388" t="s">
         <v>167</v>
       </c>
-      <c r="E387" t="s">
+      <c r="E388" t="s">
         <v>255</v>
       </c>
-      <c r="F387" t="s">
+      <c r="F388" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A388" t="s">
-        <v>684</v>
-      </c>
-      <c r="B388" t="s">
-        <v>569</v>
-      </c>
-      <c r="C388" t="s">
-        <v>571</v>
-      </c>
-      <c r="E388" t="s">
-        <v>256</v>
-      </c>
-      <c r="F388" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>684</v>
       </c>
@@ -9775,10 +9784,10 @@
         <v>256</v>
       </c>
       <c r="F389" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>684</v>
       </c>
@@ -9786,67 +9795,67 @@
         <v>569</v>
       </c>
       <c r="C390" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E390" t="s">
         <v>256</v>
       </c>
       <c r="F390" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>684</v>
+      </c>
+      <c r="B391" t="s">
+        <v>569</v>
+      </c>
+      <c r="C391" t="s">
+        <v>570</v>
+      </c>
+      <c r="E391" t="s">
+        <v>256</v>
+      </c>
+      <c r="F391" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
-        <v>684</v>
-      </c>
-      <c r="B391" t="s">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>684</v>
+      </c>
+      <c r="B392" t="s">
         <v>756</v>
-      </c>
-      <c r="D391" t="s">
-        <v>712</v>
-      </c>
-      <c r="E391" t="s">
-        <v>255</v>
-      </c>
-      <c r="F391" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>684</v>
-      </c>
-      <c r="B392" t="s">
-        <v>754</v>
       </c>
       <c r="D392" t="s">
         <v>712</v>
       </c>
       <c r="E392" t="s">
+        <v>255</v>
+      </c>
+      <c r="F392" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>684</v>
+      </c>
+      <c r="B393" t="s">
+        <v>754</v>
+      </c>
+      <c r="D393" t="s">
+        <v>712</v>
+      </c>
+      <c r="E393" t="s">
         <v>256</v>
       </c>
-      <c r="F392" t="s">
+      <c r="F393" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>684</v>
-      </c>
-      <c r="B393" t="s">
-        <v>48</v>
-      </c>
-      <c r="C393" t="s">
-        <v>171</v>
-      </c>
-      <c r="E393" t="s">
-        <v>255</v>
-      </c>
-      <c r="F393" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>684</v>
       </c>
@@ -9854,16 +9863,16 @@
         <v>48</v>
       </c>
       <c r="C394" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E394" t="s">
         <v>255</v>
       </c>
       <c r="F394" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>684</v>
       </c>
@@ -9871,16 +9880,16 @@
         <v>48</v>
       </c>
       <c r="C395" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E395" t="s">
         <v>255</v>
       </c>
       <c r="F395" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>684</v>
       </c>
@@ -9888,19 +9897,16 @@
         <v>48</v>
       </c>
       <c r="C396" t="s">
-        <v>55</v>
-      </c>
-      <c r="D396">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E396" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F396" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>684</v>
       </c>
@@ -9908,7 +9914,7 @@
         <v>48</v>
       </c>
       <c r="C397" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D397">
         <v>1</v>
@@ -9920,47 +9926,47 @@
         <v>53</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>684</v>
       </c>
       <c r="B398" t="s">
+        <v>48</v>
+      </c>
+      <c r="C398" t="s">
+        <v>57</v>
+      </c>
+      <c r="D398">
+        <v>1</v>
+      </c>
+      <c r="E398" t="s">
+        <v>50</v>
+      </c>
+      <c r="F398" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>684</v>
+      </c>
+      <c r="B399" t="s">
         <v>456</v>
       </c>
-      <c r="C398" t="s">
+      <c r="C399" t="s">
         <v>8</v>
       </c>
-      <c r="D398">
-        <v>1</v>
-      </c>
-      <c r="E398" t="s">
+      <c r="D399">
+        <v>1</v>
+      </c>
+      <c r="E399" t="s">
         <v>453</v>
       </c>
-      <c r="F398" t="s">
+      <c r="F399" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>684</v>
-      </c>
-      <c r="B399" t="s">
-        <v>108</v>
-      </c>
-      <c r="C399" t="s">
-        <v>114</v>
-      </c>
-      <c r="D399">
-        <v>1</v>
-      </c>
-      <c r="E399" t="s">
-        <v>115</v>
-      </c>
-      <c r="F399" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>684</v>
       </c>
@@ -9968,7 +9974,7 @@
         <v>108</v>
       </c>
       <c r="C400" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D400">
         <v>1</v>
@@ -9977,10 +9983,10 @@
         <v>115</v>
       </c>
       <c r="F400" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>684</v>
       </c>
@@ -9988,7 +9994,7 @@
         <v>108</v>
       </c>
       <c r="C401" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D401">
         <v>1</v>
@@ -9997,10 +10003,10 @@
         <v>115</v>
       </c>
       <c r="F401" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>684</v>
       </c>
@@ -10008,7 +10014,7 @@
         <v>108</v>
       </c>
       <c r="C402" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D402">
         <v>1</v>
@@ -10017,10 +10023,10 @@
         <v>115</v>
       </c>
       <c r="F402" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>684</v>
       </c>
@@ -10028,7 +10034,7 @@
         <v>108</v>
       </c>
       <c r="C403" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D403">
         <v>1</v>
@@ -10037,47 +10043,47 @@
         <v>115</v>
       </c>
       <c r="F403" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>684</v>
+      </c>
+      <c r="B404" t="s">
+        <v>108</v>
+      </c>
+      <c r="C404" t="s">
+        <v>120</v>
+      </c>
+      <c r="D404">
+        <v>1</v>
+      </c>
+      <c r="E404" t="s">
+        <v>115</v>
+      </c>
+      <c r="F404" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>684</v>
-      </c>
-      <c r="B404" t="s">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>684</v>
+      </c>
+      <c r="B405" t="s">
         <v>680</v>
       </c>
-      <c r="D404" t="s">
+      <c r="D405" t="s">
         <v>582</v>
       </c>
-      <c r="E404" t="s">
+      <c r="E405" t="s">
         <v>298</v>
       </c>
-      <c r="F404" t="s">
+      <c r="F405" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>684</v>
-      </c>
-      <c r="B405" t="s">
-        <v>197</v>
-      </c>
-      <c r="C405" t="s">
-        <v>189</v>
-      </c>
-      <c r="D405">
-        <v>1</v>
-      </c>
-      <c r="E405" t="s">
-        <v>244</v>
-      </c>
-      <c r="F405" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>684</v>
       </c>
@@ -10085,7 +10091,7 @@
         <v>197</v>
       </c>
       <c r="C406" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D406">
         <v>1</v>
@@ -10094,27 +10100,30 @@
         <v>244</v>
       </c>
       <c r="F406" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>684</v>
+      </c>
+      <c r="B407" t="s">
+        <v>197</v>
+      </c>
+      <c r="C407" t="s">
+        <v>191</v>
+      </c>
+      <c r="D407">
+        <v>1</v>
+      </c>
+      <c r="E407" t="s">
+        <v>244</v>
+      </c>
+      <c r="F407" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>684</v>
-      </c>
-      <c r="B407" t="s">
-        <v>566</v>
-      </c>
-      <c r="C407" t="s">
-        <v>567</v>
-      </c>
-      <c r="E407" t="s">
-        <v>563</v>
-      </c>
-      <c r="F407" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>684</v>
       </c>
@@ -10122,7 +10131,7 @@
         <v>566</v>
       </c>
       <c r="C408" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E408" t="s">
         <v>563</v>
@@ -10131,7 +10140,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>684</v>
       </c>
@@ -10139,7 +10148,7 @@
         <v>566</v>
       </c>
       <c r="C409" t="s">
-        <v>167</v>
+        <v>568</v>
       </c>
       <c r="E409" t="s">
         <v>563</v>
@@ -10148,20 +10157,37 @@
         <v>565</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>684</v>
       </c>
       <c r="B410" t="s">
+        <v>566</v>
+      </c>
+      <c r="C410" t="s">
+        <v>167</v>
+      </c>
+      <c r="E410" t="s">
+        <v>563</v>
+      </c>
+      <c r="F410" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>684</v>
+      </c>
+      <c r="B411" t="s">
         <v>403</v>
       </c>
-      <c r="C410" t="s">
+      <c r="C411" t="s">
         <v>104</v>
       </c>
-      <c r="E410" t="s">
+      <c r="E411" t="s">
         <v>400</v>
       </c>
-      <c r="F410" t="s">
+      <c r="F411" t="s">
         <v>401</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD7A633-E16E-4789-A570-43C33A6FA2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBDED19-3AD8-42F5-9BA6-D0187CF498B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="767">
   <si>
     <t>Class</t>
   </si>
@@ -2314,6 +2314,15 @@
   </si>
   <si>
     <t>CardLayoutTwoColumnSection</t>
+  </si>
+  <si>
+    <t>RunOptions</t>
+  </si>
+  <si>
+    <t>excel-workbook-undo-grouping</t>
+  </si>
+  <si>
+    <t>formatWithGrouping</t>
   </si>
   <si>
     <t>getSolidColor</t>
@@ -2427,10 +2436,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F411" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F411" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F411">
-    <sortCondition ref="B1:B411"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F412" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F412" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F412">
+    <sortCondition ref="B1:B412"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2761,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F411"/>
+  <dimension ref="A1:F412"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
@@ -3725,7 +3734,7 @@
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3734,7 +3743,7 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -7855,16 +7864,16 @@
         <v>684</v>
       </c>
       <c r="B284" t="s">
-        <v>239</v>
-      </c>
-      <c r="C284" t="s">
-        <v>240</v>
+        <v>762</v>
+      </c>
+      <c r="D284" t="s">
+        <v>712</v>
       </c>
       <c r="E284" t="s">
-        <v>241</v>
+        <v>763</v>
       </c>
       <c r="F284" t="s">
-        <v>242</v>
+        <v>764</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.35">
@@ -7872,16 +7881,16 @@
         <v>684</v>
       </c>
       <c r="B285" t="s">
-        <v>660</v>
-      </c>
-      <c r="D285" t="s">
-        <v>582</v>
+        <v>239</v>
+      </c>
+      <c r="C285" t="s">
+        <v>240</v>
       </c>
       <c r="E285" t="s">
-        <v>324</v>
+        <v>241</v>
       </c>
       <c r="F285" t="s">
-        <v>661</v>
+        <v>242</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.35">
@@ -7889,16 +7898,16 @@
         <v>684</v>
       </c>
       <c r="B286" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D286" t="s">
         <v>582</v>
       </c>
       <c r="E286" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="F286" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.35">
@@ -7906,16 +7915,16 @@
         <v>684</v>
       </c>
       <c r="B287" t="s">
-        <v>399</v>
-      </c>
-      <c r="C287" t="s">
-        <v>77</v>
+        <v>662</v>
+      </c>
+      <c r="D287" t="s">
+        <v>582</v>
       </c>
       <c r="E287" t="s">
-        <v>391</v>
+        <v>289</v>
       </c>
       <c r="F287" t="s">
-        <v>392</v>
+        <v>663</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.35">
@@ -7923,19 +7932,16 @@
         <v>684</v>
       </c>
       <c r="B288" t="s">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="C288" t="s">
-        <v>10</v>
-      </c>
-      <c r="D288">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E288" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="F288" t="s">
-        <v>21</v>
+        <v>392</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.35">
@@ -7943,19 +7949,19 @@
         <v>684</v>
       </c>
       <c r="B289" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C289" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D289">
         <v>1</v>
       </c>
       <c r="E289" t="s">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F289" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.35">
@@ -7966,7 +7972,10 @@
         <v>16</v>
       </c>
       <c r="C290" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
       </c>
       <c r="E290" t="s">
         <v>255</v>
@@ -7983,16 +7992,13 @@
         <v>16</v>
       </c>
       <c r="C291" t="s">
-        <v>22</v>
-      </c>
-      <c r="D291">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E291" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F291" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.35">
@@ -8000,19 +8006,19 @@
         <v>684</v>
       </c>
       <c r="B292" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="C292" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D292">
         <v>1</v>
       </c>
       <c r="E292" t="s">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="F292" t="s">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.35">
@@ -8023,13 +8029,16 @@
         <v>267</v>
       </c>
       <c r="C293" t="s">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="D293">
+        <v>1</v>
       </c>
       <c r="E293" t="s">
         <v>287</v>
       </c>
       <c r="F293" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.35">
@@ -8040,13 +8049,13 @@
         <v>267</v>
       </c>
       <c r="C294" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E294" t="s">
         <v>287</v>
       </c>
       <c r="F294" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.35">
@@ -8057,13 +8066,13 @@
         <v>267</v>
       </c>
       <c r="C295" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="E295" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F295" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.35">
@@ -8074,16 +8083,13 @@
         <v>267</v>
       </c>
       <c r="C296" t="s">
-        <v>354</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="E296" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F296" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.35">
@@ -8094,7 +8100,7 @@
         <v>267</v>
       </c>
       <c r="C297" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -8103,7 +8109,7 @@
         <v>291</v>
       </c>
       <c r="F297" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.35">
@@ -8114,13 +8120,16 @@
         <v>267</v>
       </c>
       <c r="C298" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F298" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.35">
@@ -8131,16 +8140,13 @@
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>299</v>
-      </c>
-      <c r="D299">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E299" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F299" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.35">
@@ -8151,7 +8157,7 @@
         <v>267</v>
       </c>
       <c r="C300" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -8160,7 +8166,7 @@
         <v>301</v>
       </c>
       <c r="F300" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.35">
@@ -8171,13 +8177,16 @@
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="D301">
+        <v>1</v>
       </c>
       <c r="E301" t="s">
         <v>301</v>
       </c>
       <c r="F301" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.35">
@@ -8188,10 +8197,7 @@
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>307</v>
-      </c>
-      <c r="D302">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="E302" t="s">
         <v>301</v>
@@ -8208,7 +8214,7 @@
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D303">
         <v>1</v>
@@ -8217,7 +8223,7 @@
         <v>301</v>
       </c>
       <c r="F303" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
@@ -8225,16 +8231,19 @@
         <v>684</v>
       </c>
       <c r="B304" t="s">
-        <v>664</v>
-      </c>
-      <c r="D304" t="s">
-        <v>582</v>
+        <v>267</v>
+      </c>
+      <c r="C304" t="s">
+        <v>306</v>
+      </c>
+      <c r="D304">
+        <v>1</v>
       </c>
       <c r="E304" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F304" t="s">
-        <v>665</v>
+        <v>305</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
@@ -8242,19 +8251,16 @@
         <v>684</v>
       </c>
       <c r="B305" t="s">
-        <v>270</v>
-      </c>
-      <c r="C305" t="s">
-        <v>271</v>
-      </c>
-      <c r="D305">
-        <v>1</v>
+        <v>664</v>
+      </c>
+      <c r="D305" t="s">
+        <v>582</v>
       </c>
       <c r="E305" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="F305" t="s">
-        <v>328</v>
+        <v>665</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
@@ -8265,16 +8271,16 @@
         <v>270</v>
       </c>
       <c r="C306" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D306">
         <v>1</v>
       </c>
       <c r="E306" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F306" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
@@ -8285,16 +8291,16 @@
         <v>270</v>
       </c>
       <c r="C307" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="D307">
         <v>1</v>
       </c>
       <c r="E307" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F307" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
@@ -8305,16 +8311,16 @@
         <v>270</v>
       </c>
       <c r="C308" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D308">
         <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F308" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
@@ -8325,16 +8331,16 @@
         <v>270</v>
       </c>
       <c r="C309" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D309">
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F309" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
@@ -8342,19 +8348,19 @@
         <v>684</v>
       </c>
       <c r="B310" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C310" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="D310">
         <v>1</v>
       </c>
       <c r="E310" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="F310" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
@@ -8362,16 +8368,19 @@
         <v>684</v>
       </c>
       <c r="B311" t="s">
-        <v>666</v>
-      </c>
-      <c r="D311" t="s">
-        <v>582</v>
+        <v>347</v>
+      </c>
+      <c r="C311" t="s">
+        <v>348</v>
+      </c>
+      <c r="D311">
+        <v>1</v>
       </c>
       <c r="E311" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
       <c r="F311" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
@@ -8379,16 +8388,16 @@
         <v>684</v>
       </c>
       <c r="B312" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D312" t="s">
         <v>582</v>
       </c>
       <c r="E312" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F312" t="s">
-        <v>668</v>
+        <v>304</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
@@ -8396,16 +8405,16 @@
         <v>684</v>
       </c>
       <c r="B313" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D313" t="s">
         <v>582</v>
       </c>
       <c r="E313" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="F313" t="s">
-        <v>305</v>
+        <v>668</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.35">
@@ -8413,16 +8422,16 @@
         <v>684</v>
       </c>
       <c r="B314" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D314" t="s">
         <v>582</v>
       </c>
       <c r="E314" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="F314" t="s">
-        <v>671</v>
+        <v>305</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
@@ -8430,16 +8439,16 @@
         <v>684</v>
       </c>
       <c r="B315" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D315" t="s">
         <v>582</v>
       </c>
       <c r="E315" t="s">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="F315" t="s">
-        <v>232</v>
+        <v>671</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
@@ -8447,16 +8456,16 @@
         <v>684</v>
       </c>
       <c r="B316" t="s">
-        <v>236</v>
-      </c>
-      <c r="C316" t="s">
-        <v>237</v>
+        <v>673</v>
+      </c>
+      <c r="D316" t="s">
+        <v>582</v>
       </c>
       <c r="E316" t="s">
         <v>234</v>
       </c>
       <c r="F316" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
@@ -8464,19 +8473,16 @@
         <v>684</v>
       </c>
       <c r="B317" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="C317" t="s">
-        <v>382</v>
-      </c>
-      <c r="D317">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="E317" t="s">
-        <v>375</v>
+        <v>234</v>
       </c>
       <c r="F317" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
@@ -8487,7 +8493,7 @@
         <v>379</v>
       </c>
       <c r="C318" t="s">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -8496,7 +8502,7 @@
         <v>375</v>
       </c>
       <c r="F318" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
@@ -8507,7 +8513,7 @@
         <v>379</v>
       </c>
       <c r="C319" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
       <c r="D319">
         <v>1</v>
@@ -8516,7 +8522,7 @@
         <v>375</v>
       </c>
       <c r="F319" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
@@ -8527,13 +8533,16 @@
         <v>379</v>
       </c>
       <c r="C320" t="s">
-        <v>77</v>
+        <v>381</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
       </c>
       <c r="E320" t="s">
         <v>375</v>
       </c>
       <c r="F320" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
@@ -8541,19 +8550,16 @@
         <v>684</v>
       </c>
       <c r="B321" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C321" t="s">
-        <v>8</v>
-      </c>
-      <c r="D321">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E321" t="s">
         <v>375</v>
       </c>
       <c r="F321" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
@@ -8564,7 +8570,7 @@
         <v>373</v>
       </c>
       <c r="C322" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D322">
         <v>1</v>
@@ -8573,7 +8579,7 @@
         <v>375</v>
       </c>
       <c r="F322" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
@@ -8581,16 +8587,19 @@
         <v>684</v>
       </c>
       <c r="B323" t="s">
-        <v>674</v>
-      </c>
-      <c r="D323" t="s">
-        <v>582</v>
+        <v>373</v>
+      </c>
+      <c r="C323" t="s">
+        <v>35</v>
+      </c>
+      <c r="D323">
+        <v>1</v>
       </c>
       <c r="E323" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="F323" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
@@ -8598,7 +8607,7 @@
         <v>684</v>
       </c>
       <c r="B324" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D324" t="s">
         <v>582</v>
@@ -8607,44 +8616,41 @@
         <v>406</v>
       </c>
       <c r="F324" t="s">
-        <v>676</v>
+        <v>407</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B325" t="s">
-        <v>685</v>
-      </c>
-      <c r="C325" t="s">
-        <v>686</v>
+        <v>675</v>
+      </c>
+      <c r="D325" t="s">
+        <v>582</v>
       </c>
       <c r="E325" t="s">
-        <v>687</v>
+        <v>406</v>
       </c>
       <c r="F325" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B326" t="s">
-        <v>148</v>
+        <v>685</v>
       </c>
       <c r="C326" t="s">
-        <v>10</v>
-      </c>
-      <c r="D326">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="E326" t="s">
-        <v>420</v>
+        <v>687</v>
       </c>
       <c r="F326" t="s">
-        <v>159</v>
+        <v>688</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
@@ -8655,13 +8661,16 @@
         <v>148</v>
       </c>
       <c r="C327" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D327">
+        <v>1</v>
       </c>
       <c r="E327" t="s">
         <v>420</v>
       </c>
       <c r="F327" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
@@ -8672,13 +8681,13 @@
         <v>148</v>
       </c>
       <c r="C328" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E328" t="s">
         <v>420</v>
       </c>
       <c r="F328" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
@@ -8689,16 +8698,13 @@
         <v>148</v>
       </c>
       <c r="C329" t="s">
-        <v>199</v>
-      </c>
-      <c r="D329">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E329" t="s">
         <v>420</v>
       </c>
       <c r="F329" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
@@ -8706,10 +8712,10 @@
         <v>684</v>
       </c>
       <c r="B330" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C330" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D330">
         <v>1</v>
@@ -8718,7 +8724,7 @@
         <v>420</v>
       </c>
       <c r="F330" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
@@ -8729,7 +8735,7 @@
         <v>152</v>
       </c>
       <c r="C331" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -8746,16 +8752,19 @@
         <v>684</v>
       </c>
       <c r="B332" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C332" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="F332" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
@@ -8766,13 +8775,13 @@
         <v>201</v>
       </c>
       <c r="C333" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E333" t="s">
         <v>180</v>
       </c>
       <c r="F333" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
@@ -8783,16 +8792,13 @@
         <v>201</v>
       </c>
       <c r="C334" t="s">
-        <v>518</v>
-      </c>
-      <c r="D334">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E334" t="s">
-        <v>520</v>
+        <v>180</v>
       </c>
       <c r="F334" t="s">
-        <v>519</v>
+        <v>164</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
@@ -8800,16 +8806,19 @@
         <v>684</v>
       </c>
       <c r="B335" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C335" t="s">
-        <v>368</v>
+        <v>518</v>
+      </c>
+      <c r="D335">
+        <v>1</v>
       </c>
       <c r="E335" t="s">
-        <v>367</v>
+        <v>520</v>
       </c>
       <c r="F335" t="s">
-        <v>366</v>
+        <v>519</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
@@ -8820,13 +8829,13 @@
         <v>204</v>
       </c>
       <c r="C336" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="E336" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="F336" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.35">
@@ -8837,7 +8846,7 @@
         <v>204</v>
       </c>
       <c r="C337" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E337" t="s">
         <v>178</v>
@@ -8851,16 +8860,16 @@
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>203</v>
-      </c>
-      <c r="D338" t="s">
-        <v>692</v>
+        <v>204</v>
+      </c>
+      <c r="C338" t="s">
+        <v>167</v>
       </c>
       <c r="E338" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F338" t="s">
-        <v>710</v>
+        <v>183</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.35">
@@ -8870,17 +8879,14 @@
       <c r="B339" t="s">
         <v>203</v>
       </c>
-      <c r="C339" t="s">
-        <v>35</v>
-      </c>
-      <c r="D339">
-        <v>1</v>
+      <c r="D339" t="s">
+        <v>692</v>
       </c>
       <c r="E339" t="s">
         <v>709</v>
       </c>
       <c r="F339" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.35">
@@ -8891,13 +8897,16 @@
         <v>203</v>
       </c>
       <c r="C340" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D340">
+        <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>178</v>
+        <v>709</v>
       </c>
       <c r="F340" t="s">
-        <v>181</v>
+        <v>722</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.35">
@@ -8905,19 +8914,16 @@
         <v>684</v>
       </c>
       <c r="B341" t="s">
-        <v>721</v>
+        <v>203</v>
       </c>
       <c r="C341" t="s">
-        <v>230</v>
-      </c>
-      <c r="D341">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E341" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F341" t="s">
-        <v>710</v>
+        <v>181</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.35">
@@ -8925,10 +8931,13 @@
         <v>684</v>
       </c>
       <c r="B342" t="s">
-        <v>723</v>
-      </c>
-      <c r="D342" t="s">
-        <v>692</v>
+        <v>721</v>
+      </c>
+      <c r="C342" t="s">
+        <v>230</v>
+      </c>
+      <c r="D342">
+        <v>1</v>
       </c>
       <c r="E342" t="s">
         <v>709</v>
@@ -8944,17 +8953,14 @@
       <c r="B343" t="s">
         <v>723</v>
       </c>
-      <c r="C343" t="s">
-        <v>35</v>
-      </c>
-      <c r="D343">
-        <v>1</v>
+      <c r="D343" t="s">
+        <v>692</v>
       </c>
       <c r="E343" t="s">
         <v>709</v>
       </c>
       <c r="F343" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.35">
@@ -8962,16 +8968,19 @@
         <v>684</v>
       </c>
       <c r="B344" t="s">
-        <v>200</v>
+        <v>723</v>
       </c>
       <c r="C344" t="s">
-        <v>104</v>
+        <v>35</v>
+      </c>
+      <c r="D344">
+        <v>1</v>
       </c>
       <c r="E344" t="s">
-        <v>180</v>
+        <v>709</v>
       </c>
       <c r="F344" t="s">
-        <v>162</v>
+        <v>717</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.35">
@@ -8979,16 +8988,16 @@
         <v>684</v>
       </c>
       <c r="B345" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="C345" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E345" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="F345" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.35">
@@ -8999,7 +9008,7 @@
         <v>80</v>
       </c>
       <c r="C346" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E346" t="s">
         <v>59</v>
@@ -9013,19 +9022,16 @@
         <v>684</v>
       </c>
       <c r="B347" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="C347" t="s">
-        <v>334</v>
-      </c>
-      <c r="D347">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E347" t="s">
-        <v>332</v>
+        <v>59</v>
       </c>
       <c r="F347" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.35">
@@ -9033,16 +9039,19 @@
         <v>684</v>
       </c>
       <c r="B348" t="s">
-        <v>677</v>
-      </c>
-      <c r="D348" t="s">
-        <v>582</v>
+        <v>335</v>
+      </c>
+      <c r="C348" t="s">
+        <v>334</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
       </c>
       <c r="E348" t="s">
-        <v>475</v>
+        <v>332</v>
       </c>
       <c r="F348" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
@@ -9050,16 +9059,16 @@
         <v>684</v>
       </c>
       <c r="B349" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D349" t="s">
         <v>582</v>
       </c>
       <c r="E349" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="F349" t="s">
-        <v>679</v>
+        <v>470</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
@@ -9067,16 +9076,16 @@
         <v>684</v>
       </c>
       <c r="B350" t="s">
-        <v>578</v>
-      </c>
-      <c r="C350" t="s">
-        <v>104</v>
+        <v>678</v>
+      </c>
+      <c r="D350" t="s">
+        <v>582</v>
       </c>
       <c r="E350" t="s">
-        <v>577</v>
+        <v>420</v>
       </c>
       <c r="F350" t="s">
-        <v>580</v>
+        <v>679</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
@@ -9087,13 +9096,13 @@
         <v>578</v>
       </c>
       <c r="C351" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E351" t="s">
         <v>577</v>
       </c>
       <c r="F351" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
@@ -9101,16 +9110,16 @@
         <v>684</v>
       </c>
       <c r="B352" t="s">
-        <v>184</v>
-      </c>
-      <c r="D352" t="s">
-        <v>692</v>
+        <v>578</v>
+      </c>
+      <c r="C352" t="s">
+        <v>78</v>
       </c>
       <c r="E352" t="s">
-        <v>186</v>
+        <v>577</v>
       </c>
       <c r="F352" t="s">
-        <v>190</v>
+        <v>579</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
@@ -9120,14 +9129,14 @@
       <c r="B353" t="s">
         <v>184</v>
       </c>
-      <c r="C353" t="s">
-        <v>153</v>
+      <c r="D353" t="s">
+        <v>692</v>
       </c>
       <c r="E353" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F353" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
@@ -9138,13 +9147,13 @@
         <v>184</v>
       </c>
       <c r="C354" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E354" t="s">
-        <v>515</v>
+        <v>154</v>
       </c>
       <c r="F354" t="s">
-        <v>516</v>
+        <v>155</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
@@ -9161,7 +9170,7 @@
         <v>515</v>
       </c>
       <c r="F355" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
@@ -9172,13 +9181,13 @@
         <v>184</v>
       </c>
       <c r="C356" t="s">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="E356" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F356" t="s">
-        <v>446</v>
+        <v>517</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.35">
@@ -9189,16 +9198,13 @@
         <v>184</v>
       </c>
       <c r="C357" t="s">
-        <v>261</v>
-      </c>
-      <c r="D357">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E357" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F357" t="s">
-        <v>262</v>
+        <v>446</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.35">
@@ -9209,13 +9215,16 @@
         <v>184</v>
       </c>
       <c r="C358" t="s">
-        <v>421</v>
+        <v>261</v>
+      </c>
+      <c r="D358">
+        <v>1</v>
       </c>
       <c r="E358" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="F358" t="s">
-        <v>157</v>
+        <v>262</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.35">
@@ -9226,16 +9235,13 @@
         <v>184</v>
       </c>
       <c r="C359" t="s">
-        <v>734</v>
-      </c>
-      <c r="D359">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="E359" t="s">
-        <v>735</v>
+        <v>420</v>
       </c>
       <c r="F359" t="s">
-        <v>736</v>
+        <v>157</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.35">
@@ -9246,16 +9252,16 @@
         <v>184</v>
       </c>
       <c r="C360" t="s">
-        <v>185</v>
+        <v>734</v>
       </c>
       <c r="D360">
         <v>1</v>
       </c>
       <c r="E360" t="s">
-        <v>186</v>
+        <v>735</v>
       </c>
       <c r="F360" t="s">
-        <v>190</v>
+        <v>736</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.35">
@@ -9266,16 +9272,16 @@
         <v>184</v>
       </c>
       <c r="C361" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="D361">
         <v>1</v>
       </c>
       <c r="E361" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="F361" t="s">
-        <v>530</v>
+        <v>190</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.35">
@@ -9295,7 +9301,7 @@
         <v>298</v>
       </c>
       <c r="F362" t="s">
-        <v>297</v>
+        <v>530</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.35">
@@ -9306,16 +9312,16 @@
         <v>184</v>
       </c>
       <c r="C363" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="D363">
         <v>1</v>
       </c>
       <c r="E363" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F363" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.35">
@@ -9326,7 +9332,7 @@
         <v>184</v>
       </c>
       <c r="C364" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D364">
         <v>1</v>
@@ -9335,7 +9341,7 @@
         <v>324</v>
       </c>
       <c r="F364" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.35">
@@ -9343,19 +9349,19 @@
         <v>684</v>
       </c>
       <c r="B365" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C365" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D365">
         <v>1</v>
       </c>
       <c r="E365" t="s">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="F365" t="s">
-        <v>194</v>
+        <v>325</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.35">
@@ -9366,7 +9372,7 @@
         <v>196</v>
       </c>
       <c r="C366" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D366">
         <v>1</v>
@@ -9375,7 +9381,7 @@
         <v>244</v>
       </c>
       <c r="F366" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.35">
@@ -9383,16 +9389,19 @@
         <v>684</v>
       </c>
       <c r="B367" t="s">
-        <v>476</v>
+        <v>196</v>
       </c>
       <c r="C367" t="s">
-        <v>477</v>
+        <v>191</v>
+      </c>
+      <c r="D367">
+        <v>1</v>
       </c>
       <c r="E367" t="s">
-        <v>538</v>
+        <v>244</v>
       </c>
       <c r="F367" t="s">
-        <v>465</v>
+        <v>195</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.35">
@@ -9400,16 +9409,16 @@
         <v>684</v>
       </c>
       <c r="B368" t="s">
-        <v>45</v>
+        <v>476</v>
       </c>
       <c r="C368" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E368" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="F368" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.35">
@@ -9420,13 +9429,13 @@
         <v>45</v>
       </c>
       <c r="C369" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="E369" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F369" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.35">
@@ -9437,13 +9446,13 @@
         <v>45</v>
       </c>
       <c r="C370" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E370" t="s">
         <v>406</v>
       </c>
       <c r="F370" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.35">
@@ -9454,13 +9463,13 @@
         <v>45</v>
       </c>
       <c r="C371" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E371" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F371" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.35">
@@ -9471,13 +9480,13 @@
         <v>45</v>
       </c>
       <c r="C372" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="E372" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="F372" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.35">
@@ -9494,7 +9503,7 @@
         <v>491</v>
       </c>
       <c r="F373" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.35">
@@ -9505,13 +9514,13 @@
         <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="E374" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="F374" t="s">
-        <v>181</v>
+        <v>493</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.35">
@@ -9522,13 +9531,13 @@
         <v>45</v>
       </c>
       <c r="C375" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="E375" t="s">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="F375" t="s">
-        <v>564</v>
+        <v>181</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.35">
@@ -9545,7 +9554,7 @@
         <v>563</v>
       </c>
       <c r="F376" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.35">
@@ -9556,16 +9565,13 @@
         <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>415</v>
-      </c>
-      <c r="D377">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="E377" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="F377" t="s">
-        <v>416</v>
+        <v>565</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.35">
@@ -9576,13 +9582,16 @@
         <v>45</v>
       </c>
       <c r="C378" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="D378">
+        <v>1</v>
       </c>
       <c r="E378" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F378" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.35">
@@ -9593,13 +9602,13 @@
         <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="E379" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="F379" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.35">
@@ -9610,16 +9619,13 @@
         <v>45</v>
       </c>
       <c r="C380" t="s">
-        <v>264</v>
-      </c>
-      <c r="D380">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E380" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F380" t="s">
-        <v>263</v>
+        <v>445</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.35">
@@ -9630,13 +9636,16 @@
         <v>45</v>
       </c>
       <c r="C381" t="s">
-        <v>372</v>
+        <v>264</v>
+      </c>
+      <c r="D381">
+        <v>1</v>
       </c>
       <c r="E381" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="F381" t="s">
-        <v>559</v>
+        <v>263</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.35">
@@ -9647,16 +9656,13 @@
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>187</v>
-      </c>
-      <c r="D382">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="E382" t="s">
-        <v>188</v>
+        <v>369</v>
       </c>
       <c r="F382" t="s">
-        <v>190</v>
+        <v>559</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.35">
@@ -9667,16 +9673,16 @@
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="D383">
         <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F383" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.35">
@@ -9687,13 +9693,16 @@
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="D384">
+        <v>1</v>
       </c>
       <c r="E384" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="F384" t="s">
-        <v>123</v>
+        <v>282</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.35">
@@ -9704,16 +9713,13 @@
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>52</v>
-      </c>
-      <c r="D385">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E385" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="F385" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.35">
@@ -9724,7 +9730,7 @@
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D386">
         <v>1</v>
@@ -9733,7 +9739,7 @@
         <v>50</v>
       </c>
       <c r="F386" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.35">
@@ -9744,13 +9750,16 @@
         <v>45</v>
       </c>
       <c r="C387" t="s">
-        <v>125</v>
+        <v>49</v>
+      </c>
+      <c r="D387">
+        <v>1</v>
       </c>
       <c r="E387" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="F387" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
@@ -9758,16 +9767,16 @@
         <v>684</v>
       </c>
       <c r="B388" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C388" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="E388" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="F388" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
@@ -9775,16 +9784,16 @@
         <v>684</v>
       </c>
       <c r="B389" t="s">
-        <v>569</v>
+        <v>202</v>
       </c>
       <c r="C389" t="s">
-        <v>571</v>
+        <v>167</v>
       </c>
       <c r="E389" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F389" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
@@ -9801,7 +9810,7 @@
         <v>256</v>
       </c>
       <c r="F390" t="s">
-        <v>572</v>
+        <v>183</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
@@ -9812,13 +9821,13 @@
         <v>569</v>
       </c>
       <c r="C391" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E391" t="s">
         <v>256</v>
       </c>
       <c r="F391" t="s">
-        <v>183</v>
+        <v>572</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
@@ -9826,16 +9835,16 @@
         <v>684</v>
       </c>
       <c r="B392" t="s">
-        <v>756</v>
-      </c>
-      <c r="D392" t="s">
-        <v>712</v>
+        <v>569</v>
+      </c>
+      <c r="C392" t="s">
+        <v>570</v>
       </c>
       <c r="E392" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F392" t="s">
-        <v>757</v>
+        <v>183</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
@@ -9843,16 +9852,16 @@
         <v>684</v>
       </c>
       <c r="B393" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D393" t="s">
         <v>712</v>
       </c>
       <c r="E393" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F393" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
@@ -9860,16 +9869,16 @@
         <v>684</v>
       </c>
       <c r="B394" t="s">
-        <v>48</v>
-      </c>
-      <c r="C394" t="s">
-        <v>171</v>
+        <v>754</v>
+      </c>
+      <c r="D394" t="s">
+        <v>712</v>
       </c>
       <c r="E394" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F394" t="s">
-        <v>172</v>
+        <v>755</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
@@ -9880,13 +9889,13 @@
         <v>48</v>
       </c>
       <c r="C395" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E395" t="s">
         <v>255</v>
       </c>
       <c r="F395" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
@@ -9897,13 +9906,13 @@
         <v>48</v>
       </c>
       <c r="C396" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E396" t="s">
         <v>255</v>
       </c>
       <c r="F396" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
@@ -9914,16 +9923,13 @@
         <v>48</v>
       </c>
       <c r="C397" t="s">
-        <v>55</v>
-      </c>
-      <c r="D397">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E397" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F397" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
@@ -9934,7 +9940,7 @@
         <v>48</v>
       </c>
       <c r="C398" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D398">
         <v>1</v>
@@ -9951,19 +9957,19 @@
         <v>684</v>
       </c>
       <c r="B399" t="s">
-        <v>456</v>
+        <v>48</v>
       </c>
       <c r="C399" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D399">
         <v>1</v>
       </c>
       <c r="E399" t="s">
-        <v>453</v>
+        <v>50</v>
       </c>
       <c r="F399" t="s">
-        <v>457</v>
+        <v>53</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
@@ -9971,19 +9977,19 @@
         <v>684</v>
       </c>
       <c r="B400" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="C400" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="D400">
         <v>1</v>
       </c>
       <c r="E400" t="s">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="F400" t="s">
-        <v>114</v>
+        <v>457</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
@@ -9994,7 +10000,7 @@
         <v>108</v>
       </c>
       <c r="C401" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D401">
         <v>1</v>
@@ -10003,7 +10009,7 @@
         <v>115</v>
       </c>
       <c r="F401" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
@@ -10014,7 +10020,7 @@
         <v>108</v>
       </c>
       <c r="C402" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D402">
         <v>1</v>
@@ -10023,7 +10029,7 @@
         <v>115</v>
       </c>
       <c r="F402" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
@@ -10034,7 +10040,7 @@
         <v>108</v>
       </c>
       <c r="C403" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D403">
         <v>1</v>
@@ -10043,7 +10049,7 @@
         <v>115</v>
       </c>
       <c r="F403" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
@@ -10054,7 +10060,7 @@
         <v>108</v>
       </c>
       <c r="C404" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D404">
         <v>1</v>
@@ -10063,7 +10069,7 @@
         <v>115</v>
       </c>
       <c r="F404" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
@@ -10071,16 +10077,19 @@
         <v>684</v>
       </c>
       <c r="B405" t="s">
-        <v>680</v>
-      </c>
-      <c r="D405" t="s">
-        <v>582</v>
+        <v>108</v>
+      </c>
+      <c r="C405" t="s">
+        <v>120</v>
+      </c>
+      <c r="D405">
+        <v>1</v>
       </c>
       <c r="E405" t="s">
-        <v>298</v>
+        <v>115</v>
       </c>
       <c r="F405" t="s">
-        <v>297</v>
+        <v>121</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
@@ -10088,19 +10097,16 @@
         <v>684</v>
       </c>
       <c r="B406" t="s">
-        <v>197</v>
-      </c>
-      <c r="C406" t="s">
-        <v>189</v>
-      </c>
-      <c r="D406">
-        <v>1</v>
+        <v>680</v>
+      </c>
+      <c r="D406" t="s">
+        <v>582</v>
       </c>
       <c r="E406" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="F406" t="s">
-        <v>192</v>
+        <v>297</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
@@ -10111,7 +10117,7 @@
         <v>197</v>
       </c>
       <c r="C407" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D407">
         <v>1</v>
@@ -10120,7 +10126,7 @@
         <v>244</v>
       </c>
       <c r="F407" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
@@ -10128,16 +10134,19 @@
         <v>684</v>
       </c>
       <c r="B408" t="s">
-        <v>566</v>
+        <v>197</v>
       </c>
       <c r="C408" t="s">
-        <v>567</v>
+        <v>191</v>
+      </c>
+      <c r="D408">
+        <v>1</v>
       </c>
       <c r="E408" t="s">
-        <v>563</v>
+        <v>244</v>
       </c>
       <c r="F408" t="s">
-        <v>565</v>
+        <v>193</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
@@ -10148,7 +10157,7 @@
         <v>566</v>
       </c>
       <c r="C409" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E409" t="s">
         <v>563</v>
@@ -10165,7 +10174,7 @@
         <v>566</v>
       </c>
       <c r="C410" t="s">
-        <v>167</v>
+        <v>568</v>
       </c>
       <c r="E410" t="s">
         <v>563</v>
@@ -10179,15 +10188,32 @@
         <v>684</v>
       </c>
       <c r="B411" t="s">
+        <v>566</v>
+      </c>
+      <c r="C411" t="s">
+        <v>167</v>
+      </c>
+      <c r="E411" t="s">
+        <v>563</v>
+      </c>
+      <c r="F411" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>684</v>
+      </c>
+      <c r="B412" t="s">
         <v>403</v>
       </c>
-      <c r="C411" t="s">
+      <c r="C412" t="s">
         <v>104</v>
       </c>
-      <c r="E411" t="s">
+      <c r="E412" t="s">
         <v>400</v>
       </c>
-      <c r="F411" t="s">
+      <c r="F412" t="s">
         <v>401</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DCE73D-81FD-594A-83A7-EDE65BD7145A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBDED19-3AD8-42F5-9BA6-D0187CF498B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="25600" windowHeight="17460" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2056" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="767">
   <si>
     <t>Class</t>
   </si>
@@ -2323,6 +2323,12 @@
   </si>
   <si>
     <t>formatWithGrouping</t>
+  </si>
+  <si>
+    <t>getSolidColor</t>
+  </si>
+  <si>
+    <t>getChartPointColor</t>
   </si>
 </sst>
 </file>
@@ -2407,7 +2413,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2430,10 +2436,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F411" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F411" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F411">
-    <sortCondition ref="B1:B411"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F412" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F412" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F412">
+    <sortCondition ref="B1:B412"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2764,18 +2770,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F411"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F412"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="28.1640625" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="25.1796875" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="55" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>682</v>
       </c>
@@ -2795,7 +2801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>684</v>
       </c>
@@ -2812,7 +2818,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>684</v>
       </c>
@@ -2829,7 +2835,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>684</v>
       </c>
@@ -2849,7 +2855,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>684</v>
       </c>
@@ -2869,7 +2875,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>684</v>
       </c>
@@ -2886,7 +2892,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>684</v>
       </c>
@@ -2903,7 +2909,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>684</v>
       </c>
@@ -2920,7 +2926,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>684</v>
       </c>
@@ -2937,7 +2943,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>684</v>
       </c>
@@ -2957,7 +2963,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>684</v>
       </c>
@@ -2977,7 +2983,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>684</v>
       </c>
@@ -2997,7 +3003,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>684</v>
       </c>
@@ -3017,7 +3023,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>684</v>
       </c>
@@ -3034,7 +3040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>684</v>
       </c>
@@ -3051,7 +3057,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>684</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>684</v>
       </c>
@@ -3085,7 +3091,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>684</v>
       </c>
@@ -3102,7 +3108,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>684</v>
       </c>
@@ -3119,7 +3125,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>684</v>
       </c>
@@ -3137,7 +3143,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>684</v>
       </c>
@@ -3155,7 +3161,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>684</v>
       </c>
@@ -3173,7 +3179,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>684</v>
       </c>
@@ -3190,7 +3196,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>684</v>
       </c>
@@ -3207,7 +3213,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>684</v>
       </c>
@@ -3224,7 +3230,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>684</v>
       </c>
@@ -3241,7 +3247,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>684</v>
       </c>
@@ -3258,7 +3264,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>684</v>
       </c>
@@ -3275,7 +3281,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>684</v>
       </c>
@@ -3292,7 +3298,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>684</v>
       </c>
@@ -3309,7 +3315,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>684</v>
       </c>
@@ -3326,7 +3332,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>684</v>
       </c>
@@ -3343,7 +3349,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>684</v>
       </c>
@@ -3360,7 +3366,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>684</v>
       </c>
@@ -3377,7 +3383,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>684</v>
       </c>
@@ -3397,7 +3403,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>684</v>
       </c>
@@ -3414,7 +3420,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>684</v>
       </c>
@@ -3431,7 +3437,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>684</v>
       </c>
@@ -3448,7 +3454,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>684</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>684</v>
       </c>
@@ -3482,7 +3488,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>684</v>
       </c>
@@ -3499,7 +3505,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>684</v>
       </c>
@@ -3516,7 +3522,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>684</v>
       </c>
@@ -3533,7 +3539,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>684</v>
       </c>
@@ -3550,7 +3556,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>684</v>
       </c>
@@ -3567,7 +3573,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>684</v>
       </c>
@@ -3584,7 +3590,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>684</v>
       </c>
@@ -3601,7 +3607,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>684</v>
       </c>
@@ -3618,7 +3624,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>684</v>
       </c>
@@ -3635,7 +3641,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>684</v>
       </c>
@@ -3652,7 +3658,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>684</v>
       </c>
@@ -3669,7 +3675,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>684</v>
       </c>
@@ -3686,7 +3692,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>684</v>
       </c>
@@ -3703,7 +3709,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>684</v>
       </c>
@@ -3720,7 +3726,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>684</v>
       </c>
@@ -3728,7 +3734,7 @@
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>765</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3737,32 +3743,35 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>684</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56" t="s">
+        <v>150</v>
+      </c>
+      <c r="F56" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>684</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>684</v>
+      </c>
+      <c r="B57" t="s">
         <v>741</v>
-      </c>
-      <c r="D56" t="s">
-        <v>692</v>
-      </c>
-      <c r="E56" t="s">
-        <v>737</v>
-      </c>
-      <c r="F56" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>684</v>
-      </c>
-      <c r="B57" t="s">
-        <v>743</v>
       </c>
       <c r="D57" t="s">
         <v>692</v>
@@ -3774,46 +3783,46 @@
         <v>742</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>684</v>
       </c>
       <c r="B58" t="s">
+        <v>743</v>
+      </c>
+      <c r="D58" t="s">
+        <v>692</v>
+      </c>
+      <c r="E58" t="s">
+        <v>737</v>
+      </c>
+      <c r="F58" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>684</v>
+      </c>
+      <c r="B59" t="s">
         <v>198</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>145</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" t="s">
         <v>146</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F59" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>684</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>684</v>
+      </c>
+      <c r="B60" t="s">
         <v>728</v>
-      </c>
-      <c r="D59" t="s">
-        <v>692</v>
-      </c>
-      <c r="E59" t="s">
-        <v>729</v>
-      </c>
-      <c r="F59" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>684</v>
-      </c>
-      <c r="B60" t="s">
-        <v>731</v>
       </c>
       <c r="D60" t="s">
         <v>692</v>
@@ -3825,27 +3834,24 @@
         <v>730</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>684</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" t="s">
-        <v>488</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
+        <v>731</v>
+      </c>
+      <c r="D61" t="s">
+        <v>692</v>
       </c>
       <c r="E61" t="s">
-        <v>485</v>
+        <v>729</v>
       </c>
       <c r="F61" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>684</v>
       </c>
@@ -3853,7 +3859,7 @@
         <v>133</v>
       </c>
       <c r="C62" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3862,10 +3868,10 @@
         <v>485</v>
       </c>
       <c r="F62" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>684</v>
       </c>
@@ -3873,19 +3879,19 @@
         <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>598</v>
+        <v>484</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>599</v>
+        <v>485</v>
       </c>
       <c r="F63" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>684</v>
       </c>
@@ -3893,7 +3899,7 @@
         <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3905,32 +3911,35 @@
         <v>600</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>684</v>
       </c>
       <c r="B65" t="s">
         <v>133</v>
       </c>
-      <c r="D65" t="s">
-        <v>692</v>
+      <c r="C65" t="s">
+        <v>601</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>737</v>
+        <v>599</v>
       </c>
       <c r="F65" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>684</v>
       </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
-      <c r="C66" t="s">
-        <v>738</v>
+      <c r="D66" t="s">
+        <v>692</v>
       </c>
       <c r="E66" t="s">
         <v>737</v>
@@ -3939,7 +3948,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>684</v>
       </c>
@@ -3947,7 +3956,7 @@
         <v>133</v>
       </c>
       <c r="C67" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E67" t="s">
         <v>737</v>
@@ -3956,7 +3965,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>684</v>
       </c>
@@ -3964,16 +3973,16 @@
         <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E68" t="s">
         <v>737</v>
       </c>
       <c r="F68" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>684</v>
       </c>
@@ -3981,19 +3990,16 @@
         <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
+        <v>740</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>737</v>
       </c>
       <c r="F69" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>684</v>
       </c>
@@ -4001,7 +4007,7 @@
         <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -4010,10 +4016,10 @@
         <v>135</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>684</v>
       </c>
@@ -4021,16 +4027,19 @@
         <v>133</v>
       </c>
       <c r="C71" t="s">
-        <v>177</v>
+        <v>138</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>684</v>
       </c>
@@ -4038,7 +4047,7 @@
         <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>404</v>
+        <v>177</v>
       </c>
       <c r="E72" t="s">
         <v>174</v>
@@ -4047,7 +4056,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>684</v>
       </c>
@@ -4055,7 +4064,7 @@
         <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>404</v>
       </c>
       <c r="E73" t="s">
         <v>174</v>
@@ -4064,7 +4073,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>684</v>
       </c>
@@ -4072,7 +4081,7 @@
         <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E74" t="s">
         <v>174</v>
@@ -4081,61 +4090,58 @@
         <v>175</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>684</v>
       </c>
       <c r="B75" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" t="s">
+        <v>174</v>
+      </c>
+      <c r="F75" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>684</v>
+      </c>
+      <c r="B76" t="s">
         <v>621</v>
-      </c>
-      <c r="D75" t="s">
-        <v>582</v>
-      </c>
-      <c r="E75" t="s">
-        <v>599</v>
-      </c>
-      <c r="F75" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>684</v>
-      </c>
-      <c r="B76" t="s">
-        <v>623</v>
       </c>
       <c r="D76" t="s">
         <v>582</v>
       </c>
       <c r="E76" t="s">
+        <v>599</v>
+      </c>
+      <c r="F76" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>684</v>
+      </c>
+      <c r="B77" t="s">
+        <v>623</v>
+      </c>
+      <c r="D77" t="s">
+        <v>582</v>
+      </c>
+      <c r="E77" t="s">
         <v>485</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F77" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>684</v>
-      </c>
-      <c r="B77" t="s">
-        <v>248</v>
-      </c>
-      <c r="C77" t="s">
-        <v>249</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-      <c r="E77" t="s">
-        <v>250</v>
-      </c>
-      <c r="F77" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>684</v>
       </c>
@@ -4143,172 +4149,175 @@
         <v>248</v>
       </c>
       <c r="C78" t="s">
-        <v>111</v>
+        <v>249</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
       </c>
       <c r="E78" t="s">
         <v>250</v>
       </c>
       <c r="F78" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>684</v>
+      </c>
+      <c r="B79" t="s">
+        <v>248</v>
+      </c>
+      <c r="C79" t="s">
+        <v>111</v>
+      </c>
+      <c r="E79" t="s">
+        <v>250</v>
+      </c>
+      <c r="F79" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>684</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>684</v>
+      </c>
+      <c r="B80" t="s">
         <v>124</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>78</v>
-      </c>
-      <c r="E79" t="s">
-        <v>129</v>
-      </c>
-      <c r="F79" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>684</v>
-      </c>
-      <c r="B80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C80" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
       </c>
       <c r="E80" t="s">
         <v>129</v>
       </c>
       <c r="F80" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>684</v>
       </c>
       <c r="B81" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
       </c>
       <c r="E81" t="s">
         <v>129</v>
       </c>
       <c r="F81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>684</v>
+      </c>
+      <c r="B82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C82" t="s">
+        <v>132</v>
+      </c>
+      <c r="E82" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>684</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>684</v>
+      </c>
+      <c r="B83" t="s">
         <v>581</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D83" t="s">
         <v>582</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
         <v>583</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F83" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>684</v>
-      </c>
-      <c r="B83" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>684</v>
+      </c>
+      <c r="B84" t="s">
         <v>711</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D84" t="s">
         <v>712</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>709</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F84" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>684</v>
-      </c>
-      <c r="B84" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>684</v>
+      </c>
+      <c r="B85" t="s">
         <v>624</v>
-      </c>
-      <c r="D84" t="s">
-        <v>582</v>
-      </c>
-      <c r="E84" t="s">
-        <v>102</v>
-      </c>
-      <c r="F84" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>684</v>
-      </c>
-      <c r="B85" t="s">
-        <v>626</v>
       </c>
       <c r="D85" t="s">
         <v>582</v>
       </c>
       <c r="E85" t="s">
+        <v>102</v>
+      </c>
+      <c r="F85" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>684</v>
+      </c>
+      <c r="B86" t="s">
+        <v>626</v>
+      </c>
+      <c r="D86" t="s">
+        <v>582</v>
+      </c>
+      <c r="E86" t="s">
         <v>324</v>
       </c>
-      <c r="F85" t="s">
+      <c r="F86" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>684</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>684</v>
+      </c>
+      <c r="B87" t="s">
         <v>58</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C87" t="s">
         <v>63</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>59</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F87" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>684</v>
-      </c>
-      <c r="B87" t="s">
-        <v>359</v>
-      </c>
-      <c r="C87" t="s">
-        <v>361</v>
-      </c>
-      <c r="E87" t="s">
-        <v>422</v>
-      </c>
-      <c r="F87" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>684</v>
       </c>
@@ -4316,19 +4325,16 @@
         <v>359</v>
       </c>
       <c r="C88" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="E88" t="s">
         <v>422</v>
       </c>
       <c r="F88" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>684</v>
       </c>
@@ -4336,19 +4342,19 @@
         <v>359</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="s">
         <v>422</v>
       </c>
       <c r="F89" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>684</v>
       </c>
@@ -4356,36 +4362,36 @@
         <v>359</v>
       </c>
       <c r="C90" t="s">
+        <v>199</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90" t="s">
+        <v>422</v>
+      </c>
+      <c r="F90" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>684</v>
+      </c>
+      <c r="B91" t="s">
+        <v>359</v>
+      </c>
+      <c r="C91" t="s">
         <v>425</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E91" t="s">
         <v>426</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F91" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>684</v>
-      </c>
-      <c r="B91" t="s">
-        <v>355</v>
-      </c>
-      <c r="C91" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91">
-        <v>1</v>
-      </c>
-      <c r="E91" t="s">
-        <v>422</v>
-      </c>
-      <c r="F91" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>684</v>
       </c>
@@ -4393,16 +4399,19 @@
         <v>355</v>
       </c>
       <c r="C92" t="s">
-        <v>165</v>
+        <v>8</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>483</v>
+        <v>422</v>
       </c>
       <c r="F92" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>684</v>
       </c>
@@ -4416,10 +4425,10 @@
         <v>483</v>
       </c>
       <c r="F93" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>684</v>
       </c>
@@ -4427,16 +4436,16 @@
         <v>355</v>
       </c>
       <c r="C94" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E94" t="s">
         <v>483</v>
       </c>
       <c r="F94" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>684</v>
       </c>
@@ -4450,10 +4459,10 @@
         <v>483</v>
       </c>
       <c r="F95" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>684</v>
       </c>
@@ -4461,16 +4470,16 @@
         <v>355</v>
       </c>
       <c r="C96" t="s">
-        <v>481</v>
+        <v>182</v>
       </c>
       <c r="E96" t="s">
         <v>483</v>
       </c>
       <c r="F96" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>684</v>
       </c>
@@ -4484,27 +4493,27 @@
         <v>483</v>
       </c>
       <c r="F97" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>684</v>
+      </c>
+      <c r="B98" t="s">
+        <v>355</v>
+      </c>
+      <c r="C98" t="s">
+        <v>481</v>
+      </c>
+      <c r="E98" t="s">
+        <v>483</v>
+      </c>
+      <c r="F98" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>684</v>
-      </c>
-      <c r="B98" t="s">
-        <v>362</v>
-      </c>
-      <c r="C98" t="s">
-        <v>361</v>
-      </c>
-      <c r="E98" t="s">
-        <v>423</v>
-      </c>
-      <c r="F98" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>684</v>
       </c>
@@ -4512,27 +4521,24 @@
         <v>362</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99">
-        <v>1</v>
+        <v>361</v>
       </c>
       <c r="E99" t="s">
         <v>423</v>
       </c>
       <c r="F99" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>684</v>
       </c>
       <c r="B100" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C100" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -4541,44 +4547,47 @@
         <v>423</v>
       </c>
       <c r="F100" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>684</v>
+      </c>
+      <c r="B101" t="s">
+        <v>357</v>
+      </c>
+      <c r="C101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101" t="s">
+        <v>423</v>
+      </c>
+      <c r="F101" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>684</v>
-      </c>
-      <c r="B101" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>684</v>
+      </c>
+      <c r="B102" t="s">
         <v>428</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>429</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E102" t="s">
         <v>430</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F102" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>684</v>
-      </c>
-      <c r="B102" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" t="s">
-        <v>59</v>
-      </c>
-      <c r="F102" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>684</v>
       </c>
@@ -4586,7 +4595,7 @@
         <v>89</v>
       </c>
       <c r="C103" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E103" t="s">
         <v>59</v>
@@ -4595,29 +4604,29 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>684</v>
       </c>
       <c r="B104" t="s">
-        <v>758</v>
-      </c>
-      <c r="D104" t="s">
-        <v>712</v>
+        <v>89</v>
+      </c>
+      <c r="C104" t="s">
+        <v>79</v>
       </c>
       <c r="E104" t="s">
         <v>59</v>
       </c>
       <c r="F104" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>684</v>
       </c>
       <c r="B105" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D105" t="s">
         <v>712</v>
@@ -4629,41 +4638,41 @@
         <v>60</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>684</v>
       </c>
       <c r="B106" t="s">
-        <v>628</v>
+        <v>759</v>
       </c>
       <c r="D106" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
       </c>
       <c r="F106" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>684</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
-      </c>
-      <c r="C107" t="s">
-        <v>87</v>
+        <v>628</v>
+      </c>
+      <c r="D107" t="s">
+        <v>582</v>
       </c>
       <c r="E107" t="s">
         <v>59</v>
       </c>
       <c r="F107" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>684</v>
       </c>
@@ -4671,16 +4680,16 @@
         <v>56</v>
       </c>
       <c r="C108" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="E108" t="s">
         <v>59</v>
       </c>
       <c r="F108" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>684</v>
       </c>
@@ -4688,16 +4697,16 @@
         <v>56</v>
       </c>
       <c r="C109" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E109" t="s">
         <v>59</v>
       </c>
       <c r="F109" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>684</v>
       </c>
@@ -4705,16 +4714,16 @@
         <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E110" t="s">
         <v>59</v>
       </c>
       <c r="F110" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>684</v>
       </c>
@@ -4722,19 +4731,16 @@
         <v>56</v>
       </c>
       <c r="C111" t="s">
-        <v>97</v>
-      </c>
-      <c r="D111">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E111" t="s">
         <v>59</v>
       </c>
       <c r="F111" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>684</v>
       </c>
@@ -4742,16 +4748,19 @@
         <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>74</v>
+        <v>97</v>
+      </c>
+      <c r="D112">
+        <v>1</v>
       </c>
       <c r="E112" t="s">
         <v>59</v>
       </c>
       <c r="F112" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>684</v>
       </c>
@@ -4759,16 +4768,16 @@
         <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E113" t="s">
         <v>59</v>
       </c>
       <c r="F113" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>684</v>
       </c>
@@ -4776,16 +4785,16 @@
         <v>56</v>
       </c>
       <c r="C114" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E114" t="s">
         <v>59</v>
       </c>
       <c r="F114" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>684</v>
       </c>
@@ -4793,36 +4802,33 @@
         <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E115" t="s">
         <v>59</v>
       </c>
       <c r="F115" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>684</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E116" t="s">
         <v>59</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>684</v>
       </c>
@@ -4830,7 +4836,7 @@
         <v>54</v>
       </c>
       <c r="C117" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4839,10 +4845,10 @@
         <v>59</v>
       </c>
       <c r="F117" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>684</v>
       </c>
@@ -4850,7 +4856,7 @@
         <v>54</v>
       </c>
       <c r="C118" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4859,32 +4865,35 @@
         <v>59</v>
       </c>
       <c r="F118" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>684</v>
       </c>
       <c r="B119" t="s">
-        <v>629</v>
-      </c>
-      <c r="D119" t="s">
-        <v>582</v>
+        <v>54</v>
+      </c>
+      <c r="C119" t="s">
+        <v>96</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
       </c>
       <c r="E119" t="s">
         <v>59</v>
       </c>
       <c r="F119" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>684</v>
       </c>
       <c r="B120" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D120" t="s">
         <v>582</v>
@@ -4893,78 +4902,78 @@
         <v>59</v>
       </c>
       <c r="F120" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>684</v>
       </c>
       <c r="B121" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D121" t="s">
         <v>582</v>
       </c>
       <c r="E121" t="s">
+        <v>59</v>
+      </c>
+      <c r="F121" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>684</v>
+      </c>
+      <c r="B122" t="s">
+        <v>631</v>
+      </c>
+      <c r="D122" t="s">
+        <v>582</v>
+      </c>
+      <c r="E122" t="s">
         <v>633</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F122" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>684</v>
-      </c>
-      <c r="B122" t="s">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>684</v>
+      </c>
+      <c r="B123" t="s">
         <v>94</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>13</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E123" t="s">
         <v>59</v>
       </c>
-      <c r="F122" t="s">
+      <c r="F123" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>684</v>
-      </c>
-      <c r="B123" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>684</v>
+      </c>
+      <c r="B124" t="s">
         <v>634</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D124" t="s">
         <v>582</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E124" t="s">
         <v>633</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F124" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>684</v>
-      </c>
-      <c r="B124" t="s">
-        <v>76</v>
-      </c>
-      <c r="C124" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" t="s">
-        <v>59</v>
-      </c>
-      <c r="F124" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>684</v>
       </c>
@@ -4972,7 +4981,7 @@
         <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E125" t="s">
         <v>59</v>
@@ -4981,7 +4990,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>684</v>
       </c>
@@ -4989,7 +4998,7 @@
         <v>76</v>
       </c>
       <c r="C126" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E126" t="s">
         <v>59</v>
@@ -4998,15 +5007,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>684</v>
       </c>
       <c r="B127" t="s">
-        <v>635</v>
-      </c>
-      <c r="D127" t="s">
-        <v>582</v>
+        <v>76</v>
+      </c>
+      <c r="C127" t="s">
+        <v>78</v>
       </c>
       <c r="E127" t="s">
         <v>59</v>
@@ -5015,49 +5024,49 @@
         <v>75</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>684</v>
       </c>
       <c r="B128" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" t="s">
-        <v>69</v>
+        <v>635</v>
+      </c>
+      <c r="D128" t="s">
+        <v>582</v>
       </c>
       <c r="E128" t="s">
         <v>59</v>
       </c>
       <c r="F128" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>684</v>
       </c>
       <c r="B129" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="C129" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E129" t="s">
         <v>59</v>
       </c>
       <c r="F129" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>684</v>
       </c>
       <c r="B130" t="s">
-        <v>636</v>
-      </c>
-      <c r="D130" t="s">
-        <v>582</v>
+        <v>83</v>
+      </c>
+      <c r="C130" t="s">
+        <v>86</v>
       </c>
       <c r="E130" t="s">
         <v>59</v>
@@ -5066,115 +5075,112 @@
         <v>82</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>684</v>
       </c>
       <c r="B131" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D131" t="s">
         <v>582</v>
       </c>
       <c r="E131" t="s">
-        <v>337</v>
+        <v>59</v>
       </c>
       <c r="F131" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>684</v>
       </c>
       <c r="B132" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D132" t="s">
         <v>582</v>
       </c>
       <c r="E132" t="s">
+        <v>337</v>
+      </c>
+      <c r="F132" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>684</v>
+      </c>
+      <c r="B133" t="s">
+        <v>638</v>
+      </c>
+      <c r="D133" t="s">
+        <v>582</v>
+      </c>
+      <c r="E133" t="s">
         <v>430</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F133" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>684</v>
-      </c>
-      <c r="B133" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>684</v>
+      </c>
+      <c r="B134" t="s">
         <v>461</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C134" t="s">
         <v>462</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E134" t="s">
         <v>463</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F134" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>684</v>
-      </c>
-      <c r="B134" t="s">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>684</v>
+      </c>
+      <c r="B135" t="s">
         <v>91</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C135" t="s">
         <v>84</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E135" t="s">
         <v>59</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F135" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>684</v>
-      </c>
-      <c r="B135" t="s">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>684</v>
+      </c>
+      <c r="B136" t="s">
         <v>455</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C136" t="s">
         <v>8</v>
       </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="D136">
+        <v>1</v>
+      </c>
+      <c r="E136" t="s">
         <v>453</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F136" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>684</v>
-      </c>
-      <c r="B136" t="s">
-        <v>32</v>
-      </c>
-      <c r="C136" t="s">
-        <v>10</v>
-      </c>
-      <c r="D136">
-        <v>1</v>
-      </c>
-      <c r="E136" t="s">
-        <v>33</v>
-      </c>
-      <c r="F136" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>684</v>
       </c>
@@ -5182,7 +5188,7 @@
         <v>32</v>
       </c>
       <c r="C137" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -5191,10 +5197,10 @@
         <v>33</v>
       </c>
       <c r="F137" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>684</v>
       </c>
@@ -5202,7 +5208,10 @@
         <v>32</v>
       </c>
       <c r="C138" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
       </c>
       <c r="E138" t="s">
         <v>33</v>
@@ -5211,7 +5220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>684</v>
       </c>
@@ -5219,27 +5228,24 @@
         <v>32</v>
       </c>
       <c r="C139" t="s">
-        <v>39</v>
-      </c>
-      <c r="D139">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E139" t="s">
         <v>33</v>
       </c>
       <c r="F139" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>684</v>
       </c>
       <c r="B140" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C140" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -5248,10 +5254,10 @@
         <v>33</v>
       </c>
       <c r="F140" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>684</v>
       </c>
@@ -5259,7 +5265,7 @@
         <v>29</v>
       </c>
       <c r="C141" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -5268,10 +5274,10 @@
         <v>33</v>
       </c>
       <c r="F141" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>684</v>
       </c>
@@ -5279,39 +5285,39 @@
         <v>29</v>
       </c>
       <c r="C142" t="s">
+        <v>35</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142" t="s">
+        <v>33</v>
+      </c>
+      <c r="F142" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>684</v>
+      </c>
+      <c r="B143" t="s">
+        <v>29</v>
+      </c>
+      <c r="C143" t="s">
         <v>42</v>
       </c>
-      <c r="D142">
-        <v>1</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143" t="s">
         <v>43</v>
       </c>
-      <c r="F142" t="s">
+      <c r="F143" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>684</v>
-      </c>
-      <c r="B143" t="s">
-        <v>41</v>
-      </c>
-      <c r="C143" t="s">
-        <v>22</v>
-      </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143" t="s">
-        <v>33</v>
-      </c>
-      <c r="F143" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>684</v>
       </c>
@@ -5319,19 +5325,19 @@
         <v>41</v>
       </c>
       <c r="C144" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D144">
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F144" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>684</v>
       </c>
@@ -5339,7 +5345,7 @@
         <v>41</v>
       </c>
       <c r="C145" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5351,41 +5357,44 @@
         <v>44</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>684</v>
       </c>
       <c r="B146" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" t="s">
+        <v>47</v>
+      </c>
+      <c r="D146">
+        <v>1</v>
+      </c>
+      <c r="E146" t="s">
+        <v>43</v>
+      </c>
+      <c r="F146" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>684</v>
+      </c>
+      <c r="B147" t="s">
         <v>68</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>73</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E147" t="s">
         <v>59</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F147" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>684</v>
-      </c>
-      <c r="B147" t="s">
-        <v>224</v>
-      </c>
-      <c r="C147" t="s">
-        <v>235</v>
-      </c>
-      <c r="E147" t="s">
-        <v>234</v>
-      </c>
-      <c r="F147" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>684</v>
       </c>
@@ -5393,50 +5402,50 @@
         <v>224</v>
       </c>
       <c r="C148" t="s">
+        <v>235</v>
+      </c>
+      <c r="E148" t="s">
+        <v>234</v>
+      </c>
+      <c r="F148" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>684</v>
+      </c>
+      <c r="B149" t="s">
+        <v>224</v>
+      </c>
+      <c r="C149" t="s">
         <v>223</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E149" t="s">
         <v>214</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F149" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>684</v>
-      </c>
-      <c r="B149" t="s">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>684</v>
+      </c>
+      <c r="B150" t="s">
         <v>745</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D150" t="s">
         <v>712</v>
-      </c>
-      <c r="E149" t="s">
-        <v>208</v>
-      </c>
-      <c r="F149" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>684</v>
-      </c>
-      <c r="B150" t="s">
-        <v>212</v>
-      </c>
-      <c r="C150" t="s">
-        <v>211</v>
       </c>
       <c r="E150" t="s">
         <v>208</v>
       </c>
       <c r="F150" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>684</v>
       </c>
@@ -5444,16 +5453,16 @@
         <v>212</v>
       </c>
       <c r="C151" t="s">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="E151" t="s">
         <v>208</v>
       </c>
       <c r="F151" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>684</v>
       </c>
@@ -5461,50 +5470,50 @@
         <v>212</v>
       </c>
       <c r="C152" t="s">
-        <v>67</v>
+        <v>387</v>
       </c>
       <c r="E152" t="s">
         <v>208</v>
       </c>
       <c r="F152" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>684</v>
       </c>
       <c r="B153" t="s">
-        <v>639</v>
-      </c>
-      <c r="D153" t="s">
-        <v>582</v>
+        <v>212</v>
+      </c>
+      <c r="C153" t="s">
+        <v>67</v>
       </c>
       <c r="E153" t="s">
         <v>208</v>
       </c>
       <c r="F153" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>684</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
-      </c>
-      <c r="C154" t="s">
-        <v>210</v>
+        <v>639</v>
+      </c>
+      <c r="D154" t="s">
+        <v>582</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
       </c>
       <c r="F154" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>684</v>
       </c>
@@ -5512,84 +5521,84 @@
         <v>243</v>
       </c>
       <c r="C155" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
       </c>
       <c r="F155" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>684</v>
+      </c>
+      <c r="B156" t="s">
+        <v>243</v>
+      </c>
+      <c r="C156" t="s">
+        <v>209</v>
+      </c>
+      <c r="E156" t="s">
+        <v>208</v>
+      </c>
+      <c r="F156" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>684</v>
-      </c>
-      <c r="B156" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>684</v>
+      </c>
+      <c r="B157" t="s">
         <v>640</v>
-      </c>
-      <c r="D156" t="s">
-        <v>582</v>
-      </c>
-      <c r="E156" t="s">
-        <v>475</v>
-      </c>
-      <c r="F156" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>684</v>
-      </c>
-      <c r="B157" t="s">
-        <v>641</v>
       </c>
       <c r="D157" t="s">
         <v>582</v>
       </c>
       <c r="E157" t="s">
+        <v>475</v>
+      </c>
+      <c r="F157" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>684</v>
+      </c>
+      <c r="B158" t="s">
+        <v>641</v>
+      </c>
+      <c r="D158" t="s">
+        <v>582</v>
+      </c>
+      <c r="E158" t="s">
         <v>256</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F158" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>684</v>
-      </c>
-      <c r="B158" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>684</v>
+      </c>
+      <c r="B159" t="s">
         <v>452</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C159" t="s">
         <v>92</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E159" t="s">
         <v>453</v>
       </c>
-      <c r="F158" t="s">
+      <c r="F159" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>684</v>
-      </c>
-      <c r="B159" t="s">
-        <v>726</v>
-      </c>
-      <c r="C159" t="s">
-        <v>576</v>
-      </c>
-      <c r="E159" t="s">
-        <v>724</v>
-      </c>
-      <c r="F159" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>684</v>
       </c>
@@ -5597,92 +5606,92 @@
         <v>726</v>
       </c>
       <c r="C160" t="s">
-        <v>78</v>
+        <v>576</v>
       </c>
       <c r="E160" t="s">
         <v>724</v>
       </c>
       <c r="F160" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>684</v>
+      </c>
+      <c r="B161" t="s">
+        <v>726</v>
+      </c>
+      <c r="C161" t="s">
+        <v>78</v>
+      </c>
+      <c r="E161" t="s">
+        <v>724</v>
+      </c>
+      <c r="F161" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>684</v>
-      </c>
-      <c r="B161" t="s">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>684</v>
+      </c>
+      <c r="B162" t="s">
         <v>642</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D162" t="s">
         <v>582</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E162" t="s">
         <v>644</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F162" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>684</v>
-      </c>
-      <c r="B162" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>684</v>
+      </c>
+      <c r="B163" t="s">
         <v>750</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D163" t="s">
         <v>712</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E163" t="s">
         <v>752</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F163" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>684</v>
-      </c>
-      <c r="B163" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>684</v>
+      </c>
+      <c r="B164" t="s">
         <v>689</v>
       </c>
-      <c r="D163" t="s">
+      <c r="D164" t="s">
         <v>582</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E164" t="s">
         <v>690</v>
       </c>
-      <c r="F163" t="s">
+      <c r="F164" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>684</v>
-      </c>
-      <c r="B164" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>684</v>
+      </c>
+      <c r="B165" t="s">
         <v>747</v>
       </c>
-      <c r="D164" t="s">
+      <c r="D165" t="s">
         <v>78</v>
-      </c>
-      <c r="E164" t="s">
-        <v>752</v>
-      </c>
-      <c r="F164" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>684</v>
-      </c>
-      <c r="B165" t="s">
-        <v>749</v>
-      </c>
-      <c r="D165" t="s">
-        <v>712</v>
       </c>
       <c r="E165" t="s">
         <v>752</v>
@@ -5691,32 +5700,32 @@
         <v>748</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>684</v>
       </c>
       <c r="B166" t="s">
+        <v>749</v>
+      </c>
+      <c r="D166" t="s">
+        <v>712</v>
+      </c>
+      <c r="E166" t="s">
+        <v>752</v>
+      </c>
+      <c r="F166" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>684</v>
+      </c>
+      <c r="B167" t="s">
         <v>589</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D167" t="s">
         <v>78</v>
-      </c>
-      <c r="E166" t="s">
-        <v>590</v>
-      </c>
-      <c r="F166" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>684</v>
-      </c>
-      <c r="B167" t="s">
-        <v>593</v>
-      </c>
-      <c r="D167" t="s">
-        <v>582</v>
       </c>
       <c r="E167" t="s">
         <v>590</v>
@@ -5725,86 +5734,83 @@
         <v>591</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>684</v>
       </c>
       <c r="B168" t="s">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="D168" t="s">
         <v>582</v>
       </c>
       <c r="E168" t="s">
+        <v>590</v>
+      </c>
+      <c r="F168" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>684</v>
+      </c>
+      <c r="B169" t="s">
+        <v>645</v>
+      </c>
+      <c r="D169" t="s">
+        <v>582</v>
+      </c>
+      <c r="E169" t="s">
         <v>391</v>
       </c>
-      <c r="F168" t="s">
+      <c r="F169" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>684</v>
-      </c>
-      <c r="B169" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>684</v>
+      </c>
+      <c r="B170" t="s">
         <v>557</v>
       </c>
-      <c r="C169" t="s">
+      <c r="C170" t="s">
         <v>558</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E170" t="s">
         <v>369</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F170" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>684</v>
-      </c>
-      <c r="B170" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>684</v>
+      </c>
+      <c r="B171" t="s">
         <v>646</v>
       </c>
-      <c r="D170" t="s">
+      <c r="D171" t="s">
         <v>582</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E171" t="s">
         <v>475</v>
       </c>
-      <c r="F170" t="s">
+      <c r="F171" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>684</v>
-      </c>
-      <c r="B171" t="s">
-        <v>694</v>
-      </c>
-      <c r="D171" t="s">
-        <v>692</v>
-      </c>
-      <c r="E171" t="s">
-        <v>697</v>
-      </c>
-      <c r="F171" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>684</v>
       </c>
       <c r="B172" t="s">
         <v>694</v>
       </c>
-      <c r="C172" t="s">
-        <v>696</v>
-      </c>
-      <c r="D172">
-        <v>1</v>
+      <c r="D172" t="s">
+        <v>692</v>
       </c>
       <c r="E172" t="s">
         <v>697</v>
@@ -5813,7 +5819,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>684</v>
       </c>
@@ -5821,7 +5827,7 @@
         <v>694</v>
       </c>
       <c r="C173" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -5830,86 +5836,89 @@
         <v>697</v>
       </c>
       <c r="F173" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>684</v>
+      </c>
+      <c r="B174" t="s">
+        <v>694</v>
+      </c>
+      <c r="C174" t="s">
+        <v>695</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+      <c r="E174" t="s">
+        <v>697</v>
+      </c>
+      <c r="F174" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>684</v>
-      </c>
-      <c r="B174" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>684</v>
+      </c>
+      <c r="B175" t="s">
         <v>647</v>
-      </c>
-      <c r="D174" t="s">
-        <v>582</v>
-      </c>
-      <c r="E174" t="s">
-        <v>287</v>
-      </c>
-      <c r="F174" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>684</v>
-      </c>
-      <c r="B175" t="s">
-        <v>648</v>
       </c>
       <c r="D175" t="s">
         <v>582</v>
       </c>
       <c r="E175" t="s">
-        <v>414</v>
+        <v>287</v>
       </c>
       <c r="F175" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>684</v>
       </c>
       <c r="B176" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D176" t="s">
         <v>582</v>
       </c>
       <c r="E176" t="s">
-        <v>537</v>
+        <v>414</v>
       </c>
       <c r="F176" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>684</v>
       </c>
       <c r="B177" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
       <c r="D177" t="s">
         <v>582</v>
       </c>
       <c r="E177" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="F177" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>684</v>
       </c>
       <c r="B178" t="s">
-        <v>72</v>
-      </c>
-      <c r="C178" t="s">
-        <v>63</v>
+        <v>681</v>
+      </c>
+      <c r="D178" t="s">
+        <v>582</v>
       </c>
       <c r="E178" t="s">
         <v>59</v>
@@ -5918,7 +5927,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>684</v>
       </c>
@@ -5926,7 +5935,7 @@
         <v>72</v>
       </c>
       <c r="C179" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E179" t="s">
         <v>59</v>
@@ -5935,95 +5944,92 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>684</v>
       </c>
       <c r="B180" t="s">
+        <v>72</v>
+      </c>
+      <c r="C180" t="s">
+        <v>77</v>
+      </c>
+      <c r="E180" t="s">
+        <v>59</v>
+      </c>
+      <c r="F180" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>684</v>
+      </c>
+      <c r="B181" t="s">
         <v>295</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>84</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E181" t="s">
         <v>291</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F181" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>684</v>
-      </c>
-      <c r="B181" t="s">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>684</v>
+      </c>
+      <c r="B182" t="s">
         <v>650</v>
-      </c>
-      <c r="D181" t="s">
-        <v>582</v>
-      </c>
-      <c r="E181" t="s">
-        <v>651</v>
-      </c>
-      <c r="F181" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>684</v>
-      </c>
-      <c r="B182" t="s">
-        <v>653</v>
       </c>
       <c r="D182" t="s">
         <v>582</v>
       </c>
       <c r="E182" t="s">
-        <v>526</v>
+        <v>651</v>
       </c>
       <c r="F182" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>684</v>
       </c>
       <c r="B183" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D183" t="s">
         <v>582</v>
       </c>
       <c r="E183" t="s">
+        <v>526</v>
+      </c>
+      <c r="F183" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>684</v>
+      </c>
+      <c r="B184" t="s">
+        <v>654</v>
+      </c>
+      <c r="D184" t="s">
+        <v>582</v>
+      </c>
+      <c r="E184" t="s">
         <v>475</v>
       </c>
-      <c r="F183" t="s">
+      <c r="F184" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>684</v>
-      </c>
-      <c r="B184" t="s">
-        <v>342</v>
-      </c>
-      <c r="C184" t="s">
-        <v>343</v>
-      </c>
-      <c r="D184">
-        <v>1</v>
-      </c>
-      <c r="E184" t="s">
-        <v>337</v>
-      </c>
-      <c r="F184" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>684</v>
       </c>
@@ -6031,7 +6037,7 @@
         <v>342</v>
       </c>
       <c r="C185" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -6043,7 +6049,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>684</v>
       </c>
@@ -6051,7 +6057,7 @@
         <v>342</v>
       </c>
       <c r="C186" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -6060,10 +6066,10 @@
         <v>337</v>
       </c>
       <c r="F186" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>684</v>
       </c>
@@ -6071,7 +6077,7 @@
         <v>342</v>
       </c>
       <c r="C187" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -6083,44 +6089,44 @@
         <v>341</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>684</v>
       </c>
       <c r="B188" t="s">
-        <v>9</v>
-      </c>
-      <c r="D188" t="s">
-        <v>692</v>
+        <v>342</v>
+      </c>
+      <c r="C188" t="s">
+        <v>346</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="F188" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>684</v>
       </c>
       <c r="B189" t="s">
         <v>9</v>
       </c>
-      <c r="C189" t="s">
-        <v>10</v>
-      </c>
-      <c r="D189">
-        <v>1</v>
+      <c r="D189" t="s">
+        <v>692</v>
       </c>
       <c r="E189" t="s">
         <v>11</v>
       </c>
       <c r="F189" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>684</v>
       </c>
@@ -6128,70 +6134,73 @@
         <v>9</v>
       </c>
       <c r="C190" t="s">
+        <v>10</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+      <c r="E190" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>684</v>
+      </c>
+      <c r="B191" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" t="s">
         <v>13</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E191" t="s">
         <v>14</v>
       </c>
-      <c r="F190" t="s">
+      <c r="F191" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>684</v>
-      </c>
-      <c r="B191" t="s">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>684</v>
+      </c>
+      <c r="B192" t="s">
         <v>7</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C192" t="s">
         <v>8</v>
       </c>
-      <c r="D191">
-        <v>1</v>
-      </c>
-      <c r="E191" t="s">
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192" t="s">
         <v>11</v>
       </c>
-      <c r="F191" t="s">
+      <c r="F192" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>684</v>
-      </c>
-      <c r="B192" t="s">
-        <v>700</v>
-      </c>
-      <c r="D192" t="s">
-        <v>692</v>
-      </c>
-      <c r="E192" t="s">
-        <v>702</v>
-      </c>
-      <c r="F192" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>684</v>
       </c>
       <c r="B193" t="s">
         <v>700</v>
       </c>
-      <c r="C193" t="s">
-        <v>361</v>
+      <c r="D193" t="s">
+        <v>692</v>
       </c>
       <c r="E193" t="s">
         <v>702</v>
       </c>
       <c r="F193" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>684</v>
       </c>
@@ -6199,16 +6208,16 @@
         <v>700</v>
       </c>
       <c r="C194" t="s">
-        <v>714</v>
+        <v>361</v>
       </c>
       <c r="E194" t="s">
         <v>702</v>
       </c>
       <c r="F194" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>684</v>
       </c>
@@ -6216,16 +6225,16 @@
         <v>700</v>
       </c>
       <c r="C195" t="s">
-        <v>546</v>
+        <v>714</v>
       </c>
       <c r="E195" t="s">
         <v>702</v>
       </c>
       <c r="F195" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>684</v>
       </c>
@@ -6233,16 +6242,16 @@
         <v>700</v>
       </c>
       <c r="C196" t="s">
-        <v>715</v>
+        <v>546</v>
       </c>
       <c r="E196" t="s">
         <v>702</v>
       </c>
       <c r="F196" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>684</v>
       </c>
@@ -6250,47 +6259,44 @@
         <v>700</v>
       </c>
       <c r="C197" t="s">
-        <v>10</v>
-      </c>
-      <c r="D197">
-        <v>1</v>
+        <v>715</v>
       </c>
       <c r="E197" t="s">
         <v>702</v>
       </c>
       <c r="F197" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>684</v>
       </c>
       <c r="B198" t="s">
-        <v>701</v>
-      </c>
-      <c r="D198" t="s">
-        <v>692</v>
+        <v>700</v>
+      </c>
+      <c r="C198" t="s">
+        <v>10</v>
+      </c>
+      <c r="D198">
+        <v>1</v>
       </c>
       <c r="E198" t="s">
         <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>684</v>
       </c>
       <c r="B199" t="s">
         <v>701</v>
       </c>
-      <c r="C199" t="s">
-        <v>8</v>
-      </c>
-      <c r="D199">
-        <v>1</v>
+      <c r="D199" t="s">
+        <v>692</v>
       </c>
       <c r="E199" t="s">
         <v>702</v>
@@ -6299,7 +6305,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>684</v>
       </c>
@@ -6307,7 +6313,7 @@
         <v>701</v>
       </c>
       <c r="C200" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -6316,10 +6322,10 @@
         <v>702</v>
       </c>
       <c r="F200" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>684</v>
       </c>
@@ -6327,7 +6333,7 @@
         <v>701</v>
       </c>
       <c r="C201" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -6336,27 +6342,30 @@
         <v>702</v>
       </c>
       <c r="F201" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>684</v>
+      </c>
+      <c r="B202" t="s">
+        <v>701</v>
+      </c>
+      <c r="C202" t="s">
+        <v>96</v>
+      </c>
+      <c r="D202">
+        <v>1</v>
+      </c>
+      <c r="E202" t="s">
+        <v>702</v>
+      </c>
+      <c r="F202" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A202" t="s">
-        <v>684</v>
-      </c>
-      <c r="B202" t="s">
-        <v>441</v>
-      </c>
-      <c r="C202" t="s">
-        <v>442</v>
-      </c>
-      <c r="E202" t="s">
-        <v>436</v>
-      </c>
-      <c r="F202" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>684</v>
       </c>
@@ -6364,53 +6373,53 @@
         <v>441</v>
       </c>
       <c r="C203" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E203" t="s">
         <v>436</v>
       </c>
       <c r="F203" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>684</v>
+      </c>
+      <c r="B204" t="s">
+        <v>441</v>
+      </c>
+      <c r="C204" t="s">
+        <v>438</v>
+      </c>
+      <c r="E204" t="s">
+        <v>436</v>
+      </c>
+      <c r="F204" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A204" t="s">
-        <v>684</v>
-      </c>
-      <c r="B204" t="s">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>684</v>
+      </c>
+      <c r="B205" t="s">
         <v>308</v>
       </c>
-      <c r="C204" t="s">
+      <c r="C205" t="s">
         <v>8</v>
       </c>
-      <c r="D204">
-        <v>1</v>
-      </c>
-      <c r="E204" t="s">
-        <v>309</v>
-      </c>
-      <c r="F204" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A205" t="s">
-        <v>684</v>
-      </c>
-      <c r="B205" t="s">
-        <v>313</v>
-      </c>
-      <c r="C205" t="s">
-        <v>311</v>
+      <c r="D205">
+        <v>1</v>
       </c>
       <c r="E205" t="s">
         <v>309</v>
       </c>
       <c r="F205" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>684</v>
       </c>
@@ -6418,7 +6427,7 @@
         <v>313</v>
       </c>
       <c r="C206" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E206" t="s">
         <v>309</v>
@@ -6427,7 +6436,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>684</v>
       </c>
@@ -6435,16 +6444,16 @@
         <v>313</v>
       </c>
       <c r="C207" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E207" t="s">
         <v>309</v>
       </c>
       <c r="F207" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>684</v>
       </c>
@@ -6452,19 +6461,16 @@
         <v>313</v>
       </c>
       <c r="C208" t="s">
-        <v>317</v>
-      </c>
-      <c r="D208">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="E208" t="s">
         <v>309</v>
       </c>
       <c r="F208" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>684</v>
       </c>
@@ -6472,7 +6478,7 @@
         <v>313</v>
       </c>
       <c r="C209" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -6481,10 +6487,10 @@
         <v>309</v>
       </c>
       <c r="F209" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>684</v>
       </c>
@@ -6492,87 +6498,90 @@
         <v>313</v>
       </c>
       <c r="C210" t="s">
-        <v>388</v>
+        <v>315</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
       </c>
       <c r="E210" t="s">
         <v>309</v>
       </c>
       <c r="F210" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>684</v>
       </c>
       <c r="B211" t="s">
-        <v>655</v>
-      </c>
-      <c r="D211" t="s">
-        <v>582</v>
+        <v>313</v>
+      </c>
+      <c r="C211" t="s">
+        <v>388</v>
       </c>
       <c r="E211" t="s">
         <v>309</v>
       </c>
       <c r="F211" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>684</v>
       </c>
       <c r="B212" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D212" t="s">
         <v>582</v>
       </c>
       <c r="E212" t="s">
+        <v>309</v>
+      </c>
+      <c r="F212" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>684</v>
+      </c>
+      <c r="B213" t="s">
+        <v>656</v>
+      </c>
+      <c r="D213" t="s">
+        <v>582</v>
+      </c>
+      <c r="E213" t="s">
         <v>291</v>
       </c>
-      <c r="F212" t="s">
+      <c r="F213" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A213" t="s">
-        <v>684</v>
-      </c>
-      <c r="B213" t="s">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>684</v>
+      </c>
+      <c r="B214" t="s">
         <v>472</v>
       </c>
-      <c r="C213" t="s">
+      <c r="C214" t="s">
         <v>471</v>
       </c>
-      <c r="D213">
-        <v>1</v>
-      </c>
-      <c r="E213" t="s">
-        <v>475</v>
-      </c>
-      <c r="F213" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
-        <v>684</v>
-      </c>
-      <c r="B214" t="s">
-        <v>466</v>
-      </c>
-      <c r="C214" t="s">
-        <v>467</v>
+      <c r="D214">
+        <v>1</v>
       </c>
       <c r="E214" t="s">
         <v>475</v>
       </c>
       <c r="F214" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>684</v>
       </c>
@@ -6580,16 +6589,16 @@
         <v>466</v>
       </c>
       <c r="C215" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E215" t="s">
         <v>475</v>
       </c>
       <c r="F215" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>684</v>
       </c>
@@ -6597,16 +6606,16 @@
         <v>466</v>
       </c>
       <c r="C216" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E216" t="s">
         <v>475</v>
       </c>
       <c r="F216" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>684</v>
       </c>
@@ -6614,24 +6623,24 @@
         <v>466</v>
       </c>
       <c r="C217" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E217" t="s">
         <v>475</v>
       </c>
       <c r="F217" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>684</v>
+      </c>
+      <c r="B218" t="s">
+        <v>466</v>
+      </c>
+      <c r="C218" t="s">
         <v>470</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A218" t="s">
-        <v>684</v>
-      </c>
-      <c r="B218" t="s">
-        <v>473</v>
-      </c>
-      <c r="C218" t="s">
-        <v>474</v>
       </c>
       <c r="E218" t="s">
         <v>475</v>
@@ -6640,27 +6649,24 @@
         <v>470</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>684</v>
       </c>
       <c r="B219" t="s">
-        <v>229</v>
+        <v>473</v>
       </c>
       <c r="C219" t="s">
-        <v>230</v>
-      </c>
-      <c r="D219">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="E219" t="s">
-        <v>233</v>
+        <v>475</v>
       </c>
       <c r="F219" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>684</v>
       </c>
@@ -6668,16 +6674,19 @@
         <v>229</v>
       </c>
       <c r="C220" t="s">
-        <v>494</v>
+        <v>230</v>
+      </c>
+      <c r="D220">
+        <v>1</v>
       </c>
       <c r="E220" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="F220" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>684</v>
       </c>
@@ -6685,19 +6694,16 @@
         <v>229</v>
       </c>
       <c r="C221" t="s">
-        <v>497</v>
-      </c>
-      <c r="D221">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="E221" t="s">
         <v>495</v>
       </c>
       <c r="F221" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>684</v>
       </c>
@@ -6705,16 +6711,19 @@
         <v>229</v>
       </c>
       <c r="C222" t="s">
-        <v>499</v>
+        <v>497</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
       </c>
       <c r="E222" t="s">
         <v>495</v>
       </c>
       <c r="F222" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>684</v>
       </c>
@@ -6722,16 +6731,16 @@
         <v>229</v>
       </c>
       <c r="C223" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E223" t="s">
         <v>495</v>
       </c>
       <c r="F223" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>684</v>
       </c>
@@ -6739,16 +6748,16 @@
         <v>229</v>
       </c>
       <c r="C224" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E224" t="s">
         <v>495</v>
       </c>
       <c r="F224" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>684</v>
       </c>
@@ -6756,16 +6765,16 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E225" t="s">
         <v>495</v>
       </c>
       <c r="F225" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>684</v>
       </c>
@@ -6773,19 +6782,16 @@
         <v>229</v>
       </c>
       <c r="C226" t="s">
-        <v>506</v>
-      </c>
-      <c r="D226">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="E226" t="s">
         <v>495</v>
       </c>
       <c r="F226" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>684</v>
       </c>
@@ -6793,16 +6799,19 @@
         <v>229</v>
       </c>
       <c r="C227" t="s">
-        <v>508</v>
+        <v>506</v>
+      </c>
+      <c r="D227">
+        <v>1</v>
       </c>
       <c r="E227" t="s">
         <v>495</v>
       </c>
       <c r="F227" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>684</v>
       </c>
@@ -6810,16 +6819,16 @@
         <v>229</v>
       </c>
       <c r="C228" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E228" t="s">
         <v>495</v>
       </c>
       <c r="F228" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>684</v>
       </c>
@@ -6827,33 +6836,33 @@
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E229" t="s">
         <v>495</v>
       </c>
       <c r="F229" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>684</v>
+      </c>
+      <c r="B230" t="s">
+        <v>229</v>
+      </c>
+      <c r="C230" t="s">
+        <v>512</v>
+      </c>
+      <c r="E230" t="s">
+        <v>495</v>
+      </c>
+      <c r="F230" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A230" t="s">
-        <v>684</v>
-      </c>
-      <c r="B230" t="s">
-        <v>216</v>
-      </c>
-      <c r="C230" t="s">
-        <v>219</v>
-      </c>
-      <c r="E230" t="s">
-        <v>214</v>
-      </c>
-      <c r="F230" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>684</v>
       </c>
@@ -6861,16 +6870,16 @@
         <v>216</v>
       </c>
       <c r="C231" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E231" t="s">
         <v>214</v>
       </c>
       <c r="F231" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>684</v>
       </c>
@@ -6878,19 +6887,16 @@
         <v>216</v>
       </c>
       <c r="C232" t="s">
-        <v>10</v>
-      </c>
-      <c r="D232">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="E232" t="s">
         <v>214</v>
       </c>
       <c r="F232" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>684</v>
       </c>
@@ -6898,16 +6904,19 @@
         <v>216</v>
       </c>
       <c r="C233" t="s">
-        <v>225</v>
+        <v>10</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
       </c>
       <c r="E233" t="s">
         <v>214</v>
       </c>
       <c r="F233" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>684</v>
       </c>
@@ -6915,19 +6924,16 @@
         <v>216</v>
       </c>
       <c r="C234" t="s">
-        <v>594</v>
-      </c>
-      <c r="D234">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="E234" t="s">
-        <v>595</v>
+        <v>214</v>
       </c>
       <c r="F234" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>684</v>
       </c>
@@ -6935,7 +6941,7 @@
         <v>216</v>
       </c>
       <c r="C235" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -6947,7 +6953,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>684</v>
       </c>
@@ -6955,16 +6961,19 @@
         <v>216</v>
       </c>
       <c r="C236" t="s">
-        <v>227</v>
+        <v>597</v>
+      </c>
+      <c r="D236">
+        <v>1</v>
       </c>
       <c r="E236" t="s">
-        <v>233</v>
+        <v>595</v>
       </c>
       <c r="F236" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>684</v>
       </c>
@@ -6972,39 +6981,36 @@
         <v>216</v>
       </c>
       <c r="C237" t="s">
+        <v>227</v>
+      </c>
+      <c r="E237" t="s">
+        <v>233</v>
+      </c>
+      <c r="F237" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>684</v>
+      </c>
+      <c r="B238" t="s">
+        <v>216</v>
+      </c>
+      <c r="C238" t="s">
         <v>602</v>
       </c>
-      <c r="D237">
-        <v>1</v>
-      </c>
-      <c r="E237" t="s">
+      <c r="D238">
+        <v>1</v>
+      </c>
+      <c r="E238" t="s">
         <v>603</v>
       </c>
-      <c r="F237" t="s">
+      <c r="F238" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A238" t="s">
-        <v>684</v>
-      </c>
-      <c r="B238" t="s">
-        <v>213</v>
-      </c>
-      <c r="C238" t="s">
-        <v>8</v>
-      </c>
-      <c r="D238">
-        <v>1</v>
-      </c>
-      <c r="E238" t="s">
-        <v>214</v>
-      </c>
-      <c r="F238" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>684</v>
       </c>
@@ -7012,56 +7018,56 @@
         <v>213</v>
       </c>
       <c r="C239" t="s">
+        <v>8</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
+        <v>214</v>
+      </c>
+      <c r="F239" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>684</v>
+      </c>
+      <c r="B240" t="s">
+        <v>213</v>
+      </c>
+      <c r="C240" t="s">
         <v>35</v>
       </c>
-      <c r="D239">
-        <v>1</v>
-      </c>
-      <c r="E239" t="s">
+      <c r="D240">
+        <v>1</v>
+      </c>
+      <c r="E240" t="s">
         <v>603</v>
       </c>
-      <c r="F239" t="s">
+      <c r="F240" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A240" t="s">
-        <v>684</v>
-      </c>
-      <c r="B240" t="s">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>684</v>
+      </c>
+      <c r="B241" t="s">
         <v>62</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C241" t="s">
         <v>67</v>
       </c>
-      <c r="E240" t="s">
+      <c r="E241" t="s">
         <v>59</v>
       </c>
-      <c r="F240" t="s">
+      <c r="F241" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A241" t="s">
-        <v>684</v>
-      </c>
-      <c r="B241" t="s">
-        <v>23</v>
-      </c>
-      <c r="C241" t="s">
-        <v>716</v>
-      </c>
-      <c r="D241">
-        <v>1</v>
-      </c>
-      <c r="E241" t="s">
-        <v>709</v>
-      </c>
-      <c r="F241" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>684</v>
       </c>
@@ -7069,16 +7075,19 @@
         <v>23</v>
       </c>
       <c r="C242" t="s">
-        <v>713</v>
+        <v>716</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
       </c>
       <c r="E242" t="s">
         <v>709</v>
       </c>
       <c r="F242" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>684</v>
       </c>
@@ -7086,16 +7095,16 @@
         <v>23</v>
       </c>
       <c r="C243" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E243" t="s">
         <v>709</v>
       </c>
       <c r="F243" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>684</v>
       </c>
@@ -7103,16 +7112,16 @@
         <v>23</v>
       </c>
       <c r="C244" t="s">
-        <v>575</v>
+        <v>718</v>
       </c>
       <c r="E244" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F244" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>684</v>
       </c>
@@ -7120,19 +7129,16 @@
         <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>513</v>
-      </c>
-      <c r="D245">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="E245" t="s">
-        <v>514</v>
+        <v>724</v>
       </c>
       <c r="F245" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>684</v>
       </c>
@@ -7140,16 +7146,19 @@
         <v>23</v>
       </c>
       <c r="C246" t="s">
-        <v>405</v>
+        <v>513</v>
+      </c>
+      <c r="D246">
+        <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
       <c r="F246" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>684</v>
       </c>
@@ -7157,19 +7166,16 @@
         <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>521</v>
-      </c>
-      <c r="D247">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="E247" t="s">
-        <v>537</v>
+        <v>406</v>
       </c>
       <c r="F247" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>684</v>
       </c>
@@ -7177,7 +7183,7 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -7186,10 +7192,10 @@
         <v>537</v>
       </c>
       <c r="F248" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>684</v>
       </c>
@@ -7197,19 +7203,19 @@
         <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>351</v>
+        <v>524</v>
       </c>
       <c r="D249">
         <v>1</v>
       </c>
       <c r="E249" t="s">
-        <v>414</v>
+        <v>537</v>
       </c>
       <c r="F249" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>684</v>
       </c>
@@ -7217,7 +7223,7 @@
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -7226,10 +7232,10 @@
         <v>414</v>
       </c>
       <c r="F250" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>684</v>
       </c>
@@ -7237,19 +7243,19 @@
         <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
       <c r="D251">
         <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="F251" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>684</v>
       </c>
@@ -7257,19 +7263,19 @@
         <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D252">
         <v>1</v>
       </c>
       <c r="E252" t="s">
-        <v>538</v>
+        <v>444</v>
       </c>
       <c r="F252" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>684</v>
       </c>
@@ -7277,7 +7283,7 @@
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -7286,10 +7292,10 @@
         <v>538</v>
       </c>
       <c r="F253" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>684</v>
       </c>
@@ -7297,19 +7303,19 @@
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>265</v>
+        <v>539</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="F254" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>684</v>
       </c>
@@ -7317,19 +7323,19 @@
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="D255">
         <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>418</v>
+        <v>286</v>
       </c>
       <c r="F255" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>684</v>
       </c>
@@ -7337,19 +7343,19 @@
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="F256" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>684</v>
       </c>
@@ -7357,7 +7363,7 @@
         <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -7366,10 +7372,10 @@
         <v>391</v>
       </c>
       <c r="F257" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>684</v>
       </c>
@@ -7377,19 +7383,19 @@
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="D258">
         <v>1</v>
       </c>
       <c r="E258" t="s">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="F258" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>684</v>
       </c>
@@ -7397,7 +7403,7 @@
         <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>433</v>
+        <v>275</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -7406,10 +7412,10 @@
         <v>288</v>
       </c>
       <c r="F259" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>684</v>
       </c>
@@ -7417,19 +7423,19 @@
         <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
       <c r="D260">
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>587</v>
+        <v>288</v>
       </c>
       <c r="F260" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>684</v>
       </c>
@@ -7437,19 +7443,19 @@
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>450</v>
+        <v>587</v>
       </c>
       <c r="F261" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>684</v>
       </c>
@@ -7457,19 +7463,19 @@
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="D262">
         <v>1</v>
       </c>
       <c r="E262" t="s">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="F262" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>684</v>
       </c>
@@ -7477,7 +7483,7 @@
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -7486,10 +7492,10 @@
         <v>289</v>
       </c>
       <c r="F263" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>684</v>
       </c>
@@ -7497,19 +7503,19 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>528</v>
+        <v>279</v>
       </c>
       <c r="D264">
         <v>1</v>
       </c>
       <c r="E264" t="s">
-        <v>526</v>
+        <v>289</v>
       </c>
       <c r="F264" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>684</v>
       </c>
@@ -7517,7 +7523,7 @@
         <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -7526,10 +7532,10 @@
         <v>526</v>
       </c>
       <c r="F265" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>684</v>
       </c>
@@ -7537,16 +7543,19 @@
         <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="F266" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>684</v>
       </c>
@@ -7554,19 +7563,16 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>26</v>
-      </c>
-      <c r="D267">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E267" t="s">
-        <v>245</v>
+        <v>102</v>
       </c>
       <c r="F267" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>684</v>
       </c>
@@ -7574,7 +7580,7 @@
         <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -7586,7 +7592,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>684</v>
       </c>
@@ -7594,19 +7600,19 @@
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="D269">
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="F269" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>684</v>
       </c>
@@ -7614,16 +7620,19 @@
         <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>77</v>
+        <v>321</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
       </c>
       <c r="E270" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="F270" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>684</v>
       </c>
@@ -7631,19 +7640,16 @@
         <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>24</v>
-      </c>
-      <c r="D271">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E271" t="s">
-        <v>257</v>
+        <v>420</v>
       </c>
       <c r="F271" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>684</v>
       </c>
@@ -7651,87 +7657,90 @@
         <v>23</v>
       </c>
       <c r="C272" t="s">
+        <v>24</v>
+      </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
+      <c r="E272" t="s">
+        <v>257</v>
+      </c>
+      <c r="F272" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>684</v>
+      </c>
+      <c r="B273" t="s">
+        <v>23</v>
+      </c>
+      <c r="C273" t="s">
         <v>30</v>
       </c>
-      <c r="D272">
+      <c r="D273">
         <v>2</v>
       </c>
-      <c r="E272" t="s">
+      <c r="E273" t="s">
         <v>247</v>
       </c>
-      <c r="F272" t="s">
+      <c r="F273" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A273" t="s">
-        <v>684</v>
-      </c>
-      <c r="B273" t="s">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>684</v>
+      </c>
+      <c r="B274" t="s">
         <v>385</v>
       </c>
-      <c r="C273" t="s">
+      <c r="C274" t="s">
         <v>84</v>
       </c>
-      <c r="E273" t="s">
+      <c r="E274" t="s">
         <v>286</v>
       </c>
-      <c r="F273" t="s">
+      <c r="F274" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A274" t="s">
-        <v>684</v>
-      </c>
-      <c r="B274" t="s">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>684</v>
+      </c>
+      <c r="B275" t="s">
         <v>657</v>
       </c>
-      <c r="D274" t="s">
+      <c r="D275" t="s">
         <v>582</v>
       </c>
-      <c r="E274" t="s">
+      <c r="E275" t="s">
         <v>288</v>
       </c>
-      <c r="F274" t="s">
+      <c r="F275" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A275" t="s">
-        <v>684</v>
-      </c>
-      <c r="B275" t="s">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>684</v>
+      </c>
+      <c r="B276" t="s">
         <v>106</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C276" t="s">
         <v>111</v>
       </c>
-      <c r="E275" t="s">
+      <c r="E276" t="s">
         <v>112</v>
       </c>
-      <c r="F275" t="s">
+      <c r="F276" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A276" t="s">
-        <v>684</v>
-      </c>
-      <c r="B276" t="s">
-        <v>98</v>
-      </c>
-      <c r="C276" t="s">
-        <v>104</v>
-      </c>
-      <c r="E276" t="s">
-        <v>102</v>
-      </c>
-      <c r="F276" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>684</v>
       </c>
@@ -7739,16 +7748,16 @@
         <v>98</v>
       </c>
       <c r="C277" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E277" t="s">
         <v>102</v>
       </c>
       <c r="F277" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>684</v>
       </c>
@@ -7756,16 +7765,16 @@
         <v>98</v>
       </c>
       <c r="C278" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E278" t="s">
         <v>102</v>
       </c>
       <c r="F278" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>684</v>
       </c>
@@ -7773,7 +7782,7 @@
         <v>98</v>
       </c>
       <c r="C279" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E279" t="s">
         <v>102</v>
@@ -7782,183 +7791,180 @@
         <v>103</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>684</v>
       </c>
       <c r="B280" t="s">
-        <v>658</v>
-      </c>
-      <c r="D280" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="C280" t="s">
+        <v>107</v>
       </c>
       <c r="E280" t="s">
         <v>102</v>
       </c>
       <c r="F280" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>684</v>
       </c>
       <c r="B281" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D281" t="s">
         <v>582</v>
       </c>
       <c r="E281" t="s">
+        <v>102</v>
+      </c>
+      <c r="F281" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>684</v>
+      </c>
+      <c r="B282" t="s">
+        <v>659</v>
+      </c>
+      <c r="D282" t="s">
+        <v>582</v>
+      </c>
+      <c r="E282" t="s">
         <v>420</v>
       </c>
-      <c r="F281" t="s">
+      <c r="F282" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A282" t="s">
-        <v>684</v>
-      </c>
-      <c r="B282" t="s">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>684</v>
+      </c>
+      <c r="B283" t="s">
         <v>330</v>
       </c>
-      <c r="C282" t="s">
+      <c r="C283" t="s">
         <v>322</v>
       </c>
-      <c r="E282" t="s">
+      <c r="E283" t="s">
         <v>320</v>
       </c>
-      <c r="F282" t="s">
+      <c r="F283" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A283" t="s">
-        <v>684</v>
-      </c>
-      <c r="B283" t="s">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>684</v>
+      </c>
+      <c r="B284" t="s">
         <v>762</v>
       </c>
-      <c r="D283" t="s">
+      <c r="D284" t="s">
         <v>712</v>
       </c>
-      <c r="E283" t="s">
+      <c r="E284" t="s">
         <v>763</v>
       </c>
-      <c r="F283" t="s">
+      <c r="F284" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A284" t="s">
-        <v>684</v>
-      </c>
-      <c r="B284" t="s">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>684</v>
+      </c>
+      <c r="B285" t="s">
         <v>239</v>
       </c>
-      <c r="C284" t="s">
+      <c r="C285" t="s">
         <v>240</v>
       </c>
-      <c r="E284" t="s">
+      <c r="E285" t="s">
         <v>241</v>
       </c>
-      <c r="F284" t="s">
+      <c r="F285" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A285" t="s">
-        <v>684</v>
-      </c>
-      <c r="B285" t="s">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>684</v>
+      </c>
+      <c r="B286" t="s">
         <v>660</v>
-      </c>
-      <c r="D285" t="s">
-        <v>582</v>
-      </c>
-      <c r="E285" t="s">
-        <v>324</v>
-      </c>
-      <c r="F285" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A286" t="s">
-        <v>684</v>
-      </c>
-      <c r="B286" t="s">
-        <v>662</v>
       </c>
       <c r="D286" t="s">
         <v>582</v>
       </c>
       <c r="E286" t="s">
+        <v>324</v>
+      </c>
+      <c r="F286" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>684</v>
+      </c>
+      <c r="B287" t="s">
+        <v>662</v>
+      </c>
+      <c r="D287" t="s">
+        <v>582</v>
+      </c>
+      <c r="E287" t="s">
         <v>289</v>
       </c>
-      <c r="F286" t="s">
+      <c r="F287" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A287" t="s">
-        <v>684</v>
-      </c>
-      <c r="B287" t="s">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>684</v>
+      </c>
+      <c r="B288" t="s">
         <v>399</v>
       </c>
-      <c r="C287" t="s">
+      <c r="C288" t="s">
         <v>77</v>
       </c>
-      <c r="E287" t="s">
+      <c r="E288" t="s">
         <v>391</v>
       </c>
-      <c r="F287" t="s">
+      <c r="F288" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A288" t="s">
-        <v>684</v>
-      </c>
-      <c r="B288" t="s">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>684</v>
+      </c>
+      <c r="B289" t="s">
         <v>19</v>
       </c>
-      <c r="C288" t="s">
+      <c r="C289" t="s">
         <v>10</v>
       </c>
-      <c r="D288">
-        <v>1</v>
-      </c>
-      <c r="E288" t="s">
+      <c r="D289">
+        <v>1</v>
+      </c>
+      <c r="E289" t="s">
         <v>20</v>
       </c>
-      <c r="F288" t="s">
+      <c r="F289" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A289" t="s">
-        <v>684</v>
-      </c>
-      <c r="B289" t="s">
-        <v>16</v>
-      </c>
-      <c r="C289" t="s">
-        <v>8</v>
-      </c>
-      <c r="D289">
-        <v>1</v>
-      </c>
-      <c r="E289" t="s">
-        <v>255</v>
-      </c>
-      <c r="F289" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>684</v>
       </c>
@@ -7966,7 +7972,10 @@
         <v>16</v>
       </c>
       <c r="C290" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D290">
+        <v>1</v>
       </c>
       <c r="E290" t="s">
         <v>255</v>
@@ -7975,7 +7984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>684</v>
       </c>
@@ -7983,39 +7992,36 @@
         <v>16</v>
       </c>
       <c r="C291" t="s">
+        <v>17</v>
+      </c>
+      <c r="E291" t="s">
+        <v>255</v>
+      </c>
+      <c r="F291" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>684</v>
+      </c>
+      <c r="B292" t="s">
+        <v>16</v>
+      </c>
+      <c r="C292" t="s">
         <v>22</v>
       </c>
-      <c r="D291">
-        <v>1</v>
-      </c>
-      <c r="E291" t="s">
+      <c r="D292">
+        <v>1</v>
+      </c>
+      <c r="E292" t="s">
         <v>20</v>
       </c>
-      <c r="F291" t="s">
+      <c r="F292" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A292" t="s">
-        <v>684</v>
-      </c>
-      <c r="B292" t="s">
-        <v>267</v>
-      </c>
-      <c r="C292" t="s">
-        <v>10</v>
-      </c>
-      <c r="D292">
-        <v>1</v>
-      </c>
-      <c r="E292" t="s">
-        <v>287</v>
-      </c>
-      <c r="F292" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>684</v>
       </c>
@@ -8023,16 +8029,19 @@
         <v>267</v>
       </c>
       <c r="C293" t="s">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="D293">
+        <v>1</v>
       </c>
       <c r="E293" t="s">
         <v>287</v>
       </c>
       <c r="F293" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>684</v>
       </c>
@@ -8040,16 +8049,16 @@
         <v>267</v>
       </c>
       <c r="C294" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E294" t="s">
         <v>287</v>
       </c>
       <c r="F294" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>684</v>
       </c>
@@ -8057,16 +8066,16 @@
         <v>267</v>
       </c>
       <c r="C295" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="E295" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F295" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>684</v>
       </c>
@@ -8074,19 +8083,16 @@
         <v>267</v>
       </c>
       <c r="C296" t="s">
-        <v>354</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="E296" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F296" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>684</v>
       </c>
@@ -8094,7 +8100,7 @@
         <v>267</v>
       </c>
       <c r="C297" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -8103,10 +8109,10 @@
         <v>291</v>
       </c>
       <c r="F297" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>684</v>
       </c>
@@ -8114,16 +8120,19 @@
         <v>267</v>
       </c>
       <c r="C298" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F298" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>684</v>
       </c>
@@ -8131,19 +8140,16 @@
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>299</v>
-      </c>
-      <c r="D299">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E299" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F299" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>684</v>
       </c>
@@ -8151,7 +8157,7 @@
         <v>267</v>
       </c>
       <c r="C300" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -8160,10 +8166,10 @@
         <v>301</v>
       </c>
       <c r="F300" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>684</v>
       </c>
@@ -8171,16 +8177,19 @@
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="D301">
+        <v>1</v>
       </c>
       <c r="E301" t="s">
         <v>301</v>
       </c>
       <c r="F301" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>684</v>
       </c>
@@ -8188,10 +8197,7 @@
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>307</v>
-      </c>
-      <c r="D302">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="E302" t="s">
         <v>301</v>
@@ -8200,7 +8206,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>684</v>
       </c>
@@ -8208,7 +8214,7 @@
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D303">
         <v>1</v>
@@ -8217,47 +8223,47 @@
         <v>301</v>
       </c>
       <c r="F303" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>684</v>
+      </c>
+      <c r="B304" t="s">
+        <v>267</v>
+      </c>
+      <c r="C304" t="s">
+        <v>306</v>
+      </c>
+      <c r="D304">
+        <v>1</v>
+      </c>
+      <c r="E304" t="s">
+        <v>301</v>
+      </c>
+      <c r="F304" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A304" t="s">
-        <v>684</v>
-      </c>
-      <c r="B304" t="s">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>684</v>
+      </c>
+      <c r="B305" t="s">
         <v>664</v>
       </c>
-      <c r="D304" t="s">
+      <c r="D305" t="s">
         <v>582</v>
       </c>
-      <c r="E304" t="s">
+      <c r="E305" t="s">
         <v>332</v>
       </c>
-      <c r="F304" t="s">
+      <c r="F305" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A305" t="s">
-        <v>684</v>
-      </c>
-      <c r="B305" t="s">
-        <v>270</v>
-      </c>
-      <c r="C305" t="s">
-        <v>271</v>
-      </c>
-      <c r="D305">
-        <v>1</v>
-      </c>
-      <c r="E305" t="s">
-        <v>287</v>
-      </c>
-      <c r="F305" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>684</v>
       </c>
@@ -8265,19 +8271,19 @@
         <v>270</v>
       </c>
       <c r="C306" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D306">
         <v>1</v>
       </c>
       <c r="E306" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F306" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>684</v>
       </c>
@@ -8285,19 +8291,19 @@
         <v>270</v>
       </c>
       <c r="C307" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="D307">
         <v>1</v>
       </c>
       <c r="E307" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F307" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>684</v>
       </c>
@@ -8305,19 +8311,19 @@
         <v>270</v>
       </c>
       <c r="C308" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D308">
         <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F308" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>684</v>
       </c>
@@ -8325,161 +8331,161 @@
         <v>270</v>
       </c>
       <c r="C309" t="s">
+        <v>336</v>
+      </c>
+      <c r="D309">
+        <v>1</v>
+      </c>
+      <c r="E309" t="s">
+        <v>337</v>
+      </c>
+      <c r="F309" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>684</v>
+      </c>
+      <c r="B310" t="s">
+        <v>270</v>
+      </c>
+      <c r="C310" t="s">
         <v>331</v>
       </c>
-      <c r="D309">
-        <v>1</v>
-      </c>
-      <c r="E309" t="s">
+      <c r="D310">
+        <v>1</v>
+      </c>
+      <c r="E310" t="s">
         <v>332</v>
       </c>
-      <c r="F309" t="s">
+      <c r="F310" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A310" t="s">
-        <v>684</v>
-      </c>
-      <c r="B310" t="s">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>684</v>
+      </c>
+      <c r="B311" t="s">
         <v>347</v>
       </c>
-      <c r="C310" t="s">
+      <c r="C311" t="s">
         <v>348</v>
       </c>
-      <c r="D310">
-        <v>1</v>
-      </c>
-      <c r="E310" t="s">
+      <c r="D311">
+        <v>1</v>
+      </c>
+      <c r="E311" t="s">
         <v>349</v>
       </c>
-      <c r="F310" t="s">
+      <c r="F311" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A311" t="s">
-        <v>684</v>
-      </c>
-      <c r="B311" t="s">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>684</v>
+      </c>
+      <c r="B312" t="s">
         <v>666</v>
-      </c>
-      <c r="D311" t="s">
-        <v>582</v>
-      </c>
-      <c r="E311" t="s">
-        <v>301</v>
-      </c>
-      <c r="F311" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A312" t="s">
-        <v>684</v>
-      </c>
-      <c r="B312" t="s">
-        <v>667</v>
       </c>
       <c r="D312" t="s">
         <v>582</v>
       </c>
       <c r="E312" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F312" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>684</v>
       </c>
       <c r="B313" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D313" t="s">
         <v>582</v>
       </c>
       <c r="E313" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="F313" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>684</v>
       </c>
       <c r="B314" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D314" t="s">
         <v>582</v>
       </c>
       <c r="E314" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="F314" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>684</v>
       </c>
       <c r="B315" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D315" t="s">
         <v>582</v>
       </c>
       <c r="E315" t="s">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="F315" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>684</v>
       </c>
       <c r="B316" t="s">
-        <v>236</v>
-      </c>
-      <c r="C316" t="s">
-        <v>237</v>
+        <v>673</v>
+      </c>
+      <c r="D316" t="s">
+        <v>582</v>
       </c>
       <c r="E316" t="s">
         <v>234</v>
       </c>
       <c r="F316" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>684</v>
+      </c>
+      <c r="B317" t="s">
+        <v>236</v>
+      </c>
+      <c r="C317" t="s">
+        <v>237</v>
+      </c>
+      <c r="E317" t="s">
+        <v>234</v>
+      </c>
+      <c r="F317" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A317" t="s">
-        <v>684</v>
-      </c>
-      <c r="B317" t="s">
-        <v>379</v>
-      </c>
-      <c r="C317" t="s">
-        <v>382</v>
-      </c>
-      <c r="D317">
-        <v>1</v>
-      </c>
-      <c r="E317" t="s">
-        <v>375</v>
-      </c>
-      <c r="F317" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>684</v>
       </c>
@@ -8487,7 +8493,7 @@
         <v>379</v>
       </c>
       <c r="C318" t="s">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -8496,10 +8502,10 @@
         <v>375</v>
       </c>
       <c r="F318" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>684</v>
       </c>
@@ -8507,7 +8513,7 @@
         <v>379</v>
       </c>
       <c r="C319" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
       <c r="D319">
         <v>1</v>
@@ -8516,10 +8522,10 @@
         <v>375</v>
       </c>
       <c r="F319" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>684</v>
       </c>
@@ -8527,36 +8533,36 @@
         <v>379</v>
       </c>
       <c r="C320" t="s">
-        <v>77</v>
+        <v>381</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
       </c>
       <c r="E320" t="s">
         <v>375</v>
       </c>
       <c r="F320" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>684</v>
       </c>
       <c r="B321" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C321" t="s">
-        <v>8</v>
-      </c>
-      <c r="D321">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E321" t="s">
         <v>375</v>
       </c>
       <c r="F321" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>684</v>
       </c>
@@ -8564,7 +8570,7 @@
         <v>373</v>
       </c>
       <c r="C322" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D322">
         <v>1</v>
@@ -8573,32 +8579,35 @@
         <v>375</v>
       </c>
       <c r="F322" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>684</v>
+      </c>
+      <c r="B323" t="s">
+        <v>373</v>
+      </c>
+      <c r="C323" t="s">
+        <v>35</v>
+      </c>
+      <c r="D323">
+        <v>1</v>
+      </c>
+      <c r="E323" t="s">
+        <v>375</v>
+      </c>
+      <c r="F323" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A323" t="s">
-        <v>684</v>
-      </c>
-      <c r="B323" t="s">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>684</v>
+      </c>
+      <c r="B324" t="s">
         <v>674</v>
-      </c>
-      <c r="D323" t="s">
-        <v>582</v>
-      </c>
-      <c r="E323" t="s">
-        <v>406</v>
-      </c>
-      <c r="F323" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A324" t="s">
-        <v>684</v>
-      </c>
-      <c r="B324" t="s">
-        <v>675</v>
       </c>
       <c r="D324" t="s">
         <v>582</v>
@@ -8607,47 +8616,44 @@
         <v>406</v>
       </c>
       <c r="F324" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>684</v>
+      </c>
+      <c r="B325" t="s">
+        <v>675</v>
+      </c>
+      <c r="D325" t="s">
+        <v>582</v>
+      </c>
+      <c r="E325" t="s">
+        <v>406</v>
+      </c>
+      <c r="F325" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A325" t="s">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
         <v>683</v>
       </c>
-      <c r="B325" t="s">
+      <c r="B326" t="s">
         <v>685</v>
       </c>
-      <c r="C325" t="s">
+      <c r="C326" t="s">
         <v>686</v>
       </c>
-      <c r="E325" t="s">
+      <c r="E326" t="s">
         <v>687</v>
       </c>
-      <c r="F325" t="s">
+      <c r="F326" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A326" t="s">
-        <v>684</v>
-      </c>
-      <c r="B326" t="s">
-        <v>148</v>
-      </c>
-      <c r="C326" t="s">
-        <v>10</v>
-      </c>
-      <c r="D326">
-        <v>1</v>
-      </c>
-      <c r="E326" t="s">
-        <v>420</v>
-      </c>
-      <c r="F326" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>684</v>
       </c>
@@ -8655,16 +8661,19 @@
         <v>148</v>
       </c>
       <c r="C327" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D327">
+        <v>1</v>
       </c>
       <c r="E327" t="s">
         <v>420</v>
       </c>
       <c r="F327" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>684</v>
       </c>
@@ -8672,16 +8681,16 @@
         <v>148</v>
       </c>
       <c r="C328" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E328" t="s">
         <v>420</v>
       </c>
       <c r="F328" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>684</v>
       </c>
@@ -8689,27 +8698,24 @@
         <v>148</v>
       </c>
       <c r="C329" t="s">
-        <v>199</v>
-      </c>
-      <c r="D329">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E329" t="s">
         <v>420</v>
       </c>
       <c r="F329" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>684</v>
       </c>
       <c r="B330" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C330" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D330">
         <v>1</v>
@@ -8718,10 +8724,10 @@
         <v>420</v>
       </c>
       <c r="F330" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>684</v>
       </c>
@@ -8729,7 +8735,7 @@
         <v>152</v>
       </c>
       <c r="C331" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -8741,24 +8747,27 @@
         <v>157</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>684</v>
       </c>
       <c r="B332" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C332" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="F332" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>684</v>
       </c>
@@ -8766,16 +8775,16 @@
         <v>201</v>
       </c>
       <c r="C333" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E333" t="s">
         <v>180</v>
       </c>
       <c r="F333" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>684</v>
       </c>
@@ -8783,36 +8792,36 @@
         <v>201</v>
       </c>
       <c r="C334" t="s">
+        <v>163</v>
+      </c>
+      <c r="E334" t="s">
+        <v>180</v>
+      </c>
+      <c r="F334" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>684</v>
+      </c>
+      <c r="B335" t="s">
+        <v>201</v>
+      </c>
+      <c r="C335" t="s">
         <v>518</v>
       </c>
-      <c r="D334">
-        <v>1</v>
-      </c>
-      <c r="E334" t="s">
+      <c r="D335">
+        <v>1</v>
+      </c>
+      <c r="E335" t="s">
         <v>520</v>
       </c>
-      <c r="F334" t="s">
+      <c r="F335" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A335" t="s">
-        <v>684</v>
-      </c>
-      <c r="B335" t="s">
-        <v>204</v>
-      </c>
-      <c r="C335" t="s">
-        <v>368</v>
-      </c>
-      <c r="E335" t="s">
-        <v>367</v>
-      </c>
-      <c r="F335" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>684</v>
       </c>
@@ -8820,16 +8829,16 @@
         <v>204</v>
       </c>
       <c r="C336" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="E336" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="F336" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>684</v>
       </c>
@@ -8837,7 +8846,7 @@
         <v>204</v>
       </c>
       <c r="C337" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E337" t="s">
         <v>178</v>
@@ -8846,44 +8855,41 @@
         <v>183</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>203</v>
-      </c>
-      <c r="D338" t="s">
-        <v>692</v>
+        <v>204</v>
+      </c>
+      <c r="C338" t="s">
+        <v>167</v>
       </c>
       <c r="E338" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F338" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>684</v>
       </c>
       <c r="B339" t="s">
         <v>203</v>
       </c>
-      <c r="C339" t="s">
-        <v>35</v>
-      </c>
-      <c r="D339">
-        <v>1</v>
+      <c r="D339" t="s">
+        <v>692</v>
       </c>
       <c r="E339" t="s">
         <v>709</v>
       </c>
       <c r="F339" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>684</v>
       </c>
@@ -8891,44 +8897,47 @@
         <v>203</v>
       </c>
       <c r="C340" t="s">
+        <v>35</v>
+      </c>
+      <c r="D340">
+        <v>1</v>
+      </c>
+      <c r="E340" t="s">
+        <v>709</v>
+      </c>
+      <c r="F340" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>684</v>
+      </c>
+      <c r="B341" t="s">
+        <v>203</v>
+      </c>
+      <c r="C341" t="s">
         <v>182</v>
       </c>
-      <c r="E340" t="s">
+      <c r="E341" t="s">
         <v>178</v>
       </c>
-      <c r="F340" t="s">
+      <c r="F341" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A341" t="s">
-        <v>684</v>
-      </c>
-      <c r="B341" t="s">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>684</v>
+      </c>
+      <c r="B342" t="s">
         <v>721</v>
       </c>
-      <c r="C341" t="s">
+      <c r="C342" t="s">
         <v>230</v>
       </c>
-      <c r="D341">
-        <v>1</v>
-      </c>
-      <c r="E341" t="s">
-        <v>709</v>
-      </c>
-      <c r="F341" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A342" t="s">
-        <v>684</v>
-      </c>
-      <c r="B342" t="s">
-        <v>723</v>
-      </c>
-      <c r="D342" t="s">
-        <v>692</v>
+      <c r="D342">
+        <v>1</v>
       </c>
       <c r="E342" t="s">
         <v>709</v>
@@ -8937,61 +8946,61 @@
         <v>710</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>684</v>
       </c>
       <c r="B343" t="s">
         <v>723</v>
       </c>
-      <c r="C343" t="s">
-        <v>35</v>
-      </c>
-      <c r="D343">
-        <v>1</v>
+      <c r="D343" t="s">
+        <v>692</v>
       </c>
       <c r="E343" t="s">
         <v>709</v>
       </c>
       <c r="F343" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>684</v>
+      </c>
+      <c r="B344" t="s">
+        <v>723</v>
+      </c>
+      <c r="C344" t="s">
+        <v>35</v>
+      </c>
+      <c r="D344">
+        <v>1</v>
+      </c>
+      <c r="E344" t="s">
+        <v>709</v>
+      </c>
+      <c r="F344" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A344" t="s">
-        <v>684</v>
-      </c>
-      <c r="B344" t="s">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>684</v>
+      </c>
+      <c r="B345" t="s">
         <v>200</v>
       </c>
-      <c r="C344" t="s">
+      <c r="C345" t="s">
         <v>104</v>
       </c>
-      <c r="E344" t="s">
+      <c r="E345" t="s">
         <v>180</v>
       </c>
-      <c r="F344" t="s">
+      <c r="F345" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A345" t="s">
-        <v>684</v>
-      </c>
-      <c r="B345" t="s">
-        <v>80</v>
-      </c>
-      <c r="C345" t="s">
-        <v>84</v>
-      </c>
-      <c r="E345" t="s">
-        <v>59</v>
-      </c>
-      <c r="F345" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>684</v>
       </c>
@@ -8999,7 +9008,7 @@
         <v>80</v>
       </c>
       <c r="C346" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E346" t="s">
         <v>59</v>
@@ -9008,78 +9017,78 @@
         <v>82</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>684</v>
       </c>
       <c r="B347" t="s">
+        <v>80</v>
+      </c>
+      <c r="C347" t="s">
+        <v>67</v>
+      </c>
+      <c r="E347" t="s">
+        <v>59</v>
+      </c>
+      <c r="F347" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>684</v>
+      </c>
+      <c r="B348" t="s">
         <v>335</v>
       </c>
-      <c r="C347" t="s">
+      <c r="C348" t="s">
         <v>334</v>
       </c>
-      <c r="D347">
-        <v>1</v>
-      </c>
-      <c r="E347" t="s">
+      <c r="D348">
+        <v>1</v>
+      </c>
+      <c r="E348" t="s">
         <v>332</v>
       </c>
-      <c r="F347" t="s">
+      <c r="F348" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A348" t="s">
-        <v>684</v>
-      </c>
-      <c r="B348" t="s">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>684</v>
+      </c>
+      <c r="B349" t="s">
         <v>677</v>
-      </c>
-      <c r="D348" t="s">
-        <v>582</v>
-      </c>
-      <c r="E348" t="s">
-        <v>475</v>
-      </c>
-      <c r="F348" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A349" t="s">
-        <v>684</v>
-      </c>
-      <c r="B349" t="s">
-        <v>678</v>
       </c>
       <c r="D349" t="s">
         <v>582</v>
       </c>
       <c r="E349" t="s">
+        <v>475</v>
+      </c>
+      <c r="F349" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>684</v>
+      </c>
+      <c r="B350" t="s">
+        <v>678</v>
+      </c>
+      <c r="D350" t="s">
+        <v>582</v>
+      </c>
+      <c r="E350" t="s">
         <v>420</v>
       </c>
-      <c r="F349" t="s">
+      <c r="F350" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A350" t="s">
-        <v>684</v>
-      </c>
-      <c r="B350" t="s">
-        <v>578</v>
-      </c>
-      <c r="C350" t="s">
-        <v>104</v>
-      </c>
-      <c r="E350" t="s">
-        <v>577</v>
-      </c>
-      <c r="F350" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>684</v>
       </c>
@@ -9087,50 +9096,50 @@
         <v>578</v>
       </c>
       <c r="C351" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E351" t="s">
         <v>577</v>
       </c>
       <c r="F351" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>684</v>
+      </c>
+      <c r="B352" t="s">
+        <v>578</v>
+      </c>
+      <c r="C352" t="s">
+        <v>78</v>
+      </c>
+      <c r="E352" t="s">
+        <v>577</v>
+      </c>
+      <c r="F352" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A352" t="s">
-        <v>684</v>
-      </c>
-      <c r="B352" t="s">
-        <v>184</v>
-      </c>
-      <c r="D352" t="s">
-        <v>692</v>
-      </c>
-      <c r="E352" t="s">
-        <v>186</v>
-      </c>
-      <c r="F352" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>684</v>
       </c>
       <c r="B353" t="s">
         <v>184</v>
       </c>
-      <c r="C353" t="s">
-        <v>153</v>
+      <c r="D353" t="s">
+        <v>692</v>
       </c>
       <c r="E353" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F353" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>684</v>
       </c>
@@ -9138,16 +9147,16 @@
         <v>184</v>
       </c>
       <c r="C354" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E354" t="s">
-        <v>515</v>
+        <v>154</v>
       </c>
       <c r="F354" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>684</v>
       </c>
@@ -9161,10 +9170,10 @@
         <v>515</v>
       </c>
       <c r="F355" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>684</v>
       </c>
@@ -9172,16 +9181,16 @@
         <v>184</v>
       </c>
       <c r="C356" t="s">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="E356" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F356" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>684</v>
       </c>
@@ -9189,19 +9198,16 @@
         <v>184</v>
       </c>
       <c r="C357" t="s">
-        <v>261</v>
-      </c>
-      <c r="D357">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E357" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F357" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>684</v>
       </c>
@@ -9209,16 +9215,19 @@
         <v>184</v>
       </c>
       <c r="C358" t="s">
-        <v>421</v>
+        <v>261</v>
+      </c>
+      <c r="D358">
+        <v>1</v>
       </c>
       <c r="E358" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="F358" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>684</v>
       </c>
@@ -9226,19 +9235,16 @@
         <v>184</v>
       </c>
       <c r="C359" t="s">
-        <v>734</v>
-      </c>
-      <c r="D359">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="E359" t="s">
-        <v>735</v>
+        <v>420</v>
       </c>
       <c r="F359" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>684</v>
       </c>
@@ -9246,19 +9252,19 @@
         <v>184</v>
       </c>
       <c r="C360" t="s">
-        <v>185</v>
+        <v>734</v>
       </c>
       <c r="D360">
         <v>1</v>
       </c>
       <c r="E360" t="s">
-        <v>186</v>
+        <v>735</v>
       </c>
       <c r="F360" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>684</v>
       </c>
@@ -9266,19 +9272,19 @@
         <v>184</v>
       </c>
       <c r="C361" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="D361">
         <v>1</v>
       </c>
       <c r="E361" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="F361" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>684</v>
       </c>
@@ -9295,10 +9301,10 @@
         <v>298</v>
       </c>
       <c r="F362" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>684</v>
       </c>
@@ -9306,19 +9312,19 @@
         <v>184</v>
       </c>
       <c r="C363" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="D363">
         <v>1</v>
       </c>
       <c r="E363" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F363" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>684</v>
       </c>
@@ -9326,7 +9332,7 @@
         <v>184</v>
       </c>
       <c r="C364" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D364">
         <v>1</v>
@@ -9335,30 +9341,30 @@
         <v>324</v>
       </c>
       <c r="F364" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>684</v>
+      </c>
+      <c r="B365" t="s">
+        <v>184</v>
+      </c>
+      <c r="C365" t="s">
+        <v>323</v>
+      </c>
+      <c r="D365">
+        <v>1</v>
+      </c>
+      <c r="E365" t="s">
+        <v>324</v>
+      </c>
+      <c r="F365" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A365" t="s">
-        <v>684</v>
-      </c>
-      <c r="B365" t="s">
-        <v>196</v>
-      </c>
-      <c r="C365" t="s">
-        <v>189</v>
-      </c>
-      <c r="D365">
-        <v>1</v>
-      </c>
-      <c r="E365" t="s">
-        <v>244</v>
-      </c>
-      <c r="F365" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>684</v>
       </c>
@@ -9366,7 +9372,7 @@
         <v>196</v>
       </c>
       <c r="C366" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D366">
         <v>1</v>
@@ -9375,44 +9381,47 @@
         <v>244</v>
       </c>
       <c r="F366" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>684</v>
+      </c>
+      <c r="B367" t="s">
+        <v>196</v>
+      </c>
+      <c r="C367" t="s">
+        <v>191</v>
+      </c>
+      <c r="D367">
+        <v>1</v>
+      </c>
+      <c r="E367" t="s">
+        <v>244</v>
+      </c>
+      <c r="F367" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A367" t="s">
-        <v>684</v>
-      </c>
-      <c r="B367" t="s">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>684</v>
+      </c>
+      <c r="B368" t="s">
         <v>476</v>
       </c>
-      <c r="C367" t="s">
+      <c r="C368" t="s">
         <v>477</v>
       </c>
-      <c r="E367" t="s">
+      <c r="E368" t="s">
         <v>538</v>
       </c>
-      <c r="F367" t="s">
+      <c r="F368" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A368" t="s">
-        <v>684</v>
-      </c>
-      <c r="B368" t="s">
-        <v>45</v>
-      </c>
-      <c r="C368" t="s">
-        <v>459</v>
-      </c>
-      <c r="E368" t="s">
-        <v>453</v>
-      </c>
-      <c r="F368" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>684</v>
       </c>
@@ -9420,16 +9429,16 @@
         <v>45</v>
       </c>
       <c r="C369" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="E369" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F369" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>684</v>
       </c>
@@ -9437,16 +9446,16 @@
         <v>45</v>
       </c>
       <c r="C370" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E370" t="s">
         <v>406</v>
       </c>
       <c r="F370" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>684</v>
       </c>
@@ -9454,16 +9463,16 @@
         <v>45</v>
       </c>
       <c r="C371" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E371" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F371" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>684</v>
       </c>
@@ -9471,16 +9480,16 @@
         <v>45</v>
       </c>
       <c r="C372" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="E372" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="F372" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>684</v>
       </c>
@@ -9494,10 +9503,10 @@
         <v>491</v>
       </c>
       <c r="F373" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>684</v>
       </c>
@@ -9505,16 +9514,16 @@
         <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="E374" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="F374" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>684</v>
       </c>
@@ -9522,16 +9531,16 @@
         <v>45</v>
       </c>
       <c r="C375" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="E375" t="s">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="F375" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>684</v>
       </c>
@@ -9545,10 +9554,10 @@
         <v>563</v>
       </c>
       <c r="F376" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>684</v>
       </c>
@@ -9556,19 +9565,16 @@
         <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>415</v>
-      </c>
-      <c r="D377">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="E377" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="F377" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>684</v>
       </c>
@@ -9576,16 +9582,19 @@
         <v>45</v>
       </c>
       <c r="C378" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="D378">
+        <v>1</v>
       </c>
       <c r="E378" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F378" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>684</v>
       </c>
@@ -9593,16 +9602,16 @@
         <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="E379" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="F379" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>684</v>
       </c>
@@ -9610,19 +9619,16 @@
         <v>45</v>
       </c>
       <c r="C380" t="s">
-        <v>264</v>
-      </c>
-      <c r="D380">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E380" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F380" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>684</v>
       </c>
@@ -9630,16 +9636,19 @@
         <v>45</v>
       </c>
       <c r="C381" t="s">
-        <v>372</v>
+        <v>264</v>
+      </c>
+      <c r="D381">
+        <v>1</v>
       </c>
       <c r="E381" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="F381" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>684</v>
       </c>
@@ -9647,19 +9656,16 @@
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>187</v>
-      </c>
-      <c r="D382">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="E382" t="s">
-        <v>188</v>
+        <v>369</v>
       </c>
       <c r="F382" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>684</v>
       </c>
@@ -9667,19 +9673,19 @@
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="D383">
         <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F383" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>684</v>
       </c>
@@ -9687,16 +9693,19 @@
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="D384">
+        <v>1</v>
       </c>
       <c r="E384" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="F384" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>684</v>
       </c>
@@ -9704,19 +9713,16 @@
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>52</v>
-      </c>
-      <c r="D385">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E385" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="F385" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>684</v>
       </c>
@@ -9724,7 +9730,7 @@
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D386">
         <v>1</v>
@@ -9733,10 +9739,10 @@
         <v>50</v>
       </c>
       <c r="F386" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>684</v>
       </c>
@@ -9744,50 +9750,53 @@
         <v>45</v>
       </c>
       <c r="C387" t="s">
+        <v>49</v>
+      </c>
+      <c r="D387">
+        <v>1</v>
+      </c>
+      <c r="E387" t="s">
+        <v>50</v>
+      </c>
+      <c r="F387" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>684</v>
+      </c>
+      <c r="B388" t="s">
+        <v>45</v>
+      </c>
+      <c r="C388" t="s">
         <v>125</v>
       </c>
-      <c r="E387" t="s">
+      <c r="E388" t="s">
         <v>126</v>
       </c>
-      <c r="F387" t="s">
+      <c r="F388" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A388" t="s">
-        <v>684</v>
-      </c>
-      <c r="B388" t="s">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>684</v>
+      </c>
+      <c r="B389" t="s">
         <v>202</v>
       </c>
-      <c r="C388" t="s">
+      <c r="C389" t="s">
         <v>167</v>
       </c>
-      <c r="E388" t="s">
+      <c r="E389" t="s">
         <v>255</v>
       </c>
-      <c r="F388" t="s">
+      <c r="F389" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A389" t="s">
-        <v>684</v>
-      </c>
-      <c r="B389" t="s">
-        <v>569</v>
-      </c>
-      <c r="C389" t="s">
-        <v>571</v>
-      </c>
-      <c r="E389" t="s">
-        <v>256</v>
-      </c>
-      <c r="F389" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>684</v>
       </c>
@@ -9801,10 +9810,10 @@
         <v>256</v>
       </c>
       <c r="F390" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>684</v>
       </c>
@@ -9812,67 +9821,67 @@
         <v>569</v>
       </c>
       <c r="C391" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E391" t="s">
         <v>256</v>
       </c>
       <c r="F391" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>684</v>
+      </c>
+      <c r="B392" t="s">
+        <v>569</v>
+      </c>
+      <c r="C392" t="s">
+        <v>570</v>
+      </c>
+      <c r="E392" t="s">
+        <v>256</v>
+      </c>
+      <c r="F392" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>684</v>
-      </c>
-      <c r="B392" t="s">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>684</v>
+      </c>
+      <c r="B393" t="s">
         <v>756</v>
-      </c>
-      <c r="D392" t="s">
-        <v>712</v>
-      </c>
-      <c r="E392" t="s">
-        <v>255</v>
-      </c>
-      <c r="F392" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>684</v>
-      </c>
-      <c r="B393" t="s">
-        <v>754</v>
       </c>
       <c r="D393" t="s">
         <v>712</v>
       </c>
       <c r="E393" t="s">
+        <v>255</v>
+      </c>
+      <c r="F393" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>684</v>
+      </c>
+      <c r="B394" t="s">
+        <v>754</v>
+      </c>
+      <c r="D394" t="s">
+        <v>712</v>
+      </c>
+      <c r="E394" t="s">
         <v>256</v>
       </c>
-      <c r="F393" t="s">
+      <c r="F394" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>684</v>
-      </c>
-      <c r="B394" t="s">
-        <v>48</v>
-      </c>
-      <c r="C394" t="s">
-        <v>171</v>
-      </c>
-      <c r="E394" t="s">
-        <v>255</v>
-      </c>
-      <c r="F394" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>684</v>
       </c>
@@ -9880,16 +9889,16 @@
         <v>48</v>
       </c>
       <c r="C395" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E395" t="s">
         <v>255</v>
       </c>
       <c r="F395" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>684</v>
       </c>
@@ -9897,16 +9906,16 @@
         <v>48</v>
       </c>
       <c r="C396" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E396" t="s">
         <v>255</v>
       </c>
       <c r="F396" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>684</v>
       </c>
@@ -9914,19 +9923,16 @@
         <v>48</v>
       </c>
       <c r="C397" t="s">
-        <v>55</v>
-      </c>
-      <c r="D397">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E397" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F397" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>684</v>
       </c>
@@ -9934,7 +9940,7 @@
         <v>48</v>
       </c>
       <c r="C398" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D398">
         <v>1</v>
@@ -9946,47 +9952,47 @@
         <v>53</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>684</v>
       </c>
       <c r="B399" t="s">
+        <v>48</v>
+      </c>
+      <c r="C399" t="s">
+        <v>57</v>
+      </c>
+      <c r="D399">
+        <v>1</v>
+      </c>
+      <c r="E399" t="s">
+        <v>50</v>
+      </c>
+      <c r="F399" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>684</v>
+      </c>
+      <c r="B400" t="s">
         <v>456</v>
       </c>
-      <c r="C399" t="s">
+      <c r="C400" t="s">
         <v>8</v>
       </c>
-      <c r="D399">
-        <v>1</v>
-      </c>
-      <c r="E399" t="s">
+      <c r="D400">
+        <v>1</v>
+      </c>
+      <c r="E400" t="s">
         <v>453</v>
       </c>
-      <c r="F399" t="s">
+      <c r="F400" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>684</v>
-      </c>
-      <c r="B400" t="s">
-        <v>108</v>
-      </c>
-      <c r="C400" t="s">
-        <v>114</v>
-      </c>
-      <c r="D400">
-        <v>1</v>
-      </c>
-      <c r="E400" t="s">
-        <v>115</v>
-      </c>
-      <c r="F400" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>684</v>
       </c>
@@ -9994,7 +10000,7 @@
         <v>108</v>
       </c>
       <c r="C401" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D401">
         <v>1</v>
@@ -10003,10 +10009,10 @@
         <v>115</v>
       </c>
       <c r="F401" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>684</v>
       </c>
@@ -10014,7 +10020,7 @@
         <v>108</v>
       </c>
       <c r="C402" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D402">
         <v>1</v>
@@ -10023,10 +10029,10 @@
         <v>115</v>
       </c>
       <c r="F402" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>684</v>
       </c>
@@ -10034,7 +10040,7 @@
         <v>108</v>
       </c>
       <c r="C403" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D403">
         <v>1</v>
@@ -10043,10 +10049,10 @@
         <v>115</v>
       </c>
       <c r="F403" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>684</v>
       </c>
@@ -10054,7 +10060,7 @@
         <v>108</v>
       </c>
       <c r="C404" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D404">
         <v>1</v>
@@ -10063,47 +10069,47 @@
         <v>115</v>
       </c>
       <c r="F404" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>684</v>
+      </c>
+      <c r="B405" t="s">
+        <v>108</v>
+      </c>
+      <c r="C405" t="s">
+        <v>120</v>
+      </c>
+      <c r="D405">
+        <v>1</v>
+      </c>
+      <c r="E405" t="s">
+        <v>115</v>
+      </c>
+      <c r="F405" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>684</v>
-      </c>
-      <c r="B405" t="s">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>684</v>
+      </c>
+      <c r="B406" t="s">
         <v>680</v>
       </c>
-      <c r="D405" t="s">
+      <c r="D406" t="s">
         <v>582</v>
       </c>
-      <c r="E405" t="s">
+      <c r="E406" t="s">
         <v>298</v>
       </c>
-      <c r="F405" t="s">
+      <c r="F406" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>684</v>
-      </c>
-      <c r="B406" t="s">
-        <v>197</v>
-      </c>
-      <c r="C406" t="s">
-        <v>189</v>
-      </c>
-      <c r="D406">
-        <v>1</v>
-      </c>
-      <c r="E406" t="s">
-        <v>244</v>
-      </c>
-      <c r="F406" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>684</v>
       </c>
@@ -10111,7 +10117,7 @@
         <v>197</v>
       </c>
       <c r="C407" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D407">
         <v>1</v>
@@ -10120,27 +10126,30 @@
         <v>244</v>
       </c>
       <c r="F407" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>684</v>
+      </c>
+      <c r="B408" t="s">
+        <v>197</v>
+      </c>
+      <c r="C408" t="s">
+        <v>191</v>
+      </c>
+      <c r="D408">
+        <v>1</v>
+      </c>
+      <c r="E408" t="s">
+        <v>244</v>
+      </c>
+      <c r="F408" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A408" t="s">
-        <v>684</v>
-      </c>
-      <c r="B408" t="s">
-        <v>566</v>
-      </c>
-      <c r="C408" t="s">
-        <v>567</v>
-      </c>
-      <c r="E408" t="s">
-        <v>563</v>
-      </c>
-      <c r="F408" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>684</v>
       </c>
@@ -10148,7 +10157,7 @@
         <v>566</v>
       </c>
       <c r="C409" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E409" t="s">
         <v>563</v>
@@ -10157,7 +10166,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>684</v>
       </c>
@@ -10165,7 +10174,7 @@
         <v>566</v>
       </c>
       <c r="C410" t="s">
-        <v>167</v>
+        <v>568</v>
       </c>
       <c r="E410" t="s">
         <v>563</v>
@@ -10174,20 +10183,37 @@
         <v>565</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>684</v>
       </c>
       <c r="B411" t="s">
+        <v>566</v>
+      </c>
+      <c r="C411" t="s">
+        <v>167</v>
+      </c>
+      <c r="E411" t="s">
+        <v>563</v>
+      </c>
+      <c r="F411" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>684</v>
+      </c>
+      <c r="B412" t="s">
         <v>403</v>
       </c>
-      <c r="C411" t="s">
+      <c r="C412" t="s">
         <v>104</v>
       </c>
-      <c r="E411" t="s">
+      <c r="E412" t="s">
         <v>400</v>
       </c>
-      <c r="F411" t="s">
+      <c r="F412" t="s">
         <v>401</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4588A2D3-9BDF-4951-90AB-2EF6A0297DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A252338-4B96-4942-9ECB-51A119DCE67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="772">
   <si>
     <t>Class</t>
   </si>
@@ -2341,6 +2341,9 @@
   </si>
   <si>
     <t>PivotValueFilter</t>
+  </si>
+  <si>
+    <t>DataValidationAlertStyle</t>
   </si>
 </sst>
 </file>
@@ -2448,10 +2451,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F416" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F416" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F416">
-    <sortCondition ref="B1:B416"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F417" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F417" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F417">
+    <sortCondition ref="B1:B417"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2782,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F416"/>
+  <dimension ref="A1:F417"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -5513,10 +5516,10 @@
         <v>684</v>
       </c>
       <c r="B154" t="s">
-        <v>745</v>
+        <v>771</v>
       </c>
       <c r="D154" t="s">
-        <v>712</v>
+        <v>582</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
@@ -5530,10 +5533,10 @@
         <v>684</v>
       </c>
       <c r="B155" t="s">
-        <v>639</v>
+        <v>745</v>
       </c>
       <c r="D155" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
@@ -5547,16 +5550,16 @@
         <v>684</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
-      </c>
-      <c r="C156" t="s">
-        <v>210</v>
+        <v>639</v>
+      </c>
+      <c r="D156" t="s">
+        <v>582</v>
       </c>
       <c r="E156" t="s">
         <v>208</v>
       </c>
       <c r="F156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5567,13 +5570,13 @@
         <v>243</v>
       </c>
       <c r="C157" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E157" t="s">
         <v>208</v>
       </c>
       <c r="F157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5581,16 +5584,16 @@
         <v>684</v>
       </c>
       <c r="B158" t="s">
-        <v>640</v>
-      </c>
-      <c r="D158" t="s">
-        <v>582</v>
+        <v>243</v>
+      </c>
+      <c r="C158" t="s">
+        <v>209</v>
       </c>
       <c r="E158" t="s">
-        <v>475</v>
+        <v>208</v>
       </c>
       <c r="F158" t="s">
-        <v>467</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,16 +5601,16 @@
         <v>684</v>
       </c>
       <c r="B159" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D159" t="s">
         <v>582</v>
       </c>
       <c r="E159" t="s">
-        <v>256</v>
+        <v>475</v>
       </c>
       <c r="F159" t="s">
-        <v>572</v>
+        <v>467</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5615,16 +5618,16 @@
         <v>684</v>
       </c>
       <c r="B160" t="s">
-        <v>452</v>
-      </c>
-      <c r="C160" t="s">
-        <v>92</v>
+        <v>641</v>
+      </c>
+      <c r="D160" t="s">
+        <v>582</v>
       </c>
       <c r="E160" t="s">
-        <v>453</v>
+        <v>256</v>
       </c>
       <c r="F160" t="s">
-        <v>454</v>
+        <v>572</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5632,16 +5635,16 @@
         <v>684</v>
       </c>
       <c r="B161" t="s">
-        <v>726</v>
+        <v>452</v>
       </c>
       <c r="C161" t="s">
-        <v>576</v>
+        <v>92</v>
       </c>
       <c r="E161" t="s">
-        <v>724</v>
+        <v>453</v>
       </c>
       <c r="F161" t="s">
-        <v>725</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5652,13 +5655,13 @@
         <v>726</v>
       </c>
       <c r="C162" t="s">
-        <v>78</v>
+        <v>576</v>
       </c>
       <c r="E162" t="s">
         <v>724</v>
       </c>
       <c r="F162" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5666,16 +5669,16 @@
         <v>684</v>
       </c>
       <c r="B163" t="s">
-        <v>642</v>
-      </c>
-      <c r="D163" t="s">
-        <v>582</v>
+        <v>726</v>
+      </c>
+      <c r="C163" t="s">
+        <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="F163" t="s">
-        <v>643</v>
+        <v>727</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5683,16 +5686,16 @@
         <v>684</v>
       </c>
       <c r="B164" t="s">
-        <v>750</v>
+        <v>642</v>
       </c>
       <c r="D164" t="s">
-        <v>712</v>
+        <v>582</v>
       </c>
       <c r="E164" t="s">
-        <v>752</v>
+        <v>644</v>
       </c>
       <c r="F164" t="s">
-        <v>748</v>
+        <v>643</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5700,16 +5703,16 @@
         <v>684</v>
       </c>
       <c r="B165" t="s">
-        <v>689</v>
+        <v>750</v>
       </c>
       <c r="D165" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E165" t="s">
-        <v>690</v>
+        <v>752</v>
       </c>
       <c r="F165" t="s">
-        <v>691</v>
+        <v>748</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5717,16 +5720,16 @@
         <v>684</v>
       </c>
       <c r="B166" t="s">
-        <v>747</v>
+        <v>689</v>
       </c>
       <c r="D166" t="s">
-        <v>78</v>
+        <v>582</v>
       </c>
       <c r="E166" t="s">
-        <v>752</v>
+        <v>690</v>
       </c>
       <c r="F166" t="s">
-        <v>748</v>
+        <v>691</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5734,10 +5737,10 @@
         <v>684</v>
       </c>
       <c r="B167" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D167" t="s">
-        <v>712</v>
+        <v>78</v>
       </c>
       <c r="E167" t="s">
         <v>752</v>
@@ -5751,16 +5754,16 @@
         <v>684</v>
       </c>
       <c r="B168" t="s">
-        <v>589</v>
+        <v>749</v>
       </c>
       <c r="D168" t="s">
-        <v>78</v>
+        <v>712</v>
       </c>
       <c r="E168" t="s">
-        <v>590</v>
+        <v>752</v>
       </c>
       <c r="F168" t="s">
-        <v>591</v>
+        <v>748</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5768,10 +5771,10 @@
         <v>684</v>
       </c>
       <c r="B169" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D169" t="s">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="E169" t="s">
         <v>590</v>
@@ -5785,16 +5788,16 @@
         <v>684</v>
       </c>
       <c r="B170" t="s">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="D170" t="s">
         <v>582</v>
       </c>
       <c r="E170" t="s">
-        <v>391</v>
+        <v>590</v>
       </c>
       <c r="F170" t="s">
-        <v>392</v>
+        <v>591</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5802,16 +5805,16 @@
         <v>684</v>
       </c>
       <c r="B171" t="s">
-        <v>557</v>
-      </c>
-      <c r="C171" t="s">
-        <v>558</v>
+        <v>645</v>
+      </c>
+      <c r="D171" t="s">
+        <v>582</v>
       </c>
       <c r="E171" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="F171" t="s">
-        <v>559</v>
+        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5819,16 +5822,16 @@
         <v>684</v>
       </c>
       <c r="B172" t="s">
-        <v>646</v>
-      </c>
-      <c r="D172" t="s">
-        <v>582</v>
+        <v>557</v>
+      </c>
+      <c r="C172" t="s">
+        <v>558</v>
       </c>
       <c r="E172" t="s">
-        <v>475</v>
+        <v>369</v>
       </c>
       <c r="F172" t="s">
-        <v>467</v>
+        <v>559</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5836,16 +5839,16 @@
         <v>684</v>
       </c>
       <c r="B173" t="s">
-        <v>768</v>
+        <v>646</v>
       </c>
       <c r="D173" t="s">
         <v>582</v>
       </c>
       <c r="E173" t="s">
-        <v>644</v>
+        <v>475</v>
       </c>
       <c r="F173" t="s">
-        <v>643</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,16 +5856,16 @@
         <v>684</v>
       </c>
       <c r="B174" t="s">
-        <v>694</v>
+        <v>768</v>
       </c>
       <c r="D174" t="s">
-        <v>692</v>
+        <v>582</v>
       </c>
       <c r="E174" t="s">
-        <v>697</v>
+        <v>644</v>
       </c>
       <c r="F174" t="s">
-        <v>699</v>
+        <v>643</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5872,11 +5875,8 @@
       <c r="B175" t="s">
         <v>694</v>
       </c>
-      <c r="C175" t="s">
-        <v>696</v>
-      </c>
-      <c r="D175">
-        <v>1</v>
+      <c r="D175" t="s">
+        <v>692</v>
       </c>
       <c r="E175" t="s">
         <v>697</v>
@@ -5893,7 +5893,7 @@
         <v>694</v>
       </c>
       <c r="C176" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>697</v>
       </c>
       <c r="F176" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5910,16 +5910,19 @@
         <v>684</v>
       </c>
       <c r="B177" t="s">
-        <v>647</v>
-      </c>
-      <c r="D177" t="s">
-        <v>582</v>
+        <v>694</v>
+      </c>
+      <c r="C177" t="s">
+        <v>695</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>287</v>
+        <v>697</v>
       </c>
       <c r="F177" t="s">
-        <v>328</v>
+        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5927,16 +5930,16 @@
         <v>684</v>
       </c>
       <c r="B178" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D178" t="s">
         <v>582</v>
       </c>
       <c r="E178" t="s">
-        <v>414</v>
+        <v>287</v>
       </c>
       <c r="F178" t="s">
-        <v>413</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,16 +5947,16 @@
         <v>684</v>
       </c>
       <c r="B179" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D179" t="s">
         <v>582</v>
       </c>
       <c r="E179" t="s">
-        <v>537</v>
+        <v>414</v>
       </c>
       <c r="F179" t="s">
-        <v>522</v>
+        <v>413</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5961,16 +5964,16 @@
         <v>684</v>
       </c>
       <c r="B180" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
       <c r="D180" t="s">
         <v>582</v>
       </c>
       <c r="E180" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="F180" t="s">
-        <v>75</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5978,10 +5981,10 @@
         <v>684</v>
       </c>
       <c r="B181" t="s">
-        <v>72</v>
-      </c>
-      <c r="C181" t="s">
-        <v>63</v>
+        <v>681</v>
+      </c>
+      <c r="D181" t="s">
+        <v>582</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -5998,7 +6001,7 @@
         <v>72</v>
       </c>
       <c r="C182" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E182" t="s">
         <v>59</v>
@@ -6012,16 +6015,16 @@
         <v>684</v>
       </c>
       <c r="B183" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="C183" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E183" t="s">
-        <v>291</v>
+        <v>59</v>
       </c>
       <c r="F183" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6029,16 +6032,16 @@
         <v>684</v>
       </c>
       <c r="B184" t="s">
-        <v>650</v>
-      </c>
-      <c r="D184" t="s">
-        <v>582</v>
+        <v>295</v>
+      </c>
+      <c r="C184" t="s">
+        <v>84</v>
       </c>
       <c r="E184" t="s">
-        <v>651</v>
+        <v>291</v>
       </c>
       <c r="F184" t="s">
-        <v>652</v>
+        <v>294</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6046,16 +6049,16 @@
         <v>684</v>
       </c>
       <c r="B185" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D185" t="s">
         <v>582</v>
       </c>
       <c r="E185" t="s">
-        <v>526</v>
+        <v>651</v>
       </c>
       <c r="F185" t="s">
-        <v>527</v>
+        <v>652</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6063,16 +6066,16 @@
         <v>684</v>
       </c>
       <c r="B186" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D186" t="s">
         <v>582</v>
       </c>
       <c r="E186" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="F186" t="s">
-        <v>468</v>
+        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6080,19 +6083,16 @@
         <v>684</v>
       </c>
       <c r="B187" t="s">
-        <v>342</v>
-      </c>
-      <c r="C187" t="s">
-        <v>343</v>
-      </c>
-      <c r="D187">
-        <v>1</v>
+        <v>654</v>
+      </c>
+      <c r="D187" t="s">
+        <v>582</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>475</v>
       </c>
       <c r="F187" t="s">
-        <v>340</v>
+        <v>468</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6103,7 +6103,7 @@
         <v>342</v>
       </c>
       <c r="C188" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         <v>342</v>
       </c>
       <c r="C189" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6132,7 +6132,7 @@
         <v>337</v>
       </c>
       <c r="F189" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6143,7 +6143,7 @@
         <v>342</v>
       </c>
       <c r="C190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -6160,16 +6160,19 @@
         <v>684</v>
       </c>
       <c r="B191" t="s">
-        <v>9</v>
-      </c>
-      <c r="D191" t="s">
-        <v>692</v>
+        <v>342</v>
+      </c>
+      <c r="C191" t="s">
+        <v>346</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="F191" t="s">
-        <v>693</v>
+        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6179,17 +6182,14 @@
       <c r="B192" t="s">
         <v>9</v>
       </c>
-      <c r="C192" t="s">
-        <v>10</v>
-      </c>
-      <c r="D192">
-        <v>1</v>
+      <c r="D192" t="s">
+        <v>692</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>12</v>
+        <v>693</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,13 +6200,16 @@
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6214,19 +6217,16 @@
         <v>684</v>
       </c>
       <c r="B194" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
-        <v>8</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E194" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F194" t="s">
-        <v>254</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6234,16 +6234,19 @@
         <v>684</v>
       </c>
       <c r="B195" t="s">
-        <v>700</v>
-      </c>
-      <c r="D195" t="s">
-        <v>692</v>
+        <v>7</v>
+      </c>
+      <c r="C195" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>702</v>
+        <v>11</v>
       </c>
       <c r="F195" t="s">
-        <v>706</v>
+        <v>254</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6253,14 +6256,14 @@
       <c r="B196" t="s">
         <v>700</v>
       </c>
-      <c r="C196" t="s">
-        <v>361</v>
+      <c r="D196" t="s">
+        <v>692</v>
       </c>
       <c r="E196" t="s">
         <v>702</v>
       </c>
       <c r="F196" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6271,13 +6274,13 @@
         <v>700</v>
       </c>
       <c r="C197" t="s">
-        <v>714</v>
+        <v>361</v>
       </c>
       <c r="E197" t="s">
         <v>702</v>
       </c>
       <c r="F197" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,13 +6291,13 @@
         <v>700</v>
       </c>
       <c r="C198" t="s">
-        <v>546</v>
+        <v>714</v>
       </c>
       <c r="E198" t="s">
         <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6305,13 +6308,13 @@
         <v>700</v>
       </c>
       <c r="C199" t="s">
-        <v>715</v>
+        <v>546</v>
       </c>
       <c r="E199" t="s">
         <v>702</v>
       </c>
       <c r="F199" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6322,16 +6325,13 @@
         <v>700</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
-      </c>
-      <c r="D200">
-        <v>1</v>
+        <v>715</v>
       </c>
       <c r="E200" t="s">
         <v>702</v>
       </c>
       <c r="F200" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6339,16 +6339,19 @@
         <v>684</v>
       </c>
       <c r="B201" t="s">
-        <v>701</v>
-      </c>
-      <c r="D201" t="s">
-        <v>692</v>
+        <v>700</v>
+      </c>
+      <c r="C201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
       </c>
       <c r="E201" t="s">
         <v>702</v>
       </c>
       <c r="F201" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6358,11 +6361,8 @@
       <c r="B202" t="s">
         <v>701</v>
       </c>
-      <c r="C202" t="s">
-        <v>8</v>
-      </c>
-      <c r="D202">
-        <v>1</v>
+      <c r="D202" t="s">
+        <v>692</v>
       </c>
       <c r="E202" t="s">
         <v>702</v>
@@ -6379,7 +6379,7 @@
         <v>701</v>
       </c>
       <c r="C203" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -6388,7 +6388,7 @@
         <v>702</v>
       </c>
       <c r="F203" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6399,7 +6399,7 @@
         <v>701</v>
       </c>
       <c r="C204" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -6408,7 +6408,7 @@
         <v>702</v>
       </c>
       <c r="F204" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6416,16 +6416,19 @@
         <v>684</v>
       </c>
       <c r="B205" t="s">
-        <v>441</v>
+        <v>701</v>
       </c>
       <c r="C205" t="s">
-        <v>442</v>
+        <v>96</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>436</v>
+        <v>702</v>
       </c>
       <c r="F205" t="s">
-        <v>437</v>
+        <v>705</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,13 +6439,13 @@
         <v>441</v>
       </c>
       <c r="C206" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E206" t="s">
         <v>436</v>
       </c>
       <c r="F206" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6450,19 +6453,16 @@
         <v>684</v>
       </c>
       <c r="B207" t="s">
-        <v>308</v>
+        <v>441</v>
       </c>
       <c r="C207" t="s">
-        <v>8</v>
-      </c>
-      <c r="D207">
-        <v>1</v>
+        <v>438</v>
       </c>
       <c r="E207" t="s">
-        <v>309</v>
+        <v>436</v>
       </c>
       <c r="F207" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,16 +6470,19 @@
         <v>684</v>
       </c>
       <c r="B208" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C208" t="s">
-        <v>311</v>
+        <v>8</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
       </c>
       <c r="E208" t="s">
         <v>309</v>
       </c>
       <c r="F208" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6490,7 +6493,7 @@
         <v>313</v>
       </c>
       <c r="C209" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E209" t="s">
         <v>309</v>
@@ -6507,13 +6510,13 @@
         <v>313</v>
       </c>
       <c r="C210" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E210" t="s">
         <v>309</v>
       </c>
       <c r="F210" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6524,16 +6527,13 @@
         <v>313</v>
       </c>
       <c r="C211" t="s">
-        <v>317</v>
-      </c>
-      <c r="D211">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="E211" t="s">
         <v>309</v>
       </c>
       <c r="F211" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6544,7 +6544,7 @@
         <v>313</v>
       </c>
       <c r="C212" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -6553,7 +6553,7 @@
         <v>309</v>
       </c>
       <c r="F212" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,13 +6564,16 @@
         <v>313</v>
       </c>
       <c r="C213" t="s">
-        <v>388</v>
+        <v>315</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
       </c>
       <c r="E213" t="s">
         <v>309</v>
       </c>
       <c r="F213" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6578,16 +6581,16 @@
         <v>684</v>
       </c>
       <c r="B214" t="s">
-        <v>655</v>
-      </c>
-      <c r="D214" t="s">
-        <v>582</v>
+        <v>313</v>
+      </c>
+      <c r="C214" t="s">
+        <v>388</v>
       </c>
       <c r="E214" t="s">
         <v>309</v>
       </c>
       <c r="F214" t="s">
-        <v>329</v>
+        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,16 +6598,16 @@
         <v>684</v>
       </c>
       <c r="B215" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D215" t="s">
         <v>582</v>
       </c>
       <c r="E215" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="F215" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6612,19 +6615,16 @@
         <v>684</v>
       </c>
       <c r="B216" t="s">
-        <v>472</v>
-      </c>
-      <c r="C216" t="s">
-        <v>471</v>
-      </c>
-      <c r="D216">
-        <v>1</v>
+        <v>656</v>
+      </c>
+      <c r="D216" t="s">
+        <v>582</v>
       </c>
       <c r="E216" t="s">
-        <v>475</v>
+        <v>291</v>
       </c>
       <c r="F216" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6632,16 +6632,19 @@
         <v>684</v>
       </c>
       <c r="B217" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C217" t="s">
-        <v>467</v>
+        <v>471</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
       </c>
       <c r="E217" t="s">
         <v>475</v>
       </c>
       <c r="F217" t="s">
-        <v>467</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6652,13 +6655,13 @@
         <v>466</v>
       </c>
       <c r="C218" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E218" t="s">
         <v>475</v>
       </c>
       <c r="F218" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6669,13 +6672,13 @@
         <v>466</v>
       </c>
       <c r="C219" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E219" t="s">
         <v>475</v>
       </c>
       <c r="F219" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6686,13 +6689,13 @@
         <v>466</v>
       </c>
       <c r="C220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E220" t="s">
         <v>475</v>
       </c>
       <c r="F220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6700,10 +6703,10 @@
         <v>684</v>
       </c>
       <c r="B221" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C221" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E221" t="s">
         <v>475</v>
@@ -6717,16 +6720,16 @@
         <v>684</v>
       </c>
       <c r="B222" t="s">
-        <v>769</v>
-      </c>
-      <c r="D222" t="s">
-        <v>712</v>
+        <v>473</v>
+      </c>
+      <c r="C222" t="s">
+        <v>474</v>
       </c>
       <c r="E222" t="s">
         <v>475</v>
       </c>
       <c r="F222" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,19 +6737,16 @@
         <v>684</v>
       </c>
       <c r="B223" t="s">
-        <v>229</v>
-      </c>
-      <c r="C223" t="s">
-        <v>230</v>
-      </c>
-      <c r="D223">
-        <v>1</v>
+        <v>769</v>
+      </c>
+      <c r="D223" t="s">
+        <v>712</v>
       </c>
       <c r="E223" t="s">
-        <v>233</v>
+        <v>475</v>
       </c>
       <c r="F223" t="s">
-        <v>231</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6757,16 @@
         <v>229</v>
       </c>
       <c r="C224" t="s">
-        <v>494</v>
+        <v>230</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="F224" t="s">
-        <v>496</v>
+        <v>231</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6774,16 +6777,13 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>497</v>
-      </c>
-      <c r="D225">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="E225" t="s">
         <v>495</v>
       </c>
       <c r="F225" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6794,13 +6794,16 @@
         <v>229</v>
       </c>
       <c r="C226" t="s">
-        <v>499</v>
+        <v>497</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
       </c>
       <c r="E226" t="s">
         <v>495</v>
       </c>
       <c r="F226" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6811,13 +6814,13 @@
         <v>229</v>
       </c>
       <c r="C227" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E227" t="s">
         <v>495</v>
       </c>
       <c r="F227" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6828,13 +6831,13 @@
         <v>229</v>
       </c>
       <c r="C228" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E228" t="s">
         <v>495</v>
       </c>
       <c r="F228" t="s">
-        <v>226</v>
+        <v>502</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6845,13 +6848,13 @@
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E229" t="s">
         <v>495</v>
       </c>
       <c r="F229" t="s">
-        <v>505</v>
+        <v>226</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,16 +6865,13 @@
         <v>229</v>
       </c>
       <c r="C230" t="s">
-        <v>506</v>
-      </c>
-      <c r="D230">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="E230" t="s">
         <v>495</v>
       </c>
       <c r="F230" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,13 +6882,16 @@
         <v>229</v>
       </c>
       <c r="C231" t="s">
-        <v>508</v>
+        <v>506</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
       </c>
       <c r="E231" t="s">
         <v>495</v>
       </c>
       <c r="F231" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6899,13 +6902,13 @@
         <v>229</v>
       </c>
       <c r="C232" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E232" t="s">
         <v>495</v>
       </c>
       <c r="F232" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,13 +6919,13 @@
         <v>229</v>
       </c>
       <c r="C233" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E233" t="s">
         <v>495</v>
       </c>
       <c r="F233" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6930,16 +6933,16 @@
         <v>684</v>
       </c>
       <c r="B234" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C234" t="s">
-        <v>219</v>
+        <v>512</v>
       </c>
       <c r="E234" t="s">
-        <v>214</v>
+        <v>495</v>
       </c>
       <c r="F234" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6950,13 +6953,13 @@
         <v>216</v>
       </c>
       <c r="C235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E235" t="s">
         <v>214</v>
       </c>
       <c r="F235" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6967,16 +6970,13 @@
         <v>216</v>
       </c>
       <c r="C236" t="s">
-        <v>10</v>
-      </c>
-      <c r="D236">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="E236" t="s">
         <v>214</v>
       </c>
       <c r="F236" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -6987,13 +6987,16 @@
         <v>216</v>
       </c>
       <c r="C237" t="s">
-        <v>225</v>
+        <v>10</v>
+      </c>
+      <c r="D237">
+        <v>1</v>
       </c>
       <c r="E237" t="s">
         <v>214</v>
       </c>
       <c r="F237" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7004,16 +7007,13 @@
         <v>216</v>
       </c>
       <c r="C238" t="s">
-        <v>594</v>
-      </c>
-      <c r="D238">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="E238" t="s">
-        <v>595</v>
+        <v>214</v>
       </c>
       <c r="F238" t="s">
-        <v>596</v>
+        <v>226</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7024,7 +7024,7 @@
         <v>216</v>
       </c>
       <c r="C239" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -7044,13 +7044,16 @@
         <v>216</v>
       </c>
       <c r="C240" t="s">
-        <v>227</v>
+        <v>597</v>
+      </c>
+      <c r="D240">
+        <v>1</v>
       </c>
       <c r="E240" t="s">
-        <v>233</v>
+        <v>595</v>
       </c>
       <c r="F240" t="s">
-        <v>228</v>
+        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7061,16 +7064,13 @@
         <v>216</v>
       </c>
       <c r="C241" t="s">
-        <v>602</v>
-      </c>
-      <c r="D241">
-        <v>1</v>
+        <v>227</v>
       </c>
       <c r="E241" t="s">
-        <v>603</v>
+        <v>233</v>
       </c>
       <c r="F241" t="s">
-        <v>604</v>
+        <v>228</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7078,19 +7078,19 @@
         <v>684</v>
       </c>
       <c r="B242" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C242" t="s">
-        <v>8</v>
+        <v>602</v>
       </c>
       <c r="D242">
         <v>1</v>
       </c>
       <c r="E242" t="s">
-        <v>214</v>
+        <v>603</v>
       </c>
       <c r="F242" t="s">
-        <v>215</v>
+        <v>604</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7101,16 +7101,16 @@
         <v>213</v>
       </c>
       <c r="C243" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D243">
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>603</v>
+        <v>214</v>
       </c>
       <c r="F243" t="s">
-        <v>604</v>
+        <v>215</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7118,16 +7118,19 @@
         <v>684</v>
       </c>
       <c r="B244" t="s">
-        <v>770</v>
-      </c>
-      <c r="D244" t="s">
-        <v>712</v>
+        <v>213</v>
+      </c>
+      <c r="C244" t="s">
+        <v>35</v>
+      </c>
+      <c r="D244">
+        <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>475</v>
+        <v>603</v>
       </c>
       <c r="F244" t="s">
-        <v>470</v>
+        <v>604</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,16 +7138,16 @@
         <v>684</v>
       </c>
       <c r="B245" t="s">
-        <v>62</v>
-      </c>
-      <c r="C245" t="s">
-        <v>67</v>
+        <v>770</v>
+      </c>
+      <c r="D245" t="s">
+        <v>712</v>
       </c>
       <c r="E245" t="s">
-        <v>59</v>
+        <v>475</v>
       </c>
       <c r="F245" t="s">
-        <v>66</v>
+        <v>470</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7152,19 +7155,16 @@
         <v>684</v>
       </c>
       <c r="B246" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C246" t="s">
-        <v>716</v>
-      </c>
-      <c r="D246">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E246" t="s">
-        <v>709</v>
+        <v>59</v>
       </c>
       <c r="F246" t="s">
-        <v>717</v>
+        <v>66</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7175,13 +7175,16 @@
         <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>713</v>
+        <v>716</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
       </c>
       <c r="E247" t="s">
         <v>709</v>
       </c>
       <c r="F247" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,13 +7195,13 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E248" t="s">
         <v>709</v>
       </c>
       <c r="F248" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7209,13 +7212,13 @@
         <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>575</v>
+        <v>718</v>
       </c>
       <c r="E249" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F249" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7226,16 +7229,13 @@
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>513</v>
-      </c>
-      <c r="D250">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="E250" t="s">
-        <v>514</v>
+        <v>724</v>
       </c>
       <c r="F250" t="s">
-        <v>513</v>
+        <v>727</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7246,13 +7246,16 @@
         <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>405</v>
+        <v>513</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
       <c r="F251" t="s">
-        <v>407</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7263,16 +7266,13 @@
         <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>521</v>
-      </c>
-      <c r="D252">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="E252" t="s">
-        <v>537</v>
+        <v>406</v>
       </c>
       <c r="F252" t="s">
-        <v>523</v>
+        <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7283,7 +7283,7 @@
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -7292,7 +7292,7 @@
         <v>537</v>
       </c>
       <c r="F253" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7303,16 +7303,16 @@
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>351</v>
+        <v>524</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>414</v>
+        <v>537</v>
       </c>
       <c r="F254" t="s">
-        <v>413</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7323,7 +7323,7 @@
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -7332,7 +7332,7 @@
         <v>414</v>
       </c>
       <c r="F255" t="s">
-        <v>348</v>
+        <v>413</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7343,16 +7343,16 @@
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="F256" t="s">
-        <v>448</v>
+        <v>348</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7363,16 +7363,16 @@
         <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D257">
         <v>1</v>
       </c>
       <c r="E257" t="s">
-        <v>538</v>
+        <v>444</v>
       </c>
       <c r="F257" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7383,7 +7383,7 @@
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -7392,7 +7392,7 @@
         <v>538</v>
       </c>
       <c r="F258" t="s">
-        <v>540</v>
+        <v>465</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7403,16 +7403,16 @@
         <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>265</v>
+        <v>539</v>
       </c>
       <c r="D259">
         <v>1</v>
       </c>
       <c r="E259" t="s">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="F259" t="s">
-        <v>266</v>
+        <v>540</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7423,16 +7423,16 @@
         <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="D260">
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>418</v>
+        <v>286</v>
       </c>
       <c r="F260" t="s">
-        <v>417</v>
+        <v>266</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7443,16 +7443,16 @@
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="F261" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7463,7 +7463,7 @@
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -7472,7 +7472,7 @@
         <v>391</v>
       </c>
       <c r="F262" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7483,16 +7483,16 @@
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="D263">
         <v>1</v>
       </c>
       <c r="E263" t="s">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="F263" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7503,7 +7503,7 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>433</v>
+        <v>275</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -7512,7 +7512,7 @@
         <v>288</v>
       </c>
       <c r="F264" t="s">
-        <v>434</v>
+        <v>276</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7523,16 +7523,16 @@
         <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
       <c r="D265">
         <v>1</v>
       </c>
       <c r="E265" t="s">
-        <v>587</v>
+        <v>288</v>
       </c>
       <c r="F265" t="s">
-        <v>588</v>
+        <v>434</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7543,16 +7543,16 @@
         <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="D266">
         <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>450</v>
+        <v>587</v>
       </c>
       <c r="F266" t="s">
-        <v>449</v>
+        <v>588</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,16 +7563,16 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="D267">
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="F267" t="s">
-        <v>278</v>
+        <v>449</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7583,7 +7583,7 @@
         <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -7592,7 +7592,7 @@
         <v>289</v>
       </c>
       <c r="F268" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7603,16 +7603,16 @@
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>528</v>
+        <v>279</v>
       </c>
       <c r="D269">
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>526</v>
+        <v>289</v>
       </c>
       <c r="F269" t="s">
-        <v>529</v>
+        <v>280</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7623,7 +7623,7 @@
         <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -7632,7 +7632,7 @@
         <v>526</v>
       </c>
       <c r="F270" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7643,13 +7643,16 @@
         <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="F271" t="s">
-        <v>103</v>
+        <v>527</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,16 +7663,13 @@
         <v>23</v>
       </c>
       <c r="C272" t="s">
-        <v>26</v>
-      </c>
-      <c r="D272">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E272" t="s">
-        <v>245</v>
+        <v>102</v>
       </c>
       <c r="F272" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
         <v>23</v>
       </c>
       <c r="C273" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -7700,16 +7700,16 @@
         <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="D274">
         <v>1</v>
       </c>
       <c r="E274" t="s">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="F274" t="s">
-        <v>319</v>
+        <v>27</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7720,13 +7720,16 @@
         <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>77</v>
+        <v>321</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="F275" t="s">
-        <v>156</v>
+        <v>319</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,16 +7740,13 @@
         <v>23</v>
       </c>
       <c r="C276" t="s">
-        <v>24</v>
-      </c>
-      <c r="D276">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E276" t="s">
-        <v>257</v>
+        <v>420</v>
       </c>
       <c r="F276" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,16 +7757,16 @@
         <v>23</v>
       </c>
       <c r="C277" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F277" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7774,16 +7774,19 @@
         <v>684</v>
       </c>
       <c r="B278" t="s">
-        <v>385</v>
+        <v>23</v>
       </c>
       <c r="C278" t="s">
-        <v>84</v>
+        <v>30</v>
+      </c>
+      <c r="D278">
+        <v>2</v>
       </c>
       <c r="E278" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="F278" t="s">
-        <v>386</v>
+        <v>31</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7791,16 +7794,16 @@
         <v>684</v>
       </c>
       <c r="B279" t="s">
-        <v>657</v>
-      </c>
-      <c r="D279" t="s">
-        <v>582</v>
+        <v>385</v>
+      </c>
+      <c r="C279" t="s">
+        <v>84</v>
       </c>
       <c r="E279" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F279" t="s">
-        <v>276</v>
+        <v>386</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7808,16 +7811,16 @@
         <v>684</v>
       </c>
       <c r="B280" t="s">
-        <v>106</v>
-      </c>
-      <c r="C280" t="s">
-        <v>111</v>
+        <v>657</v>
+      </c>
+      <c r="D280" t="s">
+        <v>582</v>
       </c>
       <c r="E280" t="s">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="F280" t="s">
-        <v>113</v>
+        <v>276</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7825,16 +7828,16 @@
         <v>684</v>
       </c>
       <c r="B281" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C281" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E281" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F281" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7845,13 +7848,13 @@
         <v>98</v>
       </c>
       <c r="C282" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E282" t="s">
         <v>102</v>
       </c>
       <c r="F282" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -7862,13 +7865,13 @@
         <v>98</v>
       </c>
       <c r="C283" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E283" t="s">
         <v>102</v>
       </c>
       <c r="F283" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -7879,7 +7882,7 @@
         <v>98</v>
       </c>
       <c r="C284" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E284" t="s">
         <v>102</v>
@@ -7893,16 +7896,16 @@
         <v>684</v>
       </c>
       <c r="B285" t="s">
-        <v>658</v>
-      </c>
-      <c r="D285" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="C285" t="s">
+        <v>107</v>
       </c>
       <c r="E285" t="s">
         <v>102</v>
       </c>
       <c r="F285" t="s">
-        <v>625</v>
+        <v>103</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7910,16 +7913,16 @@
         <v>684</v>
       </c>
       <c r="B286" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D286" t="s">
         <v>582</v>
       </c>
       <c r="E286" t="s">
-        <v>420</v>
+        <v>102</v>
       </c>
       <c r="F286" t="s">
-        <v>161</v>
+        <v>625</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -7927,16 +7930,16 @@
         <v>684</v>
       </c>
       <c r="B287" t="s">
-        <v>330</v>
-      </c>
-      <c r="C287" t="s">
-        <v>322</v>
+        <v>659</v>
+      </c>
+      <c r="D287" t="s">
+        <v>582</v>
       </c>
       <c r="E287" t="s">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="F287" t="s">
-        <v>319</v>
+        <v>161</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -7944,16 +7947,16 @@
         <v>684</v>
       </c>
       <c r="B288" t="s">
-        <v>762</v>
-      </c>
-      <c r="D288" t="s">
-        <v>712</v>
+        <v>330</v>
+      </c>
+      <c r="C288" t="s">
+        <v>322</v>
       </c>
       <c r="E288" t="s">
-        <v>763</v>
+        <v>320</v>
       </c>
       <c r="F288" t="s">
-        <v>764</v>
+        <v>319</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7961,16 +7964,16 @@
         <v>684</v>
       </c>
       <c r="B289" t="s">
-        <v>239</v>
-      </c>
-      <c r="C289" t="s">
-        <v>240</v>
+        <v>762</v>
+      </c>
+      <c r="D289" t="s">
+        <v>712</v>
       </c>
       <c r="E289" t="s">
-        <v>241</v>
+        <v>763</v>
       </c>
       <c r="F289" t="s">
-        <v>242</v>
+        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7978,16 +7981,16 @@
         <v>684</v>
       </c>
       <c r="B290" t="s">
-        <v>660</v>
-      </c>
-      <c r="D290" t="s">
-        <v>582</v>
+        <v>239</v>
+      </c>
+      <c r="C290" t="s">
+        <v>240</v>
       </c>
       <c r="E290" t="s">
-        <v>324</v>
+        <v>241</v>
       </c>
       <c r="F290" t="s">
-        <v>661</v>
+        <v>242</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -7995,16 +7998,16 @@
         <v>684</v>
       </c>
       <c r="B291" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D291" t="s">
         <v>582</v>
       </c>
       <c r="E291" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="F291" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,16 +8015,16 @@
         <v>684</v>
       </c>
       <c r="B292" t="s">
-        <v>399</v>
-      </c>
-      <c r="C292" t="s">
-        <v>77</v>
+        <v>662</v>
+      </c>
+      <c r="D292" t="s">
+        <v>582</v>
       </c>
       <c r="E292" t="s">
-        <v>391</v>
+        <v>289</v>
       </c>
       <c r="F292" t="s">
-        <v>392</v>
+        <v>663</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8029,19 +8032,16 @@
         <v>684</v>
       </c>
       <c r="B293" t="s">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="C293" t="s">
-        <v>10</v>
-      </c>
-      <c r="D293">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E293" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="F293" t="s">
-        <v>21</v>
+        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8049,19 +8049,19 @@
         <v>684</v>
       </c>
       <c r="B294" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C294" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D294">
         <v>1</v>
       </c>
       <c r="E294" t="s">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F294" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8072,7 +8072,10 @@
         <v>16</v>
       </c>
       <c r="C295" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D295">
+        <v>1</v>
       </c>
       <c r="E295" t="s">
         <v>255</v>
@@ -8089,16 +8092,13 @@
         <v>16</v>
       </c>
       <c r="C296" t="s">
-        <v>22</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E296" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F296" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,19 +8106,19 @@
         <v>684</v>
       </c>
       <c r="B297" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="C297" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D297">
         <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="F297" t="s">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8129,13 +8129,16 @@
         <v>267</v>
       </c>
       <c r="C298" t="s">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
       </c>
       <c r="E298" t="s">
         <v>287</v>
       </c>
       <c r="F298" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8146,13 +8149,13 @@
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E299" t="s">
         <v>287</v>
       </c>
       <c r="F299" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8163,13 +8166,13 @@
         <v>267</v>
       </c>
       <c r="C300" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="E300" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F300" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,16 +8183,13 @@
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>354</v>
-      </c>
-      <c r="D301">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="E301" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F301" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,7 +8200,7 @@
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -8209,7 +8209,7 @@
         <v>291</v>
       </c>
       <c r="F302" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,13 +8220,16 @@
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D303">
+        <v>1</v>
       </c>
       <c r="E303" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F303" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8237,16 +8240,13 @@
         <v>267</v>
       </c>
       <c r="C304" t="s">
-        <v>299</v>
-      </c>
-      <c r="D304">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E304" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F304" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,7 +8257,7 @@
         <v>267</v>
       </c>
       <c r="C305" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -8266,7 +8266,7 @@
         <v>301</v>
       </c>
       <c r="F305" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8277,13 +8277,16 @@
         <v>267</v>
       </c>
       <c r="C306" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
       </c>
       <c r="E306" t="s">
         <v>301</v>
       </c>
       <c r="F306" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8294,10 +8297,7 @@
         <v>267</v>
       </c>
       <c r="C307" t="s">
-        <v>307</v>
-      </c>
-      <c r="D307">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="E307" t="s">
         <v>301</v>
@@ -8314,7 +8314,7 @@
         <v>267</v>
       </c>
       <c r="C308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -8323,7 +8323,7 @@
         <v>301</v>
       </c>
       <c r="F308" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8331,16 +8331,19 @@
         <v>684</v>
       </c>
       <c r="B309" t="s">
-        <v>664</v>
-      </c>
-      <c r="D309" t="s">
-        <v>582</v>
+        <v>267</v>
+      </c>
+      <c r="C309" t="s">
+        <v>306</v>
+      </c>
+      <c r="D309">
+        <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F309" t="s">
-        <v>665</v>
+        <v>305</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8348,19 +8351,16 @@
         <v>684</v>
       </c>
       <c r="B310" t="s">
-        <v>270</v>
-      </c>
-      <c r="C310" t="s">
-        <v>271</v>
-      </c>
-      <c r="D310">
-        <v>1</v>
+        <v>664</v>
+      </c>
+      <c r="D310" t="s">
+        <v>582</v>
       </c>
       <c r="E310" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="F310" t="s">
-        <v>328</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8371,16 +8371,16 @@
         <v>270</v>
       </c>
       <c r="C311" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D311">
         <v>1</v>
       </c>
       <c r="E311" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F311" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -8391,16 +8391,16 @@
         <v>270</v>
       </c>
       <c r="C312" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="D312">
         <v>1</v>
       </c>
       <c r="E312" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F312" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8411,16 +8411,16 @@
         <v>270</v>
       </c>
       <c r="C313" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D313">
         <v>1</v>
       </c>
       <c r="E313" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F313" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8431,16 +8431,16 @@
         <v>270</v>
       </c>
       <c r="C314" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D314">
         <v>1</v>
       </c>
       <c r="E314" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F314" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8448,19 +8448,19 @@
         <v>684</v>
       </c>
       <c r="B315" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C315" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="D315">
         <v>1</v>
       </c>
       <c r="E315" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="F315" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8468,16 +8468,19 @@
         <v>684</v>
       </c>
       <c r="B316" t="s">
-        <v>666</v>
-      </c>
-      <c r="D316" t="s">
-        <v>582</v>
+        <v>347</v>
+      </c>
+      <c r="C316" t="s">
+        <v>348</v>
+      </c>
+      <c r="D316">
+        <v>1</v>
       </c>
       <c r="E316" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
       <c r="F316" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8485,16 +8488,16 @@
         <v>684</v>
       </c>
       <c r="B317" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D317" t="s">
         <v>582</v>
       </c>
       <c r="E317" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F317" t="s">
-        <v>668</v>
+        <v>304</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8502,16 +8505,16 @@
         <v>684</v>
       </c>
       <c r="B318" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D318" t="s">
         <v>582</v>
       </c>
       <c r="E318" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="F318" t="s">
-        <v>305</v>
+        <v>668</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8519,16 +8522,16 @@
         <v>684</v>
       </c>
       <c r="B319" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D319" t="s">
         <v>582</v>
       </c>
       <c r="E319" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="F319" t="s">
-        <v>671</v>
+        <v>305</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8536,16 +8539,16 @@
         <v>684</v>
       </c>
       <c r="B320" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D320" t="s">
         <v>582</v>
       </c>
       <c r="E320" t="s">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="F320" t="s">
-        <v>232</v>
+        <v>671</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,16 +8556,16 @@
         <v>684</v>
       </c>
       <c r="B321" t="s">
-        <v>236</v>
-      </c>
-      <c r="C321" t="s">
-        <v>237</v>
+        <v>673</v>
+      </c>
+      <c r="D321" t="s">
+        <v>582</v>
       </c>
       <c r="E321" t="s">
         <v>234</v>
       </c>
       <c r="F321" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8570,19 +8573,16 @@
         <v>684</v>
       </c>
       <c r="B322" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="C322" t="s">
-        <v>382</v>
-      </c>
-      <c r="D322">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="E322" t="s">
-        <v>375</v>
+        <v>234</v>
       </c>
       <c r="F322" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>379</v>
       </c>
       <c r="C323" t="s">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -8602,7 +8602,7 @@
         <v>375</v>
       </c>
       <c r="F323" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,7 +8613,7 @@
         <v>379</v>
       </c>
       <c r="C324" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -8622,7 +8622,7 @@
         <v>375</v>
       </c>
       <c r="F324" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,13 +8633,16 @@
         <v>379</v>
       </c>
       <c r="C325" t="s">
-        <v>77</v>
+        <v>381</v>
+      </c>
+      <c r="D325">
+        <v>1</v>
       </c>
       <c r="E325" t="s">
         <v>375</v>
       </c>
       <c r="F325" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -8647,19 +8650,16 @@
         <v>684</v>
       </c>
       <c r="B326" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C326" t="s">
-        <v>8</v>
-      </c>
-      <c r="D326">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E326" t="s">
         <v>375</v>
       </c>
       <c r="F326" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -8670,7 +8670,7 @@
         <v>373</v>
       </c>
       <c r="C327" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D327">
         <v>1</v>
@@ -8679,7 +8679,7 @@
         <v>375</v>
       </c>
       <c r="F327" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -8687,16 +8687,19 @@
         <v>684</v>
       </c>
       <c r="B328" t="s">
-        <v>674</v>
-      </c>
-      <c r="D328" t="s">
-        <v>582</v>
+        <v>373</v>
+      </c>
+      <c r="C328" t="s">
+        <v>35</v>
+      </c>
+      <c r="D328">
+        <v>1</v>
       </c>
       <c r="E328" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="F328" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -8704,7 +8707,7 @@
         <v>684</v>
       </c>
       <c r="B329" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D329" t="s">
         <v>582</v>
@@ -8713,44 +8716,41 @@
         <v>406</v>
       </c>
       <c r="F329" t="s">
-        <v>676</v>
+        <v>407</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B330" t="s">
-        <v>685</v>
-      </c>
-      <c r="C330" t="s">
-        <v>686</v>
+        <v>675</v>
+      </c>
+      <c r="D330" t="s">
+        <v>582</v>
       </c>
       <c r="E330" t="s">
-        <v>687</v>
+        <v>406</v>
       </c>
       <c r="F330" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B331" t="s">
-        <v>148</v>
+        <v>685</v>
       </c>
       <c r="C331" t="s">
-        <v>10</v>
-      </c>
-      <c r="D331">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="E331" t="s">
-        <v>420</v>
+        <v>687</v>
       </c>
       <c r="F331" t="s">
-        <v>159</v>
+        <v>688</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -8761,13 +8761,16 @@
         <v>148</v>
       </c>
       <c r="C332" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
       </c>
       <c r="E332" t="s">
         <v>420</v>
       </c>
       <c r="F332" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -8778,13 +8781,13 @@
         <v>148</v>
       </c>
       <c r="C333" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E333" t="s">
         <v>420</v>
       </c>
       <c r="F333" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -8795,16 +8798,13 @@
         <v>148</v>
       </c>
       <c r="C334" t="s">
-        <v>199</v>
-      </c>
-      <c r="D334">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E334" t="s">
         <v>420</v>
       </c>
       <c r="F334" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -8812,10 +8812,10 @@
         <v>684</v>
       </c>
       <c r="B335" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C335" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D335">
         <v>1</v>
@@ -8824,7 +8824,7 @@
         <v>420</v>
       </c>
       <c r="F335" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -8835,7 +8835,7 @@
         <v>152</v>
       </c>
       <c r="C336" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D336">
         <v>1</v>
@@ -8852,16 +8852,19 @@
         <v>684</v>
       </c>
       <c r="B337" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C337" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D337">
+        <v>1</v>
       </c>
       <c r="E337" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="F337" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,13 +8875,13 @@
         <v>201</v>
       </c>
       <c r="C338" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E338" t="s">
         <v>180</v>
       </c>
       <c r="F338" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -8889,16 +8892,13 @@
         <v>201</v>
       </c>
       <c r="C339" t="s">
-        <v>518</v>
-      </c>
-      <c r="D339">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E339" t="s">
-        <v>520</v>
+        <v>180</v>
       </c>
       <c r="F339" t="s">
-        <v>519</v>
+        <v>164</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -8906,16 +8906,19 @@
         <v>684</v>
       </c>
       <c r="B340" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C340" t="s">
-        <v>368</v>
+        <v>518</v>
+      </c>
+      <c r="D340">
+        <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>367</v>
+        <v>520</v>
       </c>
       <c r="F340" t="s">
-        <v>366</v>
+        <v>519</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -8926,13 +8929,13 @@
         <v>204</v>
       </c>
       <c r="C341" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="E341" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="F341" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -8943,7 +8946,7 @@
         <v>204</v>
       </c>
       <c r="C342" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E342" t="s">
         <v>178</v>
@@ -8957,16 +8960,16 @@
         <v>684</v>
       </c>
       <c r="B343" t="s">
-        <v>203</v>
-      </c>
-      <c r="D343" t="s">
-        <v>692</v>
+        <v>204</v>
+      </c>
+      <c r="C343" t="s">
+        <v>167</v>
       </c>
       <c r="E343" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F343" t="s">
-        <v>710</v>
+        <v>183</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -8976,17 +8979,14 @@
       <c r="B344" t="s">
         <v>203</v>
       </c>
-      <c r="C344" t="s">
-        <v>35</v>
-      </c>
-      <c r="D344">
-        <v>1</v>
+      <c r="D344" t="s">
+        <v>692</v>
       </c>
       <c r="E344" t="s">
         <v>709</v>
       </c>
       <c r="F344" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -8997,13 +8997,16 @@
         <v>203</v>
       </c>
       <c r="C345" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D345">
+        <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>178</v>
+        <v>709</v>
       </c>
       <c r="F345" t="s">
-        <v>181</v>
+        <v>722</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9011,19 +9014,16 @@
         <v>684</v>
       </c>
       <c r="B346" t="s">
-        <v>721</v>
+        <v>203</v>
       </c>
       <c r="C346" t="s">
-        <v>230</v>
-      </c>
-      <c r="D346">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E346" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F346" t="s">
-        <v>710</v>
+        <v>181</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9031,10 +9031,13 @@
         <v>684</v>
       </c>
       <c r="B347" t="s">
-        <v>723</v>
-      </c>
-      <c r="D347" t="s">
-        <v>692</v>
+        <v>721</v>
+      </c>
+      <c r="C347" t="s">
+        <v>230</v>
+      </c>
+      <c r="D347">
+        <v>1</v>
       </c>
       <c r="E347" t="s">
         <v>709</v>
@@ -9050,17 +9053,14 @@
       <c r="B348" t="s">
         <v>723</v>
       </c>
-      <c r="C348" t="s">
-        <v>35</v>
-      </c>
-      <c r="D348">
-        <v>1</v>
+      <c r="D348" t="s">
+        <v>692</v>
       </c>
       <c r="E348" t="s">
         <v>709</v>
       </c>
       <c r="F348" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9068,16 +9068,19 @@
         <v>684</v>
       </c>
       <c r="B349" t="s">
-        <v>200</v>
+        <v>723</v>
       </c>
       <c r="C349" t="s">
-        <v>104</v>
+        <v>35</v>
+      </c>
+      <c r="D349">
+        <v>1</v>
       </c>
       <c r="E349" t="s">
-        <v>180</v>
+        <v>709</v>
       </c>
       <c r="F349" t="s">
-        <v>162</v>
+        <v>717</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9085,16 +9088,16 @@
         <v>684</v>
       </c>
       <c r="B350" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="C350" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E350" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="F350" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9105,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="C351" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E351" t="s">
         <v>59</v>
@@ -9119,19 +9122,16 @@
         <v>684</v>
       </c>
       <c r="B352" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="C352" t="s">
-        <v>334</v>
-      </c>
-      <c r="D352">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E352" t="s">
-        <v>332</v>
+        <v>59</v>
       </c>
       <c r="F352" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -9139,16 +9139,19 @@
         <v>684</v>
       </c>
       <c r="B353" t="s">
-        <v>677</v>
-      </c>
-      <c r="D353" t="s">
-        <v>582</v>
+        <v>335</v>
+      </c>
+      <c r="C353" t="s">
+        <v>334</v>
+      </c>
+      <c r="D353">
+        <v>1</v>
       </c>
       <c r="E353" t="s">
-        <v>475</v>
+        <v>332</v>
       </c>
       <c r="F353" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -9156,16 +9159,16 @@
         <v>684</v>
       </c>
       <c r="B354" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D354" t="s">
         <v>582</v>
       </c>
       <c r="E354" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="F354" t="s">
-        <v>679</v>
+        <v>470</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -9173,16 +9176,16 @@
         <v>684</v>
       </c>
       <c r="B355" t="s">
-        <v>578</v>
-      </c>
-      <c r="C355" t="s">
-        <v>104</v>
+        <v>678</v>
+      </c>
+      <c r="D355" t="s">
+        <v>582</v>
       </c>
       <c r="E355" t="s">
-        <v>577</v>
+        <v>420</v>
       </c>
       <c r="F355" t="s">
-        <v>580</v>
+        <v>679</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -9193,13 +9196,13 @@
         <v>578</v>
       </c>
       <c r="C356" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E356" t="s">
         <v>577</v>
       </c>
       <c r="F356" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -9207,16 +9210,16 @@
         <v>684</v>
       </c>
       <c r="B357" t="s">
-        <v>184</v>
-      </c>
-      <c r="D357" t="s">
-        <v>692</v>
+        <v>578</v>
+      </c>
+      <c r="C357" t="s">
+        <v>78</v>
       </c>
       <c r="E357" t="s">
-        <v>186</v>
+        <v>577</v>
       </c>
       <c r="F357" t="s">
-        <v>190</v>
+        <v>579</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -9226,14 +9229,14 @@
       <c r="B358" t="s">
         <v>184</v>
       </c>
-      <c r="C358" t="s">
-        <v>153</v>
+      <c r="D358" t="s">
+        <v>692</v>
       </c>
       <c r="E358" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F358" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -9244,13 +9247,13 @@
         <v>184</v>
       </c>
       <c r="C359" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E359" t="s">
-        <v>515</v>
+        <v>154</v>
       </c>
       <c r="F359" t="s">
-        <v>516</v>
+        <v>155</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -9267,7 +9270,7 @@
         <v>515</v>
       </c>
       <c r="F360" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -9278,13 +9281,13 @@
         <v>184</v>
       </c>
       <c r="C361" t="s">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="E361" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F361" t="s">
-        <v>446</v>
+        <v>517</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -9295,16 +9298,13 @@
         <v>184</v>
       </c>
       <c r="C362" t="s">
-        <v>261</v>
-      </c>
-      <c r="D362">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E362" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F362" t="s">
-        <v>262</v>
+        <v>446</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9315,16 @@
         <v>184</v>
       </c>
       <c r="C363" t="s">
-        <v>421</v>
+        <v>261</v>
+      </c>
+      <c r="D363">
+        <v>1</v>
       </c>
       <c r="E363" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="F363" t="s">
-        <v>157</v>
+        <v>262</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -9332,16 +9335,13 @@
         <v>184</v>
       </c>
       <c r="C364" t="s">
-        <v>734</v>
-      </c>
-      <c r="D364">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="E364" t="s">
-        <v>735</v>
+        <v>420</v>
       </c>
       <c r="F364" t="s">
-        <v>736</v>
+        <v>157</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -9352,16 +9352,16 @@
         <v>184</v>
       </c>
       <c r="C365" t="s">
-        <v>185</v>
+        <v>734</v>
       </c>
       <c r="D365">
         <v>1</v>
       </c>
       <c r="E365" t="s">
-        <v>186</v>
+        <v>735</v>
       </c>
       <c r="F365" t="s">
-        <v>190</v>
+        <v>736</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -9372,16 +9372,16 @@
         <v>184</v>
       </c>
       <c r="C366" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="D366">
         <v>1</v>
       </c>
       <c r="E366" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="F366" t="s">
-        <v>530</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -9401,7 +9401,7 @@
         <v>298</v>
       </c>
       <c r="F367" t="s">
-        <v>297</v>
+        <v>530</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -9412,16 +9412,16 @@
         <v>184</v>
       </c>
       <c r="C368" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="D368">
         <v>1</v>
       </c>
       <c r="E368" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F368" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -9432,7 +9432,7 @@
         <v>184</v>
       </c>
       <c r="C369" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D369">
         <v>1</v>
@@ -9441,7 +9441,7 @@
         <v>324</v>
       </c>
       <c r="F369" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>684</v>
       </c>
       <c r="B370" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C370" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D370">
         <v>1</v>
       </c>
       <c r="E370" t="s">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="F370" t="s">
-        <v>194</v>
+        <v>325</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -9472,7 +9472,7 @@
         <v>196</v>
       </c>
       <c r="C371" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D371">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>244</v>
       </c>
       <c r="F371" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -9489,16 +9489,19 @@
         <v>684</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>196</v>
       </c>
       <c r="C372" t="s">
-        <v>477</v>
+        <v>191</v>
+      </c>
+      <c r="D372">
+        <v>1</v>
       </c>
       <c r="E372" t="s">
-        <v>538</v>
+        <v>244</v>
       </c>
       <c r="F372" t="s">
-        <v>465</v>
+        <v>195</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -9506,16 +9509,16 @@
         <v>684</v>
       </c>
       <c r="B373" t="s">
-        <v>45</v>
+        <v>476</v>
       </c>
       <c r="C373" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E373" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="F373" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -9526,13 +9529,13 @@
         <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="E374" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F374" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -9543,13 +9546,13 @@
         <v>45</v>
       </c>
       <c r="C375" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E375" t="s">
         <v>406</v>
       </c>
       <c r="F375" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -9560,13 +9563,13 @@
         <v>45</v>
       </c>
       <c r="C376" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E376" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F376" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -9577,13 +9580,13 @@
         <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="E377" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="F377" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -9600,7 +9603,7 @@
         <v>491</v>
       </c>
       <c r="F378" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -9611,13 +9614,13 @@
         <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="E379" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="F379" t="s">
-        <v>181</v>
+        <v>493</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -9628,13 +9631,13 @@
         <v>45</v>
       </c>
       <c r="C380" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="E380" t="s">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="F380" t="s">
-        <v>564</v>
+        <v>181</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9651,7 +9654,7 @@
         <v>563</v>
       </c>
       <c r="F381" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9662,16 +9665,13 @@
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>415</v>
-      </c>
-      <c r="D382">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="E382" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="F382" t="s">
-        <v>416</v>
+        <v>565</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -9682,13 +9682,16 @@
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="D383">
+        <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F383" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -9699,13 +9702,13 @@
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="E384" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="F384" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -9716,16 +9719,13 @@
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>264</v>
-      </c>
-      <c r="D385">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E385" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F385" t="s">
-        <v>263</v>
+        <v>445</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -9736,13 +9736,16 @@
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>372</v>
+        <v>264</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
       </c>
       <c r="E386" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="F386" t="s">
-        <v>559</v>
+        <v>263</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,16 +9756,13 @@
         <v>45</v>
       </c>
       <c r="C387" t="s">
-        <v>187</v>
-      </c>
-      <c r="D387">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="E387" t="s">
-        <v>188</v>
+        <v>369</v>
       </c>
       <c r="F387" t="s">
-        <v>190</v>
+        <v>559</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -9773,16 +9773,16 @@
         <v>45</v>
       </c>
       <c r="C388" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="D388">
         <v>1</v>
       </c>
       <c r="E388" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F388" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -9793,13 +9793,16 @@
         <v>45</v>
       </c>
       <c r="C389" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="D389">
+        <v>1</v>
       </c>
       <c r="E389" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="F389" t="s">
-        <v>123</v>
+        <v>282</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9810,16 +9813,13 @@
         <v>45</v>
       </c>
       <c r="C390" t="s">
-        <v>52</v>
-      </c>
-      <c r="D390">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E390" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="F390" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -9830,7 +9830,7 @@
         <v>45</v>
       </c>
       <c r="C391" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D391">
         <v>1</v>
@@ -9839,7 +9839,7 @@
         <v>50</v>
       </c>
       <c r="F391" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -9850,13 +9850,16 @@
         <v>45</v>
       </c>
       <c r="C392" t="s">
-        <v>125</v>
+        <v>49</v>
+      </c>
+      <c r="D392">
+        <v>1</v>
       </c>
       <c r="E392" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="F392" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -9864,16 +9867,16 @@
         <v>684</v>
       </c>
       <c r="B393" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C393" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="E393" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="F393" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -9881,16 +9884,16 @@
         <v>684</v>
       </c>
       <c r="B394" t="s">
-        <v>569</v>
+        <v>202</v>
       </c>
       <c r="C394" t="s">
-        <v>571</v>
+        <v>167</v>
       </c>
       <c r="E394" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F394" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -9907,7 +9910,7 @@
         <v>256</v>
       </c>
       <c r="F395" t="s">
-        <v>572</v>
+        <v>183</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9918,13 +9921,13 @@
         <v>569</v>
       </c>
       <c r="C396" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E396" t="s">
         <v>256</v>
       </c>
       <c r="F396" t="s">
-        <v>183</v>
+        <v>572</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9932,16 +9935,16 @@
         <v>684</v>
       </c>
       <c r="B397" t="s">
-        <v>48</v>
+        <v>569</v>
       </c>
       <c r="C397" t="s">
-        <v>171</v>
+        <v>570</v>
       </c>
       <c r="E397" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F397" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9952,13 +9955,13 @@
         <v>48</v>
       </c>
       <c r="C398" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E398" t="s">
         <v>255</v>
       </c>
       <c r="F398" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -9969,13 +9972,13 @@
         <v>48</v>
       </c>
       <c r="C399" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E399" t="s">
         <v>255</v>
       </c>
       <c r="F399" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -9986,16 +9989,13 @@
         <v>48</v>
       </c>
       <c r="C400" t="s">
-        <v>55</v>
-      </c>
-      <c r="D400">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E400" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F400" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -10006,7 +10006,7 @@
         <v>48</v>
       </c>
       <c r="C401" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D401">
         <v>1</v>
@@ -10023,19 +10023,19 @@
         <v>684</v>
       </c>
       <c r="B402" t="s">
-        <v>456</v>
+        <v>48</v>
       </c>
       <c r="C402" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D402">
         <v>1</v>
       </c>
       <c r="E402" t="s">
-        <v>453</v>
+        <v>50</v>
       </c>
       <c r="F402" t="s">
-        <v>457</v>
+        <v>53</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -10043,19 +10043,19 @@
         <v>684</v>
       </c>
       <c r="B403" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="C403" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="D403">
         <v>1</v>
       </c>
       <c r="E403" t="s">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="F403" t="s">
-        <v>114</v>
+        <v>457</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
         <v>108</v>
       </c>
       <c r="C404" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D404">
         <v>1</v>
@@ -10075,7 +10075,7 @@
         <v>115</v>
       </c>
       <c r="F404" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -10086,7 +10086,7 @@
         <v>108</v>
       </c>
       <c r="C405" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D405">
         <v>1</v>
@@ -10095,7 +10095,7 @@
         <v>115</v>
       </c>
       <c r="F405" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -10106,7 +10106,7 @@
         <v>108</v>
       </c>
       <c r="C406" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D406">
         <v>1</v>
@@ -10115,7 +10115,7 @@
         <v>115</v>
       </c>
       <c r="F406" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -10126,7 +10126,7 @@
         <v>108</v>
       </c>
       <c r="C407" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D407">
         <v>1</v>
@@ -10135,7 +10135,7 @@
         <v>115</v>
       </c>
       <c r="F407" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -10143,16 +10143,19 @@
         <v>684</v>
       </c>
       <c r="B408" t="s">
-        <v>756</v>
-      </c>
-      <c r="D408" t="s">
-        <v>712</v>
+        <v>108</v>
+      </c>
+      <c r="C408" t="s">
+        <v>120</v>
+      </c>
+      <c r="D408">
+        <v>1</v>
       </c>
       <c r="E408" t="s">
-        <v>255</v>
+        <v>115</v>
       </c>
       <c r="F408" t="s">
-        <v>757</v>
+        <v>121</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -10160,16 +10163,16 @@
         <v>684</v>
       </c>
       <c r="B409" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D409" t="s">
         <v>712</v>
       </c>
       <c r="E409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F409" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -10177,16 +10180,16 @@
         <v>684</v>
       </c>
       <c r="B410" t="s">
-        <v>680</v>
+        <v>754</v>
       </c>
       <c r="D410" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E410" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="F410" t="s">
-        <v>297</v>
+        <v>755</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -10194,19 +10197,16 @@
         <v>684</v>
       </c>
       <c r="B411" t="s">
-        <v>197</v>
-      </c>
-      <c r="C411" t="s">
-        <v>189</v>
-      </c>
-      <c r="D411">
-        <v>1</v>
+        <v>680</v>
+      </c>
+      <c r="D411" t="s">
+        <v>582</v>
       </c>
       <c r="E411" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="F411" t="s">
-        <v>192</v>
+        <v>297</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -10217,7 +10217,7 @@
         <v>197</v>
       </c>
       <c r="C412" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D412">
         <v>1</v>
@@ -10226,7 +10226,7 @@
         <v>244</v>
       </c>
       <c r="F412" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -10234,16 +10234,19 @@
         <v>684</v>
       </c>
       <c r="B413" t="s">
-        <v>566</v>
+        <v>197</v>
       </c>
       <c r="C413" t="s">
-        <v>567</v>
+        <v>191</v>
+      </c>
+      <c r="D413">
+        <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>563</v>
+        <v>244</v>
       </c>
       <c r="F413" t="s">
-        <v>565</v>
+        <v>193</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -10254,7 +10257,7 @@
         <v>566</v>
       </c>
       <c r="C414" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E414" t="s">
         <v>563</v>
@@ -10271,7 +10274,7 @@
         <v>566</v>
       </c>
       <c r="C415" t="s">
-        <v>167</v>
+        <v>568</v>
       </c>
       <c r="E415" t="s">
         <v>563</v>
@@ -10285,15 +10288,32 @@
         <v>684</v>
       </c>
       <c r="B416" t="s">
+        <v>566</v>
+      </c>
+      <c r="C416" t="s">
+        <v>167</v>
+      </c>
+      <c r="E416" t="s">
+        <v>563</v>
+      </c>
+      <c r="F416" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>684</v>
+      </c>
+      <c r="B417" t="s">
         <v>403</v>
       </c>
-      <c r="C416" t="s">
+      <c r="C417" t="s">
         <v>104</v>
       </c>
-      <c r="E416" t="s">
+      <c r="E417" t="s">
         <v>400</v>
       </c>
-      <c r="F416" t="s">
+      <c r="F417" t="s">
         <v>401</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A252338-4B96-4942-9ECB-51A119DCE67A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00039A75-A20C-4A49-B392-46CC2E41BB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -2765,7 +2765,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="765" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="628" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4588A2D3-9BDF-4951-90AB-2EF6A0297DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00039A75-A20C-4A49-B392-46CC2E41BB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="772">
   <si>
     <t>Class</t>
   </si>
@@ -2341,6 +2341,9 @@
   </si>
   <si>
     <t>PivotValueFilter</t>
+  </si>
+  <si>
+    <t>DataValidationAlertStyle</t>
   </si>
 </sst>
 </file>
@@ -2448,10 +2451,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F416" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F416" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F416">
-    <sortCondition ref="B1:B416"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F417" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F417" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F417">
+    <sortCondition ref="B1:B417"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2762,7 +2765,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="765" row="6">
+  <wetp:taskpane dockstate="right" visibility="0" width="628" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -2782,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F416"/>
+  <dimension ref="A1:F417"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -5513,10 +5516,10 @@
         <v>684</v>
       </c>
       <c r="B154" t="s">
-        <v>745</v>
+        <v>771</v>
       </c>
       <c r="D154" t="s">
-        <v>712</v>
+        <v>582</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
@@ -5530,10 +5533,10 @@
         <v>684</v>
       </c>
       <c r="B155" t="s">
-        <v>639</v>
+        <v>745</v>
       </c>
       <c r="D155" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
@@ -5547,16 +5550,16 @@
         <v>684</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
-      </c>
-      <c r="C156" t="s">
-        <v>210</v>
+        <v>639</v>
+      </c>
+      <c r="D156" t="s">
+        <v>582</v>
       </c>
       <c r="E156" t="s">
         <v>208</v>
       </c>
       <c r="F156" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5567,13 +5570,13 @@
         <v>243</v>
       </c>
       <c r="C157" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E157" t="s">
         <v>208</v>
       </c>
       <c r="F157" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5581,16 +5584,16 @@
         <v>684</v>
       </c>
       <c r="B158" t="s">
-        <v>640</v>
-      </c>
-      <c r="D158" t="s">
-        <v>582</v>
+        <v>243</v>
+      </c>
+      <c r="C158" t="s">
+        <v>209</v>
       </c>
       <c r="E158" t="s">
-        <v>475</v>
+        <v>208</v>
       </c>
       <c r="F158" t="s">
-        <v>467</v>
+        <v>205</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5598,16 +5601,16 @@
         <v>684</v>
       </c>
       <c r="B159" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D159" t="s">
         <v>582</v>
       </c>
       <c r="E159" t="s">
-        <v>256</v>
+        <v>475</v>
       </c>
       <c r="F159" t="s">
-        <v>572</v>
+        <v>467</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5615,16 +5618,16 @@
         <v>684</v>
       </c>
       <c r="B160" t="s">
-        <v>452</v>
-      </c>
-      <c r="C160" t="s">
-        <v>92</v>
+        <v>641</v>
+      </c>
+      <c r="D160" t="s">
+        <v>582</v>
       </c>
       <c r="E160" t="s">
-        <v>453</v>
+        <v>256</v>
       </c>
       <c r="F160" t="s">
-        <v>454</v>
+        <v>572</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -5632,16 +5635,16 @@
         <v>684</v>
       </c>
       <c r="B161" t="s">
-        <v>726</v>
+        <v>452</v>
       </c>
       <c r="C161" t="s">
-        <v>576</v>
+        <v>92</v>
       </c>
       <c r="E161" t="s">
-        <v>724</v>
+        <v>453</v>
       </c>
       <c r="F161" t="s">
-        <v>725</v>
+        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -5652,13 +5655,13 @@
         <v>726</v>
       </c>
       <c r="C162" t="s">
-        <v>78</v>
+        <v>576</v>
       </c>
       <c r="E162" t="s">
         <v>724</v>
       </c>
       <c r="F162" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5666,16 +5669,16 @@
         <v>684</v>
       </c>
       <c r="B163" t="s">
-        <v>642</v>
-      </c>
-      <c r="D163" t="s">
-        <v>582</v>
+        <v>726</v>
+      </c>
+      <c r="C163" t="s">
+        <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>644</v>
+        <v>724</v>
       </c>
       <c r="F163" t="s">
-        <v>643</v>
+        <v>727</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5683,16 +5686,16 @@
         <v>684</v>
       </c>
       <c r="B164" t="s">
-        <v>750</v>
+        <v>642</v>
       </c>
       <c r="D164" t="s">
-        <v>712</v>
+        <v>582</v>
       </c>
       <c r="E164" t="s">
-        <v>752</v>
+        <v>644</v>
       </c>
       <c r="F164" t="s">
-        <v>748</v>
+        <v>643</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -5700,16 +5703,16 @@
         <v>684</v>
       </c>
       <c r="B165" t="s">
-        <v>689</v>
+        <v>750</v>
       </c>
       <c r="D165" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E165" t="s">
-        <v>690</v>
+        <v>752</v>
       </c>
       <c r="F165" t="s">
-        <v>691</v>
+        <v>748</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -5717,16 +5720,16 @@
         <v>684</v>
       </c>
       <c r="B166" t="s">
-        <v>747</v>
+        <v>689</v>
       </c>
       <c r="D166" t="s">
-        <v>78</v>
+        <v>582</v>
       </c>
       <c r="E166" t="s">
-        <v>752</v>
+        <v>690</v>
       </c>
       <c r="F166" t="s">
-        <v>748</v>
+        <v>691</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -5734,10 +5737,10 @@
         <v>684</v>
       </c>
       <c r="B167" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D167" t="s">
-        <v>712</v>
+        <v>78</v>
       </c>
       <c r="E167" t="s">
         <v>752</v>
@@ -5751,16 +5754,16 @@
         <v>684</v>
       </c>
       <c r="B168" t="s">
-        <v>589</v>
+        <v>749</v>
       </c>
       <c r="D168" t="s">
-        <v>78</v>
+        <v>712</v>
       </c>
       <c r="E168" t="s">
-        <v>590</v>
+        <v>752</v>
       </c>
       <c r="F168" t="s">
-        <v>591</v>
+        <v>748</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5768,10 +5771,10 @@
         <v>684</v>
       </c>
       <c r="B169" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D169" t="s">
-        <v>582</v>
+        <v>78</v>
       </c>
       <c r="E169" t="s">
         <v>590</v>
@@ -5785,16 +5788,16 @@
         <v>684</v>
       </c>
       <c r="B170" t="s">
-        <v>645</v>
+        <v>593</v>
       </c>
       <c r="D170" t="s">
         <v>582</v>
       </c>
       <c r="E170" t="s">
-        <v>391</v>
+        <v>590</v>
       </c>
       <c r="F170" t="s">
-        <v>392</v>
+        <v>591</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5802,16 +5805,16 @@
         <v>684</v>
       </c>
       <c r="B171" t="s">
-        <v>557</v>
-      </c>
-      <c r="C171" t="s">
-        <v>558</v>
+        <v>645</v>
+      </c>
+      <c r="D171" t="s">
+        <v>582</v>
       </c>
       <c r="E171" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="F171" t="s">
-        <v>559</v>
+        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5819,16 +5822,16 @@
         <v>684</v>
       </c>
       <c r="B172" t="s">
-        <v>646</v>
-      </c>
-      <c r="D172" t="s">
-        <v>582</v>
+        <v>557</v>
+      </c>
+      <c r="C172" t="s">
+        <v>558</v>
       </c>
       <c r="E172" t="s">
-        <v>475</v>
+        <v>369</v>
       </c>
       <c r="F172" t="s">
-        <v>467</v>
+        <v>559</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5836,16 +5839,16 @@
         <v>684</v>
       </c>
       <c r="B173" t="s">
-        <v>768</v>
+        <v>646</v>
       </c>
       <c r="D173" t="s">
         <v>582</v>
       </c>
       <c r="E173" t="s">
-        <v>644</v>
+        <v>475</v>
       </c>
       <c r="F173" t="s">
-        <v>643</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,16 +5856,16 @@
         <v>684</v>
       </c>
       <c r="B174" t="s">
-        <v>694</v>
+        <v>768</v>
       </c>
       <c r="D174" t="s">
-        <v>692</v>
+        <v>582</v>
       </c>
       <c r="E174" t="s">
-        <v>697</v>
+        <v>644</v>
       </c>
       <c r="F174" t="s">
-        <v>699</v>
+        <v>643</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5872,11 +5875,8 @@
       <c r="B175" t="s">
         <v>694</v>
       </c>
-      <c r="C175" t="s">
-        <v>696</v>
-      </c>
-      <c r="D175">
-        <v>1</v>
+      <c r="D175" t="s">
+        <v>692</v>
       </c>
       <c r="E175" t="s">
         <v>697</v>
@@ -5893,7 +5893,7 @@
         <v>694</v>
       </c>
       <c r="C176" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -5902,7 +5902,7 @@
         <v>697</v>
       </c>
       <c r="F176" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5910,16 +5910,19 @@
         <v>684</v>
       </c>
       <c r="B177" t="s">
-        <v>647</v>
-      </c>
-      <c r="D177" t="s">
-        <v>582</v>
+        <v>694</v>
+      </c>
+      <c r="C177" t="s">
+        <v>695</v>
+      </c>
+      <c r="D177">
+        <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>287</v>
+        <v>697</v>
       </c>
       <c r="F177" t="s">
-        <v>328</v>
+        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5927,16 +5930,16 @@
         <v>684</v>
       </c>
       <c r="B178" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D178" t="s">
         <v>582</v>
       </c>
       <c r="E178" t="s">
-        <v>414</v>
+        <v>287</v>
       </c>
       <c r="F178" t="s">
-        <v>413</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5944,16 +5947,16 @@
         <v>684</v>
       </c>
       <c r="B179" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D179" t="s">
         <v>582</v>
       </c>
       <c r="E179" t="s">
-        <v>537</v>
+        <v>414</v>
       </c>
       <c r="F179" t="s">
-        <v>522</v>
+        <v>413</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5961,16 +5964,16 @@
         <v>684</v>
       </c>
       <c r="B180" t="s">
-        <v>681</v>
+        <v>649</v>
       </c>
       <c r="D180" t="s">
         <v>582</v>
       </c>
       <c r="E180" t="s">
-        <v>59</v>
+        <v>537</v>
       </c>
       <c r="F180" t="s">
-        <v>75</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5978,10 +5981,10 @@
         <v>684</v>
       </c>
       <c r="B181" t="s">
-        <v>72</v>
-      </c>
-      <c r="C181" t="s">
-        <v>63</v>
+        <v>681</v>
+      </c>
+      <c r="D181" t="s">
+        <v>582</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -5998,7 +6001,7 @@
         <v>72</v>
       </c>
       <c r="C182" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E182" t="s">
         <v>59</v>
@@ -6012,16 +6015,16 @@
         <v>684</v>
       </c>
       <c r="B183" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="C183" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E183" t="s">
-        <v>291</v>
+        <v>59</v>
       </c>
       <c r="F183" t="s">
-        <v>294</v>
+        <v>75</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6029,16 +6032,16 @@
         <v>684</v>
       </c>
       <c r="B184" t="s">
-        <v>650</v>
-      </c>
-      <c r="D184" t="s">
-        <v>582</v>
+        <v>295</v>
+      </c>
+      <c r="C184" t="s">
+        <v>84</v>
       </c>
       <c r="E184" t="s">
-        <v>651</v>
+        <v>291</v>
       </c>
       <c r="F184" t="s">
-        <v>652</v>
+        <v>294</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6046,16 +6049,16 @@
         <v>684</v>
       </c>
       <c r="B185" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D185" t="s">
         <v>582</v>
       </c>
       <c r="E185" t="s">
-        <v>526</v>
+        <v>651</v>
       </c>
       <c r="F185" t="s">
-        <v>527</v>
+        <v>652</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6063,16 +6066,16 @@
         <v>684</v>
       </c>
       <c r="B186" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D186" t="s">
         <v>582</v>
       </c>
       <c r="E186" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="F186" t="s">
-        <v>468</v>
+        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -6080,19 +6083,16 @@
         <v>684</v>
       </c>
       <c r="B187" t="s">
-        <v>342</v>
-      </c>
-      <c r="C187" t="s">
-        <v>343</v>
-      </c>
-      <c r="D187">
-        <v>1</v>
+        <v>654</v>
+      </c>
+      <c r="D187" t="s">
+        <v>582</v>
       </c>
       <c r="E187" t="s">
-        <v>337</v>
+        <v>475</v>
       </c>
       <c r="F187" t="s">
-        <v>340</v>
+        <v>468</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -6103,7 +6103,7 @@
         <v>342</v>
       </c>
       <c r="C188" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         <v>342</v>
       </c>
       <c r="C189" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -6132,7 +6132,7 @@
         <v>337</v>
       </c>
       <c r="F189" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6143,7 +6143,7 @@
         <v>342</v>
       </c>
       <c r="C190" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -6160,16 +6160,19 @@
         <v>684</v>
       </c>
       <c r="B191" t="s">
-        <v>9</v>
-      </c>
-      <c r="D191" t="s">
-        <v>692</v>
+        <v>342</v>
+      </c>
+      <c r="C191" t="s">
+        <v>346</v>
+      </c>
+      <c r="D191">
+        <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="F191" t="s">
-        <v>693</v>
+        <v>341</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6179,17 +6182,14 @@
       <c r="B192" t="s">
         <v>9</v>
       </c>
-      <c r="C192" t="s">
-        <v>10</v>
-      </c>
-      <c r="D192">
-        <v>1</v>
+      <c r="D192" t="s">
+        <v>692</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>12</v>
+        <v>693</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6200,13 +6200,16 @@
         <v>9</v>
       </c>
       <c r="C193" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F193" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -6214,19 +6217,16 @@
         <v>684</v>
       </c>
       <c r="B194" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C194" t="s">
-        <v>8</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E194" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F194" t="s">
-        <v>254</v>
+        <v>15</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6234,16 +6234,19 @@
         <v>684</v>
       </c>
       <c r="B195" t="s">
-        <v>700</v>
-      </c>
-      <c r="D195" t="s">
-        <v>692</v>
+        <v>7</v>
+      </c>
+      <c r="C195" t="s">
+        <v>8</v>
+      </c>
+      <c r="D195">
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>702</v>
+        <v>11</v>
       </c>
       <c r="F195" t="s">
-        <v>706</v>
+        <v>254</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -6253,14 +6256,14 @@
       <c r="B196" t="s">
         <v>700</v>
       </c>
-      <c r="C196" t="s">
-        <v>361</v>
+      <c r="D196" t="s">
+        <v>692</v>
       </c>
       <c r="E196" t="s">
         <v>702</v>
       </c>
       <c r="F196" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -6271,13 +6274,13 @@
         <v>700</v>
       </c>
       <c r="C197" t="s">
-        <v>714</v>
+        <v>361</v>
       </c>
       <c r="E197" t="s">
         <v>702</v>
       </c>
       <c r="F197" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -6288,13 +6291,13 @@
         <v>700</v>
       </c>
       <c r="C198" t="s">
-        <v>546</v>
+        <v>714</v>
       </c>
       <c r="E198" t="s">
         <v>702</v>
       </c>
       <c r="F198" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -6305,13 +6308,13 @@
         <v>700</v>
       </c>
       <c r="C199" t="s">
-        <v>715</v>
+        <v>546</v>
       </c>
       <c r="E199" t="s">
         <v>702</v>
       </c>
       <c r="F199" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6322,16 +6325,13 @@
         <v>700</v>
       </c>
       <c r="C200" t="s">
-        <v>10</v>
-      </c>
-      <c r="D200">
-        <v>1</v>
+        <v>715</v>
       </c>
       <c r="E200" t="s">
         <v>702</v>
       </c>
       <c r="F200" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -6339,16 +6339,19 @@
         <v>684</v>
       </c>
       <c r="B201" t="s">
-        <v>701</v>
-      </c>
-      <c r="D201" t="s">
-        <v>692</v>
+        <v>700</v>
+      </c>
+      <c r="C201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201">
+        <v>1</v>
       </c>
       <c r="E201" t="s">
         <v>702</v>
       </c>
       <c r="F201" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -6358,11 +6361,8 @@
       <c r="B202" t="s">
         <v>701</v>
       </c>
-      <c r="C202" t="s">
-        <v>8</v>
-      </c>
-      <c r="D202">
-        <v>1</v>
+      <c r="D202" t="s">
+        <v>692</v>
       </c>
       <c r="E202" t="s">
         <v>702</v>
@@ -6379,7 +6379,7 @@
         <v>701</v>
       </c>
       <c r="C203" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D203">
         <v>1</v>
@@ -6388,7 +6388,7 @@
         <v>702</v>
       </c>
       <c r="F203" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -6399,7 +6399,7 @@
         <v>701</v>
       </c>
       <c r="C204" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="D204">
         <v>1</v>
@@ -6408,7 +6408,7 @@
         <v>702</v>
       </c>
       <c r="F204" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -6416,16 +6416,19 @@
         <v>684</v>
       </c>
       <c r="B205" t="s">
-        <v>441</v>
+        <v>701</v>
       </c>
       <c r="C205" t="s">
-        <v>442</v>
+        <v>96</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>436</v>
+        <v>702</v>
       </c>
       <c r="F205" t="s">
-        <v>437</v>
+        <v>705</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -6436,13 +6439,13 @@
         <v>441</v>
       </c>
       <c r="C206" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E206" t="s">
         <v>436</v>
       </c>
       <c r="F206" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -6450,19 +6453,16 @@
         <v>684</v>
       </c>
       <c r="B207" t="s">
-        <v>308</v>
+        <v>441</v>
       </c>
       <c r="C207" t="s">
-        <v>8</v>
-      </c>
-      <c r="D207">
-        <v>1</v>
+        <v>438</v>
       </c>
       <c r="E207" t="s">
-        <v>309</v>
+        <v>436</v>
       </c>
       <c r="F207" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,16 +6470,19 @@
         <v>684</v>
       </c>
       <c r="B208" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C208" t="s">
-        <v>311</v>
+        <v>8</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
       </c>
       <c r="E208" t="s">
         <v>309</v>
       </c>
       <c r="F208" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6490,7 +6493,7 @@
         <v>313</v>
       </c>
       <c r="C209" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E209" t="s">
         <v>309</v>
@@ -6507,13 +6510,13 @@
         <v>313</v>
       </c>
       <c r="C210" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E210" t="s">
         <v>309</v>
       </c>
       <c r="F210" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -6524,16 +6527,13 @@
         <v>313</v>
       </c>
       <c r="C211" t="s">
-        <v>317</v>
-      </c>
-      <c r="D211">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="E211" t="s">
         <v>309</v>
       </c>
       <c r="F211" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6544,7 +6544,7 @@
         <v>313</v>
       </c>
       <c r="C212" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -6553,7 +6553,7 @@
         <v>309</v>
       </c>
       <c r="F212" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,13 +6564,16 @@
         <v>313</v>
       </c>
       <c r="C213" t="s">
-        <v>388</v>
+        <v>315</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
       </c>
       <c r="E213" t="s">
         <v>309</v>
       </c>
       <c r="F213" t="s">
-        <v>389</v>
+        <v>316</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -6578,16 +6581,16 @@
         <v>684</v>
       </c>
       <c r="B214" t="s">
-        <v>655</v>
-      </c>
-      <c r="D214" t="s">
-        <v>582</v>
+        <v>313</v>
+      </c>
+      <c r="C214" t="s">
+        <v>388</v>
       </c>
       <c r="E214" t="s">
         <v>309</v>
       </c>
       <c r="F214" t="s">
-        <v>329</v>
+        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,16 +6598,16 @@
         <v>684</v>
       </c>
       <c r="B215" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D215" t="s">
         <v>582</v>
       </c>
       <c r="E215" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="F215" t="s">
-        <v>296</v>
+        <v>329</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -6612,19 +6615,16 @@
         <v>684</v>
       </c>
       <c r="B216" t="s">
-        <v>472</v>
-      </c>
-      <c r="C216" t="s">
-        <v>471</v>
-      </c>
-      <c r="D216">
-        <v>1</v>
+        <v>656</v>
+      </c>
+      <c r="D216" t="s">
+        <v>582</v>
       </c>
       <c r="E216" t="s">
-        <v>475</v>
+        <v>291</v>
       </c>
       <c r="F216" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -6632,16 +6632,19 @@
         <v>684</v>
       </c>
       <c r="B217" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C217" t="s">
-        <v>467</v>
+        <v>471</v>
+      </c>
+      <c r="D217">
+        <v>1</v>
       </c>
       <c r="E217" t="s">
         <v>475</v>
       </c>
       <c r="F217" t="s">
-        <v>467</v>
+        <v>382</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -6652,13 +6655,13 @@
         <v>466</v>
       </c>
       <c r="C218" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E218" t="s">
         <v>475</v>
       </c>
       <c r="F218" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -6669,13 +6672,13 @@
         <v>466</v>
       </c>
       <c r="C219" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E219" t="s">
         <v>475</v>
       </c>
       <c r="F219" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -6686,13 +6689,13 @@
         <v>466</v>
       </c>
       <c r="C220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E220" t="s">
         <v>475</v>
       </c>
       <c r="F220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -6700,10 +6703,10 @@
         <v>684</v>
       </c>
       <c r="B221" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C221" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E221" t="s">
         <v>475</v>
@@ -6717,16 +6720,16 @@
         <v>684</v>
       </c>
       <c r="B222" t="s">
-        <v>769</v>
-      </c>
-      <c r="D222" t="s">
-        <v>712</v>
+        <v>473</v>
+      </c>
+      <c r="C222" t="s">
+        <v>474</v>
       </c>
       <c r="E222" t="s">
         <v>475</v>
       </c>
       <c r="F222" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,19 +6737,16 @@
         <v>684</v>
       </c>
       <c r="B223" t="s">
-        <v>229</v>
-      </c>
-      <c r="C223" t="s">
-        <v>230</v>
-      </c>
-      <c r="D223">
-        <v>1</v>
+        <v>769</v>
+      </c>
+      <c r="D223" t="s">
+        <v>712</v>
       </c>
       <c r="E223" t="s">
-        <v>233</v>
+        <v>475</v>
       </c>
       <c r="F223" t="s">
-        <v>231</v>
+        <v>468</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6757,13 +6757,16 @@
         <v>229</v>
       </c>
       <c r="C224" t="s">
-        <v>494</v>
+        <v>230</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
       </c>
       <c r="E224" t="s">
-        <v>495</v>
+        <v>233</v>
       </c>
       <c r="F224" t="s">
-        <v>496</v>
+        <v>231</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6774,16 +6777,13 @@
         <v>229</v>
       </c>
       <c r="C225" t="s">
-        <v>497</v>
-      </c>
-      <c r="D225">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="E225" t="s">
         <v>495</v>
       </c>
       <c r="F225" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6794,13 +6794,16 @@
         <v>229</v>
       </c>
       <c r="C226" t="s">
-        <v>499</v>
+        <v>497</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
       </c>
       <c r="E226" t="s">
         <v>495</v>
       </c>
       <c r="F226" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -6811,13 +6814,13 @@
         <v>229</v>
       </c>
       <c r="C227" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E227" t="s">
         <v>495</v>
       </c>
       <c r="F227" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -6828,13 +6831,13 @@
         <v>229</v>
       </c>
       <c r="C228" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E228" t="s">
         <v>495</v>
       </c>
       <c r="F228" t="s">
-        <v>226</v>
+        <v>502</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -6845,13 +6848,13 @@
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E229" t="s">
         <v>495</v>
       </c>
       <c r="F229" t="s">
-        <v>505</v>
+        <v>226</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -6862,16 +6865,13 @@
         <v>229</v>
       </c>
       <c r="C230" t="s">
-        <v>506</v>
-      </c>
-      <c r="D230">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="E230" t="s">
         <v>495</v>
       </c>
       <c r="F230" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,13 +6882,16 @@
         <v>229</v>
       </c>
       <c r="C231" t="s">
-        <v>508</v>
+        <v>506</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
       </c>
       <c r="E231" t="s">
         <v>495</v>
       </c>
       <c r="F231" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -6899,13 +6902,13 @@
         <v>229</v>
       </c>
       <c r="C232" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E232" t="s">
         <v>495</v>
       </c>
       <c r="F232" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,13 +6919,13 @@
         <v>229</v>
       </c>
       <c r="C233" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E233" t="s">
         <v>495</v>
       </c>
       <c r="F233" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6930,16 +6933,16 @@
         <v>684</v>
       </c>
       <c r="B234" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C234" t="s">
-        <v>219</v>
+        <v>512</v>
       </c>
       <c r="E234" t="s">
-        <v>214</v>
+        <v>495</v>
       </c>
       <c r="F234" t="s">
-        <v>218</v>
+        <v>509</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6950,13 +6953,13 @@
         <v>216</v>
       </c>
       <c r="C235" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E235" t="s">
         <v>214</v>
       </c>
       <c r="F235" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6967,16 +6970,13 @@
         <v>216</v>
       </c>
       <c r="C236" t="s">
-        <v>10</v>
-      </c>
-      <c r="D236">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="E236" t="s">
         <v>214</v>
       </c>
       <c r="F236" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -6987,13 +6987,16 @@
         <v>216</v>
       </c>
       <c r="C237" t="s">
-        <v>225</v>
+        <v>10</v>
+      </c>
+      <c r="D237">
+        <v>1</v>
       </c>
       <c r="E237" t="s">
         <v>214</v>
       </c>
       <c r="F237" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7004,16 +7007,13 @@
         <v>216</v>
       </c>
       <c r="C238" t="s">
-        <v>594</v>
-      </c>
-      <c r="D238">
-        <v>1</v>
+        <v>225</v>
       </c>
       <c r="E238" t="s">
-        <v>595</v>
+        <v>214</v>
       </c>
       <c r="F238" t="s">
-        <v>596</v>
+        <v>226</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -7024,7 +7024,7 @@
         <v>216</v>
       </c>
       <c r="C239" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -7044,13 +7044,16 @@
         <v>216</v>
       </c>
       <c r="C240" t="s">
-        <v>227</v>
+        <v>597</v>
+      </c>
+      <c r="D240">
+        <v>1</v>
       </c>
       <c r="E240" t="s">
-        <v>233</v>
+        <v>595</v>
       </c>
       <c r="F240" t="s">
-        <v>228</v>
+        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7061,16 +7064,13 @@
         <v>216</v>
       </c>
       <c r="C241" t="s">
-        <v>602</v>
-      </c>
-      <c r="D241">
-        <v>1</v>
+        <v>227</v>
       </c>
       <c r="E241" t="s">
-        <v>603</v>
+        <v>233</v>
       </c>
       <c r="F241" t="s">
-        <v>604</v>
+        <v>228</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7078,19 +7078,19 @@
         <v>684</v>
       </c>
       <c r="B242" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C242" t="s">
-        <v>8</v>
+        <v>602</v>
       </c>
       <c r="D242">
         <v>1</v>
       </c>
       <c r="E242" t="s">
-        <v>214</v>
+        <v>603</v>
       </c>
       <c r="F242" t="s">
-        <v>215</v>
+        <v>604</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7101,16 +7101,16 @@
         <v>213</v>
       </c>
       <c r="C243" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D243">
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>603</v>
+        <v>214</v>
       </c>
       <c r="F243" t="s">
-        <v>604</v>
+        <v>215</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7118,16 +7118,19 @@
         <v>684</v>
       </c>
       <c r="B244" t="s">
-        <v>770</v>
-      </c>
-      <c r="D244" t="s">
-        <v>712</v>
+        <v>213</v>
+      </c>
+      <c r="C244" t="s">
+        <v>35</v>
+      </c>
+      <c r="D244">
+        <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>475</v>
+        <v>603</v>
       </c>
       <c r="F244" t="s">
-        <v>470</v>
+        <v>604</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,16 +7138,16 @@
         <v>684</v>
       </c>
       <c r="B245" t="s">
-        <v>62</v>
-      </c>
-      <c r="C245" t="s">
-        <v>67</v>
+        <v>770</v>
+      </c>
+      <c r="D245" t="s">
+        <v>712</v>
       </c>
       <c r="E245" t="s">
-        <v>59</v>
+        <v>475</v>
       </c>
       <c r="F245" t="s">
-        <v>66</v>
+        <v>470</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7152,19 +7155,16 @@
         <v>684</v>
       </c>
       <c r="B246" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C246" t="s">
-        <v>716</v>
-      </c>
-      <c r="D246">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E246" t="s">
-        <v>709</v>
+        <v>59</v>
       </c>
       <c r="F246" t="s">
-        <v>717</v>
+        <v>66</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7175,13 +7175,16 @@
         <v>23</v>
       </c>
       <c r="C247" t="s">
-        <v>713</v>
+        <v>716</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
       </c>
       <c r="E247" t="s">
         <v>709</v>
       </c>
       <c r="F247" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,13 +7195,13 @@
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E248" t="s">
         <v>709</v>
       </c>
       <c r="F248" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7209,13 +7212,13 @@
         <v>23</v>
       </c>
       <c r="C249" t="s">
-        <v>575</v>
+        <v>718</v>
       </c>
       <c r="E249" t="s">
-        <v>724</v>
+        <v>709</v>
       </c>
       <c r="F249" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7226,16 +7229,13 @@
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>513</v>
-      </c>
-      <c r="D250">
-        <v>1</v>
+        <v>575</v>
       </c>
       <c r="E250" t="s">
-        <v>514</v>
+        <v>724</v>
       </c>
       <c r="F250" t="s">
-        <v>513</v>
+        <v>727</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -7246,13 +7246,16 @@
         <v>23</v>
       </c>
       <c r="C251" t="s">
-        <v>405</v>
+        <v>513</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>406</v>
+        <v>514</v>
       </c>
       <c r="F251" t="s">
-        <v>407</v>
+        <v>513</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -7263,16 +7266,13 @@
         <v>23</v>
       </c>
       <c r="C252" t="s">
-        <v>521</v>
-      </c>
-      <c r="D252">
-        <v>1</v>
+        <v>405</v>
       </c>
       <c r="E252" t="s">
-        <v>537</v>
+        <v>406</v>
       </c>
       <c r="F252" t="s">
-        <v>523</v>
+        <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7283,7 +7283,7 @@
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -7292,7 +7292,7 @@
         <v>537</v>
       </c>
       <c r="F253" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7303,16 +7303,16 @@
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>351</v>
+        <v>524</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>414</v>
+        <v>537</v>
       </c>
       <c r="F254" t="s">
-        <v>413</v>
+        <v>522</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -7323,7 +7323,7 @@
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -7332,7 +7332,7 @@
         <v>414</v>
       </c>
       <c r="F255" t="s">
-        <v>348</v>
+        <v>413</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -7343,16 +7343,16 @@
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>447</v>
+        <v>348</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
       <c r="F256" t="s">
-        <v>448</v>
+        <v>348</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7363,16 +7363,16 @@
         <v>23</v>
       </c>
       <c r="C257" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="D257">
         <v>1</v>
       </c>
       <c r="E257" t="s">
-        <v>538</v>
+        <v>444</v>
       </c>
       <c r="F257" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7383,7 +7383,7 @@
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>539</v>
+        <v>465</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -7392,7 +7392,7 @@
         <v>538</v>
       </c>
       <c r="F258" t="s">
-        <v>540</v>
+        <v>465</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -7403,16 +7403,16 @@
         <v>23</v>
       </c>
       <c r="C259" t="s">
-        <v>265</v>
+        <v>539</v>
       </c>
       <c r="D259">
         <v>1</v>
       </c>
       <c r="E259" t="s">
-        <v>286</v>
+        <v>538</v>
       </c>
       <c r="F259" t="s">
-        <v>266</v>
+        <v>540</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7423,16 +7423,16 @@
         <v>23</v>
       </c>
       <c r="C260" t="s">
-        <v>419</v>
+        <v>265</v>
       </c>
       <c r="D260">
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>418</v>
+        <v>286</v>
       </c>
       <c r="F260" t="s">
-        <v>417</v>
+        <v>266</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7443,16 +7443,16 @@
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="F261" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -7463,7 +7463,7 @@
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -7472,7 +7472,7 @@
         <v>391</v>
       </c>
       <c r="F262" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -7483,16 +7483,16 @@
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>275</v>
+        <v>392</v>
       </c>
       <c r="D263">
         <v>1</v>
       </c>
       <c r="E263" t="s">
-        <v>288</v>
+        <v>391</v>
       </c>
       <c r="F263" t="s">
-        <v>276</v>
+        <v>392</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7503,7 +7503,7 @@
         <v>23</v>
       </c>
       <c r="C264" t="s">
-        <v>433</v>
+        <v>275</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -7512,7 +7512,7 @@
         <v>288</v>
       </c>
       <c r="F264" t="s">
-        <v>434</v>
+        <v>276</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -7523,16 +7523,16 @@
         <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>586</v>
+        <v>433</v>
       </c>
       <c r="D265">
         <v>1</v>
       </c>
       <c r="E265" t="s">
-        <v>587</v>
+        <v>288</v>
       </c>
       <c r="F265" t="s">
-        <v>588</v>
+        <v>434</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -7543,16 +7543,16 @@
         <v>23</v>
       </c>
       <c r="C266" t="s">
-        <v>451</v>
+        <v>586</v>
       </c>
       <c r="D266">
         <v>1</v>
       </c>
       <c r="E266" t="s">
-        <v>450</v>
+        <v>587</v>
       </c>
       <c r="F266" t="s">
-        <v>449</v>
+        <v>588</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,16 +7563,16 @@
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>277</v>
+        <v>451</v>
       </c>
       <c r="D267">
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>289</v>
+        <v>450</v>
       </c>
       <c r="F267" t="s">
-        <v>278</v>
+        <v>449</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7583,7 +7583,7 @@
         <v>23</v>
       </c>
       <c r="C268" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -7592,7 +7592,7 @@
         <v>289</v>
       </c>
       <c r="F268" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -7603,16 +7603,16 @@
         <v>23</v>
       </c>
       <c r="C269" t="s">
-        <v>528</v>
+        <v>279</v>
       </c>
       <c r="D269">
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>526</v>
+        <v>289</v>
       </c>
       <c r="F269" t="s">
-        <v>529</v>
+        <v>280</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -7623,7 +7623,7 @@
         <v>23</v>
       </c>
       <c r="C270" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -7632,7 +7632,7 @@
         <v>526</v>
       </c>
       <c r="F270" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -7643,13 +7643,16 @@
         <v>23</v>
       </c>
       <c r="C271" t="s">
-        <v>101</v>
+        <v>525</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>102</v>
+        <v>526</v>
       </c>
       <c r="F271" t="s">
-        <v>103</v>
+        <v>527</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -7660,16 +7663,13 @@
         <v>23</v>
       </c>
       <c r="C272" t="s">
-        <v>26</v>
-      </c>
-      <c r="D272">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E272" t="s">
-        <v>245</v>
+        <v>102</v>
       </c>
       <c r="F272" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -7680,7 +7680,7 @@
         <v>23</v>
       </c>
       <c r="C273" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -7700,16 +7700,16 @@
         <v>23</v>
       </c>
       <c r="C274" t="s">
-        <v>321</v>
+        <v>28</v>
       </c>
       <c r="D274">
         <v>1</v>
       </c>
       <c r="E274" t="s">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="F274" t="s">
-        <v>319</v>
+        <v>27</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -7720,13 +7720,16 @@
         <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>77</v>
+        <v>321</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="F275" t="s">
-        <v>156</v>
+        <v>319</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -7737,16 +7740,13 @@
         <v>23</v>
       </c>
       <c r="C276" t="s">
-        <v>24</v>
-      </c>
-      <c r="D276">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E276" t="s">
-        <v>257</v>
+        <v>420</v>
       </c>
       <c r="F276" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -7757,16 +7757,16 @@
         <v>23</v>
       </c>
       <c r="C277" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D277">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E277" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F277" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -7774,16 +7774,19 @@
         <v>684</v>
       </c>
       <c r="B278" t="s">
-        <v>385</v>
+        <v>23</v>
       </c>
       <c r="C278" t="s">
-        <v>84</v>
+        <v>30</v>
+      </c>
+      <c r="D278">
+        <v>2</v>
       </c>
       <c r="E278" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="F278" t="s">
-        <v>386</v>
+        <v>31</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -7791,16 +7794,16 @@
         <v>684</v>
       </c>
       <c r="B279" t="s">
-        <v>657</v>
-      </c>
-      <c r="D279" t="s">
-        <v>582</v>
+        <v>385</v>
+      </c>
+      <c r="C279" t="s">
+        <v>84</v>
       </c>
       <c r="E279" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F279" t="s">
-        <v>276</v>
+        <v>386</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -7808,16 +7811,16 @@
         <v>684</v>
       </c>
       <c r="B280" t="s">
-        <v>106</v>
-      </c>
-      <c r="C280" t="s">
-        <v>111</v>
+        <v>657</v>
+      </c>
+      <c r="D280" t="s">
+        <v>582</v>
       </c>
       <c r="E280" t="s">
-        <v>112</v>
+        <v>288</v>
       </c>
       <c r="F280" t="s">
-        <v>113</v>
+        <v>276</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -7825,16 +7828,16 @@
         <v>684</v>
       </c>
       <c r="B281" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C281" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E281" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F281" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -7845,13 +7848,13 @@
         <v>98</v>
       </c>
       <c r="C282" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E282" t="s">
         <v>102</v>
       </c>
       <c r="F282" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -7862,13 +7865,13 @@
         <v>98</v>
       </c>
       <c r="C283" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E283" t="s">
         <v>102</v>
       </c>
       <c r="F283" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -7879,7 +7882,7 @@
         <v>98</v>
       </c>
       <c r="C284" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E284" t="s">
         <v>102</v>
@@ -7893,16 +7896,16 @@
         <v>684</v>
       </c>
       <c r="B285" t="s">
-        <v>658</v>
-      </c>
-      <c r="D285" t="s">
-        <v>582</v>
+        <v>98</v>
+      </c>
+      <c r="C285" t="s">
+        <v>107</v>
       </c>
       <c r="E285" t="s">
         <v>102</v>
       </c>
       <c r="F285" t="s">
-        <v>625</v>
+        <v>103</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7910,16 +7913,16 @@
         <v>684</v>
       </c>
       <c r="B286" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D286" t="s">
         <v>582</v>
       </c>
       <c r="E286" t="s">
-        <v>420</v>
+        <v>102</v>
       </c>
       <c r="F286" t="s">
-        <v>161</v>
+        <v>625</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -7927,16 +7930,16 @@
         <v>684</v>
       </c>
       <c r="B287" t="s">
-        <v>330</v>
-      </c>
-      <c r="C287" t="s">
-        <v>322</v>
+        <v>659</v>
+      </c>
+      <c r="D287" t="s">
+        <v>582</v>
       </c>
       <c r="E287" t="s">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="F287" t="s">
-        <v>319</v>
+        <v>161</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -7944,16 +7947,16 @@
         <v>684</v>
       </c>
       <c r="B288" t="s">
-        <v>762</v>
-      </c>
-      <c r="D288" t="s">
-        <v>712</v>
+        <v>330</v>
+      </c>
+      <c r="C288" t="s">
+        <v>322</v>
       </c>
       <c r="E288" t="s">
-        <v>763</v>
+        <v>320</v>
       </c>
       <c r="F288" t="s">
-        <v>764</v>
+        <v>319</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -7961,16 +7964,16 @@
         <v>684</v>
       </c>
       <c r="B289" t="s">
-        <v>239</v>
-      </c>
-      <c r="C289" t="s">
-        <v>240</v>
+        <v>762</v>
+      </c>
+      <c r="D289" t="s">
+        <v>712</v>
       </c>
       <c r="E289" t="s">
-        <v>241</v>
+        <v>763</v>
       </c>
       <c r="F289" t="s">
-        <v>242</v>
+        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -7978,16 +7981,16 @@
         <v>684</v>
       </c>
       <c r="B290" t="s">
-        <v>660</v>
-      </c>
-      <c r="D290" t="s">
-        <v>582</v>
+        <v>239</v>
+      </c>
+      <c r="C290" t="s">
+        <v>240</v>
       </c>
       <c r="E290" t="s">
-        <v>324</v>
+        <v>241</v>
       </c>
       <c r="F290" t="s">
-        <v>661</v>
+        <v>242</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -7995,16 +7998,16 @@
         <v>684</v>
       </c>
       <c r="B291" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D291" t="s">
         <v>582</v>
       </c>
       <c r="E291" t="s">
-        <v>289</v>
+        <v>324</v>
       </c>
       <c r="F291" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,16 +8015,16 @@
         <v>684</v>
       </c>
       <c r="B292" t="s">
-        <v>399</v>
-      </c>
-      <c r="C292" t="s">
-        <v>77</v>
+        <v>662</v>
+      </c>
+      <c r="D292" t="s">
+        <v>582</v>
       </c>
       <c r="E292" t="s">
-        <v>391</v>
+        <v>289</v>
       </c>
       <c r="F292" t="s">
-        <v>392</v>
+        <v>663</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -8029,19 +8032,16 @@
         <v>684</v>
       </c>
       <c r="B293" t="s">
-        <v>19</v>
+        <v>399</v>
       </c>
       <c r="C293" t="s">
-        <v>10</v>
-      </c>
-      <c r="D293">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E293" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="F293" t="s">
-        <v>21</v>
+        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8049,19 +8049,19 @@
         <v>684</v>
       </c>
       <c r="B294" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C294" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D294">
         <v>1</v>
       </c>
       <c r="E294" t="s">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="F294" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8072,7 +8072,10 @@
         <v>16</v>
       </c>
       <c r="C295" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="D295">
+        <v>1</v>
       </c>
       <c r="E295" t="s">
         <v>255</v>
@@ -8089,16 +8092,13 @@
         <v>16</v>
       </c>
       <c r="C296" t="s">
-        <v>22</v>
-      </c>
-      <c r="D296">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E296" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="F296" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,19 +8106,19 @@
         <v>684</v>
       </c>
       <c r="B297" t="s">
-        <v>267</v>
+        <v>16</v>
       </c>
       <c r="C297" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D297">
         <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="F297" t="s">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8129,13 +8129,16 @@
         <v>267</v>
       </c>
       <c r="C298" t="s">
-        <v>273</v>
+        <v>10</v>
+      </c>
+      <c r="D298">
+        <v>1</v>
       </c>
       <c r="E298" t="s">
         <v>287</v>
       </c>
       <c r="F298" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8146,13 +8149,13 @@
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E299" t="s">
         <v>287</v>
       </c>
       <c r="F299" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8163,13 +8166,13 @@
         <v>267</v>
       </c>
       <c r="C300" t="s">
-        <v>351</v>
+        <v>268</v>
       </c>
       <c r="E300" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F300" t="s">
-        <v>350</v>
+        <v>269</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8180,16 +8183,13 @@
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>354</v>
-      </c>
-      <c r="D301">
-        <v>1</v>
+        <v>351</v>
       </c>
       <c r="E301" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F301" t="s">
-        <v>296</v>
+        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8200,7 +8200,7 @@
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -8209,7 +8209,7 @@
         <v>291</v>
       </c>
       <c r="F302" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8220,13 +8220,16 @@
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>132</v>
+        <v>293</v>
+      </c>
+      <c r="D303">
+        <v>1</v>
       </c>
       <c r="E303" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F303" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8237,16 +8240,13 @@
         <v>267</v>
       </c>
       <c r="C304" t="s">
-        <v>299</v>
-      </c>
-      <c r="D304">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="E304" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="F304" t="s">
-        <v>302</v>
+        <v>339</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8257,7 +8257,7 @@
         <v>267</v>
       </c>
       <c r="C305" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D305">
         <v>1</v>
@@ -8266,7 +8266,7 @@
         <v>301</v>
       </c>
       <c r="F305" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8277,13 +8277,16 @@
         <v>267</v>
       </c>
       <c r="C306" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
       </c>
       <c r="E306" t="s">
         <v>301</v>
       </c>
       <c r="F306" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -8294,10 +8297,7 @@
         <v>267</v>
       </c>
       <c r="C307" t="s">
-        <v>307</v>
-      </c>
-      <c r="D307">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="E307" t="s">
         <v>301</v>
@@ -8314,7 +8314,7 @@
         <v>267</v>
       </c>
       <c r="C308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -8323,7 +8323,7 @@
         <v>301</v>
       </c>
       <c r="F308" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -8331,16 +8331,19 @@
         <v>684</v>
       </c>
       <c r="B309" t="s">
-        <v>664</v>
-      </c>
-      <c r="D309" t="s">
-        <v>582</v>
+        <v>267</v>
+      </c>
+      <c r="C309" t="s">
+        <v>306</v>
+      </c>
+      <c r="D309">
+        <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F309" t="s">
-        <v>665</v>
+        <v>305</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -8348,19 +8351,16 @@
         <v>684</v>
       </c>
       <c r="B310" t="s">
-        <v>270</v>
-      </c>
-      <c r="C310" t="s">
-        <v>271</v>
-      </c>
-      <c r="D310">
-        <v>1</v>
+        <v>664</v>
+      </c>
+      <c r="D310" t="s">
+        <v>582</v>
       </c>
       <c r="E310" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="F310" t="s">
-        <v>328</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8371,16 +8371,16 @@
         <v>270</v>
       </c>
       <c r="C311" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D311">
         <v>1</v>
       </c>
       <c r="E311" t="s">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="F311" t="s">
-        <v>353</v>
+        <v>328</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -8391,16 +8391,16 @@
         <v>270</v>
       </c>
       <c r="C312" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="D312">
         <v>1</v>
       </c>
       <c r="E312" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="F312" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -8411,16 +8411,16 @@
         <v>270</v>
       </c>
       <c r="C313" t="s">
-        <v>336</v>
+        <v>283</v>
       </c>
       <c r="D313">
         <v>1</v>
       </c>
       <c r="E313" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="F313" t="s">
-        <v>338</v>
+        <v>284</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -8431,16 +8431,16 @@
         <v>270</v>
       </c>
       <c r="C314" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D314">
         <v>1</v>
       </c>
       <c r="E314" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F314" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -8448,19 +8448,19 @@
         <v>684</v>
       </c>
       <c r="B315" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C315" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="D315">
         <v>1</v>
       </c>
       <c r="E315" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="F315" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -8468,16 +8468,19 @@
         <v>684</v>
       </c>
       <c r="B316" t="s">
-        <v>666</v>
-      </c>
-      <c r="D316" t="s">
-        <v>582</v>
+        <v>347</v>
+      </c>
+      <c r="C316" t="s">
+        <v>348</v>
+      </c>
+      <c r="D316">
+        <v>1</v>
       </c>
       <c r="E316" t="s">
-        <v>301</v>
+        <v>349</v>
       </c>
       <c r="F316" t="s">
-        <v>304</v>
+        <v>350</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -8485,16 +8488,16 @@
         <v>684</v>
       </c>
       <c r="B317" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D317" t="s">
         <v>582</v>
       </c>
       <c r="E317" t="s">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="F317" t="s">
-        <v>668</v>
+        <v>304</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8502,16 +8505,16 @@
         <v>684</v>
       </c>
       <c r="B318" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D318" t="s">
         <v>582</v>
       </c>
       <c r="E318" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="F318" t="s">
-        <v>305</v>
+        <v>668</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8519,16 +8522,16 @@
         <v>684</v>
       </c>
       <c r="B319" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D319" t="s">
         <v>582</v>
       </c>
       <c r="E319" t="s">
-        <v>672</v>
+        <v>301</v>
       </c>
       <c r="F319" t="s">
-        <v>671</v>
+        <v>305</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8536,16 +8539,16 @@
         <v>684</v>
       </c>
       <c r="B320" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D320" t="s">
         <v>582</v>
       </c>
       <c r="E320" t="s">
-        <v>234</v>
+        <v>672</v>
       </c>
       <c r="F320" t="s">
-        <v>232</v>
+        <v>671</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,16 +8556,16 @@
         <v>684</v>
       </c>
       <c r="B321" t="s">
-        <v>236</v>
-      </c>
-      <c r="C321" t="s">
-        <v>237</v>
+        <v>673</v>
+      </c>
+      <c r="D321" t="s">
+        <v>582</v>
       </c>
       <c r="E321" t="s">
         <v>234</v>
       </c>
       <c r="F321" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8570,19 +8573,16 @@
         <v>684</v>
       </c>
       <c r="B322" t="s">
-        <v>379</v>
+        <v>236</v>
       </c>
       <c r="C322" t="s">
-        <v>382</v>
-      </c>
-      <c r="D322">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="E322" t="s">
-        <v>375</v>
+        <v>234</v>
       </c>
       <c r="F322" t="s">
-        <v>383</v>
+        <v>238</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>379</v>
       </c>
       <c r="C323" t="s">
-        <v>10</v>
+        <v>382</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -8602,7 +8602,7 @@
         <v>375</v>
       </c>
       <c r="F323" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,7 +8613,7 @@
         <v>379</v>
       </c>
       <c r="C324" t="s">
-        <v>381</v>
+        <v>10</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -8622,7 +8622,7 @@
         <v>375</v>
       </c>
       <c r="F324" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,13 +8633,16 @@
         <v>379</v>
       </c>
       <c r="C325" t="s">
-        <v>77</v>
+        <v>381</v>
+      </c>
+      <c r="D325">
+        <v>1</v>
       </c>
       <c r="E325" t="s">
         <v>375</v>
       </c>
       <c r="F325" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -8647,19 +8650,16 @@
         <v>684</v>
       </c>
       <c r="B326" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C326" t="s">
-        <v>8</v>
-      </c>
-      <c r="D326">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E326" t="s">
         <v>375</v>
       </c>
       <c r="F326" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -8670,7 +8670,7 @@
         <v>373</v>
       </c>
       <c r="C327" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D327">
         <v>1</v>
@@ -8679,7 +8679,7 @@
         <v>375</v>
       </c>
       <c r="F327" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -8687,16 +8687,19 @@
         <v>684</v>
       </c>
       <c r="B328" t="s">
-        <v>674</v>
-      </c>
-      <c r="D328" t="s">
-        <v>582</v>
+        <v>373</v>
+      </c>
+      <c r="C328" t="s">
+        <v>35</v>
+      </c>
+      <c r="D328">
+        <v>1</v>
       </c>
       <c r="E328" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="F328" t="s">
-        <v>407</v>
+        <v>377</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -8704,7 +8707,7 @@
         <v>684</v>
       </c>
       <c r="B329" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D329" t="s">
         <v>582</v>
@@ -8713,44 +8716,41 @@
         <v>406</v>
       </c>
       <c r="F329" t="s">
-        <v>676</v>
+        <v>407</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B330" t="s">
-        <v>685</v>
-      </c>
-      <c r="C330" t="s">
-        <v>686</v>
+        <v>675</v>
+      </c>
+      <c r="D330" t="s">
+        <v>582</v>
       </c>
       <c r="E330" t="s">
-        <v>687</v>
+        <v>406</v>
       </c>
       <c r="F330" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B331" t="s">
-        <v>148</v>
+        <v>685</v>
       </c>
       <c r="C331" t="s">
-        <v>10</v>
-      </c>
-      <c r="D331">
-        <v>1</v>
+        <v>686</v>
       </c>
       <c r="E331" t="s">
-        <v>420</v>
+        <v>687</v>
       </c>
       <c r="F331" t="s">
-        <v>159</v>
+        <v>688</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -8761,13 +8761,16 @@
         <v>148</v>
       </c>
       <c r="C332" t="s">
-        <v>145</v>
+        <v>10</v>
+      </c>
+      <c r="D332">
+        <v>1</v>
       </c>
       <c r="E332" t="s">
         <v>420</v>
       </c>
       <c r="F332" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -8778,13 +8781,13 @@
         <v>148</v>
       </c>
       <c r="C333" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="E333" t="s">
         <v>420</v>
       </c>
       <c r="F333" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -8795,16 +8798,13 @@
         <v>148</v>
       </c>
       <c r="C334" t="s">
-        <v>199</v>
-      </c>
-      <c r="D334">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E334" t="s">
         <v>420</v>
       </c>
       <c r="F334" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -8812,10 +8812,10 @@
         <v>684</v>
       </c>
       <c r="B335" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C335" t="s">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="D335">
         <v>1</v>
@@ -8824,7 +8824,7 @@
         <v>420</v>
       </c>
       <c r="F335" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -8835,7 +8835,7 @@
         <v>152</v>
       </c>
       <c r="C336" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D336">
         <v>1</v>
@@ -8852,16 +8852,19 @@
         <v>684</v>
       </c>
       <c r="B337" t="s">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="C337" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D337">
+        <v>1</v>
       </c>
       <c r="E337" t="s">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="F337" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,13 +8875,13 @@
         <v>201</v>
       </c>
       <c r="C338" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="E338" t="s">
         <v>180</v>
       </c>
       <c r="F338" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -8889,16 +8892,13 @@
         <v>201</v>
       </c>
       <c r="C339" t="s">
-        <v>518</v>
-      </c>
-      <c r="D339">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E339" t="s">
-        <v>520</v>
+        <v>180</v>
       </c>
       <c r="F339" t="s">
-        <v>519</v>
+        <v>164</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -8906,16 +8906,19 @@
         <v>684</v>
       </c>
       <c r="B340" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C340" t="s">
-        <v>368</v>
+        <v>518</v>
+      </c>
+      <c r="D340">
+        <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>367</v>
+        <v>520</v>
       </c>
       <c r="F340" t="s">
-        <v>366</v>
+        <v>519</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -8926,13 +8929,13 @@
         <v>204</v>
       </c>
       <c r="C341" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="E341" t="s">
-        <v>178</v>
+        <v>367</v>
       </c>
       <c r="F341" t="s">
-        <v>183</v>
+        <v>366</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -8943,7 +8946,7 @@
         <v>204</v>
       </c>
       <c r="C342" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E342" t="s">
         <v>178</v>
@@ -8957,16 +8960,16 @@
         <v>684</v>
       </c>
       <c r="B343" t="s">
-        <v>203</v>
-      </c>
-      <c r="D343" t="s">
-        <v>692</v>
+        <v>204</v>
+      </c>
+      <c r="C343" t="s">
+        <v>167</v>
       </c>
       <c r="E343" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F343" t="s">
-        <v>710</v>
+        <v>183</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -8976,17 +8979,14 @@
       <c r="B344" t="s">
         <v>203</v>
       </c>
-      <c r="C344" t="s">
-        <v>35</v>
-      </c>
-      <c r="D344">
-        <v>1</v>
+      <c r="D344" t="s">
+        <v>692</v>
       </c>
       <c r="E344" t="s">
         <v>709</v>
       </c>
       <c r="F344" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -8997,13 +8997,16 @@
         <v>203</v>
       </c>
       <c r="C345" t="s">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="D345">
+        <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>178</v>
+        <v>709</v>
       </c>
       <c r="F345" t="s">
-        <v>181</v>
+        <v>722</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9011,19 +9014,16 @@
         <v>684</v>
       </c>
       <c r="B346" t="s">
-        <v>721</v>
+        <v>203</v>
       </c>
       <c r="C346" t="s">
-        <v>230</v>
-      </c>
-      <c r="D346">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E346" t="s">
-        <v>709</v>
+        <v>178</v>
       </c>
       <c r="F346" t="s">
-        <v>710</v>
+        <v>181</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9031,10 +9031,13 @@
         <v>684</v>
       </c>
       <c r="B347" t="s">
-        <v>723</v>
-      </c>
-      <c r="D347" t="s">
-        <v>692</v>
+        <v>721</v>
+      </c>
+      <c r="C347" t="s">
+        <v>230</v>
+      </c>
+      <c r="D347">
+        <v>1</v>
       </c>
       <c r="E347" t="s">
         <v>709</v>
@@ -9050,17 +9053,14 @@
       <c r="B348" t="s">
         <v>723</v>
       </c>
-      <c r="C348" t="s">
-        <v>35</v>
-      </c>
-      <c r="D348">
-        <v>1</v>
+      <c r="D348" t="s">
+        <v>692</v>
       </c>
       <c r="E348" t="s">
         <v>709</v>
       </c>
       <c r="F348" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9068,16 +9068,19 @@
         <v>684</v>
       </c>
       <c r="B349" t="s">
-        <v>200</v>
+        <v>723</v>
       </c>
       <c r="C349" t="s">
-        <v>104</v>
+        <v>35</v>
+      </c>
+      <c r="D349">
+        <v>1</v>
       </c>
       <c r="E349" t="s">
-        <v>180</v>
+        <v>709</v>
       </c>
       <c r="F349" t="s">
-        <v>162</v>
+        <v>717</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9085,16 +9088,16 @@
         <v>684</v>
       </c>
       <c r="B350" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="C350" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="E350" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="F350" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9105,7 +9108,7 @@
         <v>80</v>
       </c>
       <c r="C351" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E351" t="s">
         <v>59</v>
@@ -9119,19 +9122,16 @@
         <v>684</v>
       </c>
       <c r="B352" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="C352" t="s">
-        <v>334</v>
-      </c>
-      <c r="D352">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E352" t="s">
-        <v>332</v>
+        <v>59</v>
       </c>
       <c r="F352" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -9139,16 +9139,19 @@
         <v>684</v>
       </c>
       <c r="B353" t="s">
-        <v>677</v>
-      </c>
-      <c r="D353" t="s">
-        <v>582</v>
+        <v>335</v>
+      </c>
+      <c r="C353" t="s">
+        <v>334</v>
+      </c>
+      <c r="D353">
+        <v>1</v>
       </c>
       <c r="E353" t="s">
-        <v>475</v>
+        <v>332</v>
       </c>
       <c r="F353" t="s">
-        <v>470</v>
+        <v>334</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -9156,16 +9159,16 @@
         <v>684</v>
       </c>
       <c r="B354" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D354" t="s">
         <v>582</v>
       </c>
       <c r="E354" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
       <c r="F354" t="s">
-        <v>679</v>
+        <v>470</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -9173,16 +9176,16 @@
         <v>684</v>
       </c>
       <c r="B355" t="s">
-        <v>578</v>
-      </c>
-      <c r="C355" t="s">
-        <v>104</v>
+        <v>678</v>
+      </c>
+      <c r="D355" t="s">
+        <v>582</v>
       </c>
       <c r="E355" t="s">
-        <v>577</v>
+        <v>420</v>
       </c>
       <c r="F355" t="s">
-        <v>580</v>
+        <v>679</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -9193,13 +9196,13 @@
         <v>578</v>
       </c>
       <c r="C356" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E356" t="s">
         <v>577</v>
       </c>
       <c r="F356" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -9207,16 +9210,16 @@
         <v>684</v>
       </c>
       <c r="B357" t="s">
-        <v>184</v>
-      </c>
-      <c r="D357" t="s">
-        <v>692</v>
+        <v>578</v>
+      </c>
+      <c r="C357" t="s">
+        <v>78</v>
       </c>
       <c r="E357" t="s">
-        <v>186</v>
+        <v>577</v>
       </c>
       <c r="F357" t="s">
-        <v>190</v>
+        <v>579</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -9226,14 +9229,14 @@
       <c r="B358" t="s">
         <v>184</v>
       </c>
-      <c r="C358" t="s">
-        <v>153</v>
+      <c r="D358" t="s">
+        <v>692</v>
       </c>
       <c r="E358" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F358" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -9244,13 +9247,13 @@
         <v>184</v>
       </c>
       <c r="C359" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E359" t="s">
-        <v>515</v>
+        <v>154</v>
       </c>
       <c r="F359" t="s">
-        <v>516</v>
+        <v>155</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -9267,7 +9270,7 @@
         <v>515</v>
       </c>
       <c r="F360" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -9278,13 +9281,13 @@
         <v>184</v>
       </c>
       <c r="C361" t="s">
-        <v>443</v>
+        <v>171</v>
       </c>
       <c r="E361" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="F361" t="s">
-        <v>446</v>
+        <v>517</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -9295,16 +9298,13 @@
         <v>184</v>
       </c>
       <c r="C362" t="s">
-        <v>261</v>
-      </c>
-      <c r="D362">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E362" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F362" t="s">
-        <v>262</v>
+        <v>446</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -9315,13 +9315,16 @@
         <v>184</v>
       </c>
       <c r="C363" t="s">
-        <v>421</v>
+        <v>261</v>
+      </c>
+      <c r="D363">
+        <v>1</v>
       </c>
       <c r="E363" t="s">
-        <v>420</v>
+        <v>286</v>
       </c>
       <c r="F363" t="s">
-        <v>157</v>
+        <v>262</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -9332,16 +9335,13 @@
         <v>184</v>
       </c>
       <c r="C364" t="s">
-        <v>734</v>
-      </c>
-      <c r="D364">
-        <v>1</v>
+        <v>421</v>
       </c>
       <c r="E364" t="s">
-        <v>735</v>
+        <v>420</v>
       </c>
       <c r="F364" t="s">
-        <v>736</v>
+        <v>157</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -9352,16 +9352,16 @@
         <v>184</v>
       </c>
       <c r="C365" t="s">
-        <v>185</v>
+        <v>734</v>
       </c>
       <c r="D365">
         <v>1</v>
       </c>
       <c r="E365" t="s">
-        <v>186</v>
+        <v>735</v>
       </c>
       <c r="F365" t="s">
-        <v>190</v>
+        <v>736</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -9372,16 +9372,16 @@
         <v>184</v>
       </c>
       <c r="C366" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="D366">
         <v>1</v>
       </c>
       <c r="E366" t="s">
-        <v>298</v>
+        <v>186</v>
       </c>
       <c r="F366" t="s">
-        <v>530</v>
+        <v>190</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -9401,7 +9401,7 @@
         <v>298</v>
       </c>
       <c r="F367" t="s">
-        <v>297</v>
+        <v>530</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -9412,16 +9412,16 @@
         <v>184</v>
       </c>
       <c r="C368" t="s">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="D368">
         <v>1</v>
       </c>
       <c r="E368" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="F368" t="s">
-        <v>327</v>
+        <v>297</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -9432,7 +9432,7 @@
         <v>184</v>
       </c>
       <c r="C369" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D369">
         <v>1</v>
@@ -9441,7 +9441,7 @@
         <v>324</v>
       </c>
       <c r="F369" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -9449,19 +9449,19 @@
         <v>684</v>
       </c>
       <c r="B370" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C370" t="s">
-        <v>189</v>
+        <v>323</v>
       </c>
       <c r="D370">
         <v>1</v>
       </c>
       <c r="E370" t="s">
-        <v>244</v>
+        <v>324</v>
       </c>
       <c r="F370" t="s">
-        <v>194</v>
+        <v>325</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -9472,7 +9472,7 @@
         <v>196</v>
       </c>
       <c r="C371" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D371">
         <v>1</v>
@@ -9481,7 +9481,7 @@
         <v>244</v>
       </c>
       <c r="F371" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -9489,16 +9489,19 @@
         <v>684</v>
       </c>
       <c r="B372" t="s">
-        <v>476</v>
+        <v>196</v>
       </c>
       <c r="C372" t="s">
-        <v>477</v>
+        <v>191</v>
+      </c>
+      <c r="D372">
+        <v>1</v>
       </c>
       <c r="E372" t="s">
-        <v>538</v>
+        <v>244</v>
       </c>
       <c r="F372" t="s">
-        <v>465</v>
+        <v>195</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -9506,16 +9509,16 @@
         <v>684</v>
       </c>
       <c r="B373" t="s">
-        <v>45</v>
+        <v>476</v>
       </c>
       <c r="C373" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="E373" t="s">
-        <v>453</v>
+        <v>538</v>
       </c>
       <c r="F373" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -9526,13 +9529,13 @@
         <v>45</v>
       </c>
       <c r="C374" t="s">
-        <v>410</v>
+        <v>459</v>
       </c>
       <c r="E374" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="F374" t="s">
-        <v>411</v>
+        <v>460</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -9543,13 +9546,13 @@
         <v>45</v>
       </c>
       <c r="C375" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E375" t="s">
         <v>406</v>
       </c>
       <c r="F375" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -9560,13 +9563,13 @@
         <v>45</v>
       </c>
       <c r="C376" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E376" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F376" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -9577,13 +9580,13 @@
         <v>45</v>
       </c>
       <c r="C377" t="s">
-        <v>490</v>
+        <v>402</v>
       </c>
       <c r="E377" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="F377" t="s">
-        <v>492</v>
+        <v>401</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -9600,7 +9603,7 @@
         <v>491</v>
       </c>
       <c r="F378" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -9611,13 +9614,13 @@
         <v>45</v>
       </c>
       <c r="C379" t="s">
-        <v>182</v>
+        <v>490</v>
       </c>
       <c r="E379" t="s">
-        <v>256</v>
+        <v>491</v>
       </c>
       <c r="F379" t="s">
-        <v>181</v>
+        <v>493</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -9628,13 +9631,13 @@
         <v>45</v>
       </c>
       <c r="C380" t="s">
-        <v>562</v>
+        <v>182</v>
       </c>
       <c r="E380" t="s">
-        <v>563</v>
+        <v>256</v>
       </c>
       <c r="F380" t="s">
-        <v>564</v>
+        <v>181</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -9651,7 +9654,7 @@
         <v>563</v>
       </c>
       <c r="F381" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -9662,16 +9665,13 @@
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>415</v>
-      </c>
-      <c r="D382">
-        <v>1</v>
+        <v>562</v>
       </c>
       <c r="E382" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="F382" t="s">
-        <v>416</v>
+        <v>565</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -9682,13 +9682,16 @@
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>376</v>
+        <v>415</v>
+      </c>
+      <c r="D383">
+        <v>1</v>
       </c>
       <c r="E383" t="s">
-        <v>375</v>
+        <v>414</v>
       </c>
       <c r="F383" t="s">
-        <v>374</v>
+        <v>416</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -9699,13 +9702,13 @@
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="E384" t="s">
-        <v>444</v>
+        <v>375</v>
       </c>
       <c r="F384" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -9716,16 +9719,13 @@
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>264</v>
-      </c>
-      <c r="D385">
-        <v>1</v>
+        <v>443</v>
       </c>
       <c r="E385" t="s">
-        <v>286</v>
+        <v>444</v>
       </c>
       <c r="F385" t="s">
-        <v>263</v>
+        <v>445</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -9736,13 +9736,16 @@
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>372</v>
+        <v>264</v>
+      </c>
+      <c r="D386">
+        <v>1</v>
       </c>
       <c r="E386" t="s">
-        <v>369</v>
+        <v>286</v>
       </c>
       <c r="F386" t="s">
-        <v>559</v>
+        <v>263</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,16 +9756,13 @@
         <v>45</v>
       </c>
       <c r="C387" t="s">
-        <v>187</v>
-      </c>
-      <c r="D387">
-        <v>1</v>
+        <v>372</v>
       </c>
       <c r="E387" t="s">
-        <v>188</v>
+        <v>369</v>
       </c>
       <c r="F387" t="s">
-        <v>190</v>
+        <v>559</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -9773,16 +9773,16 @@
         <v>45</v>
       </c>
       <c r="C388" t="s">
-        <v>281</v>
+        <v>187</v>
       </c>
       <c r="D388">
         <v>1</v>
       </c>
       <c r="E388" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="F388" t="s">
-        <v>282</v>
+        <v>190</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -9793,13 +9793,16 @@
         <v>45</v>
       </c>
       <c r="C389" t="s">
-        <v>123</v>
+        <v>281</v>
+      </c>
+      <c r="D389">
+        <v>1</v>
       </c>
       <c r="E389" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="F389" t="s">
-        <v>123</v>
+        <v>282</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -9810,16 +9813,13 @@
         <v>45</v>
       </c>
       <c r="C390" t="s">
-        <v>52</v>
-      </c>
-      <c r="D390">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E390" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="F390" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -9830,7 +9830,7 @@
         <v>45</v>
       </c>
       <c r="C391" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D391">
         <v>1</v>
@@ -9839,7 +9839,7 @@
         <v>50</v>
       </c>
       <c r="F391" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -9850,13 +9850,16 @@
         <v>45</v>
       </c>
       <c r="C392" t="s">
-        <v>125</v>
+        <v>49</v>
+      </c>
+      <c r="D392">
+        <v>1</v>
       </c>
       <c r="E392" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="F392" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -9864,16 +9867,16 @@
         <v>684</v>
       </c>
       <c r="B393" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C393" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="E393" t="s">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="F393" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -9881,16 +9884,16 @@
         <v>684</v>
       </c>
       <c r="B394" t="s">
-        <v>569</v>
+        <v>202</v>
       </c>
       <c r="C394" t="s">
-        <v>571</v>
+        <v>167</v>
       </c>
       <c r="E394" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F394" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -9907,7 +9910,7 @@
         <v>256</v>
       </c>
       <c r="F395" t="s">
-        <v>572</v>
+        <v>183</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -9918,13 +9921,13 @@
         <v>569</v>
       </c>
       <c r="C396" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E396" t="s">
         <v>256</v>
       </c>
       <c r="F396" t="s">
-        <v>183</v>
+        <v>572</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -9932,16 +9935,16 @@
         <v>684</v>
       </c>
       <c r="B397" t="s">
-        <v>48</v>
+        <v>569</v>
       </c>
       <c r="C397" t="s">
-        <v>171</v>
+        <v>570</v>
       </c>
       <c r="E397" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F397" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -9952,13 +9955,13 @@
         <v>48</v>
       </c>
       <c r="C398" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E398" t="s">
         <v>255</v>
       </c>
       <c r="F398" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -9969,13 +9972,13 @@
         <v>48</v>
       </c>
       <c r="C399" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E399" t="s">
         <v>255</v>
       </c>
       <c r="F399" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -9986,16 +9989,13 @@
         <v>48</v>
       </c>
       <c r="C400" t="s">
-        <v>55</v>
-      </c>
-      <c r="D400">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E400" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F400" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -10006,7 +10006,7 @@
         <v>48</v>
       </c>
       <c r="C401" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D401">
         <v>1</v>
@@ -10023,19 +10023,19 @@
         <v>684</v>
       </c>
       <c r="B402" t="s">
-        <v>456</v>
+        <v>48</v>
       </c>
       <c r="C402" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="D402">
         <v>1</v>
       </c>
       <c r="E402" t="s">
-        <v>453</v>
+        <v>50</v>
       </c>
       <c r="F402" t="s">
-        <v>457</v>
+        <v>53</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -10043,19 +10043,19 @@
         <v>684</v>
       </c>
       <c r="B403" t="s">
-        <v>108</v>
+        <v>456</v>
       </c>
       <c r="C403" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="D403">
         <v>1</v>
       </c>
       <c r="E403" t="s">
-        <v>115</v>
+        <v>453</v>
       </c>
       <c r="F403" t="s">
-        <v>114</v>
+        <v>457</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -10066,7 +10066,7 @@
         <v>108</v>
       </c>
       <c r="C404" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D404">
         <v>1</v>
@@ -10075,7 +10075,7 @@
         <v>115</v>
       </c>
       <c r="F404" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -10086,7 +10086,7 @@
         <v>108</v>
       </c>
       <c r="C405" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D405">
         <v>1</v>
@@ -10095,7 +10095,7 @@
         <v>115</v>
       </c>
       <c r="F405" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -10106,7 +10106,7 @@
         <v>108</v>
       </c>
       <c r="C406" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D406">
         <v>1</v>
@@ -10115,7 +10115,7 @@
         <v>115</v>
       </c>
       <c r="F406" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -10126,7 +10126,7 @@
         <v>108</v>
       </c>
       <c r="C407" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D407">
         <v>1</v>
@@ -10135,7 +10135,7 @@
         <v>115</v>
       </c>
       <c r="F407" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -10143,16 +10143,19 @@
         <v>684</v>
       </c>
       <c r="B408" t="s">
-        <v>756</v>
-      </c>
-      <c r="D408" t="s">
-        <v>712</v>
+        <v>108</v>
+      </c>
+      <c r="C408" t="s">
+        <v>120</v>
+      </c>
+      <c r="D408">
+        <v>1</v>
       </c>
       <c r="E408" t="s">
-        <v>255</v>
+        <v>115</v>
       </c>
       <c r="F408" t="s">
-        <v>757</v>
+        <v>121</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -10160,16 +10163,16 @@
         <v>684</v>
       </c>
       <c r="B409" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D409" t="s">
         <v>712</v>
       </c>
       <c r="E409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F409" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -10177,16 +10180,16 @@
         <v>684</v>
       </c>
       <c r="B410" t="s">
-        <v>680</v>
+        <v>754</v>
       </c>
       <c r="D410" t="s">
-        <v>582</v>
+        <v>712</v>
       </c>
       <c r="E410" t="s">
-        <v>298</v>
+        <v>256</v>
       </c>
       <c r="F410" t="s">
-        <v>297</v>
+        <v>755</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -10194,19 +10197,16 @@
         <v>684</v>
       </c>
       <c r="B411" t="s">
-        <v>197</v>
-      </c>
-      <c r="C411" t="s">
-        <v>189</v>
-      </c>
-      <c r="D411">
-        <v>1</v>
+        <v>680</v>
+      </c>
+      <c r="D411" t="s">
+        <v>582</v>
       </c>
       <c r="E411" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="F411" t="s">
-        <v>192</v>
+        <v>297</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -10217,7 +10217,7 @@
         <v>197</v>
       </c>
       <c r="C412" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D412">
         <v>1</v>
@@ -10226,7 +10226,7 @@
         <v>244</v>
       </c>
       <c r="F412" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -10234,16 +10234,19 @@
         <v>684</v>
       </c>
       <c r="B413" t="s">
-        <v>566</v>
+        <v>197</v>
       </c>
       <c r="C413" t="s">
-        <v>567</v>
+        <v>191</v>
+      </c>
+      <c r="D413">
+        <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>563</v>
+        <v>244</v>
       </c>
       <c r="F413" t="s">
-        <v>565</v>
+        <v>193</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -10254,7 +10257,7 @@
         <v>566</v>
       </c>
       <c r="C414" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E414" t="s">
         <v>563</v>
@@ -10271,7 +10274,7 @@
         <v>566</v>
       </c>
       <c r="C415" t="s">
-        <v>167</v>
+        <v>568</v>
       </c>
       <c r="E415" t="s">
         <v>563</v>
@@ -10285,15 +10288,32 @@
         <v>684</v>
       </c>
       <c r="B416" t="s">
+        <v>566</v>
+      </c>
+      <c r="C416" t="s">
+        <v>167</v>
+      </c>
+      <c r="E416" t="s">
+        <v>563</v>
+      </c>
+      <c r="F416" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>684</v>
+      </c>
+      <c r="B417" t="s">
         <v>403</v>
       </c>
-      <c r="C416" t="s">
+      <c r="C417" t="s">
         <v>104</v>
       </c>
-      <c r="E416" t="s">
+      <c r="E417" t="s">
         <v>400</v>
       </c>
-      <c r="F416" t="s">
+      <c r="F417" t="s">
         <v>401</v>
       </c>
     </row>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30013"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00039A75-A20C-4A49-B392-46CC2E41BB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC677896-8741-4F3B-A5BD-9CC686A06A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="785">
   <si>
     <t>Class</t>
   </si>
@@ -846,9 +846,6 @@
     <t>addGeometricShape</t>
   </si>
   <si>
-    <t>createSmileyFace</t>
-  </si>
-  <si>
     <t>fill</t>
   </si>
   <si>
@@ -2344,6 +2341,48 @@
   </si>
   <si>
     <t>DataValidationAlertStyle</t>
+  </si>
+  <si>
+    <t>ShapeFill</t>
+  </si>
+  <si>
+    <t>excel-shape-fill-and-line-formatting</t>
+  </si>
+  <si>
+    <t>setSolidFill</t>
+  </si>
+  <si>
+    <t>setFillProperties</t>
+  </si>
+  <si>
+    <t>transparency</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>clearFill</t>
+  </si>
+  <si>
+    <t>ShapeLineFormat</t>
+  </si>
+  <si>
+    <t>formatLine</t>
+  </si>
+  <si>
+    <t>hideLine</t>
+  </si>
+  <si>
+    <t>lineFormat</t>
+  </si>
+  <si>
+    <t>inspectFormatting</t>
+  </si>
+  <si>
+    <t>ShapeLineDashStyle</t>
+  </si>
+  <si>
+    <t>ShapeLineStyle</t>
   </si>
 </sst>
 </file>
@@ -2451,10 +2490,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F417" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F417" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F417">
-    <sortCondition ref="B1:B417"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F425" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F425" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F425">
+    <sortCondition ref="B1:B425"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2785,7 +2824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F417"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -2798,16 +2837,16 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -2818,61 +2857,61 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E2" t="s">
         <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B3" t="s">
         <v>258</v>
       </c>
       <c r="C3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E3" t="s">
         <v>435</v>
       </c>
-      <c r="E3" t="s">
-        <v>436</v>
-      </c>
       <c r="F3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B4" t="s">
         <v>258</v>
       </c>
       <c r="C4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" t="s">
         <v>573</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B5" t="s">
         <v>258</v>
@@ -2884,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F5" t="s">
         <v>260</v>
@@ -2892,155 +2931,155 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B9" t="s">
+        <v>609</v>
+      </c>
+      <c r="D9" t="s">
+        <v>581</v>
+      </c>
+      <c r="E9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" t="s">
         <v>610</v>
-      </c>
-      <c r="D9" t="s">
-        <v>582</v>
-      </c>
-      <c r="E9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F9" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" t="s">
         <v>370</v>
       </c>
-      <c r="C10" t="s">
-        <v>371</v>
-      </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F12" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F13" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -3057,299 +3096,299 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E15" t="s">
         <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B16" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E16" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" t="s">
         <v>391</v>
-      </c>
-      <c r="F16" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E17" t="s">
+        <v>390</v>
+      </c>
+      <c r="F17" t="s">
         <v>391</v>
-      </c>
-      <c r="F17" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B18" t="s">
+        <v>615</v>
+      </c>
+      <c r="D18" t="s">
+        <v>581</v>
+      </c>
+      <c r="E18" t="s">
         <v>616</v>
       </c>
-      <c r="D18" t="s">
-        <v>582</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>617</v>
-      </c>
-      <c r="F18" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B19" t="s">
+        <v>618</v>
+      </c>
+      <c r="D19" t="s">
+        <v>581</v>
+      </c>
+      <c r="E19" t="s">
+        <v>616</v>
+      </c>
+      <c r="F19" t="s">
         <v>619</v>
-      </c>
-      <c r="D19" t="s">
-        <v>582</v>
-      </c>
-      <c r="E19" t="s">
-        <v>617</v>
-      </c>
-      <c r="F19" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B23" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D23" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E23" t="s">
+        <v>390</v>
+      </c>
+      <c r="F23" t="s">
         <v>391</v>
-      </c>
-      <c r="F23" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D24" t="s">
         <v>78</v>
       </c>
       <c r="E24" t="s">
+        <v>708</v>
+      </c>
+      <c r="F24" t="s">
         <v>709</v>
-      </c>
-      <c r="F24" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B25" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D25" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
+        <v>708</v>
+      </c>
+      <c r="F25" t="s">
         <v>709</v>
-      </c>
-      <c r="F25" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
+        <v>389</v>
+      </c>
+      <c r="E26" t="s">
         <v>390</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>391</v>
-      </c>
-      <c r="F26" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C27" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" t="s">
         <v>390</v>
       </c>
-      <c r="E27" t="s">
-        <v>391</v>
-      </c>
       <c r="F27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C28" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" t="s">
         <v>390</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>391</v>
-      </c>
-      <c r="F28" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C29" t="s">
+        <v>389</v>
+      </c>
+      <c r="E29" t="s">
         <v>390</v>
       </c>
-      <c r="E29" t="s">
-        <v>391</v>
-      </c>
       <c r="F29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B30" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C30" t="s">
         <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F30" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B31" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D31" t="s">
         <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F31" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B32" t="s">
         <v>85</v>
@@ -3366,7 +3405,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -3383,112 +3422,112 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E34" t="s">
+        <v>589</v>
+      </c>
+      <c r="F34" t="s">
         <v>590</v>
-      </c>
-      <c r="F34" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B35" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
+        <v>542</v>
+      </c>
+      <c r="F35" t="s">
         <v>543</v>
-      </c>
-      <c r="F35" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B36" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C36" t="s">
         <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B37" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C37" t="s">
         <v>171</v>
       </c>
       <c r="E37" t="s">
+        <v>531</v>
+      </c>
+      <c r="F37" t="s">
         <v>532</v>
-      </c>
-      <c r="F37" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B38" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C38" t="s">
         <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C39" t="s">
         <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B40" t="s">
         <v>136</v>
@@ -3505,7 +3544,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B41" t="s">
         <v>136</v>
@@ -3522,234 +3561,234 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B42" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" t="s">
         <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F42" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B43" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C43" t="s">
         <v>171</v>
       </c>
       <c r="E43" t="s">
+        <v>531</v>
+      </c>
+      <c r="F43" t="s">
         <v>532</v>
-      </c>
-      <c r="F43" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B44" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
         <v>169</v>
       </c>
       <c r="E44" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C45" t="s">
         <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B46" t="s">
+        <v>731</v>
+      </c>
+      <c r="D46" t="s">
+        <v>691</v>
+      </c>
+      <c r="E46" t="s">
+        <v>728</v>
+      </c>
+      <c r="F46" t="s">
         <v>732</v>
-      </c>
-      <c r="D46" t="s">
-        <v>692</v>
-      </c>
-      <c r="E46" t="s">
-        <v>729</v>
-      </c>
-      <c r="F46" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C47" t="s">
         <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F47" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B48" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C48" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E48" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F48" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B49" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C49" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E49" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F49" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B51" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E51" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F51" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B52" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E52" t="s">
+        <v>542</v>
+      </c>
+      <c r="F52" t="s">
         <v>543</v>
-      </c>
-      <c r="F52" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B53" t="s">
+        <v>541</v>
+      </c>
+      <c r="C53" t="s">
+        <v>551</v>
+      </c>
+      <c r="E53" t="s">
         <v>542</v>
       </c>
-      <c r="C53" t="s">
-        <v>552</v>
-      </c>
-      <c r="E53" t="s">
-        <v>543</v>
-      </c>
       <c r="F53" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B54" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C54" t="s">
         <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F54" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B55" t="s">
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3758,12 +3797,12 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B56" t="s">
         <v>142</v>
@@ -3783,41 +3822,41 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B57" t="s">
+        <v>740</v>
+      </c>
+      <c r="D57" t="s">
+        <v>691</v>
+      </c>
+      <c r="E57" t="s">
+        <v>736</v>
+      </c>
+      <c r="F57" t="s">
         <v>741</v>
-      </c>
-      <c r="D57" t="s">
-        <v>692</v>
-      </c>
-      <c r="E57" t="s">
-        <v>737</v>
-      </c>
-      <c r="F57" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B58" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D58" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E58" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F58" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B59" t="s">
         <v>198</v>
@@ -3834,206 +3873,206 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B60" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D60" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E60" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F60" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B61" t="s">
+        <v>727</v>
+      </c>
+      <c r="D61" t="s">
+        <v>691</v>
+      </c>
+      <c r="E61" t="s">
         <v>728</v>
       </c>
-      <c r="D61" t="s">
-        <v>692</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>729</v>
-      </c>
-      <c r="F61" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B62" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D62" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E62" t="s">
+        <v>728</v>
+      </c>
+      <c r="F62" t="s">
         <v>729</v>
-      </c>
-      <c r="F62" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B63" t="s">
         <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F63" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B64" t="s">
         <v>133</v>
       </c>
       <c r="C64" t="s">
+        <v>483</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
         <v>484</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>485</v>
-      </c>
-      <c r="F64" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B65" t="s">
         <v>133</v>
       </c>
       <c r="C65" t="s">
+        <v>597</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
         <v>598</v>
       </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>599</v>
-      </c>
-      <c r="F65" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
+        <v>598</v>
+      </c>
+      <c r="F66" t="s">
         <v>599</v>
-      </c>
-      <c r="F66" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B67" t="s">
         <v>133</v>
       </c>
       <c r="D67" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E67" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F67" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B68" t="s">
         <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E68" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F68" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B69" t="s">
         <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E69" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F69" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B70" t="s">
         <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E70" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F70" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B71" t="s">
         <v>133</v>
@@ -4053,7 +4092,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B72" t="s">
         <v>133</v>
@@ -4073,7 +4112,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B73" t="s">
         <v>133</v>
@@ -4090,13 +4129,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B74" t="s">
         <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E74" t="s">
         <v>174</v>
@@ -4107,7 +4146,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B75" t="s">
         <v>133</v>
@@ -4124,7 +4163,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B76" t="s">
         <v>133</v>
@@ -4141,41 +4180,41 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B77" t="s">
+        <v>620</v>
+      </c>
+      <c r="D77" t="s">
+        <v>581</v>
+      </c>
+      <c r="E77" t="s">
+        <v>598</v>
+      </c>
+      <c r="F77" t="s">
         <v>621</v>
-      </c>
-      <c r="D77" t="s">
-        <v>582</v>
-      </c>
-      <c r="E77" t="s">
-        <v>599</v>
-      </c>
-      <c r="F77" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B78" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D78" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E78" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F78" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B79" t="s">
         <v>248</v>
@@ -4195,7 +4234,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B80" t="s">
         <v>248</v>
@@ -4212,7 +4251,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B81" t="s">
         <v>124</v>
@@ -4229,7 +4268,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B82" t="s">
         <v>122</v>
@@ -4249,7 +4288,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B83" t="s">
         <v>128</v>
@@ -4266,75 +4305,75 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B84" t="s">
+        <v>580</v>
+      </c>
+      <c r="D84" t="s">
         <v>581</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>582</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>583</v>
-      </c>
-      <c r="F84" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B85" t="s">
+        <v>710</v>
+      </c>
+      <c r="D85" t="s">
         <v>711</v>
       </c>
-      <c r="D85" t="s">
-        <v>712</v>
-      </c>
       <c r="E85" t="s">
+        <v>708</v>
+      </c>
+      <c r="F85" t="s">
         <v>709</v>
-      </c>
-      <c r="F85" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B86" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D86" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E86" t="s">
         <v>102</v>
       </c>
       <c r="F86" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B87" t="s">
+        <v>625</v>
+      </c>
+      <c r="D87" t="s">
+        <v>581</v>
+      </c>
+      <c r="E87" t="s">
+        <v>323</v>
+      </c>
+      <c r="F87" t="s">
         <v>626</v>
-      </c>
-      <c r="D87" t="s">
-        <v>582</v>
-      </c>
-      <c r="E87" t="s">
-        <v>324</v>
-      </c>
-      <c r="F87" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B88" t="s">
         <v>58</v>
@@ -4351,27 +4390,27 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B89" t="s">
+        <v>358</v>
+      </c>
+      <c r="C89" t="s">
+        <v>360</v>
+      </c>
+      <c r="E89" t="s">
+        <v>421</v>
+      </c>
+      <c r="F89" t="s">
         <v>359</v>
-      </c>
-      <c r="C89" t="s">
-        <v>361</v>
-      </c>
-      <c r="E89" t="s">
-        <v>422</v>
-      </c>
-      <c r="F89" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
@@ -4380,18 +4419,18 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F90" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B91" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C91" t="s">
         <v>199</v>
@@ -4400,35 +4439,35 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F91" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B92" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C92" t="s">
+        <v>424</v>
+      </c>
+      <c r="E92" t="s">
         <v>425</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>426</v>
-      </c>
-      <c r="F92" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B93" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C93" t="s">
         <v>8</v>
@@ -4437,137 +4476,137 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B94" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C94" t="s">
         <v>165</v>
       </c>
       <c r="E94" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F94" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B95" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C95" t="s">
         <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F95" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C96" t="s">
         <v>182</v>
       </c>
       <c r="E96" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F96" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B97" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C97" t="s">
         <v>182</v>
       </c>
       <c r="E97" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F97" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C98" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E98" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F98" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B99" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C99" t="s">
+        <v>480</v>
+      </c>
+      <c r="E99" t="s">
+        <v>482</v>
+      </c>
+      <c r="F99" t="s">
         <v>481</v>
-      </c>
-      <c r="E99" t="s">
-        <v>483</v>
-      </c>
-      <c r="F99" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C100" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E100" t="s">
+        <v>422</v>
+      </c>
+      <c r="F100" t="s">
         <v>423</v>
-      </c>
-      <c r="F100" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
@@ -4576,18 +4615,18 @@
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
@@ -4596,32 +4635,32 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F102" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B103" t="s">
+        <v>427</v>
+      </c>
+      <c r="C103" t="s">
         <v>428</v>
       </c>
-      <c r="C103" t="s">
+      <c r="E103" t="s">
         <v>429</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>430</v>
-      </c>
-      <c r="F103" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B104" t="s">
         <v>89</v>
@@ -4638,7 +4677,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B105" t="s">
         <v>89</v>
@@ -4655,13 +4694,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B106" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D106" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -4672,13 +4711,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B107" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D107" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E107" t="s">
         <v>59</v>
@@ -4689,13 +4728,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B108" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D108" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E108" t="s">
         <v>59</v>
@@ -4706,7 +4745,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B109" t="s">
         <v>56</v>
@@ -4723,7 +4762,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B110" t="s">
         <v>56</v>
@@ -4740,7 +4779,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B111" t="s">
         <v>56</v>
@@ -4757,7 +4796,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B112" t="s">
         <v>56</v>
@@ -4774,7 +4813,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B113" t="s">
         <v>56</v>
@@ -4794,7 +4833,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B114" t="s">
         <v>56</v>
@@ -4811,7 +4850,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B115" t="s">
         <v>56</v>
@@ -4828,7 +4867,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B116" t="s">
         <v>56</v>
@@ -4845,7 +4884,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B117" t="s">
         <v>56</v>
@@ -4862,7 +4901,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s">
         <v>54</v>
@@ -4882,7 +4921,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B119" t="s">
         <v>54</v>
@@ -4902,7 +4941,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B120" t="s">
         <v>54</v>
@@ -4922,13 +4961,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B121" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D121" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E121" t="s">
         <v>59</v>
@@ -4939,13 +4978,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B122" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D122" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E122" t="s">
         <v>59</v>
@@ -4956,24 +4995,24 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B123" t="s">
+        <v>630</v>
+      </c>
+      <c r="D123" t="s">
+        <v>581</v>
+      </c>
+      <c r="E123" t="s">
+        <v>632</v>
+      </c>
+      <c r="F123" t="s">
         <v>631</v>
-      </c>
-      <c r="D123" t="s">
-        <v>582</v>
-      </c>
-      <c r="E123" t="s">
-        <v>633</v>
-      </c>
-      <c r="F123" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B124" t="s">
         <v>94</v>
@@ -4990,24 +5029,24 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B125" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D125" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E125" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F125" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B126" t="s">
         <v>76</v>
@@ -5024,7 +5063,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B127" t="s">
         <v>76</v>
@@ -5041,7 +5080,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B128" t="s">
         <v>76</v>
@@ -5058,13 +5097,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B129" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D129" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E129" t="s">
         <v>59</v>
@@ -5075,7 +5114,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B130" t="s">
         <v>64</v>
@@ -5092,7 +5131,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B131" t="s">
         <v>83</v>
@@ -5109,13 +5148,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B132" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E132" t="s">
         <v>59</v>
@@ -5126,58 +5165,58 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B133" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D133" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E133" t="s">
+        <v>336</v>
+      </c>
+      <c r="F133" t="s">
         <v>337</v>
-      </c>
-      <c r="F133" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B134" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D134" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E134" t="s">
+        <v>429</v>
+      </c>
+      <c r="F134" t="s">
         <v>430</v>
-      </c>
-      <c r="F134" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B135" t="s">
+        <v>460</v>
+      </c>
+      <c r="C135" t="s">
         <v>461</v>
       </c>
-      <c r="C135" t="s">
+      <c r="E135" t="s">
         <v>462</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>463</v>
-      </c>
-      <c r="F135" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B136" t="s">
         <v>91</v>
@@ -5194,10 +5233,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B137" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -5206,15 +5245,15 @@
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F137" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B138" t="s">
         <v>32</v>
@@ -5234,7 +5273,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B139" t="s">
         <v>32</v>
@@ -5254,7 +5293,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B140" t="s">
         <v>32</v>
@@ -5271,7 +5310,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B141" t="s">
         <v>32</v>
@@ -5291,7 +5330,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B142" t="s">
         <v>29</v>
@@ -5311,7 +5350,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B143" t="s">
         <v>29</v>
@@ -5331,7 +5370,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B144" t="s">
         <v>29</v>
@@ -5351,7 +5390,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B145" t="s">
         <v>41</v>
@@ -5371,7 +5410,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B146" t="s">
         <v>41</v>
@@ -5391,7 +5430,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B147" t="s">
         <v>41</v>
@@ -5411,7 +5450,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s">
         <v>68</v>
@@ -5428,7 +5467,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B149" t="s">
         <v>224</v>
@@ -5445,7 +5484,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B150" t="s">
         <v>224</v>
@@ -5462,7 +5501,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B151" t="s">
         <v>212</v>
@@ -5479,13 +5518,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B152" t="s">
         <v>212</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E152" t="s">
         <v>208</v>
@@ -5496,7 +5535,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B153" t="s">
         <v>212</v>
@@ -5513,13 +5552,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B154" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D154" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
@@ -5530,13 +5569,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D155" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
@@ -5547,13 +5586,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B156" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D156" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E156" t="s">
         <v>208</v>
@@ -5564,7 +5603,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B157" t="s">
         <v>243</v>
@@ -5581,7 +5620,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B158" t="s">
         <v>243</v>
@@ -5598,393 +5637,393 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B159" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D159" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E159" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F159" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B160" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D160" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E160" t="s">
         <v>256</v>
       </c>
       <c r="F160" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B161" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C161" t="s">
         <v>92</v>
       </c>
       <c r="E161" t="s">
+        <v>452</v>
+      </c>
+      <c r="F161" t="s">
         <v>453</v>
-      </c>
-      <c r="F161" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B162" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C162" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E162" t="s">
+        <v>723</v>
+      </c>
+      <c r="F162" t="s">
         <v>724</v>
-      </c>
-      <c r="F162" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B163" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C163" t="s">
         <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F163" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B164" t="s">
+        <v>641</v>
+      </c>
+      <c r="D164" t="s">
+        <v>581</v>
+      </c>
+      <c r="E164" t="s">
+        <v>643</v>
+      </c>
+      <c r="F164" t="s">
         <v>642</v>
-      </c>
-      <c r="D164" t="s">
-        <v>582</v>
-      </c>
-      <c r="E164" t="s">
-        <v>644</v>
-      </c>
-      <c r="F164" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B165" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D165" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E165" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F165" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B166" t="s">
+        <v>688</v>
+      </c>
+      <c r="D166" t="s">
+        <v>581</v>
+      </c>
+      <c r="E166" t="s">
         <v>689</v>
       </c>
-      <c r="D166" t="s">
-        <v>582</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>690</v>
-      </c>
-      <c r="F166" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B167" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D167" t="s">
         <v>78</v>
       </c>
       <c r="E167" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F167" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B168" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D168" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E168" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F168" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B169" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D169" t="s">
         <v>78</v>
       </c>
       <c r="E169" t="s">
+        <v>589</v>
+      </c>
+      <c r="F169" t="s">
         <v>590</v>
-      </c>
-      <c r="F169" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B170" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D170" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E170" t="s">
+        <v>589</v>
+      </c>
+      <c r="F170" t="s">
         <v>590</v>
-      </c>
-      <c r="F170" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B171" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D171" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E171" t="s">
+        <v>390</v>
+      </c>
+      <c r="F171" t="s">
         <v>391</v>
-      </c>
-      <c r="F171" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B172" t="s">
+        <v>556</v>
+      </c>
+      <c r="C172" t="s">
         <v>557</v>
       </c>
-      <c r="C172" t="s">
+      <c r="E172" t="s">
+        <v>368</v>
+      </c>
+      <c r="F172" t="s">
         <v>558</v>
-      </c>
-      <c r="E172" t="s">
-        <v>369</v>
-      </c>
-      <c r="F172" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B173" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D173" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E173" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F173" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B174" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D174" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E174" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F174" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B175" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D175" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E175" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F175" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B176" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C176" t="s">
+        <v>695</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176" t="s">
         <v>696</v>
       </c>
-      <c r="D176">
-        <v>1</v>
-      </c>
-      <c r="E176" t="s">
-        <v>697</v>
-      </c>
       <c r="F176" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B177" t="s">
+        <v>693</v>
+      </c>
+      <c r="C177" t="s">
         <v>694</v>
       </c>
-      <c r="C177" t="s">
-        <v>695</v>
-      </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177" t="s">
+        <v>696</v>
+      </c>
+      <c r="F177" t="s">
         <v>697</v>
-      </c>
-      <c r="F177" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B178" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D178" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E178" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B179" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D179" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E179" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F179" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B180" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D180" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E180" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F180" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B181" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D181" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -5995,7 +6034,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B182" t="s">
         <v>72</v>
@@ -6012,7 +6051,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B183" t="s">
         <v>72</v>
@@ -6029,172 +6068,172 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B184" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C184" t="s">
         <v>84</v>
       </c>
       <c r="E184" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F184" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B185" t="s">
+        <v>649</v>
+      </c>
+      <c r="D185" t="s">
+        <v>581</v>
+      </c>
+      <c r="E185" t="s">
         <v>650</v>
       </c>
-      <c r="D185" t="s">
-        <v>582</v>
-      </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>651</v>
-      </c>
-      <c r="F185" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B186" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D186" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E186" t="s">
+        <v>525</v>
+      </c>
+      <c r="F186" t="s">
         <v>526</v>
-      </c>
-      <c r="F186" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B187" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D187" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E187" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F187" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B188" t="s">
+        <v>341</v>
+      </c>
+      <c r="C188" t="s">
         <v>342</v>
       </c>
-      <c r="C188" t="s">
-        <v>343</v>
-      </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B189" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C189" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F189" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B190" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C190" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F190" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B191" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F191" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B192" t="s">
         <v>9</v>
       </c>
       <c r="D192" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B193" t="s">
         <v>9</v>
@@ -6214,7 +6253,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B194" t="s">
         <v>9</v>
@@ -6231,7 +6270,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
@@ -6251,95 +6290,95 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B196" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D196" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E196" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F196" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B197" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C197" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E197" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F197" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B198" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C198" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E198" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F198" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B199" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C199" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E199" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F199" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B200" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C200" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E200" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F200" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B201" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C201" t="s">
         <v>10</v>
@@ -6348,35 +6387,35 @@
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F201" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B202" t="s">
+        <v>700</v>
+      </c>
+      <c r="D202" t="s">
+        <v>691</v>
+      </c>
+      <c r="E202" t="s">
         <v>701</v>
       </c>
-      <c r="D202" t="s">
-        <v>692</v>
-      </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>702</v>
-      </c>
-      <c r="F202" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B203" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C203" t="s">
         <v>8</v>
@@ -6385,18 +6424,18 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
+        <v>701</v>
+      </c>
+      <c r="F203" t="s">
         <v>702</v>
-      </c>
-      <c r="F203" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B204" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C204" t="s">
         <v>35</v>
@@ -6405,18 +6444,18 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F204" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B205" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C205" t="s">
         <v>96</v>
@@ -6425,52 +6464,52 @@
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F205" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B206" t="s">
+        <v>440</v>
+      </c>
+      <c r="C206" t="s">
         <v>441</v>
       </c>
-      <c r="C206" t="s">
-        <v>442</v>
-      </c>
       <c r="E206" t="s">
+        <v>435</v>
+      </c>
+      <c r="F206" t="s">
         <v>436</v>
-      </c>
-      <c r="F206" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B207" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C207" t="s">
+        <v>437</v>
+      </c>
+      <c r="E207" t="s">
+        <v>435</v>
+      </c>
+      <c r="F207" t="s">
         <v>438</v>
-      </c>
-      <c r="E207" t="s">
-        <v>436</v>
-      </c>
-      <c r="F207" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B208" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C208" t="s">
         <v>8</v>
@@ -6479,279 +6518,279 @@
         <v>1</v>
       </c>
       <c r="E208" t="s">
+        <v>308</v>
+      </c>
+      <c r="F208" t="s">
         <v>309</v>
-      </c>
-      <c r="F208" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B209" t="s">
+        <v>312</v>
+      </c>
+      <c r="C209" t="s">
+        <v>310</v>
+      </c>
+      <c r="E209" t="s">
+        <v>308</v>
+      </c>
+      <c r="F209" t="s">
         <v>313</v>
-      </c>
-      <c r="C209" t="s">
-        <v>311</v>
-      </c>
-      <c r="E209" t="s">
-        <v>309</v>
-      </c>
-      <c r="F209" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B210" t="s">
+        <v>312</v>
+      </c>
+      <c r="C210" t="s">
+        <v>311</v>
+      </c>
+      <c r="E210" t="s">
+        <v>308</v>
+      </c>
+      <c r="F210" t="s">
         <v>313</v>
-      </c>
-      <c r="C210" t="s">
-        <v>312</v>
-      </c>
-      <c r="E210" t="s">
-        <v>309</v>
-      </c>
-      <c r="F210" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B211" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C211" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E211" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F211" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B212" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B213" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C213" t="s">
+        <v>314</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213" t="s">
+        <v>308</v>
+      </c>
+      <c r="F213" t="s">
         <v>315</v>
-      </c>
-      <c r="D213">
-        <v>1</v>
-      </c>
-      <c r="E213" t="s">
-        <v>309</v>
-      </c>
-      <c r="F213" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B214" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C214" t="s">
+        <v>387</v>
+      </c>
+      <c r="E214" t="s">
+        <v>308</v>
+      </c>
+      <c r="F214" t="s">
         <v>388</v>
-      </c>
-      <c r="E214" t="s">
-        <v>309</v>
-      </c>
-      <c r="F214" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B215" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D215" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E215" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F215" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B216" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D216" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E216" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F216" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B217" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C217" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D217">
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F217" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B218" t="s">
+        <v>465</v>
+      </c>
+      <c r="C218" t="s">
         <v>466</v>
       </c>
-      <c r="C218" t="s">
-        <v>467</v>
-      </c>
       <c r="E218" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F218" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B219" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C219" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E219" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F219" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B220" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C220" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E220" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F220" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B221" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C221" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E221" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F221" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B222" t="s">
+        <v>472</v>
+      </c>
+      <c r="C222" t="s">
         <v>473</v>
       </c>
-      <c r="C222" t="s">
+      <c r="E222" t="s">
         <v>474</v>
       </c>
-      <c r="E222" t="s">
-        <v>475</v>
-      </c>
       <c r="F222" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B223" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D223" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E223" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F223" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B224" t="s">
         <v>229</v>
@@ -6771,87 +6810,87 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B225" t="s">
         <v>229</v>
       </c>
       <c r="C225" t="s">
+        <v>493</v>
+      </c>
+      <c r="E225" t="s">
         <v>494</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>495</v>
-      </c>
-      <c r="F225" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B226" t="s">
         <v>229</v>
       </c>
       <c r="C226" t="s">
+        <v>496</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226" t="s">
+        <v>494</v>
+      </c>
+      <c r="F226" t="s">
         <v>497</v>
-      </c>
-      <c r="D226">
-        <v>1</v>
-      </c>
-      <c r="E226" t="s">
-        <v>495</v>
-      </c>
-      <c r="F226" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B227" t="s">
         <v>229</v>
       </c>
       <c r="C227" t="s">
+        <v>498</v>
+      </c>
+      <c r="E227" t="s">
+        <v>494</v>
+      </c>
+      <c r="F227" t="s">
         <v>499</v>
-      </c>
-      <c r="E227" t="s">
-        <v>495</v>
-      </c>
-      <c r="F227" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B228" t="s">
         <v>229</v>
       </c>
       <c r="C228" t="s">
+        <v>500</v>
+      </c>
+      <c r="E228" t="s">
+        <v>494</v>
+      </c>
+      <c r="F228" t="s">
         <v>501</v>
-      </c>
-      <c r="E228" t="s">
-        <v>495</v>
-      </c>
-      <c r="F228" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B229" t="s">
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E229" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F229" t="s">
         <v>226</v>
@@ -6859,95 +6898,95 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B230" t="s">
         <v>229</v>
       </c>
       <c r="C230" t="s">
+        <v>503</v>
+      </c>
+      <c r="E230" t="s">
+        <v>494</v>
+      </c>
+      <c r="F230" t="s">
         <v>504</v>
-      </c>
-      <c r="E230" t="s">
-        <v>495</v>
-      </c>
-      <c r="F230" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B231" t="s">
         <v>229</v>
       </c>
       <c r="C231" t="s">
+        <v>505</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231" t="s">
+        <v>494</v>
+      </c>
+      <c r="F231" t="s">
         <v>506</v>
-      </c>
-      <c r="D231">
-        <v>1</v>
-      </c>
-      <c r="E231" t="s">
-        <v>495</v>
-      </c>
-      <c r="F231" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B232" t="s">
         <v>229</v>
       </c>
       <c r="C232" t="s">
+        <v>507</v>
+      </c>
+      <c r="E232" t="s">
+        <v>494</v>
+      </c>
+      <c r="F232" t="s">
         <v>508</v>
-      </c>
-      <c r="E232" t="s">
-        <v>495</v>
-      </c>
-      <c r="F232" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B233" t="s">
         <v>229</v>
       </c>
       <c r="C233" t="s">
+        <v>509</v>
+      </c>
+      <c r="E233" t="s">
+        <v>494</v>
+      </c>
+      <c r="F233" t="s">
         <v>510</v>
-      </c>
-      <c r="E233" t="s">
-        <v>495</v>
-      </c>
-      <c r="F233" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B234" t="s">
         <v>229</v>
       </c>
       <c r="C234" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F234" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B235" t="s">
         <v>216</v>
@@ -6964,7 +7003,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B236" t="s">
         <v>216</v>
@@ -6981,7 +7020,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B237" t="s">
         <v>216</v>
@@ -7001,7 +7040,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B238" t="s">
         <v>216</v>
@@ -7018,47 +7057,47 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B239" t="s">
         <v>216</v>
       </c>
       <c r="C239" t="s">
+        <v>593</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
         <v>594</v>
       </c>
-      <c r="D239">
-        <v>1</v>
-      </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>595</v>
-      </c>
-      <c r="F239" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B240" t="s">
         <v>216</v>
       </c>
       <c r="C240" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D240">
         <v>1</v>
       </c>
       <c r="E240" t="s">
+        <v>594</v>
+      </c>
+      <c r="F240" t="s">
         <v>595</v>
-      </c>
-      <c r="F240" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B241" t="s">
         <v>216</v>
@@ -7075,27 +7114,27 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B242" t="s">
         <v>216</v>
       </c>
       <c r="C242" t="s">
+        <v>601</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+      <c r="E242" t="s">
         <v>602</v>
       </c>
-      <c r="D242">
-        <v>1</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>603</v>
-      </c>
-      <c r="F242" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B243" t="s">
         <v>213</v>
@@ -7115,7 +7154,7 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B244" t="s">
         <v>213</v>
@@ -7127,32 +7166,32 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
+        <v>602</v>
+      </c>
+      <c r="F244" t="s">
         <v>603</v>
-      </c>
-      <c r="F244" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B245" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D245" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E245" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F245" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B246" t="s">
         <v>62</v>
@@ -7169,255 +7208,255 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B247" t="s">
         <v>23</v>
       </c>
       <c r="C247" t="s">
+        <v>715</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+      <c r="E247" t="s">
+        <v>708</v>
+      </c>
+      <c r="F247" t="s">
         <v>716</v>
-      </c>
-      <c r="D247">
-        <v>1</v>
-      </c>
-      <c r="E247" t="s">
-        <v>709</v>
-      </c>
-      <c r="F247" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B248" t="s">
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E248" t="s">
+        <v>708</v>
+      </c>
+      <c r="F248" t="s">
         <v>709</v>
-      </c>
-      <c r="F248" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B249" t="s">
         <v>23</v>
       </c>
       <c r="C249" t="s">
+        <v>717</v>
+      </c>
+      <c r="E249" t="s">
+        <v>708</v>
+      </c>
+      <c r="F249" t="s">
         <v>718</v>
-      </c>
-      <c r="E249" t="s">
-        <v>709</v>
-      </c>
-      <c r="F249" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B250" t="s">
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E250" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F250" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B251" t="s">
         <v>23</v>
       </c>
       <c r="C251" t="s">
+        <v>512</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+      <c r="E251" t="s">
         <v>513</v>
       </c>
-      <c r="D251">
-        <v>1</v>
-      </c>
-      <c r="E251" t="s">
-        <v>514</v>
-      </c>
       <c r="F251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B252" t="s">
         <v>23</v>
       </c>
       <c r="C252" t="s">
+        <v>404</v>
+      </c>
+      <c r="E252" t="s">
         <v>405</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>406</v>
-      </c>
-      <c r="F252" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B253" t="s">
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D253">
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F253" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B254" t="s">
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F254" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B255" t="s">
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D255">
         <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F255" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B256" t="s">
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F256" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B257" t="s">
         <v>23</v>
       </c>
       <c r="C257" t="s">
+        <v>446</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257" t="s">
+        <v>443</v>
+      </c>
+      <c r="F257" t="s">
         <v>447</v>
-      </c>
-      <c r="D257">
-        <v>1</v>
-      </c>
-      <c r="E257" t="s">
-        <v>444</v>
-      </c>
-      <c r="F257" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B258" t="s">
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D258">
         <v>1</v>
       </c>
       <c r="E258" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F258" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B259" t="s">
         <v>23</v>
       </c>
       <c r="C259" t="s">
+        <v>538</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259" t="s">
+        <v>537</v>
+      </c>
+      <c r="F259" t="s">
         <v>539</v>
-      </c>
-      <c r="D259">
-        <v>1</v>
-      </c>
-      <c r="E259" t="s">
-        <v>538</v>
-      </c>
-      <c r="F259" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B260" t="s">
         <v>23</v>
@@ -7429,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F260" t="s">
         <v>266</v>
@@ -7437,227 +7476,227 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B261" t="s">
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F261" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B262" t="s">
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D262">
         <v>1</v>
       </c>
       <c r="E262" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F262" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B263" t="s">
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D263">
         <v>1</v>
       </c>
       <c r="E263" t="s">
+        <v>390</v>
+      </c>
+      <c r="F263" t="s">
         <v>391</v>
-      </c>
-      <c r="F263" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B264" t="s">
         <v>23</v>
       </c>
       <c r="C264" t="s">
+        <v>274</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+      <c r="E264" t="s">
+        <v>287</v>
+      </c>
+      <c r="F264" t="s">
         <v>275</v>
-      </c>
-      <c r="D264">
-        <v>1</v>
-      </c>
-      <c r="E264" t="s">
-        <v>288</v>
-      </c>
-      <c r="F264" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B265" t="s">
         <v>23</v>
       </c>
       <c r="C265" t="s">
+        <v>432</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+      <c r="E265" t="s">
+        <v>287</v>
+      </c>
+      <c r="F265" t="s">
         <v>433</v>
-      </c>
-      <c r="D265">
-        <v>1</v>
-      </c>
-      <c r="E265" t="s">
-        <v>288</v>
-      </c>
-      <c r="F265" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B266" t="s">
         <v>23</v>
       </c>
       <c r="C266" t="s">
+        <v>585</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+      <c r="E266" t="s">
         <v>586</v>
       </c>
-      <c r="D266">
-        <v>1</v>
-      </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>587</v>
-      </c>
-      <c r="F266" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B267" t="s">
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D267">
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F267" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B268" t="s">
         <v>23</v>
       </c>
       <c r="C268" t="s">
+        <v>276</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+      <c r="E268" t="s">
+        <v>288</v>
+      </c>
+      <c r="F268" t="s">
         <v>277</v>
-      </c>
-      <c r="D268">
-        <v>1</v>
-      </c>
-      <c r="E268" t="s">
-        <v>289</v>
-      </c>
-      <c r="F268" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B269" t="s">
         <v>23</v>
       </c>
       <c r="C269" t="s">
+        <v>278</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+      <c r="E269" t="s">
+        <v>288</v>
+      </c>
+      <c r="F269" t="s">
         <v>279</v>
-      </c>
-      <c r="D269">
-        <v>1</v>
-      </c>
-      <c r="E269" t="s">
-        <v>289</v>
-      </c>
-      <c r="F269" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B270" t="s">
         <v>23</v>
       </c>
       <c r="C270" t="s">
+        <v>527</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+      <c r="E270" t="s">
+        <v>525</v>
+      </c>
+      <c r="F270" t="s">
         <v>528</v>
-      </c>
-      <c r="D270">
-        <v>1</v>
-      </c>
-      <c r="E270" t="s">
-        <v>526</v>
-      </c>
-      <c r="F270" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B271" t="s">
         <v>23</v>
       </c>
       <c r="C271" t="s">
+        <v>524</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+      <c r="E271" t="s">
         <v>525</v>
       </c>
-      <c r="D271">
-        <v>1</v>
-      </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>526</v>
-      </c>
-      <c r="F271" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B272" t="s">
         <v>23</v>
@@ -7674,7 +7713,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B273" t="s">
         <v>23</v>
@@ -7694,7 +7733,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B274" t="s">
         <v>23</v>
@@ -7714,27 +7753,27 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B275" t="s">
         <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D275">
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F275" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B276" t="s">
         <v>23</v>
@@ -7743,7 +7782,7 @@
         <v>77</v>
       </c>
       <c r="E276" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F276" t="s">
         <v>156</v>
@@ -7751,7 +7790,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B277" t="s">
         <v>23</v>
@@ -7771,7 +7810,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B278" t="s">
         <v>23</v>
@@ -7791,41 +7830,41 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B279" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C279" t="s">
         <v>84</v>
       </c>
       <c r="E279" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F279" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B280" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D280" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E280" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F280" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B281" t="s">
         <v>106</v>
@@ -7842,7 +7881,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B282" t="s">
         <v>98</v>
@@ -7859,7 +7898,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B283" t="s">
         <v>98</v>
@@ -7876,7 +7915,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B284" t="s">
         <v>98</v>
@@ -7893,7 +7932,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B285" t="s">
         <v>98</v>
@@ -7910,33 +7949,33 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B286" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D286" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E286" t="s">
         <v>102</v>
       </c>
       <c r="F286" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B287" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D287" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E287" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F287" t="s">
         <v>161</v>
@@ -7944,41 +7983,41 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B288" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C288" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E288" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F288" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B289" t="s">
+        <v>761</v>
+      </c>
+      <c r="D289" t="s">
+        <v>711</v>
+      </c>
+      <c r="E289" t="s">
         <v>762</v>
       </c>
-      <c r="D289" t="s">
-        <v>712</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>763</v>
-      </c>
-      <c r="F289" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B290" t="s">
         <v>239</v>
@@ -7995,58 +8034,58 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B291" t="s">
+        <v>659</v>
+      </c>
+      <c r="D291" t="s">
+        <v>581</v>
+      </c>
+      <c r="E291" t="s">
+        <v>323</v>
+      </c>
+      <c r="F291" t="s">
         <v>660</v>
-      </c>
-      <c r="D291" t="s">
-        <v>582</v>
-      </c>
-      <c r="E291" t="s">
-        <v>324</v>
-      </c>
-      <c r="F291" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B292" t="s">
+        <v>661</v>
+      </c>
+      <c r="D292" t="s">
+        <v>581</v>
+      </c>
+      <c r="E292" t="s">
+        <v>288</v>
+      </c>
+      <c r="F292" t="s">
         <v>662</v>
-      </c>
-      <c r="D292" t="s">
-        <v>582</v>
-      </c>
-      <c r="E292" t="s">
-        <v>289</v>
-      </c>
-      <c r="F292" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B293" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C293" t="s">
         <v>77</v>
       </c>
       <c r="E293" t="s">
+        <v>390</v>
+      </c>
+      <c r="F293" t="s">
         <v>391</v>
-      </c>
-      <c r="F293" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B294" t="s">
         <v>19</v>
@@ -8066,7 +8105,7 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B295" t="s">
         <v>16</v>
@@ -8086,7 +8125,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B296" t="s">
         <v>16</v>
@@ -8103,7 +8142,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B297" t="s">
         <v>16</v>
@@ -8123,7 +8162,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B298" t="s">
         <v>267</v>
@@ -8135,32 +8174,35 @@
         <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F298" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B299" t="s">
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>273</v>
+        <v>272</v>
+      </c>
+      <c r="D299">
+        <v>1</v>
       </c>
       <c r="E299" t="s">
-        <v>287</v>
+        <v>772</v>
       </c>
       <c r="F299" t="s">
-        <v>272</v>
+        <v>773</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B300" t="s">
         <v>267</v>
@@ -8169,7 +8211,7 @@
         <v>268</v>
       </c>
       <c r="E300" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F300" t="s">
         <v>269</v>
@@ -8177,64 +8219,64 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B301" t="s">
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E301" t="s">
+        <v>348</v>
+      </c>
+      <c r="F301" t="s">
         <v>349</v>
-      </c>
-      <c r="F301" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B302" t="s">
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D302">
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F302" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B303" t="s">
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D303">
         <v>1</v>
       </c>
       <c r="E303" t="s">
+        <v>290</v>
+      </c>
+      <c r="F303" t="s">
         <v>291</v>
-      </c>
-      <c r="F303" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B304" t="s">
         <v>267</v>
@@ -8243,497 +8285,491 @@
         <v>132</v>
       </c>
       <c r="E304" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F304" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B305" t="s">
         <v>267</v>
       </c>
       <c r="C305" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D305">
         <v>1</v>
       </c>
       <c r="E305" t="s">
+        <v>300</v>
+      </c>
+      <c r="F305" t="s">
         <v>301</v>
-      </c>
-      <c r="F305" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B306" t="s">
         <v>267</v>
       </c>
       <c r="C306" t="s">
+        <v>299</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
+      </c>
+      <c r="E306" t="s">
         <v>300</v>
       </c>
-      <c r="D306">
-        <v>1</v>
-      </c>
-      <c r="E306" t="s">
-        <v>301</v>
-      </c>
       <c r="F306" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B307" t="s">
         <v>267</v>
       </c>
       <c r="C307" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E307" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F307" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B308" t="s">
         <v>267</v>
       </c>
       <c r="C308" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D308">
         <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F308" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B309" t="s">
         <v>267</v>
       </c>
       <c r="C309" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D309">
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F309" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B310" t="s">
-        <v>664</v>
-      </c>
-      <c r="D310" t="s">
-        <v>582</v>
+        <v>267</v>
+      </c>
+      <c r="C310" t="s">
+        <v>781</v>
       </c>
       <c r="E310" t="s">
-        <v>332</v>
+        <v>772</v>
       </c>
       <c r="F310" t="s">
-        <v>665</v>
+        <v>782</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B311" t="s">
-        <v>270</v>
-      </c>
-      <c r="C311" t="s">
-        <v>271</v>
-      </c>
-      <c r="D311">
-        <v>1</v>
+        <v>663</v>
+      </c>
+      <c r="D311" t="s">
+        <v>581</v>
       </c>
       <c r="E311" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="F311" t="s">
-        <v>328</v>
+        <v>664</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B312" t="s">
         <v>270</v>
       </c>
       <c r="C312" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D312">
         <v>1</v>
       </c>
       <c r="E312" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="F312" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B313" t="s">
         <v>270</v>
       </c>
       <c r="C313" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="D313">
         <v>1</v>
       </c>
       <c r="E313" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="F313" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B314" t="s">
         <v>270</v>
       </c>
       <c r="C314" t="s">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="D314">
         <v>1</v>
       </c>
       <c r="E314" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="F314" t="s">
-        <v>338</v>
+        <v>283</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B315" t="s">
         <v>270</v>
       </c>
       <c r="C315" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D315">
         <v>1</v>
       </c>
       <c r="E315" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F315" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B316" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C316" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="D316">
         <v>1</v>
       </c>
       <c r="E316" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="F316" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B317" t="s">
-        <v>666</v>
-      </c>
-      <c r="D317" t="s">
-        <v>582</v>
+        <v>771</v>
+      </c>
+      <c r="C317" t="s">
+        <v>149</v>
+      </c>
+      <c r="D317">
+        <v>1</v>
       </c>
       <c r="E317" t="s">
-        <v>301</v>
+        <v>772</v>
       </c>
       <c r="F317" t="s">
-        <v>304</v>
+        <v>773</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B318" t="s">
-        <v>667</v>
-      </c>
-      <c r="D318" t="s">
-        <v>582</v>
+        <v>771</v>
+      </c>
+      <c r="C318" t="s">
+        <v>775</v>
       </c>
       <c r="E318" t="s">
-        <v>332</v>
+        <v>772</v>
       </c>
       <c r="F318" t="s">
-        <v>668</v>
+        <v>774</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B319" t="s">
-        <v>669</v>
-      </c>
-      <c r="D319" t="s">
-        <v>582</v>
+        <v>771</v>
+      </c>
+      <c r="C319" t="s">
+        <v>776</v>
+      </c>
+      <c r="D319">
+        <v>1</v>
       </c>
       <c r="E319" t="s">
-        <v>301</v>
+        <v>772</v>
       </c>
       <c r="F319" t="s">
-        <v>305</v>
+        <v>777</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B320" t="s">
-        <v>670</v>
-      </c>
-      <c r="D320" t="s">
-        <v>582</v>
+        <v>346</v>
+      </c>
+      <c r="C320" t="s">
+        <v>347</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
       </c>
       <c r="E320" t="s">
-        <v>672</v>
+        <v>348</v>
       </c>
       <c r="F320" t="s">
-        <v>671</v>
+        <v>349</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B321" t="s">
-        <v>673</v>
-      </c>
-      <c r="D321" t="s">
-        <v>582</v>
+        <v>778</v>
+      </c>
+      <c r="C321" t="s">
+        <v>30</v>
+      </c>
+      <c r="D321">
+        <v>2</v>
       </c>
       <c r="E321" t="s">
-        <v>234</v>
+        <v>772</v>
       </c>
       <c r="F321" t="s">
-        <v>232</v>
+        <v>779</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B322" t="s">
-        <v>236</v>
+        <v>778</v>
       </c>
       <c r="C322" t="s">
-        <v>237</v>
+        <v>545</v>
       </c>
       <c r="E322" t="s">
-        <v>234</v>
+        <v>772</v>
       </c>
       <c r="F322" t="s">
-        <v>238</v>
+        <v>780</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B323" t="s">
-        <v>379</v>
-      </c>
-      <c r="C323" t="s">
-        <v>382</v>
-      </c>
-      <c r="D323">
-        <v>1</v>
+        <v>783</v>
+      </c>
+      <c r="D323" t="s">
+        <v>581</v>
       </c>
       <c r="E323" t="s">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="F323" t="s">
-        <v>383</v>
+        <v>779</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B324" t="s">
-        <v>379</v>
-      </c>
-      <c r="C324" t="s">
-        <v>10</v>
-      </c>
-      <c r="D324">
-        <v>1</v>
+        <v>784</v>
+      </c>
+      <c r="D324" t="s">
+        <v>581</v>
       </c>
       <c r="E324" t="s">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="F324" t="s">
-        <v>384</v>
+        <v>779</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B325" t="s">
-        <v>379</v>
-      </c>
-      <c r="C325" t="s">
-        <v>381</v>
-      </c>
-      <c r="D325">
-        <v>1</v>
+        <v>665</v>
+      </c>
+      <c r="D325" t="s">
+        <v>581</v>
       </c>
       <c r="E325" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F325" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B326" t="s">
-        <v>379</v>
-      </c>
-      <c r="C326" t="s">
-        <v>77</v>
+        <v>666</v>
+      </c>
+      <c r="D326" t="s">
+        <v>581</v>
       </c>
       <c r="E326" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="F326" t="s">
-        <v>378</v>
+        <v>667</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B327" t="s">
-        <v>373</v>
-      </c>
-      <c r="C327" t="s">
-        <v>8</v>
-      </c>
-      <c r="D327">
-        <v>1</v>
+        <v>668</v>
+      </c>
+      <c r="D327" t="s">
+        <v>581</v>
       </c>
       <c r="E327" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F327" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B328" t="s">
-        <v>373</v>
-      </c>
-      <c r="C328" t="s">
-        <v>35</v>
-      </c>
-      <c r="D328">
-        <v>1</v>
+        <v>669</v>
+      </c>
+      <c r="D328" t="s">
+        <v>581</v>
       </c>
       <c r="E328" t="s">
-        <v>375</v>
+        <v>671</v>
       </c>
       <c r="F328" t="s">
-        <v>377</v>
+        <v>670</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B329" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D329" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E329" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="F329" t="s">
-        <v>407</v>
+        <v>232</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B330" t="s">
-        <v>675</v>
-      </c>
-      <c r="D330" t="s">
-        <v>582</v>
+        <v>236</v>
+      </c>
+      <c r="C330" t="s">
+        <v>237</v>
       </c>
       <c r="E330" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="F330" t="s">
-        <v>676</v>
+        <v>238</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -8741,24 +8777,27 @@
         <v>683</v>
       </c>
       <c r="B331" t="s">
-        <v>685</v>
+        <v>378</v>
       </c>
       <c r="C331" t="s">
-        <v>686</v>
+        <v>381</v>
+      </c>
+      <c r="D331">
+        <v>1</v>
       </c>
       <c r="E331" t="s">
-        <v>687</v>
+        <v>374</v>
       </c>
       <c r="F331" t="s">
-        <v>688</v>
+        <v>382</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B332" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C332" t="s">
         <v>10</v>
@@ -8767,234 +8806,240 @@
         <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F332" t="s">
-        <v>159</v>
+        <v>383</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B333" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C333" t="s">
-        <v>145</v>
+        <v>380</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
       </c>
       <c r="E333" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F333" t="s">
-        <v>158</v>
+        <v>379</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B334" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C334" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="E334" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F334" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B335" t="s">
-        <v>148</v>
+        <v>372</v>
       </c>
       <c r="C335" t="s">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="D335">
         <v>1</v>
       </c>
       <c r="E335" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F335" t="s">
-        <v>161</v>
+        <v>373</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B336" t="s">
-        <v>152</v>
+        <v>372</v>
       </c>
       <c r="C336" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D336">
         <v>1</v>
       </c>
       <c r="E336" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F336" t="s">
-        <v>157</v>
+        <v>376</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B337" t="s">
-        <v>152</v>
-      </c>
-      <c r="C337" t="s">
-        <v>35</v>
-      </c>
-      <c r="D337">
-        <v>1</v>
+        <v>673</v>
+      </c>
+      <c r="D337" t="s">
+        <v>581</v>
       </c>
       <c r="E337" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="F337" t="s">
-        <v>157</v>
+        <v>406</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B338" t="s">
-        <v>201</v>
-      </c>
-      <c r="C338" t="s">
-        <v>182</v>
+        <v>674</v>
+      </c>
+      <c r="D338" t="s">
+        <v>581</v>
       </c>
       <c r="E338" t="s">
-        <v>180</v>
+        <v>405</v>
       </c>
       <c r="F338" t="s">
-        <v>181</v>
+        <v>675</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
+        <v>682</v>
+      </c>
+      <c r="B339" t="s">
         <v>684</v>
       </c>
-      <c r="B339" t="s">
-        <v>201</v>
-      </c>
       <c r="C339" t="s">
-        <v>163</v>
+        <v>685</v>
       </c>
       <c r="E339" t="s">
-        <v>180</v>
+        <v>686</v>
       </c>
       <c r="F339" t="s">
-        <v>164</v>
+        <v>687</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B340" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="C340" t="s">
-        <v>518</v>
+        <v>10</v>
       </c>
       <c r="D340">
         <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>520</v>
+        <v>419</v>
       </c>
       <c r="F340" t="s">
-        <v>519</v>
+        <v>159</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B341" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C341" t="s">
-        <v>368</v>
+        <v>145</v>
       </c>
       <c r="E341" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="F341" t="s">
-        <v>366</v>
+        <v>158</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B342" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C342" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E342" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="F342" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B343" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C343" t="s">
-        <v>167</v>
+        <v>199</v>
+      </c>
+      <c r="D343">
+        <v>1</v>
       </c>
       <c r="E343" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="F343" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B344" t="s">
-        <v>203</v>
-      </c>
-      <c r="D344" t="s">
-        <v>692</v>
+        <v>152</v>
+      </c>
+      <c r="C344" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344">
+        <v>1</v>
       </c>
       <c r="E344" t="s">
-        <v>709</v>
+        <v>419</v>
       </c>
       <c r="F344" t="s">
-        <v>710</v>
+        <v>157</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B345" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="C345" t="s">
         <v>35</v>
@@ -9003,24 +9048,24 @@
         <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>709</v>
+        <v>419</v>
       </c>
       <c r="F345" t="s">
-        <v>722</v>
+        <v>157</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B346" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C346" t="s">
         <v>182</v>
       </c>
       <c r="E346" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F346" t="s">
         <v>181</v>
@@ -9028,354 +9073,351 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B347" t="s">
-        <v>721</v>
+        <v>201</v>
       </c>
       <c r="C347" t="s">
-        <v>230</v>
-      </c>
-      <c r="D347">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E347" t="s">
-        <v>709</v>
+        <v>180</v>
       </c>
       <c r="F347" t="s">
-        <v>710</v>
+        <v>164</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B348" t="s">
-        <v>723</v>
-      </c>
-      <c r="D348" t="s">
-        <v>692</v>
+        <v>201</v>
+      </c>
+      <c r="C348" t="s">
+        <v>517</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
       </c>
       <c r="E348" t="s">
-        <v>709</v>
+        <v>519</v>
       </c>
       <c r="F348" t="s">
-        <v>710</v>
+        <v>518</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B349" t="s">
-        <v>723</v>
+        <v>204</v>
       </c>
       <c r="C349" t="s">
-        <v>35</v>
-      </c>
-      <c r="D349">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="E349" t="s">
-        <v>709</v>
+        <v>366</v>
       </c>
       <c r="F349" t="s">
-        <v>717</v>
+        <v>365</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B350" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C350" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="E350" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F350" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B351" t="s">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="C351" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="E351" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="F351" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B352" t="s">
-        <v>80</v>
-      </c>
-      <c r="C352" t="s">
-        <v>67</v>
+        <v>203</v>
+      </c>
+      <c r="D352" t="s">
+        <v>691</v>
       </c>
       <c r="E352" t="s">
-        <v>59</v>
+        <v>708</v>
       </c>
       <c r="F352" t="s">
-        <v>82</v>
+        <v>709</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B353" t="s">
-        <v>335</v>
+        <v>203</v>
       </c>
       <c r="C353" t="s">
-        <v>334</v>
+        <v>35</v>
       </c>
       <c r="D353">
         <v>1</v>
       </c>
       <c r="E353" t="s">
-        <v>332</v>
+        <v>708</v>
       </c>
       <c r="F353" t="s">
-        <v>334</v>
+        <v>721</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B354" t="s">
-        <v>677</v>
-      </c>
-      <c r="D354" t="s">
-        <v>582</v>
+        <v>203</v>
+      </c>
+      <c r="C354" t="s">
+        <v>182</v>
       </c>
       <c r="E354" t="s">
-        <v>475</v>
+        <v>178</v>
       </c>
       <c r="F354" t="s">
-        <v>470</v>
+        <v>181</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B355" t="s">
-        <v>678</v>
-      </c>
-      <c r="D355" t="s">
-        <v>582</v>
+        <v>720</v>
+      </c>
+      <c r="C355" t="s">
+        <v>230</v>
+      </c>
+      <c r="D355">
+        <v>1</v>
       </c>
       <c r="E355" t="s">
-        <v>420</v>
+        <v>708</v>
       </c>
       <c r="F355" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B356" t="s">
-        <v>578</v>
-      </c>
-      <c r="C356" t="s">
-        <v>104</v>
+        <v>722</v>
+      </c>
+      <c r="D356" t="s">
+        <v>691</v>
       </c>
       <c r="E356" t="s">
-        <v>577</v>
+        <v>708</v>
       </c>
       <c r="F356" t="s">
-        <v>580</v>
+        <v>709</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B357" t="s">
-        <v>578</v>
+        <v>722</v>
       </c>
       <c r="C357" t="s">
-        <v>78</v>
+        <v>35</v>
+      </c>
+      <c r="D357">
+        <v>1</v>
       </c>
       <c r="E357" t="s">
-        <v>577</v>
+        <v>708</v>
       </c>
       <c r="F357" t="s">
-        <v>579</v>
+        <v>716</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B358" t="s">
-        <v>184</v>
-      </c>
-      <c r="D358" t="s">
-        <v>692</v>
+        <v>200</v>
+      </c>
+      <c r="C358" t="s">
+        <v>104</v>
       </c>
       <c r="E358" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F358" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B359" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="C359" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="E359" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="F359" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B360" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="C360" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="E360" t="s">
-        <v>515</v>
+        <v>59</v>
       </c>
       <c r="F360" t="s">
-        <v>516</v>
+        <v>82</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B361" t="s">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="C361" t="s">
-        <v>171</v>
+        <v>333</v>
+      </c>
+      <c r="D361">
+        <v>1</v>
       </c>
       <c r="E361" t="s">
-        <v>515</v>
+        <v>331</v>
       </c>
       <c r="F361" t="s">
-        <v>517</v>
+        <v>333</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B362" t="s">
-        <v>184</v>
-      </c>
-      <c r="C362" t="s">
-        <v>443</v>
+        <v>676</v>
+      </c>
+      <c r="D362" t="s">
+        <v>581</v>
       </c>
       <c r="E362" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="F362" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B363" t="s">
-        <v>184</v>
-      </c>
-      <c r="C363" t="s">
-        <v>261</v>
-      </c>
-      <c r="D363">
-        <v>1</v>
+        <v>677</v>
+      </c>
+      <c r="D363" t="s">
+        <v>581</v>
       </c>
       <c r="E363" t="s">
-        <v>286</v>
+        <v>419</v>
       </c>
       <c r="F363" t="s">
-        <v>262</v>
+        <v>678</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B364" t="s">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="C364" t="s">
-        <v>421</v>
+        <v>104</v>
       </c>
       <c r="E364" t="s">
-        <v>420</v>
+        <v>576</v>
       </c>
       <c r="F364" t="s">
-        <v>157</v>
+        <v>579</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B365" t="s">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="C365" t="s">
-        <v>734</v>
-      </c>
-      <c r="D365">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E365" t="s">
-        <v>735</v>
+        <v>576</v>
       </c>
       <c r="F365" t="s">
-        <v>736</v>
+        <v>578</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B366" t="s">
         <v>184</v>
       </c>
-      <c r="C366" t="s">
-        <v>185</v>
-      </c>
-      <c r="D366">
-        <v>1</v>
+      <c r="D366" t="s">
+        <v>691</v>
       </c>
       <c r="E366" t="s">
         <v>186</v>
@@ -9386,935 +9428,1080 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B367" t="s">
         <v>184</v>
       </c>
       <c r="C367" t="s">
-        <v>489</v>
-      </c>
-      <c r="D367">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E367" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="F367" t="s">
-        <v>530</v>
+        <v>155</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B368" t="s">
         <v>184</v>
       </c>
       <c r="C368" t="s">
-        <v>489</v>
-      </c>
-      <c r="D368">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E368" t="s">
-        <v>298</v>
+        <v>514</v>
       </c>
       <c r="F368" t="s">
-        <v>297</v>
+        <v>515</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B369" t="s">
         <v>184</v>
       </c>
       <c r="C369" t="s">
-        <v>326</v>
-      </c>
-      <c r="D369">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E369" t="s">
-        <v>324</v>
+        <v>514</v>
       </c>
       <c r="F369" t="s">
-        <v>327</v>
+        <v>516</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B370" t="s">
         <v>184</v>
       </c>
       <c r="C370" t="s">
-        <v>323</v>
-      </c>
-      <c r="D370">
-        <v>1</v>
+        <v>442</v>
       </c>
       <c r="E370" t="s">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="F370" t="s">
-        <v>325</v>
+        <v>445</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B371" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C371" t="s">
-        <v>189</v>
+        <v>261</v>
       </c>
       <c r="D371">
         <v>1</v>
       </c>
       <c r="E371" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="F371" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B372" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C372" t="s">
-        <v>191</v>
-      </c>
-      <c r="D372">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="E372" t="s">
-        <v>244</v>
+        <v>419</v>
       </c>
       <c r="F372" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B373" t="s">
-        <v>476</v>
+        <v>184</v>
       </c>
       <c r="C373" t="s">
-        <v>477</v>
+        <v>733</v>
+      </c>
+      <c r="D373">
+        <v>1</v>
       </c>
       <c r="E373" t="s">
-        <v>538</v>
+        <v>734</v>
       </c>
       <c r="F373" t="s">
-        <v>465</v>
+        <v>735</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B374" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C374" t="s">
-        <v>459</v>
+        <v>185</v>
+      </c>
+      <c r="D374">
+        <v>1</v>
       </c>
       <c r="E374" t="s">
-        <v>453</v>
+        <v>186</v>
       </c>
       <c r="F374" t="s">
-        <v>460</v>
+        <v>190</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B375" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C375" t="s">
-        <v>410</v>
+        <v>488</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
       </c>
       <c r="E375" t="s">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="F375" t="s">
-        <v>411</v>
+        <v>529</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B376" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C376" t="s">
-        <v>409</v>
+        <v>488</v>
+      </c>
+      <c r="D376">
+        <v>1</v>
       </c>
       <c r="E376" t="s">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="F376" t="s">
-        <v>408</v>
+        <v>296</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B377" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C377" t="s">
-        <v>402</v>
+        <v>325</v>
+      </c>
+      <c r="D377">
+        <v>1</v>
       </c>
       <c r="E377" t="s">
-        <v>400</v>
+        <v>323</v>
       </c>
       <c r="F377" t="s">
-        <v>401</v>
+        <v>326</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B378" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C378" t="s">
-        <v>490</v>
+        <v>322</v>
+      </c>
+      <c r="D378">
+        <v>1</v>
       </c>
       <c r="E378" t="s">
-        <v>491</v>
+        <v>323</v>
       </c>
       <c r="F378" t="s">
-        <v>492</v>
+        <v>324</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B379" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="C379" t="s">
-        <v>490</v>
+        <v>189</v>
+      </c>
+      <c r="D379">
+        <v>1</v>
       </c>
       <c r="E379" t="s">
-        <v>491</v>
+        <v>244</v>
       </c>
       <c r="F379" t="s">
-        <v>493</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B380" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="C380" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="D380">
+        <v>1</v>
       </c>
       <c r="E380" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F380" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B381" t="s">
-        <v>45</v>
+        <v>475</v>
       </c>
       <c r="C381" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="E381" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="F381" t="s">
-        <v>564</v>
+        <v>464</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B382" t="s">
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>562</v>
+        <v>458</v>
       </c>
       <c r="E382" t="s">
-        <v>563</v>
+        <v>452</v>
       </c>
       <c r="F382" t="s">
-        <v>565</v>
+        <v>459</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B383" t="s">
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>415</v>
-      </c>
-      <c r="D383">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="E383" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F383" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B384" t="s">
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="E384" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="F384" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B385" t="s">
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="E385" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="F385" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B386" t="s">
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>264</v>
-      </c>
-      <c r="D386">
-        <v>1</v>
+        <v>489</v>
       </c>
       <c r="E386" t="s">
-        <v>286</v>
+        <v>490</v>
       </c>
       <c r="F386" t="s">
-        <v>263</v>
+        <v>491</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B387" t="s">
         <v>45</v>
       </c>
       <c r="C387" t="s">
-        <v>372</v>
+        <v>489</v>
       </c>
       <c r="E387" t="s">
-        <v>369</v>
+        <v>490</v>
       </c>
       <c r="F387" t="s">
-        <v>559</v>
+        <v>492</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B388" t="s">
         <v>45</v>
       </c>
       <c r="C388" t="s">
-        <v>187</v>
-      </c>
-      <c r="D388">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E388" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="F388" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B389" t="s">
         <v>45</v>
       </c>
       <c r="C389" t="s">
-        <v>281</v>
-      </c>
-      <c r="D389">
-        <v>1</v>
+        <v>561</v>
       </c>
       <c r="E389" t="s">
-        <v>290</v>
+        <v>562</v>
       </c>
       <c r="F389" t="s">
-        <v>282</v>
+        <v>563</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B390" t="s">
         <v>45</v>
       </c>
       <c r="C390" t="s">
-        <v>123</v>
+        <v>561</v>
       </c>
       <c r="E390" t="s">
-        <v>246</v>
+        <v>562</v>
       </c>
       <c r="F390" t="s">
-        <v>123</v>
+        <v>564</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B391" t="s">
         <v>45</v>
       </c>
       <c r="C391" t="s">
-        <v>52</v>
+        <v>414</v>
       </c>
       <c r="D391">
         <v>1</v>
       </c>
       <c r="E391" t="s">
-        <v>50</v>
+        <v>413</v>
       </c>
       <c r="F391" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B392" t="s">
         <v>45</v>
       </c>
       <c r="C392" t="s">
-        <v>49</v>
-      </c>
-      <c r="D392">
-        <v>1</v>
+        <v>375</v>
       </c>
       <c r="E392" t="s">
-        <v>50</v>
+        <v>374</v>
       </c>
       <c r="F392" t="s">
-        <v>51</v>
+        <v>373</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B393" t="s">
         <v>45</v>
       </c>
       <c r="C393" t="s">
-        <v>125</v>
+        <v>442</v>
       </c>
       <c r="E393" t="s">
-        <v>126</v>
+        <v>443</v>
       </c>
       <c r="F393" t="s">
-        <v>127</v>
+        <v>444</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B394" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C394" t="s">
-        <v>167</v>
+        <v>264</v>
+      </c>
+      <c r="D394">
+        <v>1</v>
       </c>
       <c r="E394" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="F394" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B395" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C395" t="s">
-        <v>571</v>
+        <v>371</v>
       </c>
       <c r="E395" t="s">
-        <v>256</v>
+        <v>368</v>
       </c>
       <c r="F395" t="s">
-        <v>183</v>
+        <v>558</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B396" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C396" t="s">
-        <v>571</v>
+        <v>187</v>
+      </c>
+      <c r="D396">
+        <v>1</v>
       </c>
       <c r="E396" t="s">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="F396" t="s">
-        <v>572</v>
+        <v>190</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B397" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C397" t="s">
-        <v>570</v>
+        <v>280</v>
+      </c>
+      <c r="D397">
+        <v>1</v>
       </c>
       <c r="E397" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="F397" t="s">
-        <v>183</v>
+        <v>281</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B398" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C398" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E398" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F398" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B399" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C399" t="s">
-        <v>165</v>
+        <v>52</v>
+      </c>
+      <c r="D399">
+        <v>1</v>
       </c>
       <c r="E399" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F399" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B400" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C400" t="s">
-        <v>169</v>
+        <v>49</v>
+      </c>
+      <c r="D400">
+        <v>1</v>
       </c>
       <c r="E400" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F400" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B401" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C401" t="s">
-        <v>55</v>
-      </c>
-      <c r="D401">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="E401" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="F401" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B402" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="C402" t="s">
-        <v>57</v>
-      </c>
-      <c r="D402">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="E402" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F402" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B403" t="s">
-        <v>456</v>
+        <v>568</v>
       </c>
       <c r="C403" t="s">
-        <v>8</v>
-      </c>
-      <c r="D403">
-        <v>1</v>
+        <v>570</v>
       </c>
       <c r="E403" t="s">
-        <v>453</v>
+        <v>256</v>
       </c>
       <c r="F403" t="s">
-        <v>457</v>
+        <v>183</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B404" t="s">
-        <v>108</v>
+        <v>568</v>
       </c>
       <c r="C404" t="s">
-        <v>114</v>
-      </c>
-      <c r="D404">
-        <v>1</v>
+        <v>570</v>
       </c>
       <c r="E404" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="F404" t="s">
-        <v>114</v>
+        <v>571</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B405" t="s">
-        <v>108</v>
+        <v>568</v>
       </c>
       <c r="C405" t="s">
-        <v>116</v>
-      </c>
-      <c r="D405">
-        <v>1</v>
+        <v>569</v>
       </c>
       <c r="E405" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="F405" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B406" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C406" t="s">
-        <v>117</v>
-      </c>
-      <c r="D406">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E406" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F406" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B407" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C407" t="s">
-        <v>118</v>
-      </c>
-      <c r="D407">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="E407" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F407" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B408" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C408" t="s">
-        <v>120</v>
-      </c>
-      <c r="D408">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E408" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F408" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B409" t="s">
-        <v>756</v>
-      </c>
-      <c r="D409" t="s">
-        <v>712</v>
+        <v>48</v>
+      </c>
+      <c r="C409" t="s">
+        <v>55</v>
+      </c>
+      <c r="D409">
+        <v>1</v>
       </c>
       <c r="E409" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F409" t="s">
-        <v>757</v>
+        <v>53</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B410" t="s">
-        <v>754</v>
-      </c>
-      <c r="D410" t="s">
-        <v>712</v>
+        <v>48</v>
+      </c>
+      <c r="C410" t="s">
+        <v>57</v>
+      </c>
+      <c r="D410">
+        <v>1</v>
       </c>
       <c r="E410" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="F410" t="s">
-        <v>755</v>
+        <v>53</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B411" t="s">
-        <v>680</v>
-      </c>
-      <c r="D411" t="s">
-        <v>582</v>
+        <v>455</v>
+      </c>
+      <c r="C411" t="s">
+        <v>8</v>
+      </c>
+      <c r="D411">
+        <v>1</v>
       </c>
       <c r="E411" t="s">
-        <v>298</v>
+        <v>452</v>
       </c>
       <c r="F411" t="s">
-        <v>297</v>
+        <v>456</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B412" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="C412" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="D412">
         <v>1</v>
       </c>
       <c r="E412" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="F412" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B413" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="C413" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="D413">
         <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="F413" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B414" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C414" t="s">
-        <v>567</v>
+        <v>117</v>
+      </c>
+      <c r="D414">
+        <v>1</v>
       </c>
       <c r="E414" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F414" t="s">
-        <v>565</v>
+        <v>117</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B415" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C415" t="s">
-        <v>568</v>
+        <v>118</v>
+      </c>
+      <c r="D415">
+        <v>1</v>
       </c>
       <c r="E415" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F415" t="s">
-        <v>565</v>
+        <v>119</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B416" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C416" t="s">
-        <v>167</v>
+        <v>120</v>
+      </c>
+      <c r="D416">
+        <v>1</v>
       </c>
       <c r="E416" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F416" t="s">
-        <v>565</v>
+        <v>121</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B417" t="s">
-        <v>403</v>
-      </c>
-      <c r="C417" t="s">
+        <v>755</v>
+      </c>
+      <c r="D417" t="s">
+        <v>711</v>
+      </c>
+      <c r="E417" t="s">
+        <v>255</v>
+      </c>
+      <c r="F417" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>683</v>
+      </c>
+      <c r="B418" t="s">
+        <v>753</v>
+      </c>
+      <c r="D418" t="s">
+        <v>711</v>
+      </c>
+      <c r="E418" t="s">
+        <v>256</v>
+      </c>
+      <c r="F418" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>683</v>
+      </c>
+      <c r="B419" t="s">
+        <v>679</v>
+      </c>
+      <c r="D419" t="s">
+        <v>581</v>
+      </c>
+      <c r="E419" t="s">
+        <v>297</v>
+      </c>
+      <c r="F419" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>683</v>
+      </c>
+      <c r="B420" t="s">
+        <v>197</v>
+      </c>
+      <c r="C420" t="s">
+        <v>189</v>
+      </c>
+      <c r="D420">
+        <v>1</v>
+      </c>
+      <c r="E420" t="s">
+        <v>244</v>
+      </c>
+      <c r="F420" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>683</v>
+      </c>
+      <c r="B421" t="s">
+        <v>197</v>
+      </c>
+      <c r="C421" t="s">
+        <v>191</v>
+      </c>
+      <c r="D421">
+        <v>1</v>
+      </c>
+      <c r="E421" t="s">
+        <v>244</v>
+      </c>
+      <c r="F421" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>683</v>
+      </c>
+      <c r="B422" t="s">
+        <v>565</v>
+      </c>
+      <c r="C422" t="s">
+        <v>566</v>
+      </c>
+      <c r="E422" t="s">
+        <v>562</v>
+      </c>
+      <c r="F422" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>683</v>
+      </c>
+      <c r="B423" t="s">
+        <v>565</v>
+      </c>
+      <c r="C423" t="s">
+        <v>567</v>
+      </c>
+      <c r="E423" t="s">
+        <v>562</v>
+      </c>
+      <c r="F423" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>683</v>
+      </c>
+      <c r="B424" t="s">
+        <v>565</v>
+      </c>
+      <c r="C424" t="s">
+        <v>167</v>
+      </c>
+      <c r="E424" t="s">
+        <v>562</v>
+      </c>
+      <c r="F424" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>683</v>
+      </c>
+      <c r="B425" t="s">
+        <v>402</v>
+      </c>
+      <c r="C425" t="s">
         <v>104</v>
       </c>
-      <c r="E417" t="s">
+      <c r="E425" t="s">
+        <v>399</v>
+      </c>
+      <c r="F425" t="s">
         <v>400</v>
-      </c>
-      <c r="F417" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC677896-8741-4F3B-A5BD-9CC686A06A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDE45DB-35E5-46D9-B88C-593E645AC22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="784">
   <si>
     <t>Class</t>
   </si>
@@ -2353,9 +2353,6 @@
   </si>
   <si>
     <t>setFillProperties</t>
-  </si>
-  <si>
-    <t>transparency</t>
   </si>
   <si>
     <t>clear</t>
@@ -8190,9 +8187,6 @@
       <c r="C299" t="s">
         <v>272</v>
       </c>
-      <c r="D299">
-        <v>1</v>
-      </c>
       <c r="E299" t="s">
         <v>772</v>
       </c>
@@ -8396,13 +8390,13 @@
         <v>267</v>
       </c>
       <c r="C310" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E310" t="s">
         <v>772</v>
       </c>
       <c r="F310" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -8529,17 +8523,14 @@
       <c r="B317" t="s">
         <v>771</v>
       </c>
-      <c r="C317" t="s">
-        <v>149</v>
-      </c>
-      <c r="D317">
-        <v>1</v>
+      <c r="D317" t="s">
+        <v>711</v>
       </c>
       <c r="E317" t="s">
         <v>772</v>
       </c>
       <c r="F317" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -8550,13 +8541,16 @@
         <v>771</v>
       </c>
       <c r="C318" t="s">
-        <v>775</v>
+        <v>149</v>
+      </c>
+      <c r="D318">
+        <v>1</v>
       </c>
       <c r="E318" t="s">
         <v>772</v>
       </c>
       <c r="F318" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -8567,7 +8561,7 @@
         <v>771</v>
       </c>
       <c r="C319" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D319">
         <v>1</v>
@@ -8576,7 +8570,7 @@
         <v>772</v>
       </c>
       <c r="F319" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -8604,7 +8598,7 @@
         <v>683</v>
       </c>
       <c r="B321" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C321" t="s">
         <v>30</v>
@@ -8616,7 +8610,7 @@
         <v>772</v>
       </c>
       <c r="F321" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -8624,7 +8618,7 @@
         <v>683</v>
       </c>
       <c r="B322" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C322" t="s">
         <v>545</v>
@@ -8633,7 +8627,7 @@
         <v>772</v>
       </c>
       <c r="F322" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -8641,7 +8635,7 @@
         <v>683</v>
       </c>
       <c r="B323" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D323" t="s">
         <v>581</v>
@@ -8650,7 +8644,7 @@
         <v>772</v>
       </c>
       <c r="F323" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -8658,7 +8652,7 @@
         <v>683</v>
       </c>
       <c r="B324" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D324" t="s">
         <v>581</v>
@@ -8667,7 +8661,7 @@
         <v>772</v>
       </c>
       <c r="F324" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDE45DB-35E5-46D9-B88C-593E645AC22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11AC911-F335-46C8-8AC5-1822D6BFBCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
@@ -8524,7 +8524,7 @@
         <v>771</v>
       </c>
       <c r="D317" t="s">
-        <v>711</v>
+        <v>691</v>
       </c>
       <c r="E317" t="s">
         <v>772</v>

--- a/snippet-extractor-metadata/excel.xlsx
+++ b/snippet-extractor-metadata/excel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30009"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30030"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00039A75-A20C-4A49-B392-46CC2E41BB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11AC911-F335-46C8-8AC5-1822D6BFBCD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-270" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CB5595D7-4492-4192-A1C1-2583BA1957AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Snippets" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2086" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="784">
   <si>
     <t>Class</t>
   </si>
@@ -846,9 +846,6 @@
     <t>addGeometricShape</t>
   </si>
   <si>
-    <t>createSmileyFace</t>
-  </si>
-  <si>
     <t>fill</t>
   </si>
   <si>
@@ -2344,6 +2341,45 @@
   </si>
   <si>
     <t>DataValidationAlertStyle</t>
+  </si>
+  <si>
+    <t>ShapeFill</t>
+  </si>
+  <si>
+    <t>excel-shape-fill-and-line-formatting</t>
+  </si>
+  <si>
+    <t>setSolidFill</t>
+  </si>
+  <si>
+    <t>setFillProperties</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>clearFill</t>
+  </si>
+  <si>
+    <t>ShapeLineFormat</t>
+  </si>
+  <si>
+    <t>formatLine</t>
+  </si>
+  <si>
+    <t>hideLine</t>
+  </si>
+  <si>
+    <t>lineFormat</t>
+  </si>
+  <si>
+    <t>inspectFormatting</t>
+  </si>
+  <si>
+    <t>ShapeLineDashStyle</t>
+  </si>
+  <si>
+    <t>ShapeLineStyle</t>
   </si>
 </sst>
 </file>
@@ -2451,10 +2487,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F417" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:F417" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F417">
-    <sortCondition ref="B1:B417"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78C585A5-D505-49C6-9CA1-8E6558948317}" name="Snippets" displayName="Snippets" ref="A1:F425" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:F425" xr:uid="{EAC65D03-FDD2-4352-A5F3-1CDEDE6251B2}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F425">
+    <sortCondition ref="B1:B425"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{3948678B-75F9-4098-8CE6-D0DBEA4A1A0F}" name="Package"/>
@@ -2785,7 +2821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809930CD-A227-47DC-AAA4-BB816AEDEB59}">
-  <dimension ref="A1:F417"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
@@ -2798,16 +2834,16 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -2818,61 +2854,61 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E2" t="s">
         <v>233</v>
       </c>
       <c r="F2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B3" t="s">
         <v>258</v>
       </c>
       <c r="C3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E3" t="s">
         <v>435</v>
       </c>
-      <c r="E3" t="s">
-        <v>436</v>
-      </c>
       <c r="F3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B4" t="s">
         <v>258</v>
       </c>
       <c r="C4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>284</v>
+      </c>
+      <c r="F4" t="s">
         <v>573</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B5" t="s">
         <v>258</v>
@@ -2884,7 +2920,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F5" t="s">
         <v>260</v>
@@ -2892,155 +2928,155 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B9" t="s">
+        <v>609</v>
+      </c>
+      <c r="D9" t="s">
+        <v>581</v>
+      </c>
+      <c r="E9" t="s">
+        <v>417</v>
+      </c>
+      <c r="F9" t="s">
         <v>610</v>
-      </c>
-      <c r="D9" t="s">
-        <v>582</v>
-      </c>
-      <c r="E9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F9" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B10" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" t="s">
         <v>370</v>
       </c>
-      <c r="C10" t="s">
-        <v>371</v>
-      </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C12" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F12" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C13" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F13" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -3057,299 +3093,299 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D15" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E15" t="s">
         <v>241</v>
       </c>
       <c r="F15" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B16" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D16" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E16" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16" t="s">
         <v>391</v>
-      </c>
-      <c r="F16" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E17" t="s">
+        <v>390</v>
+      </c>
+      <c r="F17" t="s">
         <v>391</v>
-      </c>
-      <c r="F17" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B18" t="s">
+        <v>615</v>
+      </c>
+      <c r="D18" t="s">
+        <v>581</v>
+      </c>
+      <c r="E18" t="s">
         <v>616</v>
       </c>
-      <c r="D18" t="s">
-        <v>582</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>617</v>
-      </c>
-      <c r="F18" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B19" t="s">
+        <v>618</v>
+      </c>
+      <c r="D19" t="s">
+        <v>581</v>
+      </c>
+      <c r="E19" t="s">
+        <v>616</v>
+      </c>
+      <c r="F19" t="s">
         <v>619</v>
-      </c>
-      <c r="D19" t="s">
-        <v>582</v>
-      </c>
-      <c r="E19" t="s">
-        <v>617</v>
-      </c>
-      <c r="F19" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B23" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D23" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E23" t="s">
+        <v>390</v>
+      </c>
+      <c r="F23" t="s">
         <v>391</v>
-      </c>
-      <c r="F23" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D24" t="s">
         <v>78</v>
       </c>
       <c r="E24" t="s">
+        <v>708</v>
+      </c>
+      <c r="F24" t="s">
         <v>709</v>
-      </c>
-      <c r="F24" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B25" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D25" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
+        <v>708</v>
+      </c>
+      <c r="F25" t="s">
         <v>709</v>
-      </c>
-      <c r="F25" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B26" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
+        <v>389</v>
+      </c>
+      <c r="E26" t="s">
         <v>390</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>391</v>
-      </c>
-      <c r="F26" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C27" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" t="s">
         <v>390</v>
       </c>
-      <c r="E27" t="s">
-        <v>391</v>
-      </c>
       <c r="F27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B28" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C28" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" t="s">
         <v>390</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>391</v>
-      </c>
-      <c r="F28" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C29" t="s">
+        <v>389</v>
+      </c>
+      <c r="E29" t="s">
         <v>390</v>
       </c>
-      <c r="E29" t="s">
-        <v>391</v>
-      </c>
       <c r="F29" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B30" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C30" t="s">
         <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F30" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B31" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D31" t="s">
         <v>78</v>
       </c>
       <c r="E31" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F31" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B32" t="s">
         <v>85</v>
@@ -3366,7 +3402,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B33" t="s">
         <v>85</v>
@@ -3383,112 +3419,112 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B34" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E34" t="s">
+        <v>589</v>
+      </c>
+      <c r="F34" t="s">
         <v>590</v>
-      </c>
-      <c r="F34" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B35" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35" t="s">
+        <v>542</v>
+      </c>
+      <c r="F35" t="s">
         <v>543</v>
-      </c>
-      <c r="F35" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B36" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C36" t="s">
         <v>171</v>
       </c>
       <c r="E36" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B37" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C37" t="s">
         <v>171</v>
       </c>
       <c r="E37" t="s">
+        <v>531</v>
+      </c>
+      <c r="F37" t="s">
         <v>532</v>
-      </c>
-      <c r="F37" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B38" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C38" t="s">
         <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C39" t="s">
         <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B40" t="s">
         <v>136</v>
@@ -3505,7 +3541,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B41" t="s">
         <v>136</v>
@@ -3522,234 +3558,234 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B42" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C42" t="s">
         <v>171</v>
       </c>
       <c r="E42" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F42" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B43" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C43" t="s">
         <v>171</v>
       </c>
       <c r="E43" t="s">
+        <v>531</v>
+      </c>
+      <c r="F43" t="s">
         <v>532</v>
-      </c>
-      <c r="F43" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B44" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
         <v>169</v>
       </c>
       <c r="E44" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C45" t="s">
         <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B46" t="s">
+        <v>731</v>
+      </c>
+      <c r="D46" t="s">
+        <v>691</v>
+      </c>
+      <c r="E46" t="s">
+        <v>728</v>
+      </c>
+      <c r="F46" t="s">
         <v>732</v>
-      </c>
-      <c r="D46" t="s">
-        <v>692</v>
-      </c>
-      <c r="E46" t="s">
-        <v>729</v>
-      </c>
-      <c r="F46" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B47" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C47" t="s">
         <v>84</v>
       </c>
       <c r="E47" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F47" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B48" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C48" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E48" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F48" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B49" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C49" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E49" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F49" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B50" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C50" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E50" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F50" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B51" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C51" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E51" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F51" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B52" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E52" t="s">
+        <v>542</v>
+      </c>
+      <c r="F52" t="s">
         <v>543</v>
-      </c>
-      <c r="F52" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B53" t="s">
+        <v>541</v>
+      </c>
+      <c r="C53" t="s">
+        <v>551</v>
+      </c>
+      <c r="E53" t="s">
         <v>542</v>
       </c>
-      <c r="C53" t="s">
-        <v>552</v>
-      </c>
-      <c r="E53" t="s">
-        <v>543</v>
-      </c>
       <c r="F53" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B54" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C54" t="s">
         <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F54" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B55" t="s">
         <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3758,12 +3794,12 @@
         <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B56" t="s">
         <v>142</v>
@@ -3783,41 +3819,41 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B57" t="s">
+        <v>740</v>
+      </c>
+      <c r="D57" t="s">
+        <v>691</v>
+      </c>
+      <c r="E57" t="s">
+        <v>736</v>
+      </c>
+      <c r="F57" t="s">
         <v>741</v>
-      </c>
-      <c r="D57" t="s">
-        <v>692</v>
-      </c>
-      <c r="E57" t="s">
-        <v>737</v>
-      </c>
-      <c r="F57" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B58" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D58" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E58" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F58" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B59" t="s">
         <v>198</v>
@@ -3834,206 +3870,206 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B60" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D60" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E60" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F60" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B61" t="s">
+        <v>727</v>
+      </c>
+      <c r="D61" t="s">
+        <v>691</v>
+      </c>
+      <c r="E61" t="s">
         <v>728</v>
       </c>
-      <c r="D61" t="s">
-        <v>692</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>729</v>
-      </c>
-      <c r="F61" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B62" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D62" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E62" t="s">
+        <v>728</v>
+      </c>
+      <c r="F62" t="s">
         <v>729</v>
-      </c>
-      <c r="F62" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B63" t="s">
         <v>133</v>
       </c>
       <c r="C63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D63">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F63" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B64" t="s">
         <v>133</v>
       </c>
       <c r="C64" t="s">
+        <v>483</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
         <v>484</v>
       </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>485</v>
-      </c>
-      <c r="F64" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B65" t="s">
         <v>133</v>
       </c>
       <c r="C65" t="s">
+        <v>597</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="s">
         <v>598</v>
       </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>599</v>
-      </c>
-      <c r="F65" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B66" t="s">
         <v>133</v>
       </c>
       <c r="C66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
+        <v>598</v>
+      </c>
+      <c r="F66" t="s">
         <v>599</v>
-      </c>
-      <c r="F66" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B67" t="s">
         <v>133</v>
       </c>
       <c r="D67" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E67" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F67" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B68" t="s">
         <v>133</v>
       </c>
       <c r="C68" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E68" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F68" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B69" t="s">
         <v>133</v>
       </c>
       <c r="C69" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E69" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F69" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B70" t="s">
         <v>133</v>
       </c>
       <c r="C70" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E70" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F70" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B71" t="s">
         <v>133</v>
@@ -4053,7 +4089,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B72" t="s">
         <v>133</v>
@@ -4073,7 +4109,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B73" t="s">
         <v>133</v>
@@ -4090,13 +4126,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B74" t="s">
         <v>133</v>
       </c>
       <c r="C74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E74" t="s">
         <v>174</v>
@@ -4107,7 +4143,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B75" t="s">
         <v>133</v>
@@ -4124,7 +4160,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B76" t="s">
         <v>133</v>
@@ -4141,41 +4177,41 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B77" t="s">
+        <v>620</v>
+      </c>
+      <c r="D77" t="s">
+        <v>581</v>
+      </c>
+      <c r="E77" t="s">
+        <v>598</v>
+      </c>
+      <c r="F77" t="s">
         <v>621</v>
-      </c>
-      <c r="D77" t="s">
-        <v>582</v>
-      </c>
-      <c r="E77" t="s">
-        <v>599</v>
-      </c>
-      <c r="F77" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B78" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D78" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E78" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F78" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B79" t="s">
         <v>248</v>
@@ -4195,7 +4231,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B80" t="s">
         <v>248</v>
@@ -4212,7 +4248,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B81" t="s">
         <v>124</v>
@@ -4229,7 +4265,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B82" t="s">
         <v>122</v>
@@ -4249,7 +4285,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B83" t="s">
         <v>128</v>
@@ -4266,75 +4302,75 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B84" t="s">
+        <v>580</v>
+      </c>
+      <c r="D84" t="s">
         <v>581</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>582</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>583</v>
-      </c>
-      <c r="F84" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B85" t="s">
+        <v>710</v>
+      </c>
+      <c r="D85" t="s">
         <v>711</v>
       </c>
-      <c r="D85" t="s">
-        <v>712</v>
-      </c>
       <c r="E85" t="s">
+        <v>708</v>
+      </c>
+      <c r="F85" t="s">
         <v>709</v>
-      </c>
-      <c r="F85" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B86" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D86" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E86" t="s">
         <v>102</v>
       </c>
       <c r="F86" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B87" t="s">
+        <v>625</v>
+      </c>
+      <c r="D87" t="s">
+        <v>581</v>
+      </c>
+      <c r="E87" t="s">
+        <v>323</v>
+      </c>
+      <c r="F87" t="s">
         <v>626</v>
-      </c>
-      <c r="D87" t="s">
-        <v>582</v>
-      </c>
-      <c r="E87" t="s">
-        <v>324</v>
-      </c>
-      <c r="F87" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B88" t="s">
         <v>58</v>
@@ -4351,27 +4387,27 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B89" t="s">
+        <v>358</v>
+      </c>
+      <c r="C89" t="s">
+        <v>360</v>
+      </c>
+      <c r="E89" t="s">
+        <v>421</v>
+      </c>
+      <c r="F89" t="s">
         <v>359</v>
-      </c>
-      <c r="C89" t="s">
-        <v>361</v>
-      </c>
-      <c r="E89" t="s">
-        <v>422</v>
-      </c>
-      <c r="F89" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B90" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
@@ -4380,18 +4416,18 @@
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F90" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B91" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C91" t="s">
         <v>199</v>
@@ -4400,35 +4436,35 @@
         <v>2</v>
       </c>
       <c r="E91" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F91" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B92" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C92" t="s">
+        <v>424</v>
+      </c>
+      <c r="E92" t="s">
         <v>425</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>426</v>
-      </c>
-      <c r="F92" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B93" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C93" t="s">
         <v>8</v>
@@ -4437,137 +4473,137 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F93" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B94" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C94" t="s">
         <v>165</v>
       </c>
       <c r="E94" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F94" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B95" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C95" t="s">
         <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F95" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B96" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C96" t="s">
         <v>182</v>
       </c>
       <c r="E96" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F96" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B97" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C97" t="s">
         <v>182</v>
       </c>
       <c r="E97" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F97" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B98" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C98" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E98" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F98" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B99" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C99" t="s">
+        <v>480</v>
+      </c>
+      <c r="E99" t="s">
+        <v>482</v>
+      </c>
+      <c r="F99" t="s">
         <v>481</v>
-      </c>
-      <c r="E99" t="s">
-        <v>483</v>
-      </c>
-      <c r="F99" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B100" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C100" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E100" t="s">
+        <v>422</v>
+      </c>
+      <c r="F100" t="s">
         <v>423</v>
-      </c>
-      <c r="F100" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B101" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C101" t="s">
         <v>10</v>
@@ -4576,18 +4612,18 @@
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F101" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B102" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C102" t="s">
         <v>8</v>
@@ -4596,32 +4632,32 @@
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F102" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B103" t="s">
+        <v>427</v>
+      </c>
+      <c r="C103" t="s">
         <v>428</v>
       </c>
-      <c r="C103" t="s">
+      <c r="E103" t="s">
         <v>429</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>430</v>
-      </c>
-      <c r="F103" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B104" t="s">
         <v>89</v>
@@ -4638,7 +4674,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B105" t="s">
         <v>89</v>
@@ -4655,13 +4691,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B106" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D106" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E106" t="s">
         <v>59</v>
@@ -4672,13 +4708,13 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B107" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D107" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E107" t="s">
         <v>59</v>
@@ -4689,13 +4725,13 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B108" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D108" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E108" t="s">
         <v>59</v>
@@ -4706,7 +4742,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B109" t="s">
         <v>56</v>
@@ -4723,7 +4759,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B110" t="s">
         <v>56</v>
@@ -4740,7 +4776,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B111" t="s">
         <v>56</v>
@@ -4757,7 +4793,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B112" t="s">
         <v>56</v>
@@ -4774,7 +4810,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B113" t="s">
         <v>56</v>
@@ -4794,7 +4830,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B114" t="s">
         <v>56</v>
@@ -4811,7 +4847,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B115" t="s">
         <v>56</v>
@@ -4828,7 +4864,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B116" t="s">
         <v>56</v>
@@ -4845,7 +4881,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B117" t="s">
         <v>56</v>
@@ -4862,7 +4898,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B118" t="s">
         <v>54</v>
@@ -4882,7 +4918,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B119" t="s">
         <v>54</v>
@@ -4902,7 +4938,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B120" t="s">
         <v>54</v>
@@ -4922,13 +4958,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B121" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D121" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E121" t="s">
         <v>59</v>
@@ -4939,13 +4975,13 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B122" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D122" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E122" t="s">
         <v>59</v>
@@ -4956,24 +4992,24 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B123" t="s">
+        <v>630</v>
+      </c>
+      <c r="D123" t="s">
+        <v>581</v>
+      </c>
+      <c r="E123" t="s">
+        <v>632</v>
+      </c>
+      <c r="F123" t="s">
         <v>631</v>
-      </c>
-      <c r="D123" t="s">
-        <v>582</v>
-      </c>
-      <c r="E123" t="s">
-        <v>633</v>
-      </c>
-      <c r="F123" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B124" t="s">
         <v>94</v>
@@ -4990,24 +5026,24 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B125" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D125" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E125" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F125" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B126" t="s">
         <v>76</v>
@@ -5024,7 +5060,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B127" t="s">
         <v>76</v>
@@ -5041,7 +5077,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B128" t="s">
         <v>76</v>
@@ -5058,13 +5094,13 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B129" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D129" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E129" t="s">
         <v>59</v>
@@ -5075,7 +5111,7 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B130" t="s">
         <v>64</v>
@@ -5092,7 +5128,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B131" t="s">
         <v>83</v>
@@ -5109,13 +5145,13 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B132" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E132" t="s">
         <v>59</v>
@@ -5126,58 +5162,58 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B133" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D133" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E133" t="s">
+        <v>336</v>
+      </c>
+      <c r="F133" t="s">
         <v>337</v>
-      </c>
-      <c r="F133" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B134" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D134" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E134" t="s">
+        <v>429</v>
+      </c>
+      <c r="F134" t="s">
         <v>430</v>
-      </c>
-      <c r="F134" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B135" t="s">
+        <v>460</v>
+      </c>
+      <c r="C135" t="s">
         <v>461</v>
       </c>
-      <c r="C135" t="s">
+      <c r="E135" t="s">
         <v>462</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>463</v>
-      </c>
-      <c r="F135" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B136" t="s">
         <v>91</v>
@@ -5194,10 +5230,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B137" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C137" t="s">
         <v>8</v>
@@ -5206,15 +5242,15 @@
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F137" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B138" t="s">
         <v>32</v>
@@ -5234,7 +5270,7 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B139" t="s">
         <v>32</v>
@@ -5254,7 +5290,7 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B140" t="s">
         <v>32</v>
@@ -5271,7 +5307,7 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B141" t="s">
         <v>32</v>
@@ -5291,7 +5327,7 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B142" t="s">
         <v>29</v>
@@ -5311,7 +5347,7 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B143" t="s">
         <v>29</v>
@@ -5331,7 +5367,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B144" t="s">
         <v>29</v>
@@ -5351,7 +5387,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B145" t="s">
         <v>41</v>
@@ -5371,7 +5407,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B146" t="s">
         <v>41</v>
@@ -5391,7 +5427,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B147" t="s">
         <v>41</v>
@@ -5411,7 +5447,7 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s">
         <v>68</v>
@@ -5428,7 +5464,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B149" t="s">
         <v>224</v>
@@ -5445,7 +5481,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B150" t="s">
         <v>224</v>
@@ -5462,7 +5498,7 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B151" t="s">
         <v>212</v>
@@ -5479,13 +5515,13 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B152" t="s">
         <v>212</v>
       </c>
       <c r="C152" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E152" t="s">
         <v>208</v>
@@ -5496,7 +5532,7 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B153" t="s">
         <v>212</v>
@@ -5513,13 +5549,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B154" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D154" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E154" t="s">
         <v>208</v>
@@ -5530,13 +5566,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B155" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D155" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E155" t="s">
         <v>208</v>
@@ -5547,13 +5583,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B156" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D156" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E156" t="s">
         <v>208</v>
@@ -5564,7 +5600,7 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B157" t="s">
         <v>243</v>
@@ -5581,7 +5617,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B158" t="s">
         <v>243</v>
@@ -5598,393 +5634,393 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B159" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D159" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E159" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F159" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B160" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D160" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E160" t="s">
         <v>256</v>
       </c>
       <c r="F160" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B161" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C161" t="s">
         <v>92</v>
       </c>
       <c r="E161" t="s">
+        <v>452</v>
+      </c>
+      <c r="F161" t="s">
         <v>453</v>
-      </c>
-      <c r="F161" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B162" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C162" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E162" t="s">
+        <v>723</v>
+      </c>
+      <c r="F162" t="s">
         <v>724</v>
-      </c>
-      <c r="F162" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B163" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C163" t="s">
         <v>78</v>
       </c>
       <c r="E163" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F163" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B164" t="s">
+        <v>641</v>
+      </c>
+      <c r="D164" t="s">
+        <v>581</v>
+      </c>
+      <c r="E164" t="s">
+        <v>643</v>
+      </c>
+      <c r="F164" t="s">
         <v>642</v>
-      </c>
-      <c r="D164" t="s">
-        <v>582</v>
-      </c>
-      <c r="E164" t="s">
-        <v>644</v>
-      </c>
-      <c r="F164" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B165" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D165" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E165" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F165" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B166" t="s">
+        <v>688</v>
+      </c>
+      <c r="D166" t="s">
+        <v>581</v>
+      </c>
+      <c r="E166" t="s">
         <v>689</v>
       </c>
-      <c r="D166" t="s">
-        <v>582</v>
-      </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>690</v>
-      </c>
-      <c r="F166" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B167" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D167" t="s">
         <v>78</v>
       </c>
       <c r="E167" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F167" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B168" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D168" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E168" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F168" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B169" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D169" t="s">
         <v>78</v>
       </c>
       <c r="E169" t="s">
+        <v>589</v>
+      </c>
+      <c r="F169" t="s">
         <v>590</v>
-      </c>
-      <c r="F169" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B170" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D170" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E170" t="s">
+        <v>589</v>
+      </c>
+      <c r="F170" t="s">
         <v>590</v>
-      </c>
-      <c r="F170" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B171" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D171" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E171" t="s">
+        <v>390</v>
+      </c>
+      <c r="F171" t="s">
         <v>391</v>
-      </c>
-      <c r="F171" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B172" t="s">
+        <v>556</v>
+      </c>
+      <c r="C172" t="s">
         <v>557</v>
       </c>
-      <c r="C172" t="s">
+      <c r="E172" t="s">
+        <v>368</v>
+      </c>
+      <c r="F172" t="s">
         <v>558</v>
-      </c>
-      <c r="E172" t="s">
-        <v>369</v>
-      </c>
-      <c r="F172" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B173" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D173" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E173" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F173" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B174" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D174" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E174" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F174" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B175" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D175" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E175" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F175" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B176" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C176" t="s">
+        <v>695</v>
+      </c>
+      <c r="D176">
+        <v>1</v>
+      </c>
+      <c r="E176" t="s">
         <v>696</v>
       </c>
-      <c r="D176">
-        <v>1</v>
-      </c>
-      <c r="E176" t="s">
-        <v>697</v>
-      </c>
       <c r="F176" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B177" t="s">
+        <v>693</v>
+      </c>
+      <c r="C177" t="s">
         <v>694</v>
       </c>
-      <c r="C177" t="s">
-        <v>695</v>
-      </c>
       <c r="D177">
         <v>1</v>
       </c>
       <c r="E177" t="s">
+        <v>696</v>
+      </c>
+      <c r="F177" t="s">
         <v>697</v>
-      </c>
-      <c r="F177" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B178" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D178" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E178" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B179" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D179" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E179" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F179" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B180" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D180" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E180" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F180" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B181" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D181" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E181" t="s">
         <v>59</v>
@@ -5995,7 +6031,7 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B182" t="s">
         <v>72</v>
@@ -6012,7 +6048,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B183" t="s">
         <v>72</v>
@@ -6029,172 +6065,172 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B184" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C184" t="s">
         <v>84</v>
       </c>
       <c r="E184" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F184" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B185" t="s">
+        <v>649</v>
+      </c>
+      <c r="D185" t="s">
+        <v>581</v>
+      </c>
+      <c r="E185" t="s">
         <v>650</v>
       </c>
-      <c r="D185" t="s">
-        <v>582</v>
-      </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>651</v>
-      </c>
-      <c r="F185" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B186" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D186" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E186" t="s">
+        <v>525</v>
+      </c>
+      <c r="F186" t="s">
         <v>526</v>
-      </c>
-      <c r="F186" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B187" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D187" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E187" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F187" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B188" t="s">
+        <v>341</v>
+      </c>
+      <c r="C188" t="s">
         <v>342</v>
       </c>
-      <c r="C188" t="s">
-        <v>343</v>
-      </c>
       <c r="D188">
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F188" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B189" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C189" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D189">
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F189" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B190" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C190" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D190">
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F190" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B191" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C191" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D191">
         <v>1</v>
       </c>
       <c r="E191" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F191" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B192" t="s">
         <v>9</v>
       </c>
       <c r="D192" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E192" t="s">
         <v>11</v>
       </c>
       <c r="F192" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B193" t="s">
         <v>9</v>
@@ -6214,7 +6250,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B194" t="s">
         <v>9</v>
@@ -6231,7 +6267,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
@@ -6251,95 +6287,95 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B196" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D196" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E196" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F196" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B197" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C197" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E197" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F197" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B198" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C198" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E198" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F198" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B199" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C199" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E199" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F199" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B200" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C200" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E200" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F200" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B201" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C201" t="s">
         <v>10</v>
@@ -6348,35 +6384,35 @@
         <v>1</v>
       </c>
       <c r="E201" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F201" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B202" t="s">
+        <v>700</v>
+      </c>
+      <c r="D202" t="s">
+        <v>691</v>
+      </c>
+      <c r="E202" t="s">
         <v>701</v>
       </c>
-      <c r="D202" t="s">
-        <v>692</v>
-      </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>702</v>
-      </c>
-      <c r="F202" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B203" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C203" t="s">
         <v>8</v>
@@ -6385,18 +6421,18 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
+        <v>701</v>
+      </c>
+      <c r="F203" t="s">
         <v>702</v>
-      </c>
-      <c r="F203" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B204" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C204" t="s">
         <v>35</v>
@@ -6405,18 +6441,18 @@
         <v>1</v>
       </c>
       <c r="E204" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F204" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B205" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C205" t="s">
         <v>96</v>
@@ -6425,52 +6461,52 @@
         <v>1</v>
       </c>
       <c r="E205" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F205" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B206" t="s">
+        <v>440</v>
+      </c>
+      <c r="C206" t="s">
         <v>441</v>
       </c>
-      <c r="C206" t="s">
-        <v>442</v>
-      </c>
       <c r="E206" t="s">
+        <v>435</v>
+      </c>
+      <c r="F206" t="s">
         <v>436</v>
-      </c>
-      <c r="F206" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B207" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C207" t="s">
+        <v>437</v>
+      </c>
+      <c r="E207" t="s">
+        <v>435</v>
+      </c>
+      <c r="F207" t="s">
         <v>438</v>
-      </c>
-      <c r="E207" t="s">
-        <v>436</v>
-      </c>
-      <c r="F207" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B208" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C208" t="s">
         <v>8</v>
@@ -6479,279 +6515,279 @@
         <v>1</v>
       </c>
       <c r="E208" t="s">
+        <v>308</v>
+      </c>
+      <c r="F208" t="s">
         <v>309</v>
-      </c>
-      <c r="F208" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B209" t="s">
+        <v>312</v>
+      </c>
+      <c r="C209" t="s">
+        <v>310</v>
+      </c>
+      <c r="E209" t="s">
+        <v>308</v>
+      </c>
+      <c r="F209" t="s">
         <v>313</v>
-      </c>
-      <c r="C209" t="s">
-        <v>311</v>
-      </c>
-      <c r="E209" t="s">
-        <v>309</v>
-      </c>
-      <c r="F209" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B210" t="s">
+        <v>312</v>
+      </c>
+      <c r="C210" t="s">
+        <v>311</v>
+      </c>
+      <c r="E210" t="s">
+        <v>308</v>
+      </c>
+      <c r="F210" t="s">
         <v>313</v>
-      </c>
-      <c r="C210" t="s">
-        <v>312</v>
-      </c>
-      <c r="E210" t="s">
-        <v>309</v>
-      </c>
-      <c r="F210" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B211" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C211" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E211" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F211" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B212" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F212" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B213" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C213" t="s">
+        <v>314</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+      <c r="E213" t="s">
+        <v>308</v>
+      </c>
+      <c r="F213" t="s">
         <v>315</v>
-      </c>
-      <c r="D213">
-        <v>1</v>
-      </c>
-      <c r="E213" t="s">
-        <v>309</v>
-      </c>
-      <c r="F213" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B214" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C214" t="s">
+        <v>387</v>
+      </c>
+      <c r="E214" t="s">
+        <v>308</v>
+      </c>
+      <c r="F214" t="s">
         <v>388</v>
-      </c>
-      <c r="E214" t="s">
-        <v>309</v>
-      </c>
-      <c r="F214" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B215" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D215" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E215" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F215" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B216" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D216" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E216" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F216" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B217" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C217" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D217">
         <v>1</v>
       </c>
       <c r="E217" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F217" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B218" t="s">
+        <v>465</v>
+      </c>
+      <c r="C218" t="s">
         <v>466</v>
       </c>
-      <c r="C218" t="s">
-        <v>467</v>
-      </c>
       <c r="E218" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F218" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B219" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C219" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E219" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F219" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B220" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C220" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E220" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F220" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B221" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C221" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E221" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F221" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B222" t="s">
+        <v>472</v>
+      </c>
+      <c r="C222" t="s">
         <v>473</v>
       </c>
-      <c r="C222" t="s">
+      <c r="E222" t="s">
         <v>474</v>
       </c>
-      <c r="E222" t="s">
-        <v>475</v>
-      </c>
       <c r="F222" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B223" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D223" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E223" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F223" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B224" t="s">
         <v>229</v>
@@ -6771,87 +6807,87 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B225" t="s">
         <v>229</v>
       </c>
       <c r="C225" t="s">
+        <v>493</v>
+      </c>
+      <c r="E225" t="s">
         <v>494</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>495</v>
-      </c>
-      <c r="F225" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B226" t="s">
         <v>229</v>
       </c>
       <c r="C226" t="s">
+        <v>496</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226" t="s">
+        <v>494</v>
+      </c>
+      <c r="F226" t="s">
         <v>497</v>
-      </c>
-      <c r="D226">
-        <v>1</v>
-      </c>
-      <c r="E226" t="s">
-        <v>495</v>
-      </c>
-      <c r="F226" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B227" t="s">
         <v>229</v>
       </c>
       <c r="C227" t="s">
+        <v>498</v>
+      </c>
+      <c r="E227" t="s">
+        <v>494</v>
+      </c>
+      <c r="F227" t="s">
         <v>499</v>
-      </c>
-      <c r="E227" t="s">
-        <v>495</v>
-      </c>
-      <c r="F227" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B228" t="s">
         <v>229</v>
       </c>
       <c r="C228" t="s">
+        <v>500</v>
+      </c>
+      <c r="E228" t="s">
+        <v>494</v>
+      </c>
+      <c r="F228" t="s">
         <v>501</v>
-      </c>
-      <c r="E228" t="s">
-        <v>495</v>
-      </c>
-      <c r="F228" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B229" t="s">
         <v>229</v>
       </c>
       <c r="C229" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E229" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F229" t="s">
         <v>226</v>
@@ -6859,95 +6895,95 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B230" t="s">
         <v>229</v>
       </c>
       <c r="C230" t="s">
+        <v>503</v>
+      </c>
+      <c r="E230" t="s">
+        <v>494</v>
+      </c>
+      <c r="F230" t="s">
         <v>504</v>
-      </c>
-      <c r="E230" t="s">
-        <v>495</v>
-      </c>
-      <c r="F230" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B231" t="s">
         <v>229</v>
       </c>
       <c r="C231" t="s">
+        <v>505</v>
+      </c>
+      <c r="D231">
+        <v>1</v>
+      </c>
+      <c r="E231" t="s">
+        <v>494</v>
+      </c>
+      <c r="F231" t="s">
         <v>506</v>
-      </c>
-      <c r="D231">
-        <v>1</v>
-      </c>
-      <c r="E231" t="s">
-        <v>495</v>
-      </c>
-      <c r="F231" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B232" t="s">
         <v>229</v>
       </c>
       <c r="C232" t="s">
+        <v>507</v>
+      </c>
+      <c r="E232" t="s">
+        <v>494</v>
+      </c>
+      <c r="F232" t="s">
         <v>508</v>
-      </c>
-      <c r="E232" t="s">
-        <v>495</v>
-      </c>
-      <c r="F232" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B233" t="s">
         <v>229</v>
       </c>
       <c r="C233" t="s">
+        <v>509</v>
+      </c>
+      <c r="E233" t="s">
+        <v>494</v>
+      </c>
+      <c r="F233" t="s">
         <v>510</v>
-      </c>
-      <c r="E233" t="s">
-        <v>495</v>
-      </c>
-      <c r="F233" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B234" t="s">
         <v>229</v>
       </c>
       <c r="C234" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F234" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B235" t="s">
         <v>216</v>
@@ -6964,7 +7000,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B236" t="s">
         <v>216</v>
@@ -6981,7 +7017,7 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B237" t="s">
         <v>216</v>
@@ -7001,7 +7037,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B238" t="s">
         <v>216</v>
@@ -7018,47 +7054,47 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B239" t="s">
         <v>216</v>
       </c>
       <c r="C239" t="s">
+        <v>593</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+      <c r="E239" t="s">
         <v>594</v>
       </c>
-      <c r="D239">
-        <v>1</v>
-      </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>595</v>
-      </c>
-      <c r="F239" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B240" t="s">
         <v>216</v>
       </c>
       <c r="C240" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D240">
         <v>1</v>
       </c>
       <c r="E240" t="s">
+        <v>594</v>
+      </c>
+      <c r="F240" t="s">
         <v>595</v>
-      </c>
-      <c r="F240" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B241" t="s">
         <v>216</v>
@@ -7075,27 +7111,27 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B242" t="s">
         <v>216</v>
       </c>
       <c r="C242" t="s">
+        <v>601</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+      <c r="E242" t="s">
         <v>602</v>
       </c>
-      <c r="D242">
-        <v>1</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>603</v>
-      </c>
-      <c r="F242" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B243" t="s">
         <v>213</v>
@@ -7115,7 +7151,7 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B244" t="s">
         <v>213</v>
@@ -7127,32 +7163,32 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
+        <v>602</v>
+      </c>
+      <c r="F244" t="s">
         <v>603</v>
-      </c>
-      <c r="F244" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B245" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D245" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E245" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F245" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B246" t="s">
         <v>62</v>
@@ -7169,255 +7205,255 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B247" t="s">
         <v>23</v>
       </c>
       <c r="C247" t="s">
+        <v>715</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+      <c r="E247" t="s">
+        <v>708</v>
+      </c>
+      <c r="F247" t="s">
         <v>716</v>
-      </c>
-      <c r="D247">
-        <v>1</v>
-      </c>
-      <c r="E247" t="s">
-        <v>709</v>
-      </c>
-      <c r="F247" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B248" t="s">
         <v>23</v>
       </c>
       <c r="C248" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E248" t="s">
+        <v>708</v>
+      </c>
+      <c r="F248" t="s">
         <v>709</v>
-      </c>
-      <c r="F248" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B249" t="s">
         <v>23</v>
       </c>
       <c r="C249" t="s">
+        <v>717</v>
+      </c>
+      <c r="E249" t="s">
+        <v>708</v>
+      </c>
+      <c r="F249" t="s">
         <v>718</v>
-      </c>
-      <c r="E249" t="s">
-        <v>709</v>
-      </c>
-      <c r="F249" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B250" t="s">
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E250" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F250" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B251" t="s">
         <v>23</v>
       </c>
       <c r="C251" t="s">
+        <v>512</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+      <c r="E251" t="s">
         <v>513</v>
       </c>
-      <c r="D251">
-        <v>1</v>
-      </c>
-      <c r="E251" t="s">
-        <v>514</v>
-      </c>
       <c r="F251" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B252" t="s">
         <v>23</v>
       </c>
       <c r="C252" t="s">
+        <v>404</v>
+      </c>
+      <c r="E252" t="s">
         <v>405</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>406</v>
-      </c>
-      <c r="F252" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B253" t="s">
         <v>23</v>
       </c>
       <c r="C253" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D253">
         <v>1</v>
       </c>
       <c r="E253" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F253" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B254" t="s">
         <v>23</v>
       </c>
       <c r="C254" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D254">
         <v>1</v>
       </c>
       <c r="E254" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F254" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B255" t="s">
         <v>23</v>
       </c>
       <c r="C255" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D255">
         <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F255" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B256" t="s">
         <v>23</v>
       </c>
       <c r="C256" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D256">
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F256" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B257" t="s">
         <v>23</v>
       </c>
       <c r="C257" t="s">
+        <v>446</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257" t="s">
+        <v>443</v>
+      </c>
+      <c r="F257" t="s">
         <v>447</v>
-      </c>
-      <c r="D257">
-        <v>1</v>
-      </c>
-      <c r="E257" t="s">
-        <v>444</v>
-      </c>
-      <c r="F257" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B258" t="s">
         <v>23</v>
       </c>
       <c r="C258" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D258">
         <v>1</v>
       </c>
       <c r="E258" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F258" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B259" t="s">
         <v>23</v>
       </c>
       <c r="C259" t="s">
+        <v>538</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+      <c r="E259" t="s">
+        <v>537</v>
+      </c>
+      <c r="F259" t="s">
         <v>539</v>
-      </c>
-      <c r="D259">
-        <v>1</v>
-      </c>
-      <c r="E259" t="s">
-        <v>538</v>
-      </c>
-      <c r="F259" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B260" t="s">
         <v>23</v>
@@ -7429,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="E260" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F260" t="s">
         <v>266</v>
@@ -7437,227 +7473,227 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B261" t="s">
         <v>23</v>
       </c>
       <c r="C261" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D261">
         <v>1</v>
       </c>
       <c r="E261" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F261" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B262" t="s">
         <v>23</v>
       </c>
       <c r="C262" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D262">
         <v>1</v>
       </c>
       <c r="E262" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F262" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B263" t="s">
         <v>23</v>
       </c>
       <c r="C263" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D263">
         <v>1</v>
       </c>
       <c r="E263" t="s">
+        <v>390</v>
+      </c>
+      <c r="F263" t="s">
         <v>391</v>
-      </c>
-      <c r="F263" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B264" t="s">
         <v>23</v>
       </c>
       <c r="C264" t="s">
+        <v>274</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+      <c r="E264" t="s">
+        <v>287</v>
+      </c>
+      <c r="F264" t="s">
         <v>275</v>
-      </c>
-      <c r="D264">
-        <v>1</v>
-      </c>
-      <c r="E264" t="s">
-        <v>288</v>
-      </c>
-      <c r="F264" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B265" t="s">
         <v>23</v>
       </c>
       <c r="C265" t="s">
+        <v>432</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+      <c r="E265" t="s">
+        <v>287</v>
+      </c>
+      <c r="F265" t="s">
         <v>433</v>
-      </c>
-      <c r="D265">
-        <v>1</v>
-      </c>
-      <c r="E265" t="s">
-        <v>288</v>
-      </c>
-      <c r="F265" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B266" t="s">
         <v>23</v>
       </c>
       <c r="C266" t="s">
+        <v>585</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+      <c r="E266" t="s">
         <v>586</v>
       </c>
-      <c r="D266">
-        <v>1</v>
-      </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>587</v>
-      </c>
-      <c r="F266" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B267" t="s">
         <v>23</v>
       </c>
       <c r="C267" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D267">
         <v>1</v>
       </c>
       <c r="E267" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F267" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B268" t="s">
         <v>23</v>
       </c>
       <c r="C268" t="s">
+        <v>276</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+      <c r="E268" t="s">
+        <v>288</v>
+      </c>
+      <c r="F268" t="s">
         <v>277</v>
-      </c>
-      <c r="D268">
-        <v>1</v>
-      </c>
-      <c r="E268" t="s">
-        <v>289</v>
-      </c>
-      <c r="F268" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B269" t="s">
         <v>23</v>
       </c>
       <c r="C269" t="s">
+        <v>278</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+      <c r="E269" t="s">
+        <v>288</v>
+      </c>
+      <c r="F269" t="s">
         <v>279</v>
-      </c>
-      <c r="D269">
-        <v>1</v>
-      </c>
-      <c r="E269" t="s">
-        <v>289</v>
-      </c>
-      <c r="F269" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B270" t="s">
         <v>23</v>
       </c>
       <c r="C270" t="s">
+        <v>527</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+      <c r="E270" t="s">
+        <v>525</v>
+      </c>
+      <c r="F270" t="s">
         <v>528</v>
-      </c>
-      <c r="D270">
-        <v>1</v>
-      </c>
-      <c r="E270" t="s">
-        <v>526</v>
-      </c>
-      <c r="F270" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B271" t="s">
         <v>23</v>
       </c>
       <c r="C271" t="s">
+        <v>524</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+      <c r="E271" t="s">
         <v>525</v>
       </c>
-      <c r="D271">
-        <v>1</v>
-      </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>526</v>
-      </c>
-      <c r="F271" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B272" t="s">
         <v>23</v>
@@ -7674,7 +7710,7 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B273" t="s">
         <v>23</v>
@@ -7694,7 +7730,7 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B274" t="s">
         <v>23</v>
@@ -7714,27 +7750,27 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B275" t="s">
         <v>23</v>
       </c>
       <c r="C275" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D275">
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F275" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B276" t="s">
         <v>23</v>
@@ -7743,7 +7779,7 @@
         <v>77</v>
       </c>
       <c r="E276" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F276" t="s">
         <v>156</v>
@@ -7751,7 +7787,7 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B277" t="s">
         <v>23</v>
@@ -7771,7 +7807,7 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B278" t="s">
         <v>23</v>
@@ -7791,41 +7827,41 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B279" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C279" t="s">
         <v>84</v>
       </c>
       <c r="E279" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F279" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B280" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D280" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E280" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F280" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B281" t="s">
         <v>106</v>
@@ -7842,7 +7878,7 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B282" t="s">
         <v>98</v>
@@ -7859,7 +7895,7 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B283" t="s">
         <v>98</v>
@@ -7876,7 +7912,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B284" t="s">
         <v>98</v>
@@ -7893,7 +7929,7 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B285" t="s">
         <v>98</v>
@@ -7910,33 +7946,33 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B286" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D286" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E286" t="s">
         <v>102</v>
       </c>
       <c r="F286" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B287" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D287" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E287" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F287" t="s">
         <v>161</v>
@@ -7944,41 +7980,41 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B288" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C288" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E288" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F288" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B289" t="s">
+        <v>761</v>
+      </c>
+      <c r="D289" t="s">
+        <v>711</v>
+      </c>
+      <c r="E289" t="s">
         <v>762</v>
       </c>
-      <c r="D289" t="s">
-        <v>712</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>763</v>
-      </c>
-      <c r="F289" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B290" t="s">
         <v>239</v>
@@ -7995,58 +8031,58 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B291" t="s">
+        <v>659</v>
+      </c>
+      <c r="D291" t="s">
+        <v>581</v>
+      </c>
+      <c r="E291" t="s">
+        <v>323</v>
+      </c>
+      <c r="F291" t="s">
         <v>660</v>
-      </c>
-      <c r="D291" t="s">
-        <v>582</v>
-      </c>
-      <c r="E291" t="s">
-        <v>324</v>
-      </c>
-      <c r="F291" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B292" t="s">
+        <v>661</v>
+      </c>
+      <c r="D292" t="s">
+        <v>581</v>
+      </c>
+      <c r="E292" t="s">
+        <v>288</v>
+      </c>
+      <c r="F292" t="s">
         <v>662</v>
-      </c>
-      <c r="D292" t="s">
-        <v>582</v>
-      </c>
-      <c r="E292" t="s">
-        <v>289</v>
-      </c>
-      <c r="F292" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B293" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C293" t="s">
         <v>77</v>
       </c>
       <c r="E293" t="s">
+        <v>390</v>
+      </c>
+      <c r="F293" t="s">
         <v>391</v>
-      </c>
-      <c r="F293" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B294" t="s">
         <v>19</v>
@@ -8066,7 +8102,7 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B295" t="s">
         <v>16</v>
@@ -8086,7 +8122,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B296" t="s">
         <v>16</v>
@@ -8103,7 +8139,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B297" t="s">
         <v>16</v>
@@ -8123,7 +8159,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B298" t="s">
         <v>267</v>
@@ -8135,32 +8171,32 @@
         <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F298" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B299" t="s">
         <v>267</v>
       </c>
       <c r="C299" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E299" t="s">
-        <v>287</v>
+        <v>772</v>
       </c>
       <c r="F299" t="s">
-        <v>272</v>
+        <v>773</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B300" t="s">
         <v>267</v>
@@ -8169,7 +8205,7 @@
         <v>268</v>
       </c>
       <c r="E300" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F300" t="s">
         <v>269</v>
@@ -8177,64 +8213,64 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B301" t="s">
         <v>267</v>
       </c>
       <c r="C301" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E301" t="s">
+        <v>348</v>
+      </c>
+      <c r="F301" t="s">
         <v>349</v>
-      </c>
-      <c r="F301" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B302" t="s">
         <v>267</v>
       </c>
       <c r="C302" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D302">
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F302" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B303" t="s">
         <v>267</v>
       </c>
       <c r="C303" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D303">
         <v>1</v>
       </c>
       <c r="E303" t="s">
+        <v>290</v>
+      </c>
+      <c r="F303" t="s">
         <v>291</v>
-      </c>
-      <c r="F303" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B304" t="s">
         <v>267</v>
@@ -8243,497 +8279,491 @@
         <v>132</v>
       </c>
       <c r="E304" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F304" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B305" t="s">
         <v>267</v>
       </c>
       <c r="C305" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D305">
         <v>1</v>
       </c>
       <c r="E305" t="s">
+        <v>300</v>
+      </c>
+      <c r="F305" t="s">
         <v>301</v>
-      </c>
-      <c r="F305" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B306" t="s">
         <v>267</v>
       </c>
       <c r="C306" t="s">
+        <v>299</v>
+      </c>
+      <c r="D306">
+        <v>1</v>
+      </c>
+      <c r="E306" t="s">
         <v>300</v>
       </c>
-      <c r="D306">
-        <v>1</v>
-      </c>
-      <c r="E306" t="s">
-        <v>301</v>
-      </c>
       <c r="F306" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B307" t="s">
         <v>267</v>
       </c>
       <c r="C307" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E307" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F307" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B308" t="s">
         <v>267</v>
       </c>
       <c r="C308" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D308">
         <v>1</v>
       </c>
       <c r="E308" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F308" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B309" t="s">
         <v>267</v>
       </c>
       <c r="C309" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D309">
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F309" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B310" t="s">
-        <v>664</v>
-      </c>
-      <c r="D310" t="s">
-        <v>582</v>
+        <v>267</v>
+      </c>
+      <c r="C310" t="s">
+        <v>780</v>
       </c>
       <c r="E310" t="s">
-        <v>332</v>
+        <v>772</v>
       </c>
       <c r="F310" t="s">
-        <v>665</v>
+        <v>781</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B311" t="s">
-        <v>270</v>
-      </c>
-      <c r="C311" t="s">
-        <v>271</v>
-      </c>
-      <c r="D311">
-        <v>1</v>
+        <v>663</v>
+      </c>
+      <c r="D311" t="s">
+        <v>581</v>
       </c>
       <c r="E311" t="s">
-        <v>287</v>
+        <v>331</v>
       </c>
       <c r="F311" t="s">
-        <v>328</v>
+        <v>664</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B312" t="s">
         <v>270</v>
       </c>
       <c r="C312" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
       <c r="D312">
         <v>1</v>
       </c>
       <c r="E312" t="s">
-        <v>349</v>
+        <v>286</v>
       </c>
       <c r="F312" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B313" t="s">
         <v>270</v>
       </c>
       <c r="C313" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="D313">
         <v>1</v>
       </c>
       <c r="E313" t="s">
-        <v>291</v>
+        <v>348</v>
       </c>
       <c r="F313" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B314" t="s">
         <v>270</v>
       </c>
       <c r="C314" t="s">
-        <v>336</v>
+        <v>282</v>
       </c>
       <c r="D314">
         <v>1</v>
       </c>
       <c r="E314" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="F314" t="s">
-        <v>338</v>
+        <v>283</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B315" t="s">
         <v>270</v>
       </c>
       <c r="C315" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D315">
         <v>1</v>
       </c>
       <c r="E315" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F315" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B316" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
       <c r="C316" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="D316">
         <v>1</v>
       </c>
       <c r="E316" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="F316" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B317" t="s">
-        <v>666</v>
+        <v>771</v>
       </c>
       <c r="D317" t="s">
-        <v>582</v>
+        <v>691</v>
       </c>
       <c r="E317" t="s">
-        <v>301</v>
+        <v>772</v>
       </c>
       <c r="F317" t="s">
-        <v>304</v>
+        <v>774</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B318" t="s">
-        <v>667</v>
-      </c>
-      <c r="D318" t="s">
-        <v>582</v>
+        <v>771</v>
+      </c>
+      <c r="C318" t="s">
+        <v>149</v>
+      </c>
+      <c r="D318">
+        <v>1</v>
       </c>
       <c r="E318" t="s">
-        <v>332</v>
+        <v>772</v>
       </c>
       <c r="F318" t="s">
-        <v>668</v>
+        <v>773</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B319" t="s">
-        <v>669</v>
-      </c>
-      <c r="D319" t="s">
-        <v>582</v>
+        <v>771</v>
+      </c>
+      <c r="C319" t="s">
+        <v>775</v>
+      </c>
+      <c r="D319">
+        <v>1</v>
       </c>
       <c r="E319" t="s">
-        <v>301</v>
+        <v>772</v>
       </c>
       <c r="F319" t="s">
-        <v>305</v>
+        <v>776</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B320" t="s">
-        <v>670</v>
-      </c>
-      <c r="D320" t="s">
-        <v>582</v>
+        <v>346</v>
+      </c>
+      <c r="C320" t="s">
+        <v>347</v>
+      </c>
+      <c r="D320">
+        <v>1</v>
       </c>
       <c r="E320" t="s">
-        <v>672</v>
+        <v>348</v>
       </c>
       <c r="F320" t="s">
-        <v>671</v>
+        <v>349</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B321" t="s">
-        <v>673</v>
-      </c>
-      <c r="D321" t="s">
-        <v>582</v>
+        <v>777</v>
+      </c>
+      <c r="C321" t="s">
+        <v>30</v>
+      </c>
+      <c r="D321">
+        <v>2</v>
       </c>
       <c r="E321" t="s">
-        <v>234</v>
+        <v>772</v>
       </c>
       <c r="F321" t="s">
-        <v>232</v>
+        <v>778</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B322" t="s">
-        <v>236</v>
+        <v>777</v>
       </c>
       <c r="C322" t="s">
-        <v>237</v>
+        <v>545</v>
       </c>
       <c r="E322" t="s">
-        <v>234</v>
+        <v>772</v>
       </c>
       <c r="F322" t="s">
-        <v>238</v>
+        <v>779</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B323" t="s">
-        <v>379</v>
-      </c>
-      <c r="C323" t="s">
-        <v>382</v>
-      </c>
-      <c r="D323">
-        <v>1</v>
+        <v>782</v>
+      </c>
+      <c r="D323" t="s">
+        <v>581</v>
       </c>
       <c r="E323" t="s">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="F323" t="s">
-        <v>383</v>
+        <v>778</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B324" t="s">
-        <v>379</v>
-      </c>
-      <c r="C324" t="s">
-        <v>10</v>
-      </c>
-      <c r="D324">
-        <v>1</v>
+        <v>783</v>
+      </c>
+      <c r="D324" t="s">
+        <v>581</v>
       </c>
       <c r="E324" t="s">
-        <v>375</v>
+        <v>772</v>
       </c>
       <c r="F324" t="s">
-        <v>384</v>
+        <v>778</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B325" t="s">
-        <v>379</v>
-      </c>
-      <c r="C325" t="s">
-        <v>381</v>
-      </c>
-      <c r="D325">
-        <v>1</v>
+        <v>665</v>
+      </c>
+      <c r="D325" t="s">
+        <v>581</v>
       </c>
       <c r="E325" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F325" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B326" t="s">
-        <v>379</v>
-      </c>
-      <c r="C326" t="s">
-        <v>77</v>
+        <v>666</v>
+      </c>
+      <c r="D326" t="s">
+        <v>581</v>
       </c>
       <c r="E326" t="s">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="F326" t="s">
-        <v>378</v>
+        <v>667</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B327" t="s">
-        <v>373</v>
-      </c>
-      <c r="C327" t="s">
-        <v>8</v>
-      </c>
-      <c r="D327">
-        <v>1</v>
+        <v>668</v>
+      </c>
+      <c r="D327" t="s">
+        <v>581</v>
       </c>
       <c r="E327" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F327" t="s">
-        <v>374</v>
+        <v>304</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B328" t="s">
-        <v>373</v>
-      </c>
-      <c r="C328" t="s">
-        <v>35</v>
-      </c>
-      <c r="D328">
-        <v>1</v>
+        <v>669</v>
+      </c>
+      <c r="D328" t="s">
+        <v>581</v>
       </c>
       <c r="E328" t="s">
-        <v>375</v>
+        <v>671</v>
       </c>
       <c r="F328" t="s">
-        <v>377</v>
+        <v>670</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B329" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D329" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E329" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="F329" t="s">
-        <v>407</v>
+        <v>232</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B330" t="s">
-        <v>675</v>
-      </c>
-      <c r="D330" t="s">
-        <v>582</v>
+        <v>236</v>
+      </c>
+      <c r="C330" t="s">
+        <v>237</v>
       </c>
       <c r="E330" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="F330" t="s">
-        <v>676</v>
+        <v>238</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -8741,24 +8771,27 @@
         <v>683</v>
       </c>
       <c r="B331" t="s">
-        <v>685</v>
+        <v>378</v>
       </c>
       <c r="C331" t="s">
-        <v>686</v>
+        <v>381</v>
+      </c>
+      <c r="D331">
+        <v>1</v>
       </c>
       <c r="E331" t="s">
-        <v>687</v>
+        <v>374</v>
       </c>
       <c r="F331" t="s">
-        <v>688</v>
+        <v>382</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B332" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C332" t="s">
         <v>10</v>
@@ -8767,234 +8800,240 @@
         <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F332" t="s">
-        <v>159</v>
+        <v>383</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B333" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C333" t="s">
-        <v>145</v>
+        <v>380</v>
+      </c>
+      <c r="D333">
+        <v>1</v>
       </c>
       <c r="E333" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F333" t="s">
-        <v>158</v>
+        <v>379</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B334" t="s">
-        <v>148</v>
+        <v>378</v>
       </c>
       <c r="C334" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="E334" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F334" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B335" t="s">
-        <v>148</v>
+        <v>372</v>
       </c>
       <c r="C335" t="s">
-        <v>199</v>
+        <v>8</v>
       </c>
       <c r="D335">
         <v>1</v>
       </c>
       <c r="E335" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F335" t="s">
-        <v>161</v>
+        <v>373</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B336" t="s">
-        <v>152</v>
+        <v>372</v>
       </c>
       <c r="C336" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D336">
         <v>1</v>
       </c>
       <c r="E336" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="F336" t="s">
-        <v>157</v>
+        <v>376</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B337" t="s">
-        <v>152</v>
-      </c>
-      <c r="C337" t="s">
-        <v>35</v>
-      </c>
-      <c r="D337">
-        <v>1</v>
+        <v>673</v>
+      </c>
+      <c r="D337" t="s">
+        <v>581</v>
       </c>
       <c r="E337" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="F337" t="s">
-        <v>157</v>
+        <v>406</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B338" t="s">
-        <v>201</v>
-      </c>
-      <c r="C338" t="s">
-        <v>182</v>
+        <v>674</v>
+      </c>
+      <c r="D338" t="s">
+        <v>581</v>
       </c>
       <c r="E338" t="s">
-        <v>180</v>
+        <v>405</v>
       </c>
       <c r="F338" t="s">
-        <v>181</v>
+        <v>675</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
+        <v>682</v>
+      </c>
+      <c r="B339" t="s">
         <v>684</v>
       </c>
-      <c r="B339" t="s">
-        <v>201</v>
-      </c>
       <c r="C339" t="s">
-        <v>163</v>
+        <v>685</v>
       </c>
       <c r="E339" t="s">
-        <v>180</v>
+        <v>686</v>
       </c>
       <c r="F339" t="s">
-        <v>164</v>
+        <v>687</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B340" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="C340" t="s">
-        <v>518</v>
+        <v>10</v>
       </c>
       <c r="D340">
         <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>520</v>
+        <v>419</v>
       </c>
       <c r="F340" t="s">
-        <v>519</v>
+        <v>159</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B341" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C341" t="s">
-        <v>368</v>
+        <v>145</v>
       </c>
       <c r="E341" t="s">
-        <v>367</v>
+        <v>419</v>
       </c>
       <c r="F341" t="s">
-        <v>366</v>
+        <v>158</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B342" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C342" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="E342" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="F342" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B343" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C343" t="s">
-        <v>167</v>
+        <v>199</v>
+      </c>
+      <c r="D343">
+        <v>1</v>
       </c>
       <c r="E343" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="F343" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B344" t="s">
-        <v>203</v>
-      </c>
-      <c r="D344" t="s">
-        <v>692</v>
+        <v>152</v>
+      </c>
+      <c r="C344" t="s">
+        <v>8</v>
+      </c>
+      <c r="D344">
+        <v>1</v>
       </c>
       <c r="E344" t="s">
-        <v>709</v>
+        <v>419</v>
       </c>
       <c r="F344" t="s">
-        <v>710</v>
+        <v>157</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B345" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="C345" t="s">
         <v>35</v>
@@ -9003,24 +9042,24 @@
         <v>1</v>
       </c>
       <c r="E345" t="s">
-        <v>709</v>
+        <v>419</v>
       </c>
       <c r="F345" t="s">
-        <v>722</v>
+        <v>157</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B346" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C346" t="s">
         <v>182</v>
       </c>
       <c r="E346" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F346" t="s">
         <v>181</v>
@@ -9028,354 +9067,351 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B347" t="s">
-        <v>721</v>
+        <v>201</v>
       </c>
       <c r="C347" t="s">
-        <v>230</v>
-      </c>
-      <c r="D347">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E347" t="s">
-        <v>709</v>
+        <v>180</v>
       </c>
       <c r="F347" t="s">
-        <v>710</v>
+        <v>164</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B348" t="s">
-        <v>723</v>
-      </c>
-      <c r="D348" t="s">
-        <v>692</v>
+        <v>201</v>
+      </c>
+      <c r="C348" t="s">
+        <v>517</v>
+      </c>
+      <c r="D348">
+        <v>1</v>
       </c>
       <c r="E348" t="s">
-        <v>709</v>
+        <v>519</v>
       </c>
       <c r="F348" t="s">
-        <v>710</v>
+        <v>518</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B349" t="s">
-        <v>723</v>
+        <v>204</v>
       </c>
       <c r="C349" t="s">
-        <v>35</v>
-      </c>
-      <c r="D349">
-        <v>1</v>
+        <v>367</v>
       </c>
       <c r="E349" t="s">
-        <v>709</v>
+        <v>366</v>
       </c>
       <c r="F349" t="s">
-        <v>717</v>
+        <v>365</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B350" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C350" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="E350" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F350" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B351" t="s">
-        <v>80</v>
+        <v>204</v>
       </c>
       <c r="C351" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="E351" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
       <c r="F351" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B352" t="s">
-        <v>80</v>
-      </c>
-      <c r="C352" t="s">
-        <v>67</v>
+        <v>203</v>
+      </c>
+      <c r="D352" t="s">
+        <v>691</v>
       </c>
       <c r="E352" t="s">
-        <v>59</v>
+        <v>708</v>
       </c>
       <c r="F352" t="s">
-        <v>82</v>
+        <v>709</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B353" t="s">
-        <v>335</v>
+        <v>203</v>
       </c>
       <c r="C353" t="s">
-        <v>334</v>
+        <v>35</v>
       </c>
       <c r="D353">
         <v>1</v>
       </c>
       <c r="E353" t="s">
-        <v>332</v>
+        <v>708</v>
       </c>
       <c r="F353" t="s">
-        <v>334</v>
+        <v>721</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B354" t="s">
-        <v>677</v>
-      </c>
-      <c r="D354" t="s">
-        <v>582</v>
+        <v>203</v>
+      </c>
+      <c r="C354" t="s">
+        <v>182</v>
       </c>
       <c r="E354" t="s">
-        <v>475</v>
+        <v>178</v>
       </c>
       <c r="F354" t="s">
-        <v>470</v>
+        <v>181</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B355" t="s">
-        <v>678</v>
-      </c>
-      <c r="D355" t="s">
-        <v>582</v>
+        <v>720</v>
+      </c>
+      <c r="C355" t="s">
+        <v>230</v>
+      </c>
+      <c r="D355">
+        <v>1</v>
       </c>
       <c r="E355" t="s">
-        <v>420</v>
+        <v>708</v>
       </c>
       <c r="F355" t="s">
-        <v>679</v>
+        <v>709</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B356" t="s">
-        <v>578</v>
-      </c>
-      <c r="C356" t="s">
-        <v>104</v>
+        <v>722</v>
+      </c>
+      <c r="D356" t="s">
+        <v>691</v>
       </c>
       <c r="E356" t="s">
-        <v>577</v>
+        <v>708</v>
       </c>
       <c r="F356" t="s">
-        <v>580</v>
+        <v>709</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B357" t="s">
-        <v>578</v>
+        <v>722</v>
       </c>
       <c r="C357" t="s">
-        <v>78</v>
+        <v>35</v>
+      </c>
+      <c r="D357">
+        <v>1</v>
       </c>
       <c r="E357" t="s">
-        <v>577</v>
+        <v>708</v>
       </c>
       <c r="F357" t="s">
-        <v>579</v>
+        <v>716</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B358" t="s">
-        <v>184</v>
-      </c>
-      <c r="D358" t="s">
-        <v>692</v>
+        <v>200</v>
+      </c>
+      <c r="C358" t="s">
+        <v>104</v>
       </c>
       <c r="E358" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F358" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B359" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="C359" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="E359" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="F359" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B360" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="C360" t="s">
-        <v>171</v>
+        <v>67</v>
       </c>
       <c r="E360" t="s">
-        <v>515</v>
+        <v>59</v>
       </c>
       <c r="F360" t="s">
-        <v>516</v>
+        <v>82</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B361" t="s">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="C361" t="s">
-        <v>171</v>
+        <v>333</v>
+      </c>
+      <c r="D361">
+        <v>1</v>
       </c>
       <c r="E361" t="s">
-        <v>515</v>
+        <v>331</v>
       </c>
       <c r="F361" t="s">
-        <v>517</v>
+        <v>333</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B362" t="s">
-        <v>184</v>
-      </c>
-      <c r="C362" t="s">
-        <v>443</v>
+        <v>676</v>
+      </c>
+      <c r="D362" t="s">
+        <v>581</v>
       </c>
       <c r="E362" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="F362" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B363" t="s">
-        <v>184</v>
-      </c>
-      <c r="C363" t="s">
-        <v>261</v>
-      </c>
-      <c r="D363">
-        <v>1</v>
+        <v>677</v>
+      </c>
+      <c r="D363" t="s">
+        <v>581</v>
       </c>
       <c r="E363" t="s">
-        <v>286</v>
+        <v>419</v>
       </c>
       <c r="F363" t="s">
-        <v>262</v>
+        <v>678</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B364" t="s">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="C364" t="s">
-        <v>421</v>
+        <v>104</v>
       </c>
       <c r="E364" t="s">
-        <v>420</v>
+        <v>576</v>
       </c>
       <c r="F364" t="s">
-        <v>157</v>
+        <v>579</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B365" t="s">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="C365" t="s">
-        <v>734</v>
-      </c>
-      <c r="D365">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E365" t="s">
-        <v>735</v>
+        <v>576</v>
       </c>
       <c r="F365" t="s">
-        <v>736</v>
+        <v>578</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B366" t="s">
         <v>184</v>
       </c>
-      <c r="C366" t="s">
-        <v>185</v>
-      </c>
-      <c r="D366">
-        <v>1</v>
+      <c r="D366" t="s">
+        <v>691</v>
       </c>
       <c r="E366" t="s">
         <v>186</v>
@@ -9386,935 +9422,1080 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B367" t="s">
         <v>184</v>
       </c>
       <c r="C367" t="s">
-        <v>489</v>
-      </c>
-      <c r="D367">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E367" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="F367" t="s">
-        <v>530</v>
+        <v>155</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B368" t="s">
         <v>184</v>
       </c>
       <c r="C368" t="s">
-        <v>489</v>
-      </c>
-      <c r="D368">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E368" t="s">
-        <v>298</v>
+        <v>514</v>
       </c>
       <c r="F368" t="s">
-        <v>297</v>
+        <v>515</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B369" t="s">
         <v>184</v>
       </c>
       <c r="C369" t="s">
-        <v>326</v>
-      </c>
-      <c r="D369">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E369" t="s">
-        <v>324</v>
+        <v>514</v>
       </c>
       <c r="F369" t="s">
-        <v>327</v>
+        <v>516</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B370" t="s">
         <v>184</v>
       </c>
       <c r="C370" t="s">
-        <v>323</v>
-      </c>
-      <c r="D370">
-        <v>1</v>
+        <v>442</v>
       </c>
       <c r="E370" t="s">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="F370" t="s">
-        <v>325</v>
+        <v>445</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B371" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C371" t="s">
-        <v>189</v>
+        <v>261</v>
       </c>
       <c r="D371">
         <v>1</v>
       </c>
       <c r="E371" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="F371" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B372" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C372" t="s">
-        <v>191</v>
-      </c>
-      <c r="D372">
-        <v>1</v>
+        <v>420</v>
       </c>
       <c r="E372" t="s">
-        <v>244</v>
+        <v>419</v>
       </c>
       <c r="F372" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B373" t="s">
-        <v>476</v>
+        <v>184</v>
       </c>
       <c r="C373" t="s">
-        <v>477</v>
+        <v>733</v>
+      </c>
+      <c r="D373">
+        <v>1</v>
       </c>
       <c r="E373" t="s">
-        <v>538</v>
+        <v>734</v>
       </c>
       <c r="F373" t="s">
-        <v>465</v>
+        <v>735</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B374" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C374" t="s">
-        <v>459</v>
+        <v>185</v>
+      </c>
+      <c r="D374">
+        <v>1</v>
       </c>
       <c r="E374" t="s">
-        <v>453</v>
+        <v>186</v>
       </c>
       <c r="F374" t="s">
-        <v>460</v>
+        <v>190</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B375" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C375" t="s">
-        <v>410</v>
+        <v>488</v>
+      </c>
+      <c r="D375">
+        <v>1</v>
       </c>
       <c r="E375" t="s">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="F375" t="s">
-        <v>411</v>
+        <v>529</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B376" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C376" t="s">
-        <v>409</v>
+        <v>488</v>
+      </c>
+      <c r="D376">
+        <v>1</v>
       </c>
       <c r="E376" t="s">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="F376" t="s">
-        <v>408</v>
+        <v>296</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B377" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C377" t="s">
-        <v>402</v>
+        <v>325</v>
+      </c>
+      <c r="D377">
+        <v>1</v>
       </c>
       <c r="E377" t="s">
-        <v>400</v>
+        <v>323</v>
       </c>
       <c r="F377" t="s">
-        <v>401</v>
+        <v>326</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B378" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="C378" t="s">
-        <v>490</v>
+        <v>322</v>
+      </c>
+      <c r="D378">
+        <v>1</v>
       </c>
       <c r="E378" t="s">
-        <v>491</v>
+        <v>323</v>
       </c>
       <c r="F378" t="s">
-        <v>492</v>
+        <v>324</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B379" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="C379" t="s">
-        <v>490</v>
+        <v>189</v>
+      </c>
+      <c r="D379">
+        <v>1</v>
       </c>
       <c r="E379" t="s">
-        <v>491</v>
+        <v>244</v>
       </c>
       <c r="F379" t="s">
-        <v>493</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B380" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="C380" t="s">
-        <v>182</v>
+        <v>191</v>
+      </c>
+      <c r="D380">
+        <v>1</v>
       </c>
       <c r="E380" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F380" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B381" t="s">
-        <v>45</v>
+        <v>475</v>
       </c>
       <c r="C381" t="s">
-        <v>562</v>
+        <v>476</v>
       </c>
       <c r="E381" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="F381" t="s">
-        <v>564</v>
+        <v>464</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B382" t="s">
         <v>45</v>
       </c>
       <c r="C382" t="s">
-        <v>562</v>
+        <v>458</v>
       </c>
       <c r="E382" t="s">
-        <v>563</v>
+        <v>452</v>
       </c>
       <c r="F382" t="s">
-        <v>565</v>
+        <v>459</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B383" t="s">
         <v>45</v>
       </c>
       <c r="C383" t="s">
-        <v>415</v>
-      </c>
-      <c r="D383">
-        <v>1</v>
+        <v>409</v>
       </c>
       <c r="E383" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="F383" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B384" t="s">
         <v>45</v>
       </c>
       <c r="C384" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="E384" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="F384" t="s">
-        <v>374</v>
+        <v>407</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B385" t="s">
         <v>45</v>
       </c>
       <c r="C385" t="s">
-        <v>443</v>
+        <v>401</v>
       </c>
       <c r="E385" t="s">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="F385" t="s">
-        <v>445</v>
+        <v>400</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B386" t="s">
         <v>45</v>
       </c>
       <c r="C386" t="s">
-        <v>264</v>
-      </c>
-      <c r="D386">
-        <v>1</v>
+        <v>489</v>
       </c>
       <c r="E386" t="s">
-        <v>286</v>
+        <v>490</v>
       </c>
       <c r="F386" t="s">
-        <v>263</v>
+        <v>491</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B387" t="s">
         <v>45</v>
       </c>
       <c r="C387" t="s">
-        <v>372</v>
+        <v>489</v>
       </c>
       <c r="E387" t="s">
-        <v>369</v>
+        <v>490</v>
       </c>
       <c r="F387" t="s">
-        <v>559</v>
+        <v>492</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B388" t="s">
         <v>45</v>
       </c>
       <c r="C388" t="s">
-        <v>187</v>
-      </c>
-      <c r="D388">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="E388" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="F388" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B389" t="s">
         <v>45</v>
       </c>
       <c r="C389" t="s">
-        <v>281</v>
-      </c>
-      <c r="D389">
-        <v>1</v>
+        <v>561</v>
       </c>
       <c r="E389" t="s">
-        <v>290</v>
+        <v>562</v>
       </c>
       <c r="F389" t="s">
-        <v>282</v>
+        <v>563</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B390" t="s">
         <v>45</v>
       </c>
       <c r="C390" t="s">
-        <v>123</v>
+        <v>561</v>
       </c>
       <c r="E390" t="s">
-        <v>246</v>
+        <v>562</v>
       </c>
       <c r="F390" t="s">
-        <v>123</v>
+        <v>564</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B391" t="s">
         <v>45</v>
       </c>
       <c r="C391" t="s">
-        <v>52</v>
+        <v>414</v>
       </c>
       <c r="D391">
         <v>1</v>
       </c>
       <c r="E391" t="s">
-        <v>50</v>
+        <v>413</v>
       </c>
       <c r="F391" t="s">
-        <v>53</v>
+        <v>415</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B392" t="s">
         <v>45</v>
       </c>
       <c r="C392" t="s">
-        <v>49</v>
-      </c>
-      <c r="D392">
-        <v>1</v>
+        <v>375</v>
       </c>
       <c r="E392" t="s">
-        <v>50</v>
+        <v>374</v>
       </c>
       <c r="F392" t="s">
-        <v>51</v>
+        <v>373</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B393" t="s">
         <v>45</v>
       </c>
       <c r="C393" t="s">
-        <v>125</v>
+        <v>442</v>
       </c>
       <c r="E393" t="s">
-        <v>126</v>
+        <v>443</v>
       </c>
       <c r="F393" t="s">
-        <v>127</v>
+        <v>444</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B394" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="C394" t="s">
-        <v>167</v>
+        <v>264</v>
+      </c>
+      <c r="D394">
+        <v>1</v>
       </c>
       <c r="E394" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="F394" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B395" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C395" t="s">
-        <v>571</v>
+        <v>371</v>
       </c>
       <c r="E395" t="s">
-        <v>256</v>
+        <v>368</v>
       </c>
       <c r="F395" t="s">
-        <v>183</v>
+        <v>558</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B396" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C396" t="s">
-        <v>571</v>
+        <v>187</v>
+      </c>
+      <c r="D396">
+        <v>1</v>
       </c>
       <c r="E396" t="s">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="F396" t="s">
-        <v>572</v>
+        <v>190</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B397" t="s">
-        <v>569</v>
+        <v>45</v>
       </c>
       <c r="C397" t="s">
-        <v>570</v>
+        <v>280</v>
+      </c>
+      <c r="D397">
+        <v>1</v>
       </c>
       <c r="E397" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="F397" t="s">
-        <v>183</v>
+        <v>281</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B398" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C398" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E398" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F398" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B399" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C399" t="s">
-        <v>165</v>
+        <v>52</v>
+      </c>
+      <c r="D399">
+        <v>1</v>
       </c>
       <c r="E399" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F399" t="s">
-        <v>166</v>
+        <v>53</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B400" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C400" t="s">
-        <v>169</v>
+        <v>49</v>
+      </c>
+      <c r="D400">
+        <v>1</v>
       </c>
       <c r="E400" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F400" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B401" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C401" t="s">
-        <v>55</v>
-      </c>
-      <c r="D401">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="E401" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="F401" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B402" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="C402" t="s">
-        <v>57</v>
-      </c>
-      <c r="D402">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="E402" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="F402" t="s">
-        <v>53</v>
+        <v>168</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B403" t="s">
-        <v>456</v>
+        <v>568</v>
       </c>
       <c r="C403" t="s">
-        <v>8</v>
-      </c>
-      <c r="D403">
-        <v>1</v>
+        <v>570</v>
       </c>
       <c r="E403" t="s">
-        <v>453</v>
+        <v>256</v>
       </c>
       <c r="F403" t="s">
-        <v>457</v>
+        <v>183</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B404" t="s">
-        <v>108</v>
+        <v>568</v>
       </c>
       <c r="C404" t="s">
-        <v>114</v>
-      </c>
-      <c r="D404">
-        <v>1</v>
+        <v>570</v>
       </c>
       <c r="E404" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="F404" t="s">
-        <v>114</v>
+        <v>571</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B405" t="s">
-        <v>108</v>
+        <v>568</v>
       </c>
       <c r="C405" t="s">
-        <v>116</v>
-      </c>
-      <c r="D405">
-        <v>1</v>
+        <v>569</v>
       </c>
       <c r="E405" t="s">
-        <v>115</v>
+        <v>256</v>
       </c>
       <c r="F405" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B406" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C406" t="s">
-        <v>117</v>
-      </c>
-      <c r="D406">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="E406" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F406" t="s">
-        <v>117</v>
+        <v>172</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B407" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C407" t="s">
-        <v>118</v>
-      </c>
-      <c r="D407">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="E407" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F407" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B408" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C408" t="s">
-        <v>120</v>
-      </c>
-      <c r="D408">
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="E408" t="s">
-        <v>115</v>
+        <v>255</v>
       </c>
       <c r="F408" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B409" t="s">
-        <v>756</v>
-      </c>
-      <c r="D409" t="s">
-        <v>712</v>
+        <v>48</v>
+      </c>
+      <c r="C409" t="s">
+        <v>55</v>
+      </c>
+      <c r="D409">
+        <v>1</v>
       </c>
       <c r="E409" t="s">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F409" t="s">
-        <v>757</v>
+        <v>53</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B410" t="s">
-        <v>754</v>
-      </c>
-      <c r="D410" t="s">
-        <v>712</v>
+        <v>48</v>
+      </c>
+      <c r="C410" t="s">
+        <v>57</v>
+      </c>
+      <c r="D410">
+        <v>1</v>
       </c>
       <c r="E410" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="F410" t="s">
-        <v>755</v>
+        <v>53</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B411" t="s">
-        <v>680</v>
-      </c>
-      <c r="D411" t="s">
-        <v>582</v>
+        <v>455</v>
+      </c>
+      <c r="C411" t="s">
+        <v>8</v>
+      </c>
+      <c r="D411">
+        <v>1</v>
       </c>
       <c r="E411" t="s">
-        <v>298</v>
+        <v>452</v>
       </c>
       <c r="F411" t="s">
-        <v>297</v>
+        <v>456</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B412" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="C412" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="D412">
         <v>1</v>
       </c>
       <c r="E412" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="F412" t="s">
-        <v>192</v>
+        <v>114</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B413" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="C413" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="D413">
         <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>244</v>
+        <v>115</v>
       </c>
       <c r="F413" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B414" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C414" t="s">
-        <v>567</v>
+        <v>117</v>
+      </c>
+      <c r="D414">
+        <v>1</v>
       </c>
       <c r="E414" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F414" t="s">
-        <v>565</v>
+        <v>117</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B415" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C415" t="s">
-        <v>568</v>
+        <v>118</v>
+      </c>
+      <c r="D415">
+        <v>1</v>
       </c>
       <c r="E415" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F415" t="s">
-        <v>565</v>
+        <v>119</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B416" t="s">
-        <v>566</v>
+        <v>108</v>
       </c>
       <c r="C416" t="s">
-        <v>167</v>
+        <v>120</v>
+      </c>
+      <c r="D416">
+        <v>1</v>
       </c>
       <c r="E416" t="s">
-        <v>563</v>
+        <v>115</v>
       </c>
       <c r="F416" t="s">
-        <v>565</v>
+        <v>121</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B417" t="s">
-        <v>403</v>
-      </c>
-      <c r="C417" t="s">
+        <v>755</v>
+      </c>
+      <c r="D417" t="s">
+        <v>711</v>
+      </c>
+      <c r="E417" t="s">
+        <v>255</v>
+      </c>
+      <c r="F417" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>683</v>
+      </c>
+      <c r="B418" t="s">
+        <v>753</v>
+      </c>
+      <c r="D418" t="s">
+        <v>711</v>
+      </c>
+      <c r="E418" t="s">
+        <v>256</v>
+      </c>
+      <c r="F418" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>683</v>
+      </c>
+      <c r="B419" t="s">
+        <v>679</v>
+      </c>
+      <c r="D419" t="s">
+        <v>581</v>
+      </c>
+      <c r="E419" t="s">
+        <v>297</v>
+      </c>
+      <c r="F419" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>683</v>
+      </c>
+      <c r="B420" t="s">
+        <v>197</v>
+      </c>
+      <c r="C420" t="s">
+        <v>189</v>
+      </c>
+      <c r="D420">
+        <v>1</v>
+      </c>
+      <c r="E420" t="s">
+        <v>244</v>
+      </c>
+      <c r="F420" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>683</v>
+      </c>
+      <c r="B421" t="s">
+        <v>197</v>
+      </c>
+      <c r="C421" t="s">
+        <v>191</v>
+      </c>
+      <c r="D421">
+        <v>1</v>
+      </c>
+      <c r="E421" t="s">
+        <v>244</v>
+      </c>
+      <c r="F421" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>683</v>
+      </c>
+      <c r="B422" t="s">
+        <v>565</v>
+      </c>
+      <c r="C422" t="s">
+        <v>566</v>
+      </c>
+      <c r="E422" t="s">
+        <v>562</v>
+      </c>
+      <c r="F422" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>683</v>
+      </c>
+      <c r="B423" t="s">
+        <v>565</v>
+      </c>
+      <c r="C423" t="s">
+        <v>567</v>
+      </c>
+      <c r="E423" t="s">
+        <v>562</v>
+      </c>
+      <c r="F423" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>683</v>
+      </c>
+      <c r="B424" t="s">
+        <v>565</v>
+      </c>
+      <c r="C424" t="s">
+        <v>167</v>
+      </c>
+      <c r="E424" t="s">
+        <v>562</v>
+      </c>
+      <c r="F424" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>683</v>
+      </c>
+      <c r="B425" t="s">
+        <v>402</v>
+      </c>
+      <c r="C425" t="s">
         <v>104</v>
       </c>
-      <c r="E417" t="s">
+      <c r="E425" t="s">
+        <v>399</v>
+      </c>
+      <c r="F425" t="s">
         <v>400</v>
-      </c>
-      <c r="F417" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
